--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Bắc Ninh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bắc Ninh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G7">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G21">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G41">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G44">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G62">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G69">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G82">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G96">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G101">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G105">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G111">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G130">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G133">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU146"/>
+  <dimension ref="A1:AU148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Lusail City</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-11 11:30:00</t>
+          <t>2026-09-11 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Musannah</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-11 11:55:00</t>
+          <t>2026-09-11 11:30:00</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Al Musannah</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-11 12:00:00</t>
+          <t>2026-09-11 11:55:00</t>
         </is>
       </c>
     </row>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G29">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-09-11 12:25:00</t>
+          <t>2026-09-11 12:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,7 +5315,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-09-11 12:45:00</t>
+          <t>2026-09-11 12:25:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-11 13:00:00</t>
+          <t>2026-09-11 12:45:00</t>
         </is>
       </c>
     </row>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G33">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G34">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G39">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-09-11 13:15:00</t>
+          <t>2026-09-11 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G41">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-09-11 13:30:00</t>
+          <t>2026-09-11 13:15:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-09-11 13:30:00</t>
+          <t>2026-09-11 13:15:00</t>
         </is>
       </c>
     </row>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G46">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:00</t>
+          <t>2026-09-11 13:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:00</t>
+          <t>2026-09-11 13:30:00</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G55">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-09-11 14:30:00</t>
+          <t>2026-09-11 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-09-11 14:30:00</t>
+          <t>2026-09-11 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,22 +10210,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G62">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:00</t>
+          <t>2026-09-11 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:00</t>
+          <t>2026-09-11 14:30:00</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-09-11 15:15:00</t>
+          <t>2026-09-11 15:00:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-09-11 15:15:00</t>
+          <t>2026-09-11 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-09-11 15:30:00</t>
+          <t>2026-09-11 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-09-11 15:30:00</t>
+          <t>2026-09-11 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G89">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-09-11 15:45:00</t>
+          <t>2026-09-11 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-09-11 15:45:00</t>
+          <t>2026-09-11 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G92">
@@ -15426,22 +15426,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,22 +16893,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G103">
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G104">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-09-11 16:00:00</t>
+          <t>2026-09-11 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17377,12 +17377,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-09-11 16:00:00</t>
+          <t>2026-09-11 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17789,10 +17789,10 @@
         <v>0</v>
       </c>
       <c r="AA107">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB107">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC107">
         <v>0</v>
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G112">
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G113">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-09-11 17:00:00</t>
+          <t>2026-09-11 16:00:00</t>
         </is>
       </c>
     </row>
@@ -18844,27 +18844,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-09-11 19:00:00</t>
+          <t>2026-09-11 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-11 19:30:00</t>
+          <t>2026-09-11 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-09-11 21:00:00</t>
+          <t>2026-09-11 19:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-09-11 21:00:00</t>
+          <t>2026-09-11 19:30:00</t>
         </is>
       </c>
     </row>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G127">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,22 +22435,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G142">
@@ -23571,27 +23571,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G143">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-09-11 22:00:00</t>
+          <t>2026-09-11 21:00:00</t>
         </is>
       </c>
     </row>
@@ -23734,27 +23734,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-09-11 22:30:00</t>
+          <t>2026-09-11 21:00:00</t>
         </is>
       </c>
     </row>
@@ -23897,12 +23897,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G145">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-09-11 23:00:00</t>
+          <t>2026-09-11 22:00:00</t>
         </is>
       </c>
     </row>
@@ -24060,156 +24060,482 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>0</v>
+      </c>
+      <c r="R146">
+        <v>0</v>
+      </c>
+      <c r="S146">
+        <v>0</v>
+      </c>
+      <c r="T146">
+        <v>0</v>
+      </c>
+      <c r="U146">
+        <v>0</v>
+      </c>
+      <c r="V146">
+        <v>0</v>
+      </c>
+      <c r="W146">
+        <v>0</v>
+      </c>
+      <c r="X146">
+        <v>0</v>
+      </c>
+      <c r="Y146">
+        <v>0</v>
+      </c>
+      <c r="Z146">
+        <v>0</v>
+      </c>
+      <c r="AA146">
+        <v>0</v>
+      </c>
+      <c r="AB146">
+        <v>0</v>
+      </c>
+      <c r="AC146">
+        <v>0</v>
+      </c>
+      <c r="AD146">
+        <v>0</v>
+      </c>
+      <c r="AE146">
+        <v>0</v>
+      </c>
+      <c r="AF146">
+        <v>0</v>
+      </c>
+      <c r="AG146">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ146">
+        <v>0</v>
+      </c>
+      <c r="AK146">
+        <v>0</v>
+      </c>
+      <c r="AL146">
+        <v>0</v>
+      </c>
+      <c r="AM146">
+        <v>-1</v>
+      </c>
+      <c r="AN146">
+        <v>-1</v>
+      </c>
+      <c r="AO146">
+        <v>-1</v>
+      </c>
+      <c r="AP146">
+        <v>-1</v>
+      </c>
+      <c r="AQ146">
+        <v>0</v>
+      </c>
+      <c r="AR146">
+        <v>0</v>
+      </c>
+      <c r="AS146">
+        <v>0</v>
+      </c>
+      <c r="AT146">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>2026-09-11 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Colorado Springs</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>0</v>
+      </c>
+      <c r="R147">
+        <v>0</v>
+      </c>
+      <c r="S147">
+        <v>0</v>
+      </c>
+      <c r="T147">
+        <v>0</v>
+      </c>
+      <c r="U147">
+        <v>0</v>
+      </c>
+      <c r="V147">
+        <v>0</v>
+      </c>
+      <c r="W147">
+        <v>0</v>
+      </c>
+      <c r="X147">
+        <v>0</v>
+      </c>
+      <c r="Y147">
+        <v>0</v>
+      </c>
+      <c r="Z147">
+        <v>0</v>
+      </c>
+      <c r="AA147">
+        <v>0</v>
+      </c>
+      <c r="AB147">
+        <v>0</v>
+      </c>
+      <c r="AC147">
+        <v>0</v>
+      </c>
+      <c r="AD147">
+        <v>0</v>
+      </c>
+      <c r="AE147">
+        <v>0</v>
+      </c>
+      <c r="AF147">
+        <v>0</v>
+      </c>
+      <c r="AG147">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ147">
+        <v>0</v>
+      </c>
+      <c r="AK147">
+        <v>0</v>
+      </c>
+      <c r="AL147">
+        <v>0</v>
+      </c>
+      <c r="AM147">
+        <v>-1</v>
+      </c>
+      <c r="AN147">
+        <v>-1</v>
+      </c>
+      <c r="AO147">
+        <v>-1</v>
+      </c>
+      <c r="AP147">
+        <v>-1</v>
+      </c>
+      <c r="AQ147">
+        <v>0</v>
+      </c>
+      <c r="AR147">
+        <v>0</v>
+      </c>
+      <c r="AS147">
+        <v>0</v>
+      </c>
+      <c r="AT147">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>2026-09-11 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>Angel City</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>Denver Summit W</t>
         </is>
       </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="I146">
-        <v>0</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146" t="inlineStr">
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>0</v>
-      </c>
-      <c r="R146">
-        <v>0</v>
-      </c>
-      <c r="S146">
-        <v>0</v>
-      </c>
-      <c r="T146">
-        <v>0</v>
-      </c>
-      <c r="U146">
-        <v>0</v>
-      </c>
-      <c r="V146">
-        <v>0</v>
-      </c>
-      <c r="W146">
-        <v>0</v>
-      </c>
-      <c r="X146">
-        <v>0</v>
-      </c>
-      <c r="Y146">
-        <v>0</v>
-      </c>
-      <c r="Z146">
-        <v>0</v>
-      </c>
-      <c r="AA146">
-        <v>0</v>
-      </c>
-      <c r="AB146">
-        <v>0</v>
-      </c>
-      <c r="AC146">
-        <v>0</v>
-      </c>
-      <c r="AD146">
-        <v>0</v>
-      </c>
-      <c r="AE146">
-        <v>0</v>
-      </c>
-      <c r="AF146">
-        <v>0</v>
-      </c>
-      <c r="AG146">
-        <v>0</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>0</v>
-      </c>
-      <c r="AK146">
-        <v>0</v>
-      </c>
-      <c r="AL146">
-        <v>0</v>
-      </c>
-      <c r="AM146">
-        <v>-1</v>
-      </c>
-      <c r="AN146">
-        <v>-1</v>
-      </c>
-      <c r="AO146">
-        <v>-1</v>
-      </c>
-      <c r="AP146">
-        <v>-1</v>
-      </c>
-      <c r="AQ146">
-        <v>0</v>
-      </c>
-      <c r="AR146">
-        <v>0</v>
-      </c>
-      <c r="AS146">
-        <v>0</v>
-      </c>
-      <c r="AT146">
-        <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>0</v>
+      </c>
+      <c r="R148">
+        <v>0</v>
+      </c>
+      <c r="S148">
+        <v>0</v>
+      </c>
+      <c r="T148">
+        <v>0</v>
+      </c>
+      <c r="U148">
+        <v>0</v>
+      </c>
+      <c r="V148">
+        <v>0</v>
+      </c>
+      <c r="W148">
+        <v>0</v>
+      </c>
+      <c r="X148">
+        <v>0</v>
+      </c>
+      <c r="Y148">
+        <v>0</v>
+      </c>
+      <c r="Z148">
+        <v>0</v>
+      </c>
+      <c r="AA148">
+        <v>0</v>
+      </c>
+      <c r="AB148">
+        <v>0</v>
+      </c>
+      <c r="AC148">
+        <v>0</v>
+      </c>
+      <c r="AD148">
+        <v>0</v>
+      </c>
+      <c r="AE148">
+        <v>0</v>
+      </c>
+      <c r="AF148">
+        <v>0</v>
+      </c>
+      <c r="AG148">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ148">
+        <v>0</v>
+      </c>
+      <c r="AK148">
+        <v>0</v>
+      </c>
+      <c r="AL148">
+        <v>0</v>
+      </c>
+      <c r="AM148">
+        <v>-1</v>
+      </c>
+      <c r="AN148">
+        <v>-1</v>
+      </c>
+      <c r="AO148">
+        <v>-1</v>
+      </c>
+      <c r="AP148">
+        <v>-1</v>
+      </c>
+      <c r="AQ148">
+        <v>0</v>
+      </c>
+      <c r="AR148">
+        <v>0</v>
+      </c>
+      <c r="AS148">
+        <v>0</v>
+      </c>
+      <c r="AT148">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
         <is>
           <t>2026-09-11 23:00:00</t>
         </is>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G135">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G135">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G135">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G40">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G103">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G144">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G46">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G64">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G73">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G83">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G95">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G98">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G114">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G130">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G144">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G47">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-11 14:00:00</t>
+          <t>2026-09-11 13:30:00</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,22 +8743,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,22 +9232,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Horsens</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>Horsens</t>
         </is>
       </c>
       <c r="G57">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-09-11 14:30:00</t>
+          <t>2026-09-11 14:00:00</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,22 +10210,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G64">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:00</t>
+          <t>2026-09-11 14:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:00</t>
+          <t>2026-09-11 14:45:00</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G67">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G76">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G84">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-09-11 15:15:00</t>
+          <t>2026-09-11 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-09-11 15:15:00</t>
+          <t>2026-09-11 15:00:00</t>
         </is>
       </c>
     </row>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-09-11 15:30:00</t>
+          <t>2026-09-11 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-09-11 15:30:00</t>
+          <t>2026-09-11 15:15:00</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G91">
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-09-11 15:45:00</t>
+          <t>2026-09-11 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-09-11 15:45:00</t>
+          <t>2026-09-11 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,22 +15915,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,22 +17382,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G105">
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-09-11 16:00:00</t>
+          <t>2026-09-11 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17703,12 +17703,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-09-11 16:00:00</t>
+          <t>2026-09-11 15:45:00</t>
         </is>
       </c>
     </row>
@@ -17871,22 +17871,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB109">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18441,10 +18441,10 @@
         <v>0</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC111">
         <v>0</v>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G114">
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-09-11 17:00:00</t>
+          <t>2026-09-11 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-09-11 19:00:00</t>
+          <t>2026-09-11 16:00:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-09-11 19:30:00</t>
+          <t>2026-09-11 16:45:00</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-09-11 21:00:00</t>
+          <t>2026-09-11 17:00:00</t>
         </is>
       </c>
     </row>
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-09-11 21:00:00</t>
+          <t>2026-09-11 19:00:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-09-11 21:00:00</t>
+          <t>2026-09-11 19:30:00</t>
         </is>
       </c>
     </row>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,22 +20153,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,22 +20316,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G129">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G49">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G85">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G100">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G100">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU148"/>
+  <dimension ref="A1:AU145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G135">
@@ -22435,22 +22435,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G141">
@@ -23408,27 +23408,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G142">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-09-11 21:00:00</t>
+          <t>2026-09-11 22:00:00</t>
         </is>
       </c>
     </row>
@@ -23571,27 +23571,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G143">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-09-11 21:00:00</t>
+          <t>2026-09-11 22:30:00</t>
         </is>
       </c>
     </row>
@@ -23734,27 +23734,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G144">
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-09-11 21:00:00</t>
+          <t>2026-09-11 23:00:00</t>
         </is>
       </c>
     </row>
@@ -23897,12 +23897,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G145">
@@ -24047,495 +24047,6 @@
         <v>0</v>
       </c>
       <c r="AU145" t="inlineStr">
-        <is>
-          <t>2026-09-11 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>New Mexico United</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="I146">
-        <v>0</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>0</v>
-      </c>
-      <c r="R146">
-        <v>0</v>
-      </c>
-      <c r="S146">
-        <v>0</v>
-      </c>
-      <c r="T146">
-        <v>0</v>
-      </c>
-      <c r="U146">
-        <v>0</v>
-      </c>
-      <c r="V146">
-        <v>0</v>
-      </c>
-      <c r="W146">
-        <v>0</v>
-      </c>
-      <c r="X146">
-        <v>0</v>
-      </c>
-      <c r="Y146">
-        <v>0</v>
-      </c>
-      <c r="Z146">
-        <v>0</v>
-      </c>
-      <c r="AA146">
-        <v>0</v>
-      </c>
-      <c r="AB146">
-        <v>0</v>
-      </c>
-      <c r="AC146">
-        <v>0</v>
-      </c>
-      <c r="AD146">
-        <v>0</v>
-      </c>
-      <c r="AE146">
-        <v>0</v>
-      </c>
-      <c r="AF146">
-        <v>0</v>
-      </c>
-      <c r="AG146">
-        <v>0</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>0</v>
-      </c>
-      <c r="AK146">
-        <v>0</v>
-      </c>
-      <c r="AL146">
-        <v>0</v>
-      </c>
-      <c r="AM146">
-        <v>-1</v>
-      </c>
-      <c r="AN146">
-        <v>-1</v>
-      </c>
-      <c r="AO146">
-        <v>-1</v>
-      </c>
-      <c r="AP146">
-        <v>-1</v>
-      </c>
-      <c r="AQ146">
-        <v>0</v>
-      </c>
-      <c r="AR146">
-        <v>0</v>
-      </c>
-      <c r="AS146">
-        <v>0</v>
-      </c>
-      <c r="AT146">
-        <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>2026-09-11 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Colorado Springs</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147">
-        <v>0</v>
-      </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>0</v>
-      </c>
-      <c r="R147">
-        <v>0</v>
-      </c>
-      <c r="S147">
-        <v>0</v>
-      </c>
-      <c r="T147">
-        <v>0</v>
-      </c>
-      <c r="U147">
-        <v>0</v>
-      </c>
-      <c r="V147">
-        <v>0</v>
-      </c>
-      <c r="W147">
-        <v>0</v>
-      </c>
-      <c r="X147">
-        <v>0</v>
-      </c>
-      <c r="Y147">
-        <v>0</v>
-      </c>
-      <c r="Z147">
-        <v>0</v>
-      </c>
-      <c r="AA147">
-        <v>0</v>
-      </c>
-      <c r="AB147">
-        <v>0</v>
-      </c>
-      <c r="AC147">
-        <v>0</v>
-      </c>
-      <c r="AD147">
-        <v>0</v>
-      </c>
-      <c r="AE147">
-        <v>0</v>
-      </c>
-      <c r="AF147">
-        <v>0</v>
-      </c>
-      <c r="AG147">
-        <v>0</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>0</v>
-      </c>
-      <c r="AK147">
-        <v>0</v>
-      </c>
-      <c r="AL147">
-        <v>0</v>
-      </c>
-      <c r="AM147">
-        <v>-1</v>
-      </c>
-      <c r="AN147">
-        <v>-1</v>
-      </c>
-      <c r="AO147">
-        <v>-1</v>
-      </c>
-      <c r="AP147">
-        <v>-1</v>
-      </c>
-      <c r="AQ147">
-        <v>0</v>
-      </c>
-      <c r="AR147">
-        <v>0</v>
-      </c>
-      <c r="AS147">
-        <v>0</v>
-      </c>
-      <c r="AT147">
-        <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>2026-09-11 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Denver Summit W</t>
-        </is>
-      </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
-        <v>0</v>
-      </c>
-      <c r="I148">
-        <v>0</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="O148">
-        <v>0</v>
-      </c>
-      <c r="P148">
-        <v>0</v>
-      </c>
-      <c r="Q148">
-        <v>0</v>
-      </c>
-      <c r="R148">
-        <v>0</v>
-      </c>
-      <c r="S148">
-        <v>0</v>
-      </c>
-      <c r="T148">
-        <v>0</v>
-      </c>
-      <c r="U148">
-        <v>0</v>
-      </c>
-      <c r="V148">
-        <v>0</v>
-      </c>
-      <c r="W148">
-        <v>0</v>
-      </c>
-      <c r="X148">
-        <v>0</v>
-      </c>
-      <c r="Y148">
-        <v>0</v>
-      </c>
-      <c r="Z148">
-        <v>0</v>
-      </c>
-      <c r="AA148">
-        <v>0</v>
-      </c>
-      <c r="AB148">
-        <v>0</v>
-      </c>
-      <c r="AC148">
-        <v>0</v>
-      </c>
-      <c r="AD148">
-        <v>0</v>
-      </c>
-      <c r="AE148">
-        <v>0</v>
-      </c>
-      <c r="AF148">
-        <v>0</v>
-      </c>
-      <c r="AG148">
-        <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ148">
-        <v>0</v>
-      </c>
-      <c r="AK148">
-        <v>0</v>
-      </c>
-      <c r="AL148">
-        <v>0</v>
-      </c>
-      <c r="AM148">
-        <v>-1</v>
-      </c>
-      <c r="AN148">
-        <v>-1</v>
-      </c>
-      <c r="AO148">
-        <v>-1</v>
-      </c>
-      <c r="AP148">
-        <v>-1</v>
-      </c>
-      <c r="AQ148">
-        <v>0</v>
-      </c>
-      <c r="AR148">
-        <v>0</v>
-      </c>
-      <c r="AS148">
-        <v>0</v>
-      </c>
-      <c r="AT148">
-        <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
         <is>
           <t>2026-09-11 23:00:00</t>
         </is>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL106">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU145"/>
+  <dimension ref="A1:AU144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Bắc Ninh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bắc Ninh</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G7">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hatta</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Hatta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19">
@@ -3904,10 +3904,10 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3916,13 +3916,13 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -3949,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O84">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="P84">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="Q84">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="S84">
         <v>1.2</v>
       </c>
       <c r="T84">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="U84">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="V84">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W84">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X84">
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z84">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA84">
+        <v>1.36</v>
+      </c>
+      <c r="AB84">
+        <v>2.7</v>
+      </c>
+      <c r="AC84">
+        <v>2.02</v>
+      </c>
+      <c r="AD84">
+        <v>1.75</v>
+      </c>
+      <c r="AE84">
+        <v>1.31</v>
+      </c>
+      <c r="AF84">
         <v>1.37</v>
       </c>
-      <c r="AB84">
-        <v>2.66</v>
-      </c>
-      <c r="AC84">
-        <v>2.05</v>
-      </c>
-      <c r="AD84">
-        <v>1.73</v>
-      </c>
-      <c r="AE84">
-        <v>1.29</v>
-      </c>
-      <c r="AF84">
-        <v>1.4</v>
-      </c>
       <c r="AG84">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="O85">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="P85">
-        <v>1.99</v>
+        <v>5.5</v>
       </c>
       <c r="Q85">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="R85">
+        <v>2.81</v>
+      </c>
+      <c r="S85">
+        <v>1.09</v>
+      </c>
+      <c r="T85">
+        <v>5.5</v>
+      </c>
+      <c r="U85">
+        <v>1.78</v>
+      </c>
+      <c r="V85">
+        <v>1.95</v>
+      </c>
+      <c r="W85">
+        <v>1.27</v>
+      </c>
+      <c r="X85">
+        <v>1.01</v>
+      </c>
+      <c r="Y85">
+        <v>1.02</v>
+      </c>
+      <c r="Z85">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA85">
+        <v>1.26</v>
+      </c>
+      <c r="AB85">
+        <v>3.62</v>
+      </c>
+      <c r="AC85">
+        <v>1.7</v>
+      </c>
+      <c r="AD85">
+        <v>2.09</v>
+      </c>
+      <c r="AE85">
+        <v>1.48</v>
+      </c>
+      <c r="AF85">
+        <v>1.36</v>
+      </c>
+      <c r="AG85">
+        <v>2.9</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <v>1.13</v>
+      </c>
+      <c r="AK85">
         <v>2.61</v>
-      </c>
-      <c r="S85">
-        <v>1.2</v>
-      </c>
-      <c r="T85">
-        <v>4</v>
-      </c>
-      <c r="U85">
-        <v>2</v>
-      </c>
-      <c r="V85">
-        <v>1.73</v>
-      </c>
-      <c r="W85">
-        <v>1.18</v>
-      </c>
-      <c r="X85">
-        <v>1.02</v>
-      </c>
-      <c r="Y85">
-        <v>1.08</v>
-      </c>
-      <c r="Z85">
-        <v>6</v>
-      </c>
-      <c r="AA85">
-        <v>1.36</v>
-      </c>
-      <c r="AB85">
-        <v>2.7</v>
-      </c>
-      <c r="AC85">
-        <v>2.02</v>
-      </c>
-      <c r="AD85">
-        <v>1.75</v>
-      </c>
-      <c r="AE85">
-        <v>1.31</v>
-      </c>
-      <c r="AF85">
-        <v>1.37</v>
-      </c>
-      <c r="AG85">
-        <v>2.86</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.22</v>
-      </c>
-      <c r="AK85">
-        <v>1.31</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
+        <v>3.3</v>
+      </c>
+      <c r="O86">
+        <v>3.7</v>
+      </c>
+      <c r="P86">
+        <v>1.91</v>
+      </c>
+      <c r="Q86">
+        <v>3.74</v>
+      </c>
+      <c r="R86">
+        <v>2.38</v>
+      </c>
+      <c r="S86">
+        <v>1.2</v>
+      </c>
+      <c r="T86">
+        <v>3.78</v>
+      </c>
+      <c r="U86">
+        <v>2.13</v>
+      </c>
+      <c r="V86">
+        <v>1.68</v>
+      </c>
+      <c r="W86">
+        <v>1.15</v>
+      </c>
+      <c r="X86">
+        <v>1.02</v>
+      </c>
+      <c r="Y86">
+        <v>1.07</v>
+      </c>
+      <c r="Z86">
+        <v>5.8</v>
+      </c>
+      <c r="AA86">
+        <v>1.37</v>
+      </c>
+      <c r="AB86">
+        <v>2.66</v>
+      </c>
+      <c r="AC86">
+        <v>2.05</v>
+      </c>
+      <c r="AD86">
+        <v>1.73</v>
+      </c>
+      <c r="AE86">
+        <v>1.29</v>
+      </c>
+      <c r="AF86">
         <v>1.4</v>
       </c>
-      <c r="O86">
-        <v>5</v>
-      </c>
-      <c r="P86">
-        <v>5.5</v>
-      </c>
-      <c r="Q86">
-        <v>1.83</v>
-      </c>
-      <c r="R86">
-        <v>2.81</v>
-      </c>
-      <c r="S86">
-        <v>1.09</v>
-      </c>
-      <c r="T86">
-        <v>5.5</v>
-      </c>
-      <c r="U86">
-        <v>1.78</v>
-      </c>
-      <c r="V86">
-        <v>1.95</v>
-      </c>
-      <c r="W86">
-        <v>1.27</v>
-      </c>
-      <c r="X86">
-        <v>1.01</v>
-      </c>
-      <c r="Y86">
-        <v>1.02</v>
-      </c>
-      <c r="Z86">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA86">
-        <v>1.26</v>
-      </c>
-      <c r="AB86">
-        <v>3.62</v>
-      </c>
-      <c r="AC86">
-        <v>1.7</v>
-      </c>
-      <c r="AD86">
-        <v>2.09</v>
-      </c>
-      <c r="AE86">
-        <v>1.48</v>
-      </c>
-      <c r="AF86">
-        <v>1.36</v>
-      </c>
       <c r="AG86">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK86">
-        <v>2.61</v>
+        <v>1.28</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15640,55 +15640,55 @@
         <v>0</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="O104">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P104">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="Q104">
+        <v>1.79</v>
+      </c>
+      <c r="R104">
+        <v>2.56</v>
+      </c>
+      <c r="S104">
+        <v>1.21</v>
+      </c>
+      <c r="T104">
+        <v>3.58</v>
+      </c>
+      <c r="U104">
+        <v>2.16</v>
+      </c>
+      <c r="V104">
+        <v>1.62</v>
+      </c>
+      <c r="W104">
+        <v>1.13</v>
+      </c>
+      <c r="X104">
+        <v>1.02</v>
+      </c>
+      <c r="Y104">
+        <v>1.1</v>
+      </c>
+      <c r="Z104">
+        <v>5.1</v>
+      </c>
+      <c r="AA104">
+        <v>1.43</v>
+      </c>
+      <c r="AB104">
         <v>2.46</v>
       </c>
-      <c r="R104">
-        <v>2.15</v>
-      </c>
-      <c r="S104">
-        <v>1.29</v>
-      </c>
-      <c r="T104">
-        <v>3.12</v>
-      </c>
-      <c r="U104">
-        <v>2.45</v>
-      </c>
-      <c r="V104">
-        <v>1.48</v>
-      </c>
-      <c r="W104">
-        <v>1.08</v>
-      </c>
-      <c r="X104">
-        <v>1.03</v>
-      </c>
-      <c r="Y104">
-        <v>1.15</v>
-      </c>
-      <c r="Z104">
-        <v>4.25</v>
-      </c>
-      <c r="AA104">
-        <v>1.65</v>
-      </c>
-      <c r="AB104">
+      <c r="AC104">
         <v>2.21</v>
       </c>
-      <c r="AC104">
-        <v>2.57</v>
-      </c>
       <c r="AD104">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AE104">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF104">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AG104">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK104">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="O105">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="P105">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q105">
-        <v>1.79</v>
+        <v>2.46</v>
       </c>
       <c r="R105">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="S105">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="T105">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="U105">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="V105">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z105">
-        <v>5.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA105">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AB105">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="AC105">
-        <v>2.21</v>
+        <v>2.57</v>
       </c>
       <c r="AD105">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AE105">
+        <v>1.18</v>
+      </c>
+      <c r="AF105">
+        <v>1.57</v>
+      </c>
+      <c r="AG105">
+        <v>2.25</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
         <v>1.22</v>
       </c>
-      <c r="AF105">
-        <v>1.68</v>
-      </c>
-      <c r="AG105">
-        <v>2.04</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.11</v>
-      </c>
       <c r="AK105">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18411,34 +18411,34 @@
         <v>3.2</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA111">
         <v>2.37</v>
@@ -18447,19 +18447,19 @@
         <v>1.57</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19878,55 +19878,55 @@
         <v>0</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q125">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R125">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S125">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T125">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U125">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V125">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X125">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y125">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC125">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD125">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE125">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF125">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG125">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK125">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,22 +21783,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G132">
@@ -21834,55 +21834,55 @@
         <v>0</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G139">
@@ -23245,27 +23245,27 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G141">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-09-11 21:00:00</t>
+          <t>2026-09-11 22:00:00</t>
         </is>
       </c>
     </row>
@@ -23408,12 +23408,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,64 +23455,64 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-09-11 22:00:00</t>
+          <t>2026-09-11 22:30:00</t>
         </is>
       </c>
     </row>
@@ -23571,7 +23571,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O143">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P143">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q143">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R143">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S143">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T143">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U143">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V143">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W143">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X143">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y143">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z143">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA143">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB143">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC143">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD143">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE143">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF143">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG143">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK143">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-09-11 22:30:00</t>
+          <t>2026-09-11 23:00:00</t>
         </is>
       </c>
     </row>
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23884,169 +23884,6 @@
         <v>0</v>
       </c>
       <c r="AU144" t="inlineStr">
-        <is>
-          <t>2026-09-11 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Angel City</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Denver Summit W</t>
-        </is>
-      </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145">
-        <v>0</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
-      </c>
-      <c r="J145">
-        <v>0</v>
-      </c>
-      <c r="K145">
-        <v>0</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>0</v>
-      </c>
-      <c r="R145">
-        <v>0</v>
-      </c>
-      <c r="S145">
-        <v>0</v>
-      </c>
-      <c r="T145">
-        <v>0</v>
-      </c>
-      <c r="U145">
-        <v>0</v>
-      </c>
-      <c r="V145">
-        <v>0</v>
-      </c>
-      <c r="W145">
-        <v>0</v>
-      </c>
-      <c r="X145">
-        <v>0</v>
-      </c>
-      <c r="Y145">
-        <v>0</v>
-      </c>
-      <c r="Z145">
-        <v>0</v>
-      </c>
-      <c r="AA145">
-        <v>0</v>
-      </c>
-      <c r="AB145">
-        <v>0</v>
-      </c>
-      <c r="AC145">
-        <v>0</v>
-      </c>
-      <c r="AD145">
-        <v>0</v>
-      </c>
-      <c r="AE145">
-        <v>0</v>
-      </c>
-      <c r="AF145">
-        <v>0</v>
-      </c>
-      <c r="AG145">
-        <v>0</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ145">
-        <v>0</v>
-      </c>
-      <c r="AK145">
-        <v>0</v>
-      </c>
-      <c r="AL145">
-        <v>0</v>
-      </c>
-      <c r="AM145">
-        <v>-1</v>
-      </c>
-      <c r="AN145">
-        <v>-1</v>
-      </c>
-      <c r="AO145">
-        <v>-1</v>
-      </c>
-      <c r="AP145">
-        <v>-1</v>
-      </c>
-      <c r="AQ145">
-        <v>0</v>
-      </c>
-      <c r="AR145">
-        <v>0</v>
-      </c>
-      <c r="AS145">
-        <v>0</v>
-      </c>
-      <c r="AT145">
-        <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
         <is>
           <t>2026-09-11 23:00:00</t>
         </is>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -2277,19 +2277,19 @@
         <v>2.27</v>
       </c>
       <c r="R12">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
         <v>2.82</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2304,26 +2304,26 @@
         <v>3.46</v>
       </c>
       <c r="AA12">
+        <v>1.85</v>
+      </c>
+      <c r="AB12">
+        <v>1.88</v>
+      </c>
+      <c r="AC12">
+        <v>2.97</v>
+      </c>
+      <c r="AD12">
+        <v>1.3</v>
+      </c>
+      <c r="AE12">
+        <v>1.11</v>
+      </c>
+      <c r="AF12">
+        <v>1.78</v>
+      </c>
+      <c r="AG12">
         <v>1.86</v>
       </c>
-      <c r="AB12">
-        <v>1.83</v>
-      </c>
-      <c r="AC12">
-        <v>3.16</v>
-      </c>
-      <c r="AD12">
-        <v>1.33</v>
-      </c>
-      <c r="AE12">
-        <v>1.08</v>
-      </c>
-      <c r="AF12">
-        <v>1.79</v>
-      </c>
-      <c r="AG12">
-        <v>1.88</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3255,10 +3255,10 @@
         <v>2.93</v>
       </c>
       <c r="R18">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
         <v>3.72</v>
@@ -3270,7 +3270,7 @@
         <v>1.65</v>
       </c>
       <c r="W18">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
         <v>1.02</v>
@@ -3282,13 +3282,13 @@
         <v>5.05</v>
       </c>
       <c r="AA18">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB18">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AC18">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="AD18">
         <v>1.63</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q22">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U22">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
         <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB22">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG22">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="O28">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q28">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="R28">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="U28">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="V28">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
         <v>1.09</v>
@@ -4909,19 +4909,19 @@
         <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.98</v>
+        <v>3.78</v>
       </c>
       <c r="AA28">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AB28">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AC28">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE28">
         <v>1.12</v>
@@ -4930,7 +4930,7 @@
         <v>1.63</v>
       </c>
       <c r="AG28">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5045,55 +5045,55 @@
         <v>3.29</v>
       </c>
       <c r="Q29">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S29">
         <v>1.39</v>
       </c>
       <c r="T29">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
         <v>2.95</v>
       </c>
       <c r="V29">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
         <v>1.02</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z29">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="AA29">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AB29">
         <v>1.76</v>
       </c>
       <c r="AC29">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD29">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,80 +10741,80 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.44</v>
+        <v>3.5</v>
       </c>
       <c r="O64">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="P64">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q64">
-        <v>1.97</v>
+        <v>3.92</v>
       </c>
       <c r="R64">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="V64">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="W64">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z64">
-        <v>6.22</v>
+        <v>5</v>
       </c>
       <c r="AA64">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB64">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AC64">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AD64">
+        <v>1.63</v>
+      </c>
+      <c r="AE64">
+        <v>1.23</v>
+      </c>
+      <c r="AF64">
+        <v>1.43</v>
+      </c>
+      <c r="AG64">
+        <v>2.59</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.79</v>
       </c>
-      <c r="AE64">
-        <v>1.28</v>
-      </c>
-      <c r="AF64">
-        <v>1.47</v>
-      </c>
-      <c r="AG64">
-        <v>2.42</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.1</v>
-      </c>
       <c r="AK64">
-        <v>2.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.5</v>
+        <v>1.44</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="P65">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q65">
-        <v>3.92</v>
+        <v>1.97</v>
       </c>
       <c r="R65">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="S65">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T65">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="V65">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
+        <v>1.08</v>
+      </c>
+      <c r="Z65">
+        <v>6.22</v>
+      </c>
+      <c r="AA65">
+        <v>1.36</v>
+      </c>
+      <c r="AB65">
+        <v>2.7</v>
+      </c>
+      <c r="AC65">
+        <v>1.96</v>
+      </c>
+      <c r="AD65">
+        <v>1.79</v>
+      </c>
+      <c r="AE65">
+        <v>1.28</v>
+      </c>
+      <c r="AF65">
+        <v>1.47</v>
+      </c>
+      <c r="AG65">
+        <v>2.42</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
         <v>1.1</v>
       </c>
-      <c r="Z65">
-        <v>5</v>
-      </c>
-      <c r="AA65">
-        <v>1.43</v>
-      </c>
-      <c r="AB65">
-        <v>2.46</v>
-      </c>
-      <c r="AC65">
-        <v>2.14</v>
-      </c>
-      <c r="AD65">
-        <v>1.63</v>
-      </c>
-      <c r="AE65">
-        <v>1.23</v>
-      </c>
-      <c r="AF65">
-        <v>1.43</v>
-      </c>
-      <c r="AG65">
-        <v>2.59</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.79</v>
-      </c>
       <c r="AK65">
-        <v>1.23</v>
+        <v>2.31</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -13521,55 +13521,55 @@
         <v>7.8</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>2.6</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="O83">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="P83">
-        <v>2.33</v>
+        <v>1.99</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O84">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="P84">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q84">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="R84">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
         <v>1.2</v>
       </c>
       <c r="T84">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="U84">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="V84">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W84">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X84">
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z84">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AA84">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB84">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AC84">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD84">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE84">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF84">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK84">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,31 +14327,31 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="O86">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P86">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="Q86">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="R86">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="U86">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="V86">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="W86">
         <v>1.15</v>
@@ -14360,47 +14360,47 @@
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z86">
-        <v>5.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA86">
+        <v>1.5</v>
+      </c>
+      <c r="AB86">
+        <v>2.48</v>
+      </c>
+      <c r="AC86">
+        <v>2.18</v>
+      </c>
+      <c r="AD86">
+        <v>1.61</v>
+      </c>
+      <c r="AE86">
+        <v>1.21</v>
+      </c>
+      <c r="AF86">
+        <v>1.41</v>
+      </c>
+      <c r="AG86">
+        <v>2.63</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
+        <v>1.24</v>
+      </c>
+      <c r="AK86">
         <v>1.37</v>
-      </c>
-      <c r="AB86">
-        <v>2.66</v>
-      </c>
-      <c r="AC86">
-        <v>2.05</v>
-      </c>
-      <c r="AD86">
-        <v>1.73</v>
-      </c>
-      <c r="AE86">
-        <v>1.29</v>
-      </c>
-      <c r="AF86">
-        <v>1.4</v>
-      </c>
-      <c r="AG86">
-        <v>2.75</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.23</v>
-      </c>
-      <c r="AK86">
-        <v>1.28</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.35</v>
+        <v>1.8</v>
       </c>
       <c r="O104">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="P104">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q104">
-        <v>1.79</v>
+        <v>2.46</v>
       </c>
       <c r="R104">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="S104">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="T104">
-        <v>3.58</v>
+        <v>3.12</v>
       </c>
       <c r="U104">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="V104">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W104">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z104">
-        <v>5.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA104">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AB104">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="AC104">
-        <v>2.21</v>
+        <v>2.57</v>
       </c>
       <c r="AD104">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AE104">
+        <v>1.18</v>
+      </c>
+      <c r="AF104">
+        <v>1.57</v>
+      </c>
+      <c r="AG104">
+        <v>2.25</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.22</v>
       </c>
-      <c r="AF104">
-        <v>1.68</v>
-      </c>
-      <c r="AG104">
-        <v>2.04</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.11</v>
-      </c>
       <c r="AK104">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="O105">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P105">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="Q105">
+        <v>1.79</v>
+      </c>
+      <c r="R105">
+        <v>2.56</v>
+      </c>
+      <c r="S105">
+        <v>1.21</v>
+      </c>
+      <c r="T105">
+        <v>3.58</v>
+      </c>
+      <c r="U105">
+        <v>2.16</v>
+      </c>
+      <c r="V105">
+        <v>1.62</v>
+      </c>
+      <c r="W105">
+        <v>1.13</v>
+      </c>
+      <c r="X105">
+        <v>1.02</v>
+      </c>
+      <c r="Y105">
+        <v>1.1</v>
+      </c>
+      <c r="Z105">
+        <v>5.1</v>
+      </c>
+      <c r="AA105">
+        <v>1.43</v>
+      </c>
+      <c r="AB105">
         <v>2.46</v>
       </c>
-      <c r="R105">
-        <v>2.15</v>
-      </c>
-      <c r="S105">
-        <v>1.29</v>
-      </c>
-      <c r="T105">
-        <v>3.12</v>
-      </c>
-      <c r="U105">
-        <v>2.45</v>
-      </c>
-      <c r="V105">
-        <v>1.48</v>
-      </c>
-      <c r="W105">
-        <v>1.08</v>
-      </c>
-      <c r="X105">
-        <v>1.03</v>
-      </c>
-      <c r="Y105">
-        <v>1.15</v>
-      </c>
-      <c r="Z105">
-        <v>4.25</v>
-      </c>
-      <c r="AA105">
-        <v>1.65</v>
-      </c>
-      <c r="AB105">
+      <c r="AC105">
         <v>2.21</v>
       </c>
-      <c r="AC105">
-        <v>2.57</v>
-      </c>
       <c r="AD105">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AE105">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF105">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AG105">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK105">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -21997,16 +21997,16 @@
         <v>0</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U133">
         <v>0</v>
@@ -22021,31 +22021,31 @@
         <v>0</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE133">
         <v>0</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G140">

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.98</v>
+        <v>2.65</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="Q3">
         <v>3.65</v>
@@ -813,10 +813,10 @@
         <v>1.96</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="U3">
         <v>2.95</v>
@@ -831,22 +831,22 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z3">
         <v>2.94</v>
       </c>
       <c r="AA3">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="AD3">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
         <v>1.07</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AK3">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.48</v>
+        <v>4.12</v>
       </c>
       <c r="O4">
         <v>3.48</v>
@@ -976,19 +976,19 @@
         <v>2.14</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="U4">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V4">
         <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1000,16 +1000,16 @@
         <v>3.3</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB4">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AD4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
         <v>1.08</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="O29">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="Q29">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R29">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
         <v>1.39</v>
@@ -5057,10 +5057,10 @@
         <v>2.88</v>
       </c>
       <c r="U29">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
         <v>1.02</v>
@@ -5069,31 +5069,31 @@
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z29">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA29">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AB29">
         <v>1.76</v>
       </c>
       <c r="AC29">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="P36">
         <v>4.05</v>
       </c>
       <c r="Q36">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R36">
+        <v>2.53</v>
+      </c>
+      <c r="S36">
+        <v>1.22</v>
+      </c>
+      <c r="T36">
+        <v>3.8</v>
+      </c>
+      <c r="U36">
+        <v>2.31</v>
+      </c>
+      <c r="V36">
+        <v>1.61</v>
+      </c>
+      <c r="W36">
+        <v>1.14</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.13</v>
+      </c>
+      <c r="Z36">
+        <v>4.5</v>
+      </c>
+      <c r="AA36">
+        <v>1.57</v>
+      </c>
+      <c r="AB36">
+        <v>2.26</v>
+      </c>
+      <c r="AC36">
         <v>2.38</v>
       </c>
-      <c r="S36">
-        <v>1.25</v>
-      </c>
-      <c r="T36">
-        <v>3.52</v>
-      </c>
-      <c r="U36">
-        <v>2.23</v>
-      </c>
-      <c r="V36">
+      <c r="AD36">
         <v>1.55</v>
       </c>
-      <c r="W36">
-        <v>1.13</v>
-      </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.15</v>
-      </c>
-      <c r="Z36">
-        <v>4.3</v>
-      </c>
-      <c r="AA36">
+      <c r="AE36">
+        <v>1.18</v>
+      </c>
+      <c r="AF36">
         <v>1.54</v>
       </c>
-      <c r="AB36">
-        <v>2.19</v>
-      </c>
-      <c r="AC36">
-        <v>2.36</v>
-      </c>
-      <c r="AD36">
-        <v>1.5</v>
-      </c>
-      <c r="AE36">
-        <v>1.19</v>
-      </c>
-      <c r="AF36">
-        <v>1.53</v>
-      </c>
       <c r="AG36">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8468,10 +8468,10 @@
         <v>3.95</v>
       </c>
       <c r="Q50">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="R50">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S50">
         <v>1.44</v>
@@ -8498,22 +8498,22 @@
         <v>2.94</v>
       </c>
       <c r="AA50">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AB50">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC50">
-        <v>4.04</v>
+        <v>3.52</v>
       </c>
       <c r="AD50">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE50">
         <v>1.04</v>
       </c>
       <c r="AF50">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG50">
         <v>1.84</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P55">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="O69">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P69">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q69">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="R69">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="S69">
         <v>1.33</v>
       </c>
       <c r="T69">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="U69">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V69">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z69">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="AA69">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB69">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC69">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AD69">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF69">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG69">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="O70">
-        <v>3.76</v>
+        <v>3.48</v>
       </c>
       <c r="P70">
-        <v>4.07</v>
+        <v>3.2</v>
       </c>
       <c r="Q70">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="R70">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T70">
-        <v>3.22</v>
+        <v>2.88</v>
       </c>
       <c r="U70">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V70">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>3.92</v>
+        <v>3.28</v>
       </c>
       <c r="AA70">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AB70">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AC70">
-        <v>2.93</v>
+        <v>3.56</v>
       </c>
       <c r="AD70">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AE70">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AG70">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK70">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
+        <v>3.3</v>
+      </c>
+      <c r="O71">
+        <v>3.2</v>
+      </c>
+      <c r="P71">
         <v>2</v>
       </c>
-      <c r="O71">
-        <v>3.7</v>
-      </c>
-      <c r="P71">
-        <v>3.55</v>
-      </c>
       <c r="Q71">
-        <v>2.52</v>
+        <v>4.22</v>
       </c>
       <c r="R71">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="S71">
         <v>1.39</v>
       </c>
       <c r="T71">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U71">
         <v>2.77</v>
       </c>
       <c r="V71">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W71">
         <v>1.05</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y71">
         <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA71">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB71">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC71">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="AD71">
         <v>1.28</v>
       </c>
       <c r="AE71">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF71">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG71">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK71">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.33</v>
+        <v>1.7</v>
       </c>
       <c r="O73">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="P73">
-        <v>3.13</v>
+        <v>4.89</v>
       </c>
       <c r="Q73">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="R73">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="S73">
+        <v>1.36</v>
+      </c>
+      <c r="T73">
+        <v>2.89</v>
+      </c>
+      <c r="U73">
+        <v>2.53</v>
+      </c>
+      <c r="V73">
         <v>1.46</v>
       </c>
-      <c r="T73">
-        <v>2.43</v>
-      </c>
-      <c r="U73">
-        <v>3.22</v>
-      </c>
-      <c r="V73">
-        <v>1.3</v>
-      </c>
       <c r="W73">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X73">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="Z73">
-        <v>2.69</v>
+        <v>3.89</v>
       </c>
       <c r="AA73">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="AB73">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="AC73">
-        <v>4.33</v>
+        <v>2.64</v>
       </c>
       <c r="AD73">
+        <v>1.39</v>
+      </c>
+      <c r="AE73">
         <v>1.14</v>
       </c>
-      <c r="AE73">
-        <v>1.01</v>
-      </c>
       <c r="AF73">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AG73">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>3.92</v>
+        <v>4.9</v>
       </c>
       <c r="O76">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="P76">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O77">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P77">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q77">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="R77">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S77">
         <v>1.36</v>
       </c>
       <c r="T77">
-        <v>2.73</v>
+        <v>2.68</v>
       </c>
       <c r="U77">
         <v>2.62</v>
       </c>
       <c r="V77">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W77">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
         <v>1.01</v>
       </c>
       <c r="Y77">
+        <v>1.23</v>
+      </c>
+      <c r="Z77">
+        <v>3.44</v>
+      </c>
+      <c r="AA77">
+        <v>1.9</v>
+      </c>
+      <c r="AB77">
+        <v>1.75</v>
+      </c>
+      <c r="AC77">
+        <v>3.26</v>
+      </c>
+      <c r="AD77">
         <v>1.28</v>
       </c>
-      <c r="Z77">
-        <v>3.49</v>
-      </c>
-      <c r="AA77">
-        <v>1.91</v>
-      </c>
-      <c r="AB77">
-        <v>1.87</v>
-      </c>
-      <c r="AC77">
-        <v>3.25</v>
-      </c>
-      <c r="AD77">
-        <v>1.32</v>
-      </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF77">
+        <v>1.75</v>
+      </c>
+      <c r="AG77">
+        <v>2</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <v>1.28</v>
+      </c>
+      <c r="AK77">
         <v>1.7</v>
-      </c>
-      <c r="AG77">
-        <v>2.01</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.27</v>
-      </c>
-      <c r="AK77">
-        <v>1.73</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="O79">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="P79">
-        <v>3.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q79">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="R79">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="S79">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="T79">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U79">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="V79">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="W79">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z79">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AA79">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AB79">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="AC79">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AD79">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AE79">
+        <v>1.42</v>
+      </c>
+      <c r="AF79">
         <v>1.3</v>
       </c>
-      <c r="AF79">
+      <c r="AG79">
+        <v>2.95</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.4</v>
       </c>
-      <c r="AG79">
-        <v>2.75</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.25</v>
-      </c>
       <c r="AK79">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.07</v>
+        <v>1.25</v>
       </c>
       <c r="O80">
-        <v>4.15</v>
+        <v>5.8</v>
       </c>
       <c r="P80">
-        <v>2.85</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q80">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="R80">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S80">
+        <v>1.18</v>
+      </c>
+      <c r="T80">
+        <v>3.85</v>
+      </c>
+      <c r="U80">
+        <v>2.01</v>
+      </c>
+      <c r="V80">
+        <v>1.74</v>
+      </c>
+      <c r="W80">
         <v>1.17</v>
-      </c>
-      <c r="T80">
-        <v>4.55</v>
-      </c>
-      <c r="U80">
-        <v>1.87</v>
-      </c>
-      <c r="V80">
-        <v>1.86</v>
-      </c>
-      <c r="W80">
-        <v>1.25</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z80">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="AA80">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB80">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="AC80">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AD80">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AE80">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AF80">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AG80">
-        <v>3.32</v>
+        <v>2.06</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK80">
-        <v>1.7</v>
+        <v>3.52</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.34</v>
+        <v>2.48</v>
       </c>
       <c r="O81">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>7.8</v>
+        <v>2.51</v>
       </c>
       <c r="Q81">
-        <v>1.67</v>
+        <v>2.89</v>
       </c>
       <c r="R81">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="S81">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T81">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="U81">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="V81">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="W81">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z81">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA81">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB81">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC81">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AD81">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AE81">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AF81">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>3.52</v>
+        <v>1.49</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.49</v>
+        <v>3.3</v>
       </c>
       <c r="O82">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="P82">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="Q82">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="R82">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.36</v>
+        <v>3.78</v>
       </c>
       <c r="U82">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="V82">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="W82">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z82">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AA82">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AB82">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="AC82">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AD82">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AE82">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AF82">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG82">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK82">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,58 +13838,58 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.25</v>
+        <v>1.43</v>
       </c>
       <c r="O83">
-        <v>3.88</v>
+        <v>4.95</v>
       </c>
       <c r="P83">
-        <v>1.99</v>
+        <v>5.82</v>
       </c>
       <c r="Q83">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="R83">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U83">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="V83">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="W83">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="X83">
+        <v>1.01</v>
+      </c>
+      <c r="Y83">
         <v>1.02</v>
       </c>
-      <c r="Y83">
-        <v>1.08</v>
-      </c>
       <c r="Z83">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="AA83">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AB83">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AC83">
-        <v>2.02</v>
+        <v>1.69</v>
       </c>
       <c r="AD83">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="AE83">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AF83">
         <v>1.37</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK83">
-        <v>1.31</v>
+        <v>2.68</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,16 +14001,16 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.3</v>
+        <v>1.77</v>
       </c>
       <c r="O84">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="P84">
-        <v>1.91</v>
+        <v>3.69</v>
       </c>
       <c r="Q84">
-        <v>3.74</v>
+        <v>2.28</v>
       </c>
       <c r="R84">
         <v>2.38</v>
@@ -14019,46 +14019,46 @@
         <v>1.2</v>
       </c>
       <c r="T84">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="U84">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V84">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W84">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X84">
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z84">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA84">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AB84">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC84">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD84">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE84">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG84">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,65 +14164,65 @@
         </is>
       </c>
       <c r="N85">
+        <v>3.05</v>
+      </c>
+      <c r="O85">
+        <v>3.84</v>
+      </c>
+      <c r="P85">
+        <v>1.96</v>
+      </c>
+      <c r="Q85">
+        <v>3.3</v>
+      </c>
+      <c r="R85">
+        <v>2.38</v>
+      </c>
+      <c r="S85">
+        <v>1.2</v>
+      </c>
+      <c r="T85">
+        <v>4</v>
+      </c>
+      <c r="U85">
+        <v>2.07</v>
+      </c>
+      <c r="V85">
+        <v>1.72</v>
+      </c>
+      <c r="W85">
+        <v>1.18</v>
+      </c>
+      <c r="X85">
+        <v>1.02</v>
+      </c>
+      <c r="Y85">
+        <v>1.14</v>
+      </c>
+      <c r="Z85">
+        <v>6</v>
+      </c>
+      <c r="AA85">
         <v>1.4</v>
       </c>
-      <c r="O85">
-        <v>5</v>
-      </c>
-      <c r="P85">
-        <v>5.5</v>
-      </c>
-      <c r="Q85">
-        <v>1.83</v>
-      </c>
-      <c r="R85">
+      <c r="AB85">
+        <v>2.82</v>
+      </c>
+      <c r="AC85">
+        <v>2.06</v>
+      </c>
+      <c r="AD85">
+        <v>1.69</v>
+      </c>
+      <c r="AE85">
+        <v>1.26</v>
+      </c>
+      <c r="AF85">
+        <v>1.38</v>
+      </c>
+      <c r="AG85">
         <v>2.81</v>
       </c>
-      <c r="S85">
-        <v>1.09</v>
-      </c>
-      <c r="T85">
-        <v>5.5</v>
-      </c>
-      <c r="U85">
-        <v>1.78</v>
-      </c>
-      <c r="V85">
-        <v>1.95</v>
-      </c>
-      <c r="W85">
-        <v>1.27</v>
-      </c>
-      <c r="X85">
-        <v>1.01</v>
-      </c>
-      <c r="Y85">
-        <v>1.02</v>
-      </c>
-      <c r="Z85">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA85">
-        <v>1.26</v>
-      </c>
-      <c r="AB85">
-        <v>3.62</v>
-      </c>
-      <c r="AC85">
-        <v>1.7</v>
-      </c>
-      <c r="AD85">
-        <v>2.09</v>
-      </c>
-      <c r="AE85">
-        <v>1.48</v>
-      </c>
-      <c r="AF85">
-        <v>1.36</v>
-      </c>
-      <c r="AG85">
-        <v>2.9</v>
-      </c>
       <c r="AH85" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>2.61</v>
+        <v>1.29</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O86">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="P86">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q86">
         <v>3</v>
@@ -14490,28 +14490,28 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O87">
         <v>3.5</v>
       </c>
       <c r="P87">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q87">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="R87">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="S87">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T87">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="U87">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V87">
         <v>1.44</v>
@@ -14526,28 +14526,28 @@
         <v>1.23</v>
       </c>
       <c r="Z87">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA87">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB87">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AC87">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="AD87">
         <v>1.36</v>
       </c>
       <c r="AE87">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF87">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AG87">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK87">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -15145,52 +15145,52 @@
         <v>1.68</v>
       </c>
       <c r="O91">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="P91">
-        <v>4.88</v>
+        <v>4.4</v>
       </c>
       <c r="Q91">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="R91">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="S91">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T91">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="U91">
-        <v>2.53</v>
+        <v>2.83</v>
       </c>
       <c r="V91">
         <v>1.44</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z91">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA91">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB91">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AC91">
         <v>3.28</v>
       </c>
       <c r="AD91">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE91">
         <v>1.1</v>
@@ -15199,7 +15199,7 @@
         <v>1.76</v>
       </c>
       <c r="AG91">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15305,25 +15305,25 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="O92">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="P92">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q92">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="R92">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S92">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T92">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="U92">
         <v>2.23</v>
@@ -15332,7 +15332,7 @@
         <v>1.6</v>
       </c>
       <c r="W92">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X92">
         <v>1.02</v>
@@ -15350,19 +15350,19 @@
         <v>2.26</v>
       </c>
       <c r="AC92">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD92">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE92">
         <v>1.16</v>
       </c>
       <c r="AF92">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG92">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15957,52 +15957,52 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O96">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="P96">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="Q96">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R96">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S96">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T96">
         <v>3.6</v>
       </c>
       <c r="U96">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V96">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W96">
+        <v>1.13</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
         <v>1.14</v>
       </c>
-      <c r="X96">
-        <v>1.03</v>
-      </c>
-      <c r="Y96">
-        <v>1.13</v>
-      </c>
       <c r="Z96">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA96">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB96">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC96">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AD96">
         <v>1.6</v>
@@ -16011,7 +16011,7 @@
         <v>1.21</v>
       </c>
       <c r="AF96">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG96">
         <v>2.6</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK96">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16126,58 +16126,58 @@
         <v>3.7</v>
       </c>
       <c r="P97">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q97">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="R97">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S97">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T97">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U97">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V97">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W97">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X97">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z97">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA97">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB97">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AC97">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AD97">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE97">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF97">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG97">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK97">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="O98">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P98">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="Q98">
-        <v>2.93</v>
+        <v>4.38</v>
       </c>
       <c r="R98">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="S98">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T98">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="U98">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="V98">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="W98">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
         <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z98">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA98">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="AB98">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="AC98">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AD98">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AE98">
+        <v>1.17</v>
+      </c>
+      <c r="AF98">
+        <v>1.6</v>
+      </c>
+      <c r="AG98">
+        <v>2.19</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
         <v>1.25</v>
       </c>
-      <c r="AF98">
-        <v>1.43</v>
-      </c>
-      <c r="AG98">
-        <v>2.5</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.47</v>
-      </c>
       <c r="AK98">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
+        <v>2.25</v>
+      </c>
+      <c r="O99">
+        <v>3.35</v>
+      </c>
+      <c r="P99">
+        <v>2.85</v>
+      </c>
+      <c r="Q99">
+        <v>2.93</v>
+      </c>
+      <c r="R99">
+        <v>2.08</v>
+      </c>
+      <c r="S99">
+        <v>1.36</v>
+      </c>
+      <c r="T99">
+        <v>2.88</v>
+      </c>
+      <c r="U99">
+        <v>2.88</v>
+      </c>
+      <c r="V99">
+        <v>1.37</v>
+      </c>
+      <c r="W99">
+        <v>1.06</v>
+      </c>
+      <c r="X99">
+        <v>1</v>
+      </c>
+      <c r="Y99">
+        <v>1.26</v>
+      </c>
+      <c r="Z99">
         <v>3.4</v>
       </c>
-      <c r="O99">
-        <v>3.65</v>
-      </c>
-      <c r="P99">
-        <v>1.85</v>
-      </c>
-      <c r="Q99">
-        <v>4.38</v>
-      </c>
-      <c r="R99">
-        <v>2.22</v>
-      </c>
-      <c r="S99">
+      <c r="AA99">
+        <v>1.98</v>
+      </c>
+      <c r="AB99">
+        <v>1.8</v>
+      </c>
+      <c r="AC99">
+        <v>3.25</v>
+      </c>
+      <c r="AD99">
+        <v>1.29</v>
+      </c>
+      <c r="AE99">
+        <v>1.08</v>
+      </c>
+      <c r="AF99">
+        <v>1.75</v>
+      </c>
+      <c r="AG99">
+        <v>1.95</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.3</v>
       </c>
-      <c r="T99">
-        <v>3.15</v>
-      </c>
-      <c r="U99">
-        <v>2.4</v>
-      </c>
-      <c r="V99">
-        <v>1.5</v>
-      </c>
-      <c r="W99">
-        <v>1.08</v>
-      </c>
-      <c r="X99">
-        <v>1.02</v>
-      </c>
-      <c r="Y99">
-        <v>1.17</v>
-      </c>
-      <c r="Z99">
-        <v>4.05</v>
-      </c>
-      <c r="AA99">
-        <v>1.69</v>
-      </c>
-      <c r="AB99">
-        <v>2.18</v>
-      </c>
-      <c r="AC99">
-        <v>2.57</v>
-      </c>
-      <c r="AD99">
-        <v>1.4</v>
-      </c>
-      <c r="AE99">
-        <v>1.12</v>
-      </c>
-      <c r="AF99">
-        <v>1.62</v>
-      </c>
-      <c r="AG99">
-        <v>2.19</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.25</v>
-      </c>
       <c r="AK99">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
+        <v>2.35</v>
+      </c>
+      <c r="O100">
+        <v>3.6</v>
+      </c>
+      <c r="P100">
+        <v>2.55</v>
+      </c>
+      <c r="Q100">
+        <v>3</v>
+      </c>
+      <c r="R100">
+        <v>2.29</v>
+      </c>
+      <c r="S100">
+        <v>1.26</v>
+      </c>
+      <c r="T100">
+        <v>3.34</v>
+      </c>
+      <c r="U100">
+        <v>2.15</v>
+      </c>
+      <c r="V100">
+        <v>1.62</v>
+      </c>
+      <c r="W100">
+        <v>1.13</v>
+      </c>
+      <c r="X100">
+        <v>1.02</v>
+      </c>
+      <c r="Y100">
+        <v>1.13</v>
+      </c>
+      <c r="Z100">
+        <v>5.27</v>
+      </c>
+      <c r="AA100">
+        <v>1.53</v>
+      </c>
+      <c r="AB100">
+        <v>2.5</v>
+      </c>
+      <c r="AC100">
         <v>2.3</v>
       </c>
-      <c r="O100">
-        <v>3.35</v>
-      </c>
-      <c r="P100">
-        <v>2.85</v>
-      </c>
-      <c r="Q100">
-        <v>2.88</v>
-      </c>
-      <c r="R100">
-        <v>2.1</v>
-      </c>
-      <c r="S100">
-        <v>1.38</v>
-      </c>
-      <c r="T100">
-        <v>2.9</v>
-      </c>
-      <c r="U100">
-        <v>2.95</v>
-      </c>
-      <c r="V100">
-        <v>1.4</v>
-      </c>
-      <c r="W100">
-        <v>1.06</v>
-      </c>
-      <c r="X100">
-        <v>1</v>
-      </c>
-      <c r="Y100">
-        <v>1.27</v>
-      </c>
-      <c r="Z100">
-        <v>3.18</v>
-      </c>
-      <c r="AA100">
-        <v>1.98</v>
-      </c>
-      <c r="AB100">
-        <v>1.8</v>
-      </c>
-      <c r="AC100">
-        <v>3.3</v>
-      </c>
       <c r="AD100">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AE100">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AF100">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="AG100">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK100">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O102">
         <v>3.75</v>
       </c>
       <c r="P102">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q102">
         <v>3.3</v>
@@ -16950,25 +16950,25 @@
         <v>2.36</v>
       </c>
       <c r="S102">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T102">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U102">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V102">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W102">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y102">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z102">
         <v>4.2</v>
@@ -16980,19 +16980,19 @@
         <v>2.12</v>
       </c>
       <c r="AC102">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD102">
         <v>1.45</v>
       </c>
       <c r="AE102">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF102">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG102">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AK102">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,22 +17098,22 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="O103">
         <v>4.6</v>
       </c>
       <c r="P103">
-        <v>6.4</v>
+        <v>6.35</v>
       </c>
       <c r="Q103">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="R103">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="S103">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T103">
         <v>3.25</v>
@@ -17122,40 +17122,40 @@
         <v>2.25</v>
       </c>
       <c r="V103">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W103">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X103">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z103">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA103">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB103">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AC103">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AD103">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AE103">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AF103">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AG103">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK103">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="O104">
         <v>3.45</v>
       </c>
       <c r="P104">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q104">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="R104">
+        <v>2.25</v>
+      </c>
+      <c r="S104">
+        <v>1.3</v>
+      </c>
+      <c r="T104">
+        <v>3.2</v>
+      </c>
+      <c r="U104">
+        <v>2.35</v>
+      </c>
+      <c r="V104">
+        <v>1.53</v>
+      </c>
+      <c r="W104">
+        <v>1.07</v>
+      </c>
+      <c r="X104">
+        <v>1.05</v>
+      </c>
+      <c r="Y104">
+        <v>1.16</v>
+      </c>
+      <c r="Z104">
+        <v>4.15</v>
+      </c>
+      <c r="AA104">
+        <v>1.64</v>
+      </c>
+      <c r="AB104">
+        <v>2.1</v>
+      </c>
+      <c r="AC104">
+        <v>2.52</v>
+      </c>
+      <c r="AD104">
+        <v>1.41</v>
+      </c>
+      <c r="AE104">
+        <v>1.17</v>
+      </c>
+      <c r="AF104">
+        <v>1.58</v>
+      </c>
+      <c r="AG104">
         <v>2.15</v>
-      </c>
-      <c r="S104">
-        <v>1.29</v>
-      </c>
-      <c r="T104">
-        <v>3.12</v>
-      </c>
-      <c r="U104">
-        <v>2.45</v>
-      </c>
-      <c r="V104">
-        <v>1.48</v>
-      </c>
-      <c r="W104">
-        <v>1.08</v>
-      </c>
-      <c r="X104">
-        <v>1.03</v>
-      </c>
-      <c r="Y104">
-        <v>1.15</v>
-      </c>
-      <c r="Z104">
-        <v>4.25</v>
-      </c>
-      <c r="AA104">
-        <v>1.65</v>
-      </c>
-      <c r="AB104">
-        <v>2.21</v>
-      </c>
-      <c r="AC104">
-        <v>2.57</v>
-      </c>
-      <c r="AD104">
-        <v>1.42</v>
-      </c>
-      <c r="AE104">
-        <v>1.18</v>
-      </c>
-      <c r="AF104">
-        <v>1.57</v>
-      </c>
-      <c r="AG104">
-        <v>2.25</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,19 +17424,19 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="O105">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="P105">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Q105">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R105">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="S105">
         <v>1.21</v>
@@ -17445,43 +17445,43 @@
         <v>3.58</v>
       </c>
       <c r="U105">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V105">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X105">
         <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z105">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA105">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB105">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AC105">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AD105">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE105">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF105">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG105">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK105">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,52 +17587,52 @@
         </is>
       </c>
       <c r="N106">
+        <v>2.96</v>
+      </c>
+      <c r="O106">
+        <v>3.5</v>
+      </c>
+      <c r="P106">
+        <v>2.37</v>
+      </c>
+      <c r="Q106">
+        <v>3.5</v>
+      </c>
+      <c r="R106">
+        <v>2.13</v>
+      </c>
+      <c r="S106">
+        <v>1.38</v>
+      </c>
+      <c r="T106">
+        <v>3</v>
+      </c>
+      <c r="U106">
         <v>2.75</v>
       </c>
-      <c r="O106">
-        <v>3.4</v>
-      </c>
-      <c r="P106">
-        <v>2.55</v>
-      </c>
-      <c r="Q106">
-        <v>3.41</v>
-      </c>
-      <c r="R106">
-        <v>2.15</v>
-      </c>
-      <c r="S106">
-        <v>1.33</v>
-      </c>
-      <c r="T106">
-        <v>2.96</v>
-      </c>
-      <c r="U106">
-        <v>2.51</v>
-      </c>
       <c r="V106">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z106">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AA106">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB106">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC106">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="AD106">
         <v>1.36</v>
@@ -17641,10 +17641,10 @@
         <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG106">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK106">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="O108">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="P108">
-        <v>2.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q108">
-        <v>3.85</v>
+        <v>2.47</v>
       </c>
       <c r="R108">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S108">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T108">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="U108">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="V108">
+        <v>1.31</v>
+      </c>
+      <c r="W108">
+        <v>1.02</v>
+      </c>
+      <c r="X108">
+        <v>1.04</v>
+      </c>
+      <c r="Y108">
         <v>1.36</v>
       </c>
-      <c r="W108">
-        <v>1.04</v>
-      </c>
-      <c r="X108">
+      <c r="Z108">
+        <v>2.72</v>
+      </c>
+      <c r="AA108">
+        <v>2.35</v>
+      </c>
+      <c r="AB108">
+        <v>1.57</v>
+      </c>
+      <c r="AC108">
+        <v>3.82</v>
+      </c>
+      <c r="AD108">
+        <v>1.19</v>
+      </c>
+      <c r="AE108">
         <v>1.03</v>
       </c>
-      <c r="Y108">
-        <v>1.28</v>
-      </c>
-      <c r="Z108">
-        <v>3.12</v>
-      </c>
-      <c r="AA108">
-        <v>1.99</v>
-      </c>
-      <c r="AB108">
-        <v>1.79</v>
-      </c>
-      <c r="AC108">
-        <v>3.18</v>
-      </c>
-      <c r="AD108">
-        <v>1.27</v>
-      </c>
-      <c r="AE108">
-        <v>1.07</v>
-      </c>
       <c r="AF108">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AG108">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK108">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
+        <v>3.1</v>
+      </c>
+      <c r="O109">
+        <v>2.87</v>
+      </c>
+      <c r="P109">
+        <v>2.25</v>
+      </c>
+      <c r="Q109">
+        <v>3.86</v>
+      </c>
+      <c r="R109">
+        <v>1.96</v>
+      </c>
+      <c r="S109">
+        <v>1.45</v>
+      </c>
+      <c r="T109">
+        <v>2.56</v>
+      </c>
+      <c r="U109">
+        <v>3.06</v>
+      </c>
+      <c r="V109">
+        <v>1.36</v>
+      </c>
+      <c r="W109">
+        <v>1.04</v>
+      </c>
+      <c r="X109">
+        <v>1.03</v>
+      </c>
+      <c r="Y109">
+        <v>1.28</v>
+      </c>
+      <c r="Z109">
+        <v>3.12</v>
+      </c>
+      <c r="AA109">
+        <v>2.1</v>
+      </c>
+      <c r="AB109">
+        <v>1.7</v>
+      </c>
+      <c r="AC109">
+        <v>3.18</v>
+      </c>
+      <c r="AD109">
+        <v>1.27</v>
+      </c>
+      <c r="AE109">
+        <v>1.07</v>
+      </c>
+      <c r="AF109">
         <v>1.73</v>
       </c>
-      <c r="O109">
-        <v>3</v>
-      </c>
-      <c r="P109">
-        <v>4.8</v>
-      </c>
-      <c r="Q109">
-        <v>2.54</v>
-      </c>
-      <c r="R109">
-        <v>1.95</v>
-      </c>
-      <c r="S109">
-        <v>1.5</v>
-      </c>
-      <c r="T109">
-        <v>2.41</v>
-      </c>
-      <c r="U109">
-        <v>3.22</v>
-      </c>
-      <c r="V109">
-        <v>1.3</v>
-      </c>
-      <c r="W109">
-        <v>1.02</v>
-      </c>
-      <c r="X109">
-        <v>1.05</v>
-      </c>
-      <c r="Y109">
-        <v>1.37</v>
-      </c>
-      <c r="Z109">
-        <v>2.68</v>
-      </c>
-      <c r="AA109">
-        <v>2.25</v>
-      </c>
-      <c r="AB109">
-        <v>1.62</v>
-      </c>
-      <c r="AC109">
-        <v>3.9</v>
-      </c>
-      <c r="AD109">
-        <v>1.18</v>
-      </c>
-      <c r="AE109">
-        <v>1.03</v>
-      </c>
-      <c r="AF109">
-        <v>1.99</v>
-      </c>
       <c r="AG109">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK109">
-        <v>1.87</v>
+        <v>1.35</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,22 +18239,22 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O110">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P110">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q110">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="R110">
         <v>2.02</v>
       </c>
       <c r="S110">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
         <v>2.92</v>
@@ -18263,34 +18263,34 @@
         <v>2.75</v>
       </c>
       <c r="V110">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W110">
+        <v>1.05</v>
+      </c>
+      <c r="X110">
         <v>1.06</v>
       </c>
-      <c r="X110">
-        <v>1.01</v>
-      </c>
       <c r="Y110">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z110">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA110">
         <v>2</v>
       </c>
       <c r="AB110">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC110">
-        <v>3.42</v>
+        <v>3.24</v>
       </c>
       <c r="AD110">
         <v>1.3</v>
       </c>
       <c r="AE110">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF110">
         <v>1.78</v>
@@ -18402,55 +18402,55 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O111">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P111">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q111">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="R111">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S111">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T111">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="U111">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="V111">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W111">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X111">
         <v>1.05</v>
       </c>
       <c r="Y111">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z111">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AA111">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AB111">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC111">
         <v>4.2</v>
       </c>
       <c r="AD111">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE111">
         <v>1.02</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AK111">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,80 +10741,80 @@
         </is>
       </c>
       <c r="N64">
-        <v>3.5</v>
+        <v>1.44</v>
       </c>
       <c r="O64">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="P64">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q64">
-        <v>3.92</v>
+        <v>1.97</v>
       </c>
       <c r="R64">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T64">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="V64">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="W64">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
+        <v>1.08</v>
+      </c>
+      <c r="Z64">
+        <v>6.22</v>
+      </c>
+      <c r="AA64">
+        <v>1.36</v>
+      </c>
+      <c r="AB64">
+        <v>2.7</v>
+      </c>
+      <c r="AC64">
+        <v>1.96</v>
+      </c>
+      <c r="AD64">
+        <v>1.79</v>
+      </c>
+      <c r="AE64">
+        <v>1.28</v>
+      </c>
+      <c r="AF64">
+        <v>1.47</v>
+      </c>
+      <c r="AG64">
+        <v>2.42</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.1</v>
       </c>
-      <c r="Z64">
-        <v>5</v>
-      </c>
-      <c r="AA64">
-        <v>1.43</v>
-      </c>
-      <c r="AB64">
-        <v>2.46</v>
-      </c>
-      <c r="AC64">
-        <v>2.14</v>
-      </c>
-      <c r="AD64">
-        <v>1.63</v>
-      </c>
-      <c r="AE64">
-        <v>1.23</v>
-      </c>
-      <c r="AF64">
-        <v>1.43</v>
-      </c>
-      <c r="AG64">
-        <v>2.59</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.79</v>
-      </c>
       <c r="AK64">
-        <v>1.23</v>
+        <v>2.31</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.44</v>
+        <v>3.5</v>
       </c>
       <c r="O65">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q65">
-        <v>1.97</v>
+        <v>3.92</v>
       </c>
       <c r="R65">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="S65">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U65">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="V65">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="W65">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>6.22</v>
+        <v>5</v>
       </c>
       <c r="AA65">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB65">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AC65">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="AD65">
+        <v>1.63</v>
+      </c>
+      <c r="AE65">
+        <v>1.23</v>
+      </c>
+      <c r="AF65">
+        <v>1.43</v>
+      </c>
+      <c r="AG65">
+        <v>2.59</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
         <v>1.79</v>
       </c>
-      <c r="AE65">
-        <v>1.28</v>
-      </c>
-      <c r="AF65">
-        <v>1.47</v>
-      </c>
-      <c r="AG65">
-        <v>2.42</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.1</v>
-      </c>
       <c r="AK65">
-        <v>2.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
+        <v>2.48</v>
+      </c>
+      <c r="O80">
+        <v>3.6</v>
+      </c>
+      <c r="P80">
+        <v>2.51</v>
+      </c>
+      <c r="Q80">
+        <v>2.89</v>
+      </c>
+      <c r="R80">
+        <v>2.31</v>
+      </c>
+      <c r="S80">
         <v>1.25</v>
       </c>
-      <c r="O80">
-        <v>5.8</v>
-      </c>
-      <c r="P80">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q80">
-        <v>1.67</v>
-      </c>
-      <c r="R80">
-        <v>2.7</v>
-      </c>
-      <c r="S80">
-        <v>1.18</v>
-      </c>
       <c r="T80">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="U80">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="V80">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="W80">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z80">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA80">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB80">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC80">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AD80">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AE80">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AF80">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AG80">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>3.52</v>
+        <v>1.49</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.48</v>
+        <v>1.77</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="P81">
-        <v>2.51</v>
+        <v>3.69</v>
       </c>
       <c r="Q81">
-        <v>2.89</v>
+        <v>2.28</v>
       </c>
       <c r="R81">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S81">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="U81">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V81">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="W81">
+        <v>1.17</v>
+      </c>
+      <c r="X81">
+        <v>1.02</v>
+      </c>
+      <c r="Y81">
         <v>1.12</v>
       </c>
-      <c r="X81">
-        <v>1.03</v>
-      </c>
-      <c r="Y81">
-        <v>1.13</v>
-      </c>
       <c r="Z81">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA81">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB81">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AC81">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AD81">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AE81">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF81">
         <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.3</v>
+        <v>1.25</v>
       </c>
       <c r="O82">
-        <v>3.82</v>
+        <v>5.8</v>
       </c>
       <c r="P82">
-        <v>1.91</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q82">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="R82">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S82">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T82">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="U82">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="V82">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="W82">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z82">
         <v>6</v>
       </c>
       <c r="AA82">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB82">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC82">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AD82">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AE82">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AF82">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AG82">
-        <v>2.81</v>
+        <v>2.06</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AK82">
-        <v>1.3</v>
+        <v>3.52</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.43</v>
+        <v>3.05</v>
       </c>
       <c r="O83">
-        <v>4.95</v>
+        <v>3.84</v>
       </c>
       <c r="P83">
-        <v>5.82</v>
+        <v>1.96</v>
       </c>
       <c r="Q83">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="R83">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="S83">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U83">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="V83">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="W83">
+        <v>1.18</v>
+      </c>
+      <c r="X83">
+        <v>1.02</v>
+      </c>
+      <c r="Y83">
+        <v>1.14</v>
+      </c>
+      <c r="Z83">
+        <v>6</v>
+      </c>
+      <c r="AA83">
+        <v>1.4</v>
+      </c>
+      <c r="AB83">
+        <v>2.82</v>
+      </c>
+      <c r="AC83">
+        <v>2.06</v>
+      </c>
+      <c r="AD83">
+        <v>1.69</v>
+      </c>
+      <c r="AE83">
         <v>1.26</v>
       </c>
-      <c r="X83">
-        <v>1.01</v>
-      </c>
-      <c r="Y83">
-        <v>1.02</v>
-      </c>
-      <c r="Z83">
-        <v>7.9</v>
-      </c>
-      <c r="AA83">
-        <v>1.28</v>
-      </c>
-      <c r="AB83">
-        <v>3.6</v>
-      </c>
-      <c r="AC83">
-        <v>1.69</v>
-      </c>
-      <c r="AD83">
-        <v>2.11</v>
-      </c>
-      <c r="AE83">
-        <v>1.49</v>
-      </c>
       <c r="AF83">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG83">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>2.68</v>
+        <v>1.29</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.77</v>
+        <v>1.43</v>
       </c>
       <c r="O84">
-        <v>3.87</v>
+        <v>4.95</v>
       </c>
       <c r="P84">
-        <v>3.69</v>
+        <v>5.82</v>
       </c>
       <c r="Q84">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="S84">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T84">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U84">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="V84">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="W84">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
         <v>1.02</v>
       </c>
-      <c r="Y84">
-        <v>1.12</v>
-      </c>
       <c r="Z84">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="AA84">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AB84">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="AC84">
-        <v>2.04</v>
+        <v>1.69</v>
       </c>
       <c r="AD84">
-        <v>1.74</v>
+        <v>2.11</v>
       </c>
       <c r="AE84">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AF84">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AG84">
-        <v>2.43</v>
+        <v>2.86</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK84">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O85">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="P85">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q85">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R85">
         <v>2.38</v>
@@ -14182,37 +14182,37 @@
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="U85">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V85">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W85">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z85">
         <v>6</v>
       </c>
       <c r="AA85">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB85">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AC85">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AD85">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE85">
         <v>1.26</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK85">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="O98">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="P98">
-        <v>1.79</v>
+        <v>2.85</v>
       </c>
       <c r="Q98">
-        <v>4.38</v>
+        <v>2.93</v>
       </c>
       <c r="R98">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="S98">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="U98">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V98">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W98">
+        <v>1.06</v>
+      </c>
+      <c r="X98">
+        <v>1</v>
+      </c>
+      <c r="Y98">
+        <v>1.26</v>
+      </c>
+      <c r="Z98">
+        <v>3.4</v>
+      </c>
+      <c r="AA98">
+        <v>1.98</v>
+      </c>
+      <c r="AB98">
+        <v>1.8</v>
+      </c>
+      <c r="AC98">
+        <v>3.25</v>
+      </c>
+      <c r="AD98">
+        <v>1.29</v>
+      </c>
+      <c r="AE98">
         <v>1.08</v>
       </c>
-      <c r="X98">
-        <v>1.02</v>
-      </c>
-      <c r="Y98">
-        <v>1.17</v>
-      </c>
-      <c r="Z98">
-        <v>4.05</v>
-      </c>
-      <c r="AA98">
-        <v>1.69</v>
-      </c>
-      <c r="AB98">
-        <v>2.13</v>
-      </c>
-      <c r="AC98">
-        <v>2.57</v>
-      </c>
-      <c r="AD98">
-        <v>1.4</v>
-      </c>
-      <c r="AE98">
-        <v>1.17</v>
-      </c>
       <c r="AF98">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG98">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK98">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O99">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P99">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="Q99">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="R99">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="S99">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T99">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="U99">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="V99">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="W99">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
+        <v>1.13</v>
+      </c>
+      <c r="Z99">
+        <v>5.27</v>
+      </c>
+      <c r="AA99">
+        <v>1.53</v>
+      </c>
+      <c r="AB99">
+        <v>2.5</v>
+      </c>
+      <c r="AC99">
+        <v>2.3</v>
+      </c>
+      <c r="AD99">
+        <v>1.62</v>
+      </c>
+      <c r="AE99">
+        <v>1.21</v>
+      </c>
+      <c r="AF99">
+        <v>1.42</v>
+      </c>
+      <c r="AG99">
+        <v>2.5</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.26</v>
       </c>
-      <c r="Z99">
-        <v>3.4</v>
-      </c>
-      <c r="AA99">
-        <v>1.98</v>
-      </c>
-      <c r="AB99">
-        <v>1.8</v>
-      </c>
-      <c r="AC99">
-        <v>3.25</v>
-      </c>
-      <c r="AD99">
-        <v>1.29</v>
-      </c>
-      <c r="AE99">
-        <v>1.08</v>
-      </c>
-      <c r="AF99">
-        <v>1.75</v>
-      </c>
-      <c r="AG99">
-        <v>1.95</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.3</v>
-      </c>
       <c r="AK99">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P100">
-        <v>2.55</v>
+        <v>1.79</v>
       </c>
       <c r="Q100">
-        <v>3</v>
+        <v>4.38</v>
       </c>
       <c r="R100">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="S100">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T100">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="U100">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="V100">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W100">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X100">
         <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z100">
-        <v>5.27</v>
+        <v>4.05</v>
       </c>
       <c r="AA100">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AB100">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AC100">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AD100">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AE100">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF100">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G133">
@@ -21997,16 +21997,16 @@
         <v>0</v>
       </c>
       <c r="Q133">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="R133">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S133">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T133">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U133">
         <v>0</v>
@@ -22021,31 +22021,31 @@
         <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z133">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA133">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB133">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC133">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD133">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE133">
         <v>0</v>
       </c>
       <c r="AF133">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG133">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK133">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G140">
@@ -23138,16 +23138,16 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U140">
         <v>0</v>
@@ -23162,31 +23162,31 @@
         <v>0</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE140">
         <v>0</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL140">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -2280,13 +2280,13 @@
         <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="V12">
         <v>1.4</v>
@@ -2301,28 +2301,28 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB12">
+        <v>1.83</v>
+      </c>
+      <c r="AC12">
+        <v>3.16</v>
+      </c>
+      <c r="AD12">
+        <v>1.33</v>
+      </c>
+      <c r="AE12">
+        <v>1.08</v>
+      </c>
+      <c r="AF12">
+        <v>1.79</v>
+      </c>
+      <c r="AG12">
         <v>1.88</v>
-      </c>
-      <c r="AC12">
-        <v>2.97</v>
-      </c>
-      <c r="AD12">
-        <v>1.3</v>
-      </c>
-      <c r="AE12">
-        <v>1.11</v>
-      </c>
-      <c r="AF12">
-        <v>1.78</v>
-      </c>
-      <c r="AG12">
-        <v>1.86</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>1.89</v>
       </c>
       <c r="AB58">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC58">
         <v>3.08</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O82">
-        <v>5.8</v>
+        <v>3.84</v>
       </c>
       <c r="P82">
-        <v>9.800000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="Q82">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="R82">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S82">
+        <v>1.2</v>
+      </c>
+      <c r="T82">
+        <v>4</v>
+      </c>
+      <c r="U82">
+        <v>2.07</v>
+      </c>
+      <c r="V82">
+        <v>1.72</v>
+      </c>
+      <c r="W82">
         <v>1.18</v>
       </c>
-      <c r="T82">
-        <v>3.85</v>
-      </c>
-      <c r="U82">
-        <v>2.01</v>
-      </c>
-      <c r="V82">
-        <v>1.74</v>
-      </c>
-      <c r="W82">
-        <v>1.17</v>
-      </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
         <v>6</v>
       </c>
       <c r="AA82">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB82">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="AC82">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AD82">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AE82">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AF82">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AG82">
-        <v>2.06</v>
+        <v>2.81</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>3.52</v>
+        <v>1.29</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,16 +13838,16 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O83">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="P83">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q83">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R83">
         <v>2.38</v>
@@ -13856,37 +13856,37 @@
         <v>1.2</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="U83">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V83">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W83">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X83">
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z83">
         <v>6</v>
       </c>
       <c r="AA83">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB83">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AC83">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AD83">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE83">
         <v>1.26</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK83">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,31 +14164,31 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="O85">
-        <v>3.82</v>
+        <v>3.64</v>
       </c>
       <c r="P85">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q85">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R85">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S85">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T85">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="U85">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="V85">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="W85">
         <v>1.15</v>
@@ -14197,31 +14197,31 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z85">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="AA85">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AB85">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AC85">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AD85">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AE85">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF85">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AG85">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK85">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.52</v>
+        <v>1.25</v>
       </c>
       <c r="O86">
-        <v>3.64</v>
+        <v>5.8</v>
       </c>
       <c r="P86">
-        <v>2.45</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q86">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="R86">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="S86">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T86">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="U86">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="V86">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="W86">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
+        <v>1.06</v>
+      </c>
+      <c r="Z86">
+        <v>6</v>
+      </c>
+      <c r="AA86">
+        <v>1.36</v>
+      </c>
+      <c r="AB86">
+        <v>3.1</v>
+      </c>
+      <c r="AC86">
+        <v>1.93</v>
+      </c>
+      <c r="AD86">
+        <v>1.83</v>
+      </c>
+      <c r="AE86">
+        <v>1.31</v>
+      </c>
+      <c r="AF86">
+        <v>1.65</v>
+      </c>
+      <c r="AG86">
+        <v>2.06</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
         <v>1.11</v>
       </c>
-      <c r="Z86">
-        <v>4.95</v>
-      </c>
-      <c r="AA86">
-        <v>1.5</v>
-      </c>
-      <c r="AB86">
-        <v>2.48</v>
-      </c>
-      <c r="AC86">
-        <v>2.18</v>
-      </c>
-      <c r="AD86">
-        <v>1.61</v>
-      </c>
-      <c r="AE86">
-        <v>1.21</v>
-      </c>
-      <c r="AF86">
-        <v>1.41</v>
-      </c>
-      <c r="AG86">
-        <v>2.63</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.24</v>
-      </c>
       <c r="AK86">
-        <v>1.37</v>
+        <v>3.52</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -19878,55 +19878,55 @@
         <v>0</v>
       </c>
       <c r="Q120">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="R120">
+        <v>2.4</v>
+      </c>
+      <c r="S120">
+        <v>1.22</v>
+      </c>
+      <c r="T120">
+        <v>3.8</v>
+      </c>
+      <c r="U120">
+        <v>2.31</v>
+      </c>
+      <c r="V120">
+        <v>1.57</v>
+      </c>
+      <c r="W120">
+        <v>1.11</v>
+      </c>
+      <c r="X120">
+        <v>1.02</v>
+      </c>
+      <c r="Y120">
+        <v>1.12</v>
+      </c>
+      <c r="Z120">
+        <v>4.7</v>
+      </c>
+      <c r="AA120">
+        <v>1.52</v>
+      </c>
+      <c r="AB120">
         <v>2.35</v>
       </c>
-      <c r="S120">
-        <v>1.25</v>
-      </c>
-      <c r="T120">
-        <v>3.4</v>
-      </c>
-      <c r="U120">
-        <v>2.33</v>
-      </c>
-      <c r="V120">
-        <v>1.55</v>
-      </c>
-      <c r="W120">
-        <v>1.12</v>
-      </c>
-      <c r="X120">
-        <v>1.03</v>
-      </c>
-      <c r="Y120">
-        <v>1.13</v>
-      </c>
-      <c r="Z120">
-        <v>4.6</v>
-      </c>
-      <c r="AA120">
-        <v>1.55</v>
-      </c>
-      <c r="AB120">
-        <v>2.27</v>
-      </c>
       <c r="AC120">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD120">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE120">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF120">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG120">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -3904,7 +3904,7 @@
         <v>1.5</v>
       </c>
       <c r="Q22">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="R22">
         <v>2.63</v>
@@ -3949,7 +3949,7 @@
         <v>1.25</v>
       </c>
       <c r="AF22">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG22">
         <v>2.44</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.14</v>
+        <v>2.4</v>
       </c>
       <c r="AK22">
         <v>1.11</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q26">
         <v>2.02</v>
@@ -4604,7 +4604,7 @@
         <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -7671,7 +7671,7 @@
         <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
         <v>1.05</v>
@@ -7680,7 +7680,7 @@
         <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="AA45">
         <v>1.95</v>
@@ -8637,19 +8637,19 @@
         <v>1.99</v>
       </c>
       <c r="S51">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U51">
         <v>3.02</v>
       </c>
       <c r="V51">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8664,22 +8664,22 @@
         <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AC51">
-        <v>3.54</v>
+        <v>4.02</v>
       </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG51">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -9437,43 +9437,43 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O56">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P56">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="Q56">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R56">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S56">
         <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="U56">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V56">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W56">
         <v>1.13</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA56">
         <v>1.6</v>
@@ -9482,19 +9482,19 @@
         <v>2.3</v>
       </c>
       <c r="AC56">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD56">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE56">
         <v>1.21</v>
       </c>
       <c r="AF56">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG56">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK56">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10756,19 +10756,19 @@
         <v>2.36</v>
       </c>
       <c r="S64">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T64">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U64">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="V64">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W64">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
         <v>1.02</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,58 +10904,58 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.47</v>
+        <v>3.5</v>
       </c>
       <c r="O65">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
-        <v>5.15</v>
+        <v>1.84</v>
       </c>
       <c r="Q65">
-        <v>1.96</v>
+        <v>4.06</v>
       </c>
       <c r="R65">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="S65">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="U65">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="V65">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z65">
-        <v>5.6</v>
+        <v>4.97</v>
       </c>
       <c r="AA65">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB65">
-        <v>2.93</v>
+        <v>2.33</v>
       </c>
       <c r="AC65">
-        <v>2.02</v>
+        <v>2.31</v>
       </c>
       <c r="AD65">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE65">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
         <v>1.47</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK65">
-        <v>2.31</v>
+        <v>1.22</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P66">
-        <v>1.84</v>
+        <v>5.15</v>
       </c>
       <c r="Q66">
-        <v>3.75</v>
+        <v>1.99</v>
       </c>
       <c r="R66">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T66">
         <v>4</v>
       </c>
       <c r="U66">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="V66">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="W66">
+        <v>1.2</v>
+      </c>
+      <c r="X66">
+        <v>1.01</v>
+      </c>
+      <c r="Y66">
+        <v>1.1</v>
+      </c>
+      <c r="Z66">
+        <v>5.2</v>
+      </c>
+      <c r="AA66">
+        <v>1.43</v>
+      </c>
+      <c r="AB66">
+        <v>2.3</v>
+      </c>
+      <c r="AC66">
+        <v>2.13</v>
+      </c>
+      <c r="AD66">
+        <v>1.67</v>
+      </c>
+      <c r="AE66">
+        <v>1.28</v>
+      </c>
+      <c r="AF66">
+        <v>1.5</v>
+      </c>
+      <c r="AG66">
+        <v>2.3</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.14</v>
       </c>
-      <c r="X66">
-        <v>1.02</v>
-      </c>
-      <c r="Y66">
-        <v>1.15</v>
-      </c>
-      <c r="Z66">
-        <v>5.14</v>
-      </c>
-      <c r="AA66">
-        <v>1.51</v>
-      </c>
-      <c r="AB66">
-        <v>2.38</v>
-      </c>
-      <c r="AC66">
-        <v>2.25</v>
-      </c>
-      <c r="AD66">
-        <v>1.6</v>
-      </c>
-      <c r="AE66">
-        <v>1.22</v>
-      </c>
-      <c r="AF66">
-        <v>1.45</v>
-      </c>
-      <c r="AG66">
-        <v>2.53</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.85</v>
-      </c>
       <c r="AK66">
-        <v>1.25</v>
+        <v>2.29</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11722,31 +11722,31 @@
         <v>1.8</v>
       </c>
       <c r="O70">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q70">
         <v>2.36</v>
       </c>
       <c r="R70">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
         <v>1.33</v>
       </c>
       <c r="T70">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U70">
         <v>2.45</v>
       </c>
       <c r="V70">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W70">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X70">
         <v>1.05</v>
@@ -11755,28 +11755,28 @@
         <v>1.2</v>
       </c>
       <c r="Z70">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="AA70">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB70">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AC70">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AD70">
         <v>1.37</v>
       </c>
       <c r="AE70">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF70">
         <v>1.67</v>
       </c>
       <c r="AG70">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
         <v>1.95</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O71">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="P71">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q71">
+        <v>3.02</v>
+      </c>
+      <c r="R71">
+        <v>1.93</v>
+      </c>
+      <c r="S71">
+        <v>1.53</v>
+      </c>
+      <c r="T71">
+        <v>2.55</v>
+      </c>
+      <c r="U71">
+        <v>3.16</v>
+      </c>
+      <c r="V71">
+        <v>1.25</v>
+      </c>
+      <c r="W71">
+        <v>1.03</v>
+      </c>
+      <c r="X71">
+        <v>1.04</v>
+      </c>
+      <c r="Y71">
+        <v>1.44</v>
+      </c>
+      <c r="Z71">
+        <v>2.72</v>
+      </c>
+      <c r="AA71">
         <v>2.35</v>
       </c>
-      <c r="R71">
-        <v>2.1</v>
-      </c>
-      <c r="S71">
-        <v>1.39</v>
-      </c>
-      <c r="T71">
-        <v>2.88</v>
-      </c>
-      <c r="U71">
-        <v>2.98</v>
-      </c>
-      <c r="V71">
-        <v>1.36</v>
-      </c>
-      <c r="W71">
-        <v>1.04</v>
-      </c>
-      <c r="X71">
-        <v>1.03</v>
-      </c>
-      <c r="Y71">
-        <v>1.28</v>
-      </c>
-      <c r="Z71">
-        <v>3.28</v>
-      </c>
-      <c r="AA71">
-        <v>1.92</v>
-      </c>
       <c r="AB71">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AC71">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="AD71">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE71">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF71">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AG71">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK71">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="O72">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="P72">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q72">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="R72">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="S72">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="T72">
-        <v>2.55</v>
+        <v>3.19</v>
       </c>
       <c r="U72">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="V72">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W72">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X72">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="Z72">
-        <v>2.72</v>
+        <v>3.9</v>
       </c>
       <c r="AA72">
-        <v>2.54</v>
+        <v>1.74</v>
       </c>
       <c r="AB72">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="AC72">
-        <v>4.25</v>
+        <v>2.64</v>
       </c>
       <c r="AD72">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AE72">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF72">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AG72">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>1.58</v>
+        <v>2.1</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
+        <v>2.03</v>
+      </c>
+      <c r="O73">
+        <v>3.48</v>
+      </c>
+      <c r="P73">
+        <v>3.2</v>
+      </c>
+      <c r="Q73">
+        <v>2.35</v>
+      </c>
+      <c r="R73">
+        <v>2.1</v>
+      </c>
+      <c r="S73">
+        <v>1.39</v>
+      </c>
+      <c r="T73">
+        <v>2.88</v>
+      </c>
+      <c r="U73">
+        <v>2.81</v>
+      </c>
+      <c r="V73">
+        <v>1.36</v>
+      </c>
+      <c r="W73">
+        <v>1.04</v>
+      </c>
+      <c r="X73">
+        <v>1</v>
+      </c>
+      <c r="Y73">
+        <v>1.28</v>
+      </c>
+      <c r="Z73">
+        <v>3.3</v>
+      </c>
+      <c r="AA73">
+        <v>1.92</v>
+      </c>
+      <c r="AB73">
         <v>1.7</v>
       </c>
-      <c r="O73">
-        <v>3.5</v>
-      </c>
-      <c r="P73">
-        <v>4.2</v>
-      </c>
-      <c r="Q73">
-        <v>2.25</v>
-      </c>
-      <c r="R73">
-        <v>2.15</v>
-      </c>
-      <c r="S73">
-        <v>1.36</v>
-      </c>
-      <c r="T73">
-        <v>2.89</v>
-      </c>
-      <c r="U73">
-        <v>2.53</v>
-      </c>
-      <c r="V73">
-        <v>1.46</v>
-      </c>
-      <c r="W73">
-        <v>1.07</v>
-      </c>
-      <c r="X73">
-        <v>1.02</v>
-      </c>
-      <c r="Y73">
-        <v>1.19</v>
-      </c>
-      <c r="Z73">
-        <v>3.89</v>
-      </c>
-      <c r="AA73">
-        <v>1.83</v>
-      </c>
-      <c r="AB73">
-        <v>2.05</v>
-      </c>
       <c r="AC73">
-        <v>2.64</v>
+        <v>3.18</v>
       </c>
       <c r="AD73">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF73">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG73">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK73">
-        <v>2.06</v>
+        <v>1.75</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,31 +12371,31 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O74">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="P74">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q74">
         <v>3.74</v>
       </c>
       <c r="R74">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="S74">
         <v>1.35</v>
       </c>
       <c r="T74">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
       <c r="U74">
-        <v>2.59</v>
+        <v>2.77</v>
       </c>
       <c r="V74">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W74">
         <v>1.06</v>
@@ -12404,22 +12404,22 @@
         <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z74">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AA74">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB74">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="AD74">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE74">
         <v>1.1</v>
@@ -12444,7 +12444,7 @@
         <v>1.61</v>
       </c>
       <c r="AK74">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,65 +14164,65 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="O85">
-        <v>5.05</v>
+        <v>5.6</v>
       </c>
       <c r="P85">
-        <v>5.3</v>
+        <v>8.75</v>
       </c>
       <c r="Q85">
+        <v>1.62</v>
+      </c>
+      <c r="R85">
+        <v>2.72</v>
+      </c>
+      <c r="S85">
+        <v>1.2</v>
+      </c>
+      <c r="T85">
+        <v>4.8</v>
+      </c>
+      <c r="U85">
+        <v>1.98</v>
+      </c>
+      <c r="V85">
         <v>1.8</v>
       </c>
-      <c r="R85">
-        <v>2.88</v>
-      </c>
-      <c r="S85">
-        <v>1.11</v>
-      </c>
-      <c r="T85">
-        <v>5.05</v>
-      </c>
-      <c r="U85">
-        <v>1.83</v>
-      </c>
-      <c r="V85">
-        <v>1.83</v>
-      </c>
       <c r="W85">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>8.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA85">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AB85">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC85">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AD85">
+        <v>1.87</v>
+      </c>
+      <c r="AE85">
+        <v>1.32</v>
+      </c>
+      <c r="AF85">
+        <v>1.62</v>
+      </c>
+      <c r="AG85">
         <v>2.11</v>
       </c>
-      <c r="AE85">
-        <v>1.47</v>
-      </c>
-      <c r="AF85">
-        <v>1.37</v>
-      </c>
-      <c r="AG85">
-        <v>2.86</v>
-      </c>
       <c r="AH85" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK85">
-        <v>2.71</v>
+        <v>3.44</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.51</v>
+        <v>3.3</v>
       </c>
       <c r="O86">
-        <v>3.64</v>
+        <v>3.82</v>
       </c>
       <c r="P86">
-        <v>2.46</v>
+        <v>1.92</v>
       </c>
       <c r="Q86">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R86">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="S86">
         <v>1.22</v>
       </c>
       <c r="T86">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="U86">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="V86">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W86">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z86">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA86">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AB86">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AC86">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AD86">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE86">
+        <v>1.24</v>
+      </c>
+      <c r="AF86">
+        <v>1.39</v>
+      </c>
+      <c r="AG86">
+        <v>2.77</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
         <v>1.23</v>
       </c>
-      <c r="AF86">
-        <v>1.41</v>
-      </c>
-      <c r="AG86">
-        <v>2.63</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.25</v>
-      </c>
       <c r="AK86">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="O87">
-        <v>5.6</v>
+        <v>5.05</v>
       </c>
       <c r="P87">
-        <v>8.75</v>
+        <v>5.3</v>
       </c>
       <c r="Q87">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="R87">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T87">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="U87">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="V87">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W87">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Z87">
-        <v>6.15</v>
+        <v>8.5</v>
       </c>
       <c r="AA87">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AB87">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AC87">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AD87">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AE87">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AF87">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AG87">
-        <v>2.11</v>
+        <v>2.86</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK87">
-        <v>3.44</v>
+        <v>2.71</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.3</v>
+        <v>2.51</v>
       </c>
       <c r="O88">
-        <v>3.82</v>
+        <v>3.64</v>
       </c>
       <c r="P88">
-        <v>1.92</v>
+        <v>2.46</v>
       </c>
       <c r="Q88">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R88">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="S88">
         <v>1.22</v>
       </c>
       <c r="T88">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="U88">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="V88">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z88">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA88">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AB88">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AC88">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AD88">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE88">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF88">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AG88">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="O99">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P99">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q99">
-        <v>2.25</v>
+        <v>2.68</v>
       </c>
       <c r="R99">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S99">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T99">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="U99">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="V99">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="W99">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="Z99">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA99">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AB99">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AC99">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AD99">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE99">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AF99">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AG99">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK99">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P100">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q100">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="R100">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="S100">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="T100">
-        <v>3.34</v>
+        <v>2.9</v>
       </c>
       <c r="U100">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="V100">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="W100">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z100">
-        <v>5.27</v>
+        <v>3.35</v>
       </c>
       <c r="AA100">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AB100">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC100">
-        <v>2.3</v>
+        <v>3.51</v>
       </c>
       <c r="AD100">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AE100">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AF100">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AG100">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK100">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O101">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P101">
-        <v>2.85</v>
+        <v>1.76</v>
       </c>
       <c r="Q101">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="R101">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="S101">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T101">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U101">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="V101">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z101">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="AA101">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AB101">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AC101">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AD101">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AE101">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF101">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG101">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.3</v>
+        <v>1.92</v>
       </c>
       <c r="AK101">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="O102">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="Q102">
-        <v>4.38</v>
+        <v>2.36</v>
       </c>
       <c r="R102">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T102">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V102">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="W102">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="Z102">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA102">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="AB102">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AC102">
-        <v>2.57</v>
+        <v>3.53</v>
       </c>
       <c r="AD102">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE102">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF102">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AG102">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17270,7 +17270,7 @@
         <v>2.15</v>
       </c>
       <c r="Q104">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="R104">
         <v>2.36</v>
@@ -17282,7 +17282,7 @@
         <v>3.32</v>
       </c>
       <c r="U104">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V104">
         <v>1.5</v>
@@ -17294,7 +17294,7 @@
         <v>1.04</v>
       </c>
       <c r="Y104">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z104">
         <v>4.2</v>
@@ -17303,13 +17303,13 @@
         <v>1.64</v>
       </c>
       <c r="AB104">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AC104">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD104">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AE104">
         <v>1.18</v>
@@ -17318,7 +17318,7 @@
         <v>1.53</v>
       </c>
       <c r="AG104">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK104">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17433,34 +17433,34 @@
         <v>6.35</v>
       </c>
       <c r="Q105">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="R105">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="S105">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T105">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U105">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="V105">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W105">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X105">
         <v>1.04</v>
       </c>
       <c r="Y105">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z105">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA105">
         <v>1.44</v>
@@ -17472,13 +17472,13 @@
         <v>2.1</v>
       </c>
       <c r="AD105">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AE105">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF105">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AG105">
         <v>2.18</v>
@@ -17596,22 +17596,22 @@
         <v>3.5</v>
       </c>
       <c r="Q106">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="S106">
         <v>1.3</v>
       </c>
       <c r="T106">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U106">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="V106">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W106">
         <v>1.07</v>
@@ -17620,10 +17620,10 @@
         <v>1.05</v>
       </c>
       <c r="Y106">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z106">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA106">
         <v>1.64</v>
@@ -17638,10 +17638,10 @@
         <v>1.41</v>
       </c>
       <c r="AE106">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG106">
         <v>2.15</v>
@@ -17660,7 +17660,7 @@
         <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,31 +17750,31 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O107">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="P107">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="Q107">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R107">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="S107">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T107">
         <v>3.58</v>
       </c>
       <c r="U107">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V107">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W107">
         <v>1.17</v>
@@ -17783,28 +17783,28 @@
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z107">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA107">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB107">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AC107">
         <v>2.15</v>
       </c>
       <c r="AD107">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE107">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AF107">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG107">
         <v>1.91</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK107">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18269,7 +18269,7 @@
         <v>1.03</v>
       </c>
       <c r="X110">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y110">
         <v>1.42</v>
@@ -18278,10 +18278,10 @@
         <v>2.72</v>
       </c>
       <c r="AA110">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AB110">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC110">
         <v>4.5</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK110">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18405,10 +18405,10 @@
         <v>3</v>
       </c>
       <c r="O111">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P111">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q111">
         <v>3.85</v>
@@ -18435,7 +18435,7 @@
         <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
         <v>3.29</v>
@@ -18444,7 +18444,7 @@
         <v>1.98</v>
       </c>
       <c r="AB111">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC111">
         <v>3.7</v>
@@ -18568,46 +18568,46 @@
         <v>1.95</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P112">
         <v>3.7</v>
       </c>
       <c r="Q112">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="R112">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S112">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T112">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="U112">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="V112">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W112">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
         <v>1.06</v>
       </c>
       <c r="Y112">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z112">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA112">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB112">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC112">
         <v>3.24</v>
@@ -18616,7 +18616,7 @@
         <v>1.3</v>
       </c>
       <c r="AE112">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF112">
         <v>1.78</v>
@@ -18635,7 +18635,7 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK112">
         <v>1.76</v>
@@ -20204,55 +20204,55 @@
         <v>0</v>
       </c>
       <c r="Q122">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="R122">
         <v>2.4</v>
       </c>
       <c r="S122">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T122">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U122">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="V122">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W122">
         <v>1.11</v>
       </c>
       <c r="X122">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
         <v>1.12</v>
       </c>
       <c r="Z122">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AA122">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB122">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC122">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD122">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE122">
         <v>1.19</v>
       </c>
       <c r="AF122">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG122">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="O127">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P127">
         <v>2.62</v>
       </c>
       <c r="Q127">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R127">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="S127">
         <v>1.44</v>
       </c>
       <c r="T127">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="U127">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="V127">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W127">
         <v>1.03</v>
       </c>
       <c r="X127">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y127">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z127">
-        <v>2.64</v>
+        <v>3.09</v>
       </c>
       <c r="AA127">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AB127">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AC127">
-        <v>4.5</v>
+        <v>4.03</v>
       </c>
       <c r="AD127">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE127">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF127">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG127">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AK127">
         <v>1.39</v>
@@ -22160,22 +22160,22 @@
         <v>0</v>
       </c>
       <c r="Q134">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="R134">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S134">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T134">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="U134">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V134">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W134">
         <v>1.12</v>
@@ -22187,16 +22187,16 @@
         <v>1.16</v>
       </c>
       <c r="Z134">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA134">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB134">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC134">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD134">
         <v>1.44</v>
@@ -22205,10 +22205,10 @@
         <v>1.15</v>
       </c>
       <c r="AF134">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG134">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK134">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,25 +22477,25 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="O136">
         <v>3.5</v>
       </c>
       <c r="P136">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q136">
-        <v>2.91</v>
+        <v>2.76</v>
       </c>
       <c r="R136">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S136">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T136">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="U136">
         <v>2.21</v>
@@ -22507,34 +22507,34 @@
         <v>1.11</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z136">
-        <v>4.63</v>
+        <v>4.45</v>
       </c>
       <c r="AA136">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB136">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AC136">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD136">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE136">
         <v>1.14</v>
       </c>
       <c r="AF136">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG136">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK136">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,31 +22640,31 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O137">
         <v>3.7</v>
       </c>
       <c r="P137">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="Q137">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R137">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S137">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T137">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="U137">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V137">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W137">
         <v>1.06</v>
@@ -22673,22 +22673,22 @@
         <v>1.04</v>
       </c>
       <c r="Y137">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z137">
         <v>3.72</v>
       </c>
       <c r="AA137">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB137">
         <v>2</v>
       </c>
       <c r="AC137">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="AD137">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE137">
         <v>1.13</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK137">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22803,31 +22803,31 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="O138">
         <v>3.25</v>
       </c>
       <c r="P138">
+        <v>2.8</v>
+      </c>
+      <c r="Q138">
+        <v>2.88</v>
+      </c>
+      <c r="R138">
+        <v>2.25</v>
+      </c>
+      <c r="S138">
+        <v>1.29</v>
+      </c>
+      <c r="T138">
+        <v>3.07</v>
+      </c>
+      <c r="U138">
         <v>2.55</v>
       </c>
-      <c r="Q138">
-        <v>2.91</v>
-      </c>
-      <c r="R138">
-        <v>2.16</v>
-      </c>
-      <c r="S138">
-        <v>1.3</v>
-      </c>
-      <c r="T138">
-        <v>3.04</v>
-      </c>
-      <c r="U138">
-        <v>2.5</v>
-      </c>
       <c r="V138">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W138">
         <v>1.09</v>
@@ -22836,31 +22836,31 @@
         <v>1.04</v>
       </c>
       <c r="Y138">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z138">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AA138">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB138">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC138">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AD138">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE138">
         <v>1.1</v>
       </c>
       <c r="AF138">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AG138">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AK138">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AL138">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="P65">
-        <v>1.84</v>
+        <v>5.15</v>
       </c>
       <c r="Q65">
-        <v>4.06</v>
+        <v>1.99</v>
       </c>
       <c r="R65">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T65">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="V65">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="W65">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>4.97</v>
+        <v>5.2</v>
       </c>
       <c r="AA65">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AB65">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC65">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="AD65">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AF65">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG65">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK65">
-        <v>1.22</v>
+        <v>2.29</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
+        <v>3.5</v>
+      </c>
+      <c r="O66">
+        <v>3.7</v>
+      </c>
+      <c r="P66">
+        <v>1.84</v>
+      </c>
+      <c r="Q66">
+        <v>4.06</v>
+      </c>
+      <c r="R66">
+        <v>2.28</v>
+      </c>
+      <c r="S66">
+        <v>1.25</v>
+      </c>
+      <c r="T66">
+        <v>3.28</v>
+      </c>
+      <c r="U66">
+        <v>2.22</v>
+      </c>
+      <c r="V66">
+        <v>1.58</v>
+      </c>
+      <c r="W66">
+        <v>1.13</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.12</v>
+      </c>
+      <c r="Z66">
+        <v>4.97</v>
+      </c>
+      <c r="AA66">
+        <v>1.53</v>
+      </c>
+      <c r="AB66">
+        <v>2.33</v>
+      </c>
+      <c r="AC66">
+        <v>2.31</v>
+      </c>
+      <c r="AD66">
+        <v>1.57</v>
+      </c>
+      <c r="AE66">
+        <v>1.2</v>
+      </c>
+      <c r="AF66">
         <v>1.47</v>
       </c>
-      <c r="O66">
-        <v>4.4</v>
-      </c>
-      <c r="P66">
-        <v>5.15</v>
-      </c>
-      <c r="Q66">
-        <v>1.99</v>
-      </c>
-      <c r="R66">
-        <v>2.43</v>
-      </c>
-      <c r="S66">
-        <v>1.17</v>
-      </c>
-      <c r="T66">
-        <v>4</v>
-      </c>
-      <c r="U66">
-        <v>2.02</v>
-      </c>
-      <c r="V66">
-        <v>1.78</v>
-      </c>
-      <c r="W66">
-        <v>1.2</v>
-      </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
-      <c r="Y66">
-        <v>1.1</v>
-      </c>
-      <c r="Z66">
-        <v>5.2</v>
-      </c>
-      <c r="AA66">
-        <v>1.43</v>
-      </c>
-      <c r="AB66">
-        <v>2.3</v>
-      </c>
-      <c r="AC66">
-        <v>2.13</v>
-      </c>
-      <c r="AD66">
-        <v>1.67</v>
-      </c>
-      <c r="AE66">
-        <v>1.28</v>
-      </c>
-      <c r="AF66">
-        <v>1.5</v>
-      </c>
       <c r="AG66">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK66">
-        <v>2.29</v>
+        <v>1.22</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -13349,31 +13349,31 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="O80">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="P80">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Q80">
         <v>1.37</v>
       </c>
       <c r="R80">
-        <v>3.29</v>
+        <v>3.42</v>
       </c>
       <c r="S80">
         <v>1.12</v>
       </c>
       <c r="T80">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="U80">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V80">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W80">
         <v>1.25</v>
@@ -13382,31 +13382,31 @@
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z80">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA80">
         <v>1.25</v>
       </c>
       <c r="AB80">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AC80">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD80">
         <v>2.1</v>
       </c>
       <c r="AE80">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AF80">
         <v>1.83</v>
       </c>
       <c r="AG80">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AK80">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.3</v>
+        <v>1.42</v>
       </c>
       <c r="O86">
-        <v>3.82</v>
+        <v>5.05</v>
       </c>
       <c r="P86">
-        <v>1.92</v>
+        <v>5.3</v>
       </c>
       <c r="Q86">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="R86">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="S86">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="T86">
-        <v>3.68</v>
+        <v>5.05</v>
       </c>
       <c r="U86">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="V86">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="W86">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="X86">
+        <v>1.01</v>
+      </c>
+      <c r="Y86">
         <v>1.02</v>
       </c>
-      <c r="Y86">
-        <v>1.08</v>
-      </c>
       <c r="Z86">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="AA86">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AB86">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AC86">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AD86">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AE86">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="AF86">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AG86">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>1.3</v>
+        <v>2.71</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.42</v>
+        <v>3.3</v>
       </c>
       <c r="O87">
-        <v>5.05</v>
+        <v>3.82</v>
       </c>
       <c r="P87">
-        <v>5.3</v>
+        <v>1.92</v>
       </c>
       <c r="Q87">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="R87">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="S87">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T87">
-        <v>5.05</v>
+        <v>3.68</v>
       </c>
       <c r="U87">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="V87">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="W87">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AA87">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AB87">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC87">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AD87">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="AE87">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AF87">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AG87">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK87">
-        <v>2.71</v>
+        <v>1.3</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O99">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q99">
-        <v>2.68</v>
+        <v>2.93</v>
       </c>
       <c r="R99">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="S99">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T99">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="U99">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="V99">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="W99">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y99">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z99">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="AA99">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AB99">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC99">
-        <v>2.3</v>
+        <v>3.51</v>
       </c>
       <c r="AD99">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AE99">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AF99">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AG99">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK99">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O100">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P100">
-        <v>2.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q100">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="R100">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="S100">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T100">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U100">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="V100">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W100">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y100">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z100">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="AA100">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AB100">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AC100">
-        <v>3.51</v>
+        <v>2.8</v>
       </c>
       <c r="AD100">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AE100">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF100">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="AK100">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
+        <v>1.7</v>
+      </c>
+      <c r="O101">
         <v>3.5</v>
       </c>
-      <c r="O101">
-        <v>3.7</v>
-      </c>
       <c r="P101">
-        <v>1.76</v>
+        <v>4.2</v>
       </c>
       <c r="Q101">
-        <v>3.64</v>
+        <v>2.36</v>
       </c>
       <c r="R101">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S101">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T101">
+        <v>2.88</v>
+      </c>
+      <c r="U101">
+        <v>2.88</v>
+      </c>
+      <c r="V101">
+        <v>1.37</v>
+      </c>
+      <c r="W101">
+        <v>1.05</v>
+      </c>
+      <c r="X101">
+        <v>1.01</v>
+      </c>
+      <c r="Y101">
+        <v>1.32</v>
+      </c>
+      <c r="Z101">
         <v>3.3</v>
       </c>
-      <c r="U101">
-        <v>2.49</v>
-      </c>
-      <c r="V101">
-        <v>1.49</v>
-      </c>
-      <c r="W101">
-        <v>1.08</v>
-      </c>
-      <c r="X101">
+      <c r="AA101">
+        <v>2.02</v>
+      </c>
+      <c r="AB101">
+        <v>1.8</v>
+      </c>
+      <c r="AC101">
+        <v>3.53</v>
+      </c>
+      <c r="AD101">
+        <v>1.29</v>
+      </c>
+      <c r="AE101">
         <v>1.04</v>
       </c>
-      <c r="Y101">
-        <v>1.17</v>
-      </c>
-      <c r="Z101">
-        <v>4.05</v>
-      </c>
-      <c r="AA101">
-        <v>1.68</v>
-      </c>
-      <c r="AB101">
-        <v>2.19</v>
-      </c>
-      <c r="AC101">
-        <v>2.8</v>
-      </c>
-      <c r="AD101">
-        <v>1.45</v>
-      </c>
-      <c r="AE101">
-        <v>1.17</v>
-      </c>
       <c r="AF101">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AG101">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.92</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>1.19</v>
+        <v>2.06</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q102">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S102">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T102">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U102">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V102">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="Z102">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA102">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="AB102">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AC102">
-        <v>3.53</v>
+        <v>2.3</v>
       </c>
       <c r="AD102">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AE102">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AF102">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AG102">
-        <v>1.84</v>
+        <v>2.63</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK102">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="AL102">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
         <v>1.35</v>
@@ -2289,10 +2289,10 @@
         <v>2.57</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2304,10 +2304,10 @@
         <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AB12">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
         <v>3.16</v>
@@ -2316,13 +2316,13 @@
         <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
         <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -5036,55 +5036,55 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="O29">
         <v>3.05</v>
       </c>
       <c r="P29">
-        <v>3.29</v>
+        <v>2.8</v>
       </c>
       <c r="Q29">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S29">
         <v>1.39</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U29">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W29">
         <v>1.02</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.28</v>
       </c>
       <c r="Z29">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA29">
         <v>2.04</v>
       </c>
       <c r="AB29">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC29">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="AD29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE29">
         <v>1.04</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK29">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -9600,16 +9600,16 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="O57">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P57">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q57">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="R57">
         <v>2</v>
@@ -9621,10 +9621,10 @@
         <v>2.75</v>
       </c>
       <c r="U57">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="V57">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W57">
         <v>1.02</v>
@@ -9633,31 +9633,31 @@
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z57">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="AA57">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AB57">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC57">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="AD57">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE57">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF57">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG57">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK57">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9935,10 +9935,10 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="R59">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S59">
         <v>1.36</v>
@@ -9947,28 +9947,28 @@
         <v>2.85</v>
       </c>
       <c r="U59">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="V59">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W59">
         <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z59">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA59">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AB59">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC59">
         <v>3.08</v>
@@ -9977,13 +9977,13 @@
         <v>1.28</v>
       </c>
       <c r="AE59">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF59">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG59">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK59">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.03</v>
+        <v>3.2</v>
       </c>
       <c r="O73">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q73">
-        <v>2.35</v>
+        <v>3.74</v>
       </c>
       <c r="R73">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S73">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T73">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="U73">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V73">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z73">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA73">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB73">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC73">
-        <v>3.18</v>
+        <v>2.95</v>
       </c>
       <c r="AD73">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE73">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF73">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG73">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="AK73">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
+        <v>2.03</v>
+      </c>
+      <c r="O74">
+        <v>3.48</v>
+      </c>
+      <c r="P74">
         <v>3.2</v>
       </c>
-      <c r="O74">
-        <v>3.2</v>
-      </c>
-      <c r="P74">
-        <v>2.05</v>
-      </c>
       <c r="Q74">
-        <v>3.74</v>
+        <v>2.35</v>
       </c>
       <c r="R74">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S74">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T74">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="U74">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V74">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W74">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X74">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z74">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA74">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB74">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC74">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AD74">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE74">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF74">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG74">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="AK74">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>4.4</v>
+        <v>4.58</v>
       </c>
       <c r="O77">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="P77">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="O85">
-        <v>5.6</v>
+        <v>5.05</v>
       </c>
       <c r="P85">
-        <v>8.75</v>
+        <v>5.3</v>
       </c>
       <c r="Q85">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="R85">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="S85">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T85">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="U85">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="V85">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W85">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Z85">
-        <v>6.15</v>
+        <v>8.5</v>
       </c>
       <c r="AA85">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AB85">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AC85">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AD85">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AE85">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AF85">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AG85">
-        <v>2.11</v>
+        <v>2.86</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK85">
-        <v>3.44</v>
+        <v>2.71</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.42</v>
+        <v>2.51</v>
       </c>
       <c r="O86">
-        <v>5.05</v>
+        <v>3.64</v>
       </c>
       <c r="P86">
-        <v>5.3</v>
+        <v>2.46</v>
       </c>
       <c r="Q86">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R86">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="S86">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="T86">
-        <v>5.05</v>
+        <v>3.8</v>
       </c>
       <c r="U86">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="V86">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="W86">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Z86">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA86">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="AB86">
-        <v>3.6</v>
+        <v>2.48</v>
       </c>
       <c r="AC86">
-        <v>1.69</v>
+        <v>2.18</v>
       </c>
       <c r="AD86">
-        <v>2.11</v>
+        <v>1.67</v>
       </c>
       <c r="AE86">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="AF86">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AG86">
-        <v>2.86</v>
+        <v>2.63</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>2.71</v>
+        <v>1.41</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.3</v>
+        <v>1.28</v>
       </c>
       <c r="O87">
-        <v>3.82</v>
+        <v>5.6</v>
       </c>
       <c r="P87">
-        <v>1.92</v>
+        <v>8.75</v>
       </c>
       <c r="Q87">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="R87">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="S87">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T87">
-        <v>3.68</v>
+        <v>4.8</v>
       </c>
       <c r="U87">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="V87">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="W87">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z87">
-        <v>6</v>
+        <v>6.15</v>
       </c>
       <c r="AA87">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB87">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC87">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AD87">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AE87">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AF87">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AG87">
-        <v>2.77</v>
+        <v>2.11</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK87">
-        <v>1.3</v>
+        <v>3.44</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,80 +14653,80 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.51</v>
+        <v>3.3</v>
       </c>
       <c r="O88">
-        <v>3.64</v>
+        <v>3.82</v>
       </c>
       <c r="P88">
-        <v>2.46</v>
+        <v>1.92</v>
       </c>
       <c r="Q88">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="R88">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="S88">
         <v>1.22</v>
       </c>
       <c r="T88">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="U88">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="V88">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W88">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z88">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA88">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AB88">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AC88">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AD88">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE88">
+        <v>1.24</v>
+      </c>
+      <c r="AF88">
+        <v>1.39</v>
+      </c>
+      <c r="AG88">
+        <v>2.77</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
         <v>1.23</v>
       </c>
-      <c r="AF88">
-        <v>1.41</v>
-      </c>
-      <c r="AG88">
-        <v>2.63</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.25</v>
-      </c>
       <c r="AK88">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O99">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P99">
-        <v>2.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q99">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="R99">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="S99">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T99">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U99">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="V99">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W99">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z99">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="AA99">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AB99">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AC99">
-        <v>3.51</v>
+        <v>2.8</v>
       </c>
       <c r="AD99">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AE99">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF99">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG99">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.28</v>
+        <v>1.92</v>
       </c>
       <c r="AK99">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="O100">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P100">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="Q100">
-        <v>3.64</v>
+        <v>2.68</v>
       </c>
       <c r="R100">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="S100">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T100">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U100">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="V100">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="W100">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X100">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z100">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="AA100">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AB100">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AC100">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD100">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AE100">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF100">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG100">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="AK100">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,25 +16772,25 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O101">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q101">
-        <v>2.36</v>
+        <v>2.93</v>
       </c>
       <c r="R101">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S101">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T101">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U101">
         <v>2.88</v>
@@ -16799,37 +16799,37 @@
         <v>1.37</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z101">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA101">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB101">
         <v>1.8</v>
       </c>
       <c r="AC101">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="AD101">
         <v>1.29</v>
       </c>
       <c r="AE101">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF101">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG101">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK101">
-        <v>2.06</v>
+        <v>1.57</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="Q102">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="R102">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T102">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="V102">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="W102">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="Z102">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA102">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AB102">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC102">
-        <v>2.3</v>
+        <v>3.53</v>
       </c>
       <c r="AD102">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AE102">
+        <v>1.04</v>
+      </c>
+      <c r="AF102">
+        <v>1.86</v>
+      </c>
+      <c r="AG102">
+        <v>1.84</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
         <v>1.25</v>
       </c>
-      <c r="AF102">
-        <v>1.44</v>
-      </c>
-      <c r="AG102">
-        <v>2.63</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.26</v>
-      </c>
       <c r="AK102">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="AL102">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -798,34 +798,34 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
         <v>3.15</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
       </c>
       <c r="R3">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S3">
         <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="U3">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.04</v>
@@ -840,22 +840,22 @@
         <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC3">
-        <v>4.5</v>
+        <v>3.62</v>
       </c>
       <c r="AD3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG3">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK3">
         <v>1.36</v>
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.12</v>
+        <v>4.24</v>
       </c>
       <c r="O4">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
         <v>1.8</v>
@@ -973,37 +973,37 @@
         <v>4.2</v>
       </c>
       <c r="R4">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="U4">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.35</v>
+        <v>4.12</v>
       </c>
       <c r="AA4">
         <v>1.75</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
         <v>3</v>
@@ -1012,10 +1012,10 @@
         <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AG4">
         <v>2.05</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -3252,22 +3252,22 @@
         <v>2.45</v>
       </c>
       <c r="Q18">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="R18">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="U18">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
         <v>1.15</v>
@@ -3285,22 +3285,22 @@
         <v>1.5</v>
       </c>
       <c r="AB18">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC18">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD18">
         <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG18">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3901,19 +3901,19 @@
         <v>4.2</v>
       </c>
       <c r="P22">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q22">
-        <v>5.11</v>
+        <v>4.95</v>
       </c>
       <c r="R22">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="U22">
         <v>2.1</v>
@@ -3928,16 +3928,16 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AA22">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC22">
         <v>2.06</v>
@@ -3946,13 +3946,13 @@
         <v>1.62</v>
       </c>
       <c r="AE22">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF22">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG22">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AK22">
         <v>1.11</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P26">
         <v>4.5</v>
       </c>
       <c r="Q26">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R26">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S26">
         <v>1.22</v>
       </c>
       <c r="T26">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="U26">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V26">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AA26">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB26">
         <v>2.3</v>
       </c>
       <c r="AC26">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD26">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF26">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK26">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="P28">
         <v>3.72</v>
       </c>
       <c r="Q28">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S28">
         <v>1.35</v>
@@ -4894,7 +4894,7 @@
         <v>3.08</v>
       </c>
       <c r="U28">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="V28">
         <v>1.48</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK28">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5706,46 +5706,46 @@
         <v>1.24</v>
       </c>
       <c r="T33">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
         <v>2.25</v>
       </c>
       <c r="V33">
+        <v>1.56</v>
+      </c>
+      <c r="W33">
+        <v>1.13</v>
+      </c>
+      <c r="X33">
+        <v>1.03</v>
+      </c>
+      <c r="Y33">
+        <v>1.13</v>
+      </c>
+      <c r="Z33">
+        <v>4.55</v>
+      </c>
+      <c r="AA33">
         <v>1.57</v>
-      </c>
-      <c r="W33">
-        <v>1.14</v>
-      </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
-      <c r="Y33">
-        <v>1.19</v>
-      </c>
-      <c r="Z33">
-        <v>3.8</v>
-      </c>
-      <c r="AA33">
-        <v>1.52</v>
       </c>
       <c r="AB33">
         <v>2.34</v>
       </c>
       <c r="AC33">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AD33">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE33">
         <v>1.2</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG33">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6177,28 +6177,28 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="O36">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P36">
         <v>3.9</v>
       </c>
       <c r="Q36">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="R36">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="U36">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V36">
         <v>1.58</v>
@@ -6210,31 +6210,31 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA36">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB36">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AC36">
         <v>2.4</v>
       </c>
       <c r="AD36">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF36">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6373,31 +6373,31 @@
         <v>0</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6675,10 +6675,10 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -6687,10 +6687,10 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
         <v>0</v>
@@ -6699,31 +6699,31 @@
         <v>0</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,10 +6838,10 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -6850,10 +6850,10 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W40">
         <v>0</v>
@@ -6868,25 +6868,25 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,25 +7155,25 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="O42">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P42">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="Q42">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R42">
         <v>2.2</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U42">
         <v>2.63</v>
@@ -7185,28 +7185,28 @@
         <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z42">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA42">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AB42">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC42">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD42">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF42">
         <v>1.6</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O43">
-        <v>3.55</v>
+        <v>3.27</v>
       </c>
       <c r="P43">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="Q43">
         <v>2.45</v>
@@ -7342,40 +7342,40 @@
         <v>2.4</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W43">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z43">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="AA43">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB43">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC43">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD43">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE43">
         <v>1.15</v>
       </c>
       <c r="AF43">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="O44">
         <v>4.2</v>
@@ -7490,7 +7490,7 @@
         <v>4.45</v>
       </c>
       <c r="Q44">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R44">
         <v>2.5</v>
@@ -7499,7 +7499,7 @@
         <v>1.19</v>
       </c>
       <c r="T44">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="U44">
         <v>2.05</v>
@@ -7523,22 +7523,22 @@
         <v>1.4</v>
       </c>
       <c r="AB44">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC44">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AD44">
         <v>1.7</v>
       </c>
       <c r="AE44">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF44">
         <v>1.45</v>
       </c>
       <c r="AG44">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,13 +7653,13 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="R45">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S45">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
         <v>2.82</v>
@@ -7671,7 +7671,7 @@
         <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
         <v>1.05</v>
@@ -7680,13 +7680,13 @@
         <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="AA45">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB45">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC45">
         <v>3.2</v>
@@ -7695,13 +7695,13 @@
         <v>1.33</v>
       </c>
       <c r="AE45">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG45">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="O46">
         <v>3.4</v>
       </c>
       <c r="P46">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7979,7 +7979,7 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="R47">
         <v>2.28</v>
@@ -7988,13 +7988,13 @@
         <v>1.28</v>
       </c>
       <c r="T47">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V47">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W47">
         <v>1.08</v>
@@ -8012,7 +8012,7 @@
         <v>1.63</v>
       </c>
       <c r="AB47">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AC47">
         <v>2.5</v>
@@ -8021,13 +8021,13 @@
         <v>1.5</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8136,40 +8136,40 @@
         <v>3.45</v>
       </c>
       <c r="O48">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="P48">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q48">
         <v>4</v>
       </c>
       <c r="R48">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="S48">
         <v>1.24</v>
       </c>
       <c r="T48">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="U48">
         <v>2.23</v>
       </c>
       <c r="V48">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W48">
         <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>5.02</v>
+        <v>4.7</v>
       </c>
       <c r="AA48">
         <v>1.57</v>
@@ -8178,19 +8178,19 @@
         <v>2.37</v>
       </c>
       <c r="AC48">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AD48">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE48">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG48">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="AK48">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,22 +8296,22 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="O49">
         <v>3.75</v>
       </c>
       <c r="P49">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q49">
         <v>3</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
         <v>3.4</v>
@@ -8320,28 +8320,28 @@
         <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA49">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AB49">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AC49">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AD49">
         <v>1.48</v>
@@ -8350,7 +8350,7 @@
         <v>1.15</v>
       </c>
       <c r="AF49">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG49">
         <v>2.5</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.51</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q50">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="R50">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T50">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V50">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA50">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB50">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC50">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD50">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AE50">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q51">
         <v>2.56</v>
@@ -8637,19 +8637,19 @@
         <v>1.99</v>
       </c>
       <c r="S51">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T51">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="U51">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="V51">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8661,25 +8661,25 @@
         <v>2.94</v>
       </c>
       <c r="AA51">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB51">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC51">
-        <v>4.02</v>
+        <v>3.54</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG51">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S52">
         <v>1.3</v>
@@ -8806,7 +8806,7 @@
         <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V52">
         <v>1.5</v>
@@ -8818,31 +8818,31 @@
         <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
         <v>4.2</v>
       </c>
       <c r="AA52">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AB52">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AC52">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="AD52">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE52">
         <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AG52">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK52">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9274,61 +9274,61 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O55">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P55">
+        <v>2.3</v>
+      </c>
+      <c r="Q55">
+        <v>3</v>
+      </c>
+      <c r="R55">
+        <v>2.43</v>
+      </c>
+      <c r="S55">
+        <v>1.18</v>
+      </c>
+      <c r="T55">
+        <v>3.42</v>
+      </c>
+      <c r="U55">
         <v>2.25</v>
       </c>
-      <c r="Q55">
-        <v>3.1</v>
-      </c>
-      <c r="R55">
-        <v>2.3</v>
-      </c>
-      <c r="S55">
-        <v>1.23</v>
-      </c>
-      <c r="T55">
-        <v>2.75</v>
-      </c>
-      <c r="U55">
-        <v>2.22</v>
-      </c>
       <c r="V55">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W55">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
         <v>1.1</v>
       </c>
       <c r="Z55">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA55">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="AB55">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC55">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AD55">
         <v>1.57</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF55">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AG55">
         <v>2.62</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AK55">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="O56">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P56">
         <v>4.75</v>
@@ -9452,16 +9452,16 @@
         <v>2.5</v>
       </c>
       <c r="S56">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V56">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
         <v>1.13</v>
@@ -9470,31 +9470,31 @@
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA56">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB56">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC56">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD56">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE56">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF56">
         <v>1.55</v>
       </c>
       <c r="AG56">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK56">
         <v>2.25</v>
@@ -9763,31 +9763,31 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="O58">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="P58">
         <v>8.800000000000001</v>
       </c>
       <c r="Q58">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R58">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S58">
         <v>1.22</v>
       </c>
       <c r="T58">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="U58">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V58">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="W58">
         <v>1.17</v>
@@ -9796,16 +9796,16 @@
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z58">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="AA58">
         <v>1.46</v>
       </c>
       <c r="AB58">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="AC58">
         <v>2.25</v>
@@ -9820,7 +9820,7 @@
         <v>1.8</v>
       </c>
       <c r="AG58">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="O62">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P62">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="Q62">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="R62">
         <v>2.5</v>
       </c>
       <c r="S62">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="U62">
         <v>2.2</v>
       </c>
       <c r="V62">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X62">
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z62">
-        <v>5.81</v>
+        <v>5.25</v>
       </c>
       <c r="AA62">
         <v>1.47</v>
       </c>
       <c r="AB62">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AC62">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AD62">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE62">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF62">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10741,25 +10741,25 @@
         </is>
       </c>
       <c r="N64">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O64">
         <v>3.65</v>
       </c>
       <c r="P64">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q64">
-        <v>3.07</v>
+        <v>3.7</v>
       </c>
       <c r="R64">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S64">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U64">
         <v>2.13</v>
@@ -10768,7 +10768,7 @@
         <v>1.63</v>
       </c>
       <c r="W64">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
         <v>1.02</v>
@@ -10786,7 +10786,7 @@
         <v>2.49</v>
       </c>
       <c r="AC64">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AD64">
         <v>1.64</v>
@@ -10798,7 +10798,7 @@
         <v>1.44</v>
       </c>
       <c r="AG64">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.79</v>
+        <v>1.16</v>
       </c>
       <c r="AK64">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O65">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="P65">
-        <v>5.15</v>
+        <v>5.75</v>
       </c>
       <c r="Q65">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R65">
         <v>2.43</v>
       </c>
       <c r="S65">
+        <v>1.18</v>
+      </c>
+      <c r="T65">
+        <v>4.5</v>
+      </c>
+      <c r="U65">
+        <v>2.13</v>
+      </c>
+      <c r="V65">
+        <v>1.68</v>
+      </c>
+      <c r="W65">
         <v>1.17</v>
-      </c>
-      <c r="T65">
-        <v>4</v>
-      </c>
-      <c r="U65">
-        <v>2.02</v>
-      </c>
-      <c r="V65">
-        <v>1.78</v>
-      </c>
-      <c r="W65">
-        <v>1.2</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z65">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA65">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB65">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AC65">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AD65">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE65">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF65">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK65">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,16 +11076,16 @@
         <v>1.84</v>
       </c>
       <c r="Q66">
-        <v>4.06</v>
+        <v>3.35</v>
       </c>
       <c r="R66">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S66">
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="U66">
         <v>2.22</v>
@@ -11094,19 +11094,19 @@
         <v>1.58</v>
       </c>
       <c r="W66">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z66">
-        <v>4.97</v>
+        <v>5</v>
       </c>
       <c r="AA66">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB66">
         <v>2.33</v>
@@ -11121,10 +11121,10 @@
         <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.21</v>
+        <v>1.77</v>
       </c>
       <c r="AK66">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,22 +11230,22 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O67">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P67">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q67">
         <v>2.75</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T67">
         <v>2.95</v>
@@ -11257,10 +11257,10 @@
         <v>1.42</v>
       </c>
       <c r="W67">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
         <v>1.22</v>
@@ -11269,25 +11269,25 @@
         <v>3.55</v>
       </c>
       <c r="AA67">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB67">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC67">
         <v>2.8</v>
       </c>
       <c r="AD67">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE67">
         <v>1.12</v>
       </c>
       <c r="AF67">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.27</v>
       </c>
       <c r="AK67">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11728,7 +11728,7 @@
         <v>3.7</v>
       </c>
       <c r="Q70">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R70">
         <v>2.25</v>
@@ -11740,34 +11740,34 @@
         <v>3.22</v>
       </c>
       <c r="U70">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V70">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W70">
         <v>1.06</v>
       </c>
       <c r="X70">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y70">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="AA70">
         <v>1.85</v>
       </c>
       <c r="AB70">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC70">
-        <v>2.68</v>
+        <v>2.93</v>
       </c>
       <c r="AD70">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE70">
         <v>1.11</v>
@@ -11776,7 +11776,7 @@
         <v>1.67</v>
       </c>
       <c r="AG70">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
         <v>1.95</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="O71">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="P71">
-        <v>3.1</v>
+        <v>4.89</v>
       </c>
       <c r="Q71">
-        <v>3.02</v>
+        <v>2.19</v>
       </c>
       <c r="R71">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="T71">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="U71">
-        <v>3.16</v>
+        <v>2.6</v>
       </c>
       <c r="V71">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="W71">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y71">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="Z71">
-        <v>2.72</v>
+        <v>3.82</v>
       </c>
       <c r="AA71">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AB71">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AC71">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="AD71">
-        <v>1.15</v>
+        <v>1.39</v>
       </c>
       <c r="AE71">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF71">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AG71">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK71">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="O72">
+        <v>3.2</v>
+      </c>
+      <c r="P72">
+        <v>2.24</v>
+      </c>
+      <c r="Q72">
         <v>3.45</v>
       </c>
-      <c r="P72">
-        <v>4.5</v>
-      </c>
-      <c r="Q72">
-        <v>2.25</v>
-      </c>
       <c r="R72">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S72">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T72">
-        <v>3.19</v>
+        <v>2.94</v>
       </c>
       <c r="U72">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V72">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W72">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z72">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA72">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB72">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC72">
-        <v>2.64</v>
+        <v>3.25</v>
       </c>
       <c r="AD72">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE72">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF72">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG72">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK72">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.2</v>
+        <v>2.03</v>
       </c>
       <c r="O73">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P73">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="Q73">
-        <v>3.74</v>
+        <v>2.67</v>
       </c>
       <c r="R73">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S73">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T73">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="U73">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="V73">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W73">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA73">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB73">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC73">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="AD73">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AE73">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF73">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AG73">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AK73">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,65 +12371,65 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.03</v>
+        <v>2.31</v>
       </c>
       <c r="O74">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="P74">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q74">
+        <v>3</v>
+      </c>
+      <c r="R74">
+        <v>1.95</v>
+      </c>
+      <c r="S74">
+        <v>1.53</v>
+      </c>
+      <c r="T74">
+        <v>2.43</v>
+      </c>
+      <c r="U74">
+        <v>3.16</v>
+      </c>
+      <c r="V74">
+        <v>1.3</v>
+      </c>
+      <c r="W74">
+        <v>1.05</v>
+      </c>
+      <c r="X74">
+        <v>1.04</v>
+      </c>
+      <c r="Y74">
+        <v>1.44</v>
+      </c>
+      <c r="Z74">
+        <v>2.72</v>
+      </c>
+      <c r="AA74">
         <v>2.35</v>
       </c>
-      <c r="R74">
-        <v>2.1</v>
-      </c>
-      <c r="S74">
-        <v>1.39</v>
-      </c>
-      <c r="T74">
-        <v>2.88</v>
-      </c>
-      <c r="U74">
-        <v>2.81</v>
-      </c>
-      <c r="V74">
-        <v>1.36</v>
-      </c>
-      <c r="W74">
-        <v>1.04</v>
-      </c>
-      <c r="X74">
-        <v>1</v>
-      </c>
-      <c r="Y74">
-        <v>1.28</v>
-      </c>
-      <c r="Z74">
-        <v>3.3</v>
-      </c>
-      <c r="AA74">
-        <v>1.92</v>
-      </c>
       <c r="AB74">
+        <v>1.57</v>
+      </c>
+      <c r="AC74">
+        <v>4.25</v>
+      </c>
+      <c r="AD74">
+        <v>1.17</v>
+      </c>
+      <c r="AE74">
+        <v>1.01</v>
+      </c>
+      <c r="AF74">
+        <v>2</v>
+      </c>
+      <c r="AG74">
         <v>1.7</v>
       </c>
-      <c r="AC74">
-        <v>3.18</v>
-      </c>
-      <c r="AD74">
-        <v>1.25</v>
-      </c>
-      <c r="AE74">
-        <v>1.09</v>
-      </c>
-      <c r="AF74">
-        <v>1.77</v>
-      </c>
-      <c r="AG74">
-        <v>1.98</v>
-      </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK74">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O78">
         <v>3.3</v>
       </c>
       <c r="P78">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q78">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R78">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
         <v>1.36</v>
       </c>
       <c r="T78">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="U78">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="V78">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W78">
         <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AA78">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB78">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC78">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="AD78">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE78">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG78">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK78">
         <v>1.7</v>
@@ -13352,7 +13352,7 @@
         <v>1.1</v>
       </c>
       <c r="O80">
-        <v>9.4</v>
+        <v>9.25</v>
       </c>
       <c r="P80">
         <v>16</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P81">
+        <v>2.45</v>
+      </c>
+      <c r="Q81">
         <v>2.8</v>
       </c>
-      <c r="Q81">
+      <c r="R81">
+        <v>2.4</v>
+      </c>
+      <c r="S81">
+        <v>1.25</v>
+      </c>
+      <c r="T81">
+        <v>3.36</v>
+      </c>
+      <c r="U81">
+        <v>2.15</v>
+      </c>
+      <c r="V81">
+        <v>1.62</v>
+      </c>
+      <c r="W81">
+        <v>1.13</v>
+      </c>
+      <c r="X81">
+        <v>1.03</v>
+      </c>
+      <c r="Y81">
+        <v>1.12</v>
+      </c>
+      <c r="Z81">
+        <v>4.75</v>
+      </c>
+      <c r="AA81">
+        <v>1.5</v>
+      </c>
+      <c r="AB81">
         <v>2.5</v>
       </c>
-      <c r="R81">
-        <v>2.48</v>
-      </c>
-      <c r="S81">
-        <v>1.16</v>
-      </c>
-      <c r="T81">
-        <v>4.25</v>
-      </c>
-      <c r="U81">
-        <v>1.8</v>
-      </c>
-      <c r="V81">
-        <v>1.89</v>
-      </c>
-      <c r="W81">
+      <c r="AC81">
+        <v>2.27</v>
+      </c>
+      <c r="AD81">
+        <v>1.62</v>
+      </c>
+      <c r="AE81">
         <v>1.25</v>
       </c>
-      <c r="X81">
-        <v>1.01</v>
-      </c>
-      <c r="Y81">
-        <v>1.09</v>
-      </c>
-      <c r="Z81">
-        <v>7</v>
-      </c>
-      <c r="AA81">
-        <v>1.3</v>
-      </c>
-      <c r="AB81">
-        <v>3.35</v>
-      </c>
-      <c r="AC81">
-        <v>1.8</v>
-      </c>
-      <c r="AD81">
-        <v>2</v>
-      </c>
-      <c r="AE81">
-        <v>1.44</v>
-      </c>
       <c r="AF81">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AG81">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P82">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q82">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="R82">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="V82">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="W82">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
         <v>1.12</v>
       </c>
       <c r="Z82">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AA82">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB82">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AC82">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AD82">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AE82">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF82">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG82">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.75</v>
+        <v>2.87</v>
       </c>
       <c r="O83">
         <v>3.8</v>
       </c>
       <c r="P83">
-        <v>3.4</v>
+        <v>2.03</v>
       </c>
       <c r="Q83">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="R83">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U83">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V83">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W83">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z83">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AA83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB83">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AC83">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AD83">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE83">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF83">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG83">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK83">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,52 +14001,52 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="O84">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P84">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="Q84">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R84">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S84">
+        <v>1.2</v>
+      </c>
+      <c r="T84">
+        <v>4</v>
+      </c>
+      <c r="U84">
+        <v>2.1</v>
+      </c>
+      <c r="V84">
+        <v>1.68</v>
+      </c>
+      <c r="W84">
         <v>1.18</v>
-      </c>
-      <c r="T84">
-        <v>4.05</v>
-      </c>
-      <c r="U84">
-        <v>2.06</v>
-      </c>
-      <c r="V84">
-        <v>1.72</v>
-      </c>
-      <c r="W84">
-        <v>1.17</v>
       </c>
       <c r="X84">
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z84">
-        <v>5.97</v>
+        <v>5.75</v>
       </c>
       <c r="AA84">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB84">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AC84">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AD84">
         <v>1.7</v>
@@ -14055,10 +14055,10 @@
         <v>1.27</v>
       </c>
       <c r="AF84">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AG84">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK84">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="O85">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="P85">
-        <v>5.3</v>
+        <v>8.75</v>
       </c>
       <c r="Q85">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="R85">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="S85">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>5.05</v>
+        <v>4.33</v>
       </c>
       <c r="U85">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="V85">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="W85">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Z85">
-        <v>8.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA85">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AB85">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC85">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AD85">
+        <v>1.87</v>
+      </c>
+      <c r="AE85">
+        <v>1.32</v>
+      </c>
+      <c r="AF85">
+        <v>1.62</v>
+      </c>
+      <c r="AG85">
         <v>2.11</v>
-      </c>
-      <c r="AE85">
-        <v>1.47</v>
-      </c>
-      <c r="AF85">
-        <v>1.37</v>
-      </c>
-      <c r="AG85">
-        <v>2.86</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.14</v>
       </c>
       <c r="AK85">
-        <v>2.71</v>
+        <v>3.4</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.51</v>
+        <v>1.4</v>
       </c>
       <c r="O86">
-        <v>3.64</v>
+        <v>5.1</v>
       </c>
       <c r="P86">
-        <v>2.46</v>
+        <v>5.25</v>
       </c>
       <c r="Q86">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="R86">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="S86">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T86">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="U86">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="V86">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="W86">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z86">
-        <v>5.25</v>
+        <v>8.5</v>
       </c>
       <c r="AA86">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AB86">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="AC86">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="AD86">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AE86">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AF86">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="O87">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="P87">
-        <v>8.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q87">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="R87">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T87">
-        <v>4.8</v>
+        <v>4.25</v>
       </c>
       <c r="U87">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="V87">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="W87">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z87">
-        <v>6.15</v>
+        <v>7.5</v>
       </c>
       <c r="AA87">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AB87">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AC87">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AD87">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AE87">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AF87">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AG87">
-        <v>2.11</v>
+        <v>2.95</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>3.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,65 +14653,65 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O88">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="P88">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="Q88">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="R88">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="S88">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U88">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="V88">
+        <v>1.67</v>
+      </c>
+      <c r="W88">
+        <v>1.15</v>
+      </c>
+      <c r="X88">
+        <v>1.03</v>
+      </c>
+      <c r="Y88">
+        <v>1.13</v>
+      </c>
+      <c r="Z88">
+        <v>5.5</v>
+      </c>
+      <c r="AA88">
+        <v>1.44</v>
+      </c>
+      <c r="AB88">
+        <v>2.49</v>
+      </c>
+      <c r="AC88">
+        <v>2.14</v>
+      </c>
+      <c r="AD88">
         <v>1.68</v>
       </c>
-      <c r="W88">
-        <v>1.17</v>
-      </c>
-      <c r="X88">
-        <v>1.02</v>
-      </c>
-      <c r="Y88">
-        <v>1.08</v>
-      </c>
-      <c r="Z88">
-        <v>6</v>
-      </c>
-      <c r="AA88">
-        <v>1.38</v>
-      </c>
-      <c r="AB88">
+      <c r="AE88">
+        <v>1.23</v>
+      </c>
+      <c r="AF88">
+        <v>1.4</v>
+      </c>
+      <c r="AG88">
         <v>2.75</v>
       </c>
-      <c r="AC88">
-        <v>2</v>
-      </c>
-      <c r="AD88">
-        <v>1.7</v>
-      </c>
-      <c r="AE88">
-        <v>1.24</v>
-      </c>
-      <c r="AF88">
-        <v>1.39</v>
-      </c>
-      <c r="AG88">
-        <v>2.77</v>
-      </c>
       <c r="AH88" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14834,10 +14834,10 @@
         <v>1.33</v>
       </c>
       <c r="T89">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V89">
         <v>1.44</v>
@@ -14849,13 +14849,13 @@
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z89">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="AA89">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB89">
         <v>1.98</v>
@@ -14864,16 +14864,16 @@
         <v>2.81</v>
       </c>
       <c r="AD89">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE89">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF89">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AG89">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>1.36</v>
       </c>
       <c r="AK89">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,55 +14988,55 @@
         <v>2.45</v>
       </c>
       <c r="Q90">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="R90">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="S90">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T90">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U90">
         <v>2.2</v>
       </c>
       <c r="V90">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="W90">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
         <v>1.12</v>
       </c>
       <c r="Z90">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AA90">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB90">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC90">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD90">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE90">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF90">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG90">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK90">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,7 +15151,7 @@
         <v>1.53</v>
       </c>
       <c r="Q91">
-        <v>5</v>
+        <v>5.44</v>
       </c>
       <c r="R91">
         <v>2.4</v>
@@ -15160,7 +15160,7 @@
         <v>1.25</v>
       </c>
       <c r="T91">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="U91">
         <v>2.31</v>
@@ -15172,31 +15172,31 @@
         <v>1.08</v>
       </c>
       <c r="X91">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z91">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA91">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB91">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC91">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AD91">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE91">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF91">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG91">
         <v>2</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK91">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,10 +15305,10 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O92">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P92">
         <v>2.7</v>
@@ -15317,7 +15317,7 @@
         <v>2.75</v>
       </c>
       <c r="R92">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S92">
         <v>1.29</v>
@@ -15326,34 +15326,34 @@
         <v>3.25</v>
       </c>
       <c r="U92">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="V92">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W92">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z92">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA92">
         <v>1.65</v>
       </c>
       <c r="AB92">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC92">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD92">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE92">
         <v>1.17</v>
@@ -15362,7 +15362,7 @@
         <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK92">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O93">
         <v>3.6</v>
@@ -15477,55 +15477,55 @@
         <v>4.4</v>
       </c>
       <c r="Q93">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="R93">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S93">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T93">
         <v>3.02</v>
       </c>
       <c r="U93">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="V93">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W93">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z93">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="AA93">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AB93">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC93">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AD93">
         <v>1.33</v>
       </c>
       <c r="AE93">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF93">
         <v>1.8</v>
       </c>
       <c r="AG93">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK93">
         <v>2.1</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="O94">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P94">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="Q94">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="R94">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S94">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T94">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="U94">
         <v>2.23</v>
       </c>
       <c r="V94">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W94">
         <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z94">
-        <v>4.7</v>
+        <v>5.03</v>
       </c>
       <c r="AA94">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB94">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="AC94">
         <v>2.29</v>
       </c>
       <c r="AD94">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE94">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF94">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG94">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15797,61 +15797,61 @@
         <v>2.2</v>
       </c>
       <c r="O95">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P95">
         <v>3</v>
       </c>
       <c r="Q95">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="R95">
         <v>2.27</v>
       </c>
       <c r="S95">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T95">
         <v>3.44</v>
       </c>
       <c r="U95">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V95">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W95">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X95">
         <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z95">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA95">
         <v>1.61</v>
       </c>
       <c r="AB95">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC95">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AD95">
         <v>1.51</v>
       </c>
       <c r="AE95">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF95">
         <v>1.5</v>
       </c>
       <c r="AG95">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>1.38</v>
       </c>
       <c r="AK95">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15975,37 +15975,37 @@
         <v>1.37</v>
       </c>
       <c r="T96">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="U96">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="V96">
         <v>1.38</v>
       </c>
       <c r="W96">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y96">
         <v>1.25</v>
       </c>
       <c r="Z96">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA96">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB96">
         <v>1.82</v>
       </c>
       <c r="AC96">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD96">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE96">
         <v>1.06</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
         <v>1.29</v>
@@ -16123,7 +16123,7 @@
         <v>1.41</v>
       </c>
       <c r="O97">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="P97">
         <v>6</v>
@@ -16132,7 +16132,7 @@
         <v>1.91</v>
       </c>
       <c r="R97">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S97">
         <v>1.29</v>
@@ -16141,43 +16141,43 @@
         <v>3.25</v>
       </c>
       <c r="U97">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V97">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W97">
         <v>1.13</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z97">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AA97">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB97">
         <v>2.2</v>
       </c>
       <c r="AC97">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AD97">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE97">
         <v>1.17</v>
       </c>
       <c r="AF97">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG97">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK97">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16298,19 +16298,19 @@
         <v>2.4</v>
       </c>
       <c r="S98">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="T98">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="U98">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V98">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W98">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X98">
         <v>1.01</v>
@@ -16322,25 +16322,25 @@
         <v>5.4</v>
       </c>
       <c r="AA98">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB98">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="AC98">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AD98">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE98">
         <v>1.2</v>
       </c>
       <c r="AF98">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK98">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="Q100">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="R100">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T100">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U100">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="V100">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="W100">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="Z100">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA100">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AB100">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC100">
-        <v>2.3</v>
+        <v>3.53</v>
       </c>
       <c r="AD100">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AE100">
+        <v>1.04</v>
+      </c>
+      <c r="AF100">
+        <v>1.86</v>
+      </c>
+      <c r="AG100">
+        <v>1.84</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
         <v>1.25</v>
       </c>
-      <c r="AF100">
-        <v>1.44</v>
-      </c>
-      <c r="AG100">
-        <v>2.63</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>1.26</v>
-      </c>
       <c r="AK100">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q102">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S102">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T102">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="U102">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="V102">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="Z102">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA102">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="AB102">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AC102">
-        <v>3.53</v>
+        <v>2.3</v>
       </c>
       <c r="AD102">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AE102">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AF102">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AG102">
-        <v>1.84</v>
+        <v>2.63</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK102">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17913,31 +17913,31 @@
         </is>
       </c>
       <c r="N108">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="O108">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P108">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
       </c>
       <c r="R108">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S108">
         <v>1.38</v>
       </c>
       <c r="T108">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U108">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V108">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W108">
         <v>1.08</v>
@@ -17949,28 +17949,28 @@
         <v>1.25</v>
       </c>
       <c r="Z108">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="AA108">
         <v>1.8</v>
       </c>
       <c r="AB108">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC108">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD108">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE108">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF108">
         <v>1.6</v>
       </c>
       <c r="AG108">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18239,34 +18239,34 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O110">
         <v>3.1</v>
       </c>
       <c r="P110">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="Q110">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="R110">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S110">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T110">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U110">
         <v>3.3</v>
       </c>
       <c r="V110">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W110">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X110">
         <v>1.05</v>
@@ -18281,13 +18281,13 @@
         <v>2.35</v>
       </c>
       <c r="AB110">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC110">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AD110">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE110">
         <v>1.03</v>
@@ -18296,7 +18296,7 @@
         <v>1.99</v>
       </c>
       <c r="AG110">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.31</v>
       </c>
       <c r="AK110">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,25 +18402,25 @@
         </is>
       </c>
       <c r="N111">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="O111">
         <v>3.1</v>
       </c>
       <c r="P111">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q111">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="R111">
-        <v>1.96</v>
+        <v>2.17</v>
       </c>
       <c r="S111">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T111">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="U111">
         <v>3.06</v>
@@ -18435,31 +18435,31 @@
         <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z111">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="AA111">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB111">
+        <v>1.7</v>
+      </c>
+      <c r="AC111">
+        <v>3.65</v>
+      </c>
+      <c r="AD111">
+        <v>1.27</v>
+      </c>
+      <c r="AE111">
+        <v>1.05</v>
+      </c>
+      <c r="AF111">
         <v>1.75</v>
       </c>
-      <c r="AC111">
-        <v>3.7</v>
-      </c>
-      <c r="AD111">
-        <v>1.28</v>
-      </c>
-      <c r="AE111">
-        <v>1.07</v>
-      </c>
-      <c r="AF111">
-        <v>1.72</v>
-      </c>
       <c r="AG111">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK111">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18728,19 +18728,19 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O113">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P113">
         <v>3.3</v>
       </c>
       <c r="Q113">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="R113">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="S113">
         <v>1.44</v>
@@ -18752,34 +18752,34 @@
         <v>3.2</v>
       </c>
       <c r="V113">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W113">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X113">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y113">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z113">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AA113">
         <v>2.3</v>
       </c>
       <c r="AB113">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC113">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AD113">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE113">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF113">
         <v>2</v>
@@ -18801,7 +18801,7 @@
         <v>1.39</v>
       </c>
       <c r="AK113">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18927,22 +18927,22 @@
         <v>1.14</v>
       </c>
       <c r="Z114">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA114">
         <v>1.57</v>
       </c>
       <c r="AB114">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC114">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="AD114">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE114">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF114">
         <v>1.62</v>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK114">
         <v>2.38</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19709,77 +19709,77 @@
         <v>2.25</v>
       </c>
       <c r="O119">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P119">
         <v>2.8</v>
       </c>
       <c r="Q119">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R119">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S119">
+        <v>1.41</v>
+      </c>
+      <c r="T119">
+        <v>2.61</v>
+      </c>
+      <c r="U119">
+        <v>2.88</v>
+      </c>
+      <c r="V119">
+        <v>1.36</v>
+      </c>
+      <c r="W119">
+        <v>1.05</v>
+      </c>
+      <c r="X119">
+        <v>1.04</v>
+      </c>
+      <c r="Y119">
         <v>1.3</v>
       </c>
-      <c r="T119">
-        <v>2.85</v>
-      </c>
-      <c r="U119">
-        <v>2.75</v>
-      </c>
-      <c r="V119">
-        <v>1.4</v>
-      </c>
-      <c r="W119">
+      <c r="Z119">
+        <v>3.3</v>
+      </c>
+      <c r="AA119">
+        <v>2</v>
+      </c>
+      <c r="AB119">
+        <v>1.79</v>
+      </c>
+      <c r="AC119">
+        <v>3.42</v>
+      </c>
+      <c r="AD119">
+        <v>1.26</v>
+      </c>
+      <c r="AE119">
         <v>1.06</v>
       </c>
-      <c r="X119">
-        <v>1.05</v>
-      </c>
-      <c r="Y119">
-        <v>1.21</v>
-      </c>
-      <c r="Z119">
-        <v>3.58</v>
-      </c>
-      <c r="AA119">
-        <v>1.8</v>
-      </c>
-      <c r="AB119">
-        <v>1.91</v>
-      </c>
-      <c r="AC119">
-        <v>3</v>
-      </c>
-      <c r="AD119">
+      <c r="AF119">
+        <v>1.73</v>
+      </c>
+      <c r="AG119">
+        <v>2</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
         <v>1.33</v>
       </c>
-      <c r="AE119">
-        <v>1.09</v>
-      </c>
-      <c r="AF119">
-        <v>1.62</v>
-      </c>
-      <c r="AG119">
-        <v>2.15</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.4</v>
-      </c>
       <c r="AK119">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20204,7 +20204,7 @@
         <v>0</v>
       </c>
       <c r="Q122">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="R122">
         <v>2.4</v>
@@ -20216,40 +20216,40 @@
         <v>3.6</v>
       </c>
       <c r="U122">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="V122">
         <v>1.55</v>
       </c>
       <c r="W122">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X122">
         <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z122">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="AA122">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB122">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC122">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AD122">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE122">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF122">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG122">
         <v>2.1</v>
@@ -20268,7 +20268,7 @@
         <v>1.16</v>
       </c>
       <c r="AK122">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G126">
@@ -22160,22 +22160,22 @@
         <v>0</v>
       </c>
       <c r="Q134">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R134">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S134">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T134">
         <v>3.42</v>
       </c>
       <c r="U134">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V134">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W134">
         <v>1.12</v>
@@ -22184,19 +22184,19 @@
         <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z134">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA134">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB134">
         <v>2.19</v>
       </c>
       <c r="AC134">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AD134">
         <v>1.44</v>
@@ -22205,10 +22205,10 @@
         <v>1.15</v>
       </c>
       <c r="AF134">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG134">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK134">
         <v>2.15</v>
@@ -22803,7 +22803,7 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O138">
         <v>3.25</v>
@@ -22812,7 +22812,7 @@
         <v>2.8</v>
       </c>
       <c r="Q138">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="R138">
         <v>2.25</v>
@@ -22824,7 +22824,7 @@
         <v>3.07</v>
       </c>
       <c r="U138">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="V138">
         <v>1.45</v>
@@ -22836,25 +22836,25 @@
         <v>1.04</v>
       </c>
       <c r="Y138">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z138">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA138">
         <v>1.7</v>
       </c>
       <c r="AB138">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AC138">
         <v>2.7</v>
       </c>
       <c r="AD138">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE138">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF138">
         <v>1.56</v>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK138">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL138">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>7.86</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P36">
         <v>3.9</v>
@@ -6189,19 +6189,19 @@
         <v>2.08</v>
       </c>
       <c r="R36">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V36">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
         <v>1.14</v>
@@ -6210,22 +6210,22 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
         <v>4.8</v>
       </c>
       <c r="AA36">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB36">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC36">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD36">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE36">
         <v>1.2</v>
@@ -6234,7 +6234,7 @@
         <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7653,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="R45">
         <v>2.25</v>
@@ -7686,7 +7686,7 @@
         <v>1.87</v>
       </c>
       <c r="AB45">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AC45">
         <v>3.2</v>
@@ -7698,10 +7698,10 @@
         <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG45">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
         <v>2.4</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O51">
         <v>3.25</v>
@@ -8631,22 +8631,22 @@
         <v>3.7</v>
       </c>
       <c r="Q51">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="R51">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T51">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U51">
-        <v>2.89</v>
+        <v>3.04</v>
       </c>
       <c r="V51">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W51">
         <v>1.04</v>
@@ -8655,19 +8655,19 @@
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z51">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AA51">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AB51">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC51">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="AD51">
         <v>1.22</v>
@@ -8695,7 +8695,7 @@
         <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9446,22 +9446,22 @@
         <v>4.75</v>
       </c>
       <c r="Q56">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R56">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="U56">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="V56">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W56">
         <v>1.13</v>
@@ -9488,13 +9488,13 @@
         <v>1.57</v>
       </c>
       <c r="AE56">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF56">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG56">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
         <v>2.25</v>
@@ -11761,16 +11761,16 @@
         <v>1.85</v>
       </c>
       <c r="AB70">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC70">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AD70">
         <v>1.36</v>
       </c>
       <c r="AE70">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF70">
         <v>1.67</v>
@@ -11882,16 +11882,16 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O71">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
         <v>4.89</v>
       </c>
       <c r="Q71">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="R71">
         <v>2.25</v>
@@ -11918,7 +11918,7 @@
         <v>1.19</v>
       </c>
       <c r="Z71">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="AA71">
         <v>1.8</v>
@@ -12045,19 +12045,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O72">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P72">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="Q72">
         <v>3.45</v>
       </c>
       <c r="R72">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S72">
         <v>1.35</v>
@@ -12118,7 +12118,7 @@
         <v>1.29</v>
       </c>
       <c r="AK72">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.03</v>
+        <v>2.31</v>
       </c>
       <c r="O73">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="P73">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q73">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="R73">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S73">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="T73">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="U73">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="V73">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z73">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="AA73">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AB73">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC73">
-        <v>3.18</v>
+        <v>4.25</v>
       </c>
       <c r="AD73">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE73">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF73">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AG73">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK73">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,80 +12371,80 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="O74">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="P74">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q74">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="R74">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S74">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="T74">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="U74">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="V74">
+        <v>1.36</v>
+      </c>
+      <c r="W74">
+        <v>1.08</v>
+      </c>
+      <c r="X74">
+        <v>1</v>
+      </c>
+      <c r="Y74">
+        <v>1.25</v>
+      </c>
+      <c r="Z74">
+        <v>3.3</v>
+      </c>
+      <c r="AA74">
+        <v>1.92</v>
+      </c>
+      <c r="AB74">
+        <v>1.74</v>
+      </c>
+      <c r="AC74">
+        <v>3.18</v>
+      </c>
+      <c r="AD74">
+        <v>1.25</v>
+      </c>
+      <c r="AE74">
+        <v>1.09</v>
+      </c>
+      <c r="AF74">
+        <v>1.78</v>
+      </c>
+      <c r="AG74">
+        <v>1.91</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ74">
         <v>1.3</v>
       </c>
-      <c r="W74">
-        <v>1.05</v>
-      </c>
-      <c r="X74">
-        <v>1.04</v>
-      </c>
-      <c r="Y74">
-        <v>1.44</v>
-      </c>
-      <c r="Z74">
-        <v>2.72</v>
-      </c>
-      <c r="AA74">
-        <v>2.35</v>
-      </c>
-      <c r="AB74">
-        <v>1.57</v>
-      </c>
-      <c r="AC74">
-        <v>4.25</v>
-      </c>
-      <c r="AD74">
-        <v>1.17</v>
-      </c>
-      <c r="AE74">
-        <v>1.01</v>
-      </c>
-      <c r="AF74">
-        <v>2</v>
-      </c>
-      <c r="AG74">
-        <v>1.7</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ74">
-        <v>1.33</v>
-      </c>
       <c r="AK74">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="O84">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P84">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q84">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R84">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S84">
         <v>1.2</v>
@@ -14022,43 +14022,43 @@
         <v>4</v>
       </c>
       <c r="U84">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V84">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W84">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z84">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA84">
         <v>1.44</v>
       </c>
       <c r="AB84">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AC84">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AD84">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE84">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF84">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,19 +14653,19 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="O88">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P88">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="Q88">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R88">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="S88">
         <v>1.2</v>
@@ -14674,43 +14674,43 @@
         <v>4</v>
       </c>
       <c r="U88">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V88">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W88">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X88">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z88">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA88">
         <v>1.44</v>
       </c>
       <c r="AB88">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AC88">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AD88">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE88">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF88">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG88">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK88">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15631,16 +15631,16 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="O94">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P94">
         <v>2.93</v>
       </c>
       <c r="Q94">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R94">
         <v>2.3</v>
@@ -15652,7 +15652,7 @@
         <v>3.6</v>
       </c>
       <c r="U94">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="V94">
         <v>1.58</v>
@@ -15676,16 +15676,16 @@
         <v>2.42</v>
       </c>
       <c r="AC94">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AD94">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE94">
         <v>1.21</v>
       </c>
       <c r="AF94">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG94">
         <v>2.32</v>
@@ -16120,10 +16120,10 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="O97">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="P97">
         <v>6</v>
@@ -16141,10 +16141,10 @@
         <v>3.25</v>
       </c>
       <c r="U97">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V97">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W97">
         <v>1.13</v>
@@ -16153,10 +16153,10 @@
         <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z97">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="AA97">
         <v>1.65</v>
@@ -16168,7 +16168,7 @@
         <v>2.6</v>
       </c>
       <c r="AD97">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE97">
         <v>1.17</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="O99">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>1.76</v>
+        <v>2.75</v>
       </c>
       <c r="Q99">
-        <v>3.64</v>
+        <v>2.91</v>
       </c>
       <c r="R99">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="S99">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T99">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="U99">
-        <v>2.49</v>
+        <v>2.95</v>
       </c>
       <c r="V99">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W99">
         <v>1.08</v>
       </c>
       <c r="X99">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y99">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="Z99">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA99">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB99">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AC99">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD99">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AE99">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AF99">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AG99">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="AK99">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,80 +16609,80 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="O100">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P100">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q100">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="R100">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S100">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="T100">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="U100">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="V100">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="W100">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="Z100">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA100">
-        <v>2.02</v>
+        <v>1.47</v>
       </c>
       <c r="AB100">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AC100">
-        <v>3.53</v>
+        <v>2.27</v>
       </c>
       <c r="AD100">
+        <v>1.61</v>
+      </c>
+      <c r="AE100">
+        <v>1.21</v>
+      </c>
+      <c r="AF100">
+        <v>1.42</v>
+      </c>
+      <c r="AG100">
+        <v>2.5</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ100">
         <v>1.29</v>
       </c>
-      <c r="AE100">
-        <v>1.04</v>
-      </c>
-      <c r="AF100">
-        <v>1.86</v>
-      </c>
-      <c r="AG100">
-        <v>1.84</v>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ100">
-        <v>1.25</v>
-      </c>
       <c r="AK100">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O101">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P101">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="Q101">
-        <v>2.93</v>
+        <v>4.42</v>
       </c>
       <c r="R101">
-        <v>2.03</v>
+        <v>2.42</v>
       </c>
       <c r="S101">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U101">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="V101">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z101">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AA101">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AB101">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AC101">
-        <v>3.51</v>
+        <v>2.7</v>
       </c>
       <c r="AD101">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE101">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF101">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG101">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P102">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="Q102">
-        <v>2.68</v>
+        <v>2.23</v>
       </c>
       <c r="R102">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="S102">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T102">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>2.23</v>
+        <v>2.98</v>
       </c>
       <c r="V102">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="W102">
+        <v>1.05</v>
+      </c>
+      <c r="X102">
+        <v>1.01</v>
+      </c>
+      <c r="Y102">
+        <v>1.32</v>
+      </c>
+      <c r="Z102">
+        <v>3.65</v>
+      </c>
+      <c r="AA102">
+        <v>1.98</v>
+      </c>
+      <c r="AB102">
+        <v>1.89</v>
+      </c>
+      <c r="AC102">
+        <v>3</v>
+      </c>
+      <c r="AD102">
+        <v>1.33</v>
+      </c>
+      <c r="AE102">
+        <v>1.04</v>
+      </c>
+      <c r="AF102">
+        <v>1.85</v>
+      </c>
+      <c r="AG102">
+        <v>1.85</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
         <v>1.17</v>
       </c>
-      <c r="X102">
-        <v>1.02</v>
-      </c>
-      <c r="Y102">
-        <v>1.12</v>
-      </c>
-      <c r="Z102">
-        <v>4.75</v>
-      </c>
-      <c r="AA102">
-        <v>1.53</v>
-      </c>
-      <c r="AB102">
-        <v>2.4</v>
-      </c>
-      <c r="AC102">
-        <v>2.3</v>
-      </c>
-      <c r="AD102">
-        <v>1.62</v>
-      </c>
-      <c r="AE102">
-        <v>1.25</v>
-      </c>
-      <c r="AF102">
-        <v>1.44</v>
-      </c>
-      <c r="AG102">
-        <v>2.63</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.26</v>
-      </c>
       <c r="AK102">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17270,10 +17270,10 @@
         <v>2.15</v>
       </c>
       <c r="Q104">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="R104">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="S104">
         <v>1.26</v>
@@ -17282,7 +17282,7 @@
         <v>3.32</v>
       </c>
       <c r="U104">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V104">
         <v>1.5</v>
@@ -17291,19 +17291,19 @@
         <v>1.13</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z104">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AA104">
         <v>1.64</v>
       </c>
       <c r="AB104">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AC104">
         <v>2.6</v>
@@ -17318,7 +17318,7 @@
         <v>1.53</v>
       </c>
       <c r="AG104">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
         <v>1.35</v>
@@ -17436,31 +17436,31 @@
         <v>1.83</v>
       </c>
       <c r="R105">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="S105">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T105">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U105">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V105">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X105">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z105">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA105">
         <v>1.44</v>
@@ -17478,10 +17478,10 @@
         <v>1.2</v>
       </c>
       <c r="AF105">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG105">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK105">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>3.5</v>
       </c>
       <c r="Q106">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="R106">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S106">
         <v>1.3</v>
       </c>
       <c r="T106">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U106">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V106">
         <v>1.5</v>
       </c>
       <c r="W106">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X106">
         <v>1.05</v>
       </c>
       <c r="Y106">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z106">
         <v>4.2</v>
       </c>
       <c r="AA106">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB106">
         <v>2.1</v>
       </c>
       <c r="AC106">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD106">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE106">
         <v>1.12</v>
       </c>
       <c r="AF106">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AG106">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17759,13 +17759,13 @@
         <v>6.95</v>
       </c>
       <c r="Q107">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R107">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="S107">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T107">
         <v>3.58</v>
@@ -17783,31 +17783,31 @@
         <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z107">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA107">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB107">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AC107">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AD107">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE107">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF107">
         <v>1.67</v>
       </c>
       <c r="AG107">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>1.13</v>
       </c>
       <c r="AK107">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18239,46 +18239,46 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="O110">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P110">
-        <v>4.67</v>
+        <v>5.1</v>
       </c>
       <c r="Q110">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R110">
         <v>2</v>
       </c>
       <c r="S110">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T110">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U110">
         <v>3.3</v>
       </c>
       <c r="V110">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X110">
         <v>1.05</v>
       </c>
       <c r="Y110">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z110">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AA110">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB110">
         <v>1.59</v>
@@ -18290,10 +18290,10 @@
         <v>1.18</v>
       </c>
       <c r="AE110">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF110">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG110">
         <v>1.75</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,19 +18402,19 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="O111">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P111">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="Q111">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R111">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S111">
         <v>1.44</v>
@@ -18423,7 +18423,7 @@
         <v>2.59</v>
       </c>
       <c r="U111">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="V111">
         <v>1.36</v>
@@ -18438,19 +18438,19 @@
         <v>1.28</v>
       </c>
       <c r="Z111">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA111">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB111">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC111">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AD111">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE111">
         <v>1.05</v>
@@ -18459,7 +18459,7 @@
         <v>1.75</v>
       </c>
       <c r="AG111">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK111">
         <v>1.36</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O112">
         <v>3.2</v>
       </c>
       <c r="P112">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q112">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R112">
         <v>2.05</v>
       </c>
       <c r="S112">
+        <v>1.4</v>
+      </c>
+      <c r="T112">
+        <v>2.9</v>
+      </c>
+      <c r="U112">
+        <v>2.75</v>
+      </c>
+      <c r="V112">
         <v>1.39</v>
-      </c>
-      <c r="T112">
-        <v>2.77</v>
-      </c>
-      <c r="U112">
-        <v>2.93</v>
-      </c>
-      <c r="V112">
-        <v>1.38</v>
       </c>
       <c r="W112">
         <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z112">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA112">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB112">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC112">
         <v>3.24</v>
       </c>
       <c r="AD112">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE112">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF112">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG112">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18891,10 +18891,10 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O114">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="P114">
         <v>5.25</v>
@@ -18927,7 +18927,7 @@
         <v>1.14</v>
       </c>
       <c r="Z114">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA114">
         <v>1.57</v>
@@ -18948,7 +18948,7 @@
         <v>1.62</v>
       </c>
       <c r="AG114">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G126">
@@ -21010,52 +21010,52 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="O127">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P127">
         <v>2.62</v>
       </c>
       <c r="Q127">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R127">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S127">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T127">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="U127">
         <v>3.04</v>
       </c>
       <c r="V127">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W127">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X127">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y127">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z127">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="AA127">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AB127">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC127">
-        <v>4.03</v>
+        <v>3.9</v>
       </c>
       <c r="AD127">
         <v>1.24</v>
@@ -21067,7 +21067,7 @@
         <v>1.85</v>
       </c>
       <c r="AG127">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK127">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22323,22 +22323,22 @@
         <v>3.4</v>
       </c>
       <c r="Q135">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R135">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="S135">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T135">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="U135">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="V135">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W135">
         <v>1.03</v>
@@ -22347,31 +22347,31 @@
         <v>1.09</v>
       </c>
       <c r="Y135">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="Z135">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AA135">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AB135">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC135">
-        <v>5.6</v>
+        <v>6.38</v>
       </c>
       <c r="AD135">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE135">
         <v>1.02</v>
       </c>
       <c r="AF135">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG135">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK135">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22477,37 +22477,37 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="O136">
         <v>3.5</v>
       </c>
       <c r="P136">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q136">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="R136">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S136">
         <v>1.24</v>
       </c>
       <c r="T136">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U136">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="V136">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W136">
         <v>1.11</v>
       </c>
       <c r="X136">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
         <v>1.18</v>
@@ -22519,7 +22519,7 @@
         <v>1.6</v>
       </c>
       <c r="AB136">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC136">
         <v>2.43</v>
@@ -22531,10 +22531,10 @@
         <v>1.14</v>
       </c>
       <c r="AF136">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG136">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK136">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22649,25 +22649,25 @@
         <v>3.65</v>
       </c>
       <c r="Q137">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R137">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S137">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T137">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="U137">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V137">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W137">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X137">
         <v>1.04</v>
@@ -22679,13 +22679,13 @@
         <v>3.72</v>
       </c>
       <c r="AA137">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB137">
         <v>2</v>
       </c>
       <c r="AC137">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AD137">
         <v>1.32</v>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK137">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AL137">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,65 +12045,65 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.05</v>
+        <v>2.31</v>
       </c>
       <c r="O72">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P72">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q72">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="R72">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="S72">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="T72">
-        <v>2.94</v>
+        <v>2.43</v>
       </c>
       <c r="U72">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="V72">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="W72">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="Z72">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="AA72">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AB72">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AC72">
-        <v>3.25</v>
+        <v>4.25</v>
       </c>
       <c r="AD72">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AE72">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF72">
+        <v>2</v>
+      </c>
+      <c r="AG72">
         <v>1.7</v>
       </c>
-      <c r="AG72">
-        <v>2.05</v>
-      </c>
       <c r="AH72" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK72">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,80 +12208,80 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="O73">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="P73">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q73">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="R73">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S73">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="T73">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="U73">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="V73">
+        <v>1.36</v>
+      </c>
+      <c r="W73">
+        <v>1.08</v>
+      </c>
+      <c r="X73">
+        <v>1</v>
+      </c>
+      <c r="Y73">
+        <v>1.25</v>
+      </c>
+      <c r="Z73">
+        <v>3.3</v>
+      </c>
+      <c r="AA73">
+        <v>1.92</v>
+      </c>
+      <c r="AB73">
+        <v>1.74</v>
+      </c>
+      <c r="AC73">
+        <v>3.18</v>
+      </c>
+      <c r="AD73">
+        <v>1.25</v>
+      </c>
+      <c r="AE73">
+        <v>1.09</v>
+      </c>
+      <c r="AF73">
+        <v>1.78</v>
+      </c>
+      <c r="AG73">
+        <v>1.91</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
         <v>1.3</v>
       </c>
-      <c r="W73">
-        <v>1.05</v>
-      </c>
-      <c r="X73">
-        <v>1.04</v>
-      </c>
-      <c r="Y73">
-        <v>1.44</v>
-      </c>
-      <c r="Z73">
-        <v>2.72</v>
-      </c>
-      <c r="AA73">
-        <v>2.35</v>
-      </c>
-      <c r="AB73">
-        <v>1.57</v>
-      </c>
-      <c r="AC73">
-        <v>4.25</v>
-      </c>
-      <c r="AD73">
-        <v>1.17</v>
-      </c>
-      <c r="AE73">
-        <v>1.01</v>
-      </c>
-      <c r="AF73">
-        <v>2</v>
-      </c>
-      <c r="AG73">
-        <v>1.7</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.33</v>
-      </c>
       <c r="AK73">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.03</v>
+        <v>3.05</v>
       </c>
       <c r="O74">
+        <v>3.4</v>
+      </c>
+      <c r="P74">
+        <v>2.15</v>
+      </c>
+      <c r="Q74">
         <v>3.45</v>
       </c>
-      <c r="P74">
-        <v>3.45</v>
-      </c>
-      <c r="Q74">
-        <v>2.67</v>
-      </c>
       <c r="R74">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S74">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T74">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="U74">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V74">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z74">
         <v>3.3</v>
       </c>
       <c r="AA74">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AB74">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="AC74">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AD74">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE74">
         <v>1.09</v>
       </c>
       <c r="AF74">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG74">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
+        <v>1.29</v>
+      </c>
+      <c r="AK74">
         <v>1.3</v>
-      </c>
-      <c r="AK74">
-        <v>1.75</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="O84">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="P84">
-        <v>2.45</v>
+        <v>5.25</v>
       </c>
       <c r="Q84">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="R84">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="S84">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T84">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="U84">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="V84">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="W84">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X84">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z84">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA84">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AB84">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="AC84">
-        <v>2.14</v>
+        <v>1.78</v>
       </c>
       <c r="AD84">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AE84">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AF84">
         <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.28</v>
+        <v>3.4</v>
       </c>
       <c r="O85">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="P85">
-        <v>8.75</v>
+        <v>1.9</v>
       </c>
       <c r="Q85">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="R85">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V85">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="W85">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z85">
-        <v>6.15</v>
+        <v>5.75</v>
       </c>
       <c r="AA85">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AC85">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AD85">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AE85">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AF85">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AG85">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="O86">
-        <v>5.1</v>
+        <v>4.05</v>
       </c>
       <c r="P86">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="Q86">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="R86">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="S86">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T86">
-        <v>5.1</v>
+        <v>4.25</v>
       </c>
       <c r="U86">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="V86">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="W86">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z86">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA86">
+        <v>1.27</v>
+      </c>
+      <c r="AB86">
+        <v>3.05</v>
+      </c>
+      <c r="AC86">
+        <v>1.8</v>
+      </c>
+      <c r="AD86">
+        <v>1.95</v>
+      </c>
+      <c r="AE86">
+        <v>1.39</v>
+      </c>
+      <c r="AF86">
         <v>1.28</v>
       </c>
-      <c r="AB86">
-        <v>3.2</v>
-      </c>
-      <c r="AC86">
-        <v>1.78</v>
-      </c>
-      <c r="AD86">
-        <v>1.89</v>
-      </c>
-      <c r="AE86">
-        <v>1.45</v>
-      </c>
-      <c r="AF86">
-        <v>1.4</v>
-      </c>
       <c r="AG86">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK86">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,34 +14490,34 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="O87">
-        <v>4.05</v>
+        <v>5.25</v>
       </c>
       <c r="P87">
-        <v>2.85</v>
+        <v>8.75</v>
       </c>
       <c r="Q87">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="R87">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="S87">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T87">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="U87">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="V87">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="W87">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14526,28 +14526,28 @@
         <v>1.07</v>
       </c>
       <c r="Z87">
-        <v>7.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA87">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AB87">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC87">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AD87">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AE87">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AF87">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AG87">
-        <v>2.95</v>
+        <v>2.11</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK87">
-        <v>1.73</v>
+        <v>3.4</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,19 +14653,19 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="O88">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P88">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q88">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R88">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S88">
         <v>1.2</v>
@@ -14674,43 +14674,43 @@
         <v>4</v>
       </c>
       <c r="U88">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V88">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W88">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z88">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA88">
         <v>1.44</v>
       </c>
       <c r="AB88">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AC88">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AD88">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE88">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF88">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG88">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK88">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O99">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P99">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="Q99">
-        <v>2.91</v>
+        <v>4.42</v>
       </c>
       <c r="R99">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="S99">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T99">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U99">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="V99">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W99">
         <v>1.08</v>
       </c>
       <c r="X99">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z99">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA99">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB99">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AC99">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD99">
+        <v>1.4</v>
+      </c>
+      <c r="AE99">
+        <v>1.15</v>
+      </c>
+      <c r="AF99">
+        <v>1.62</v>
+      </c>
+      <c r="AG99">
+        <v>2.1</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.25</v>
       </c>
-      <c r="AE99">
-        <v>1.05</v>
-      </c>
-      <c r="AF99">
-        <v>1.74</v>
-      </c>
-      <c r="AG99">
-        <v>1.95</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.38</v>
-      </c>
       <c r="AK99">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.37</v>
+        <v>1.7</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P100">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q100">
+        <v>2.23</v>
+      </c>
+      <c r="R100">
+        <v>2.08</v>
+      </c>
+      <c r="S100">
+        <v>1.36</v>
+      </c>
+      <c r="T100">
         <v>2.88</v>
       </c>
-      <c r="R100">
-        <v>2.4</v>
-      </c>
-      <c r="S100">
-        <v>1.26</v>
-      </c>
-      <c r="T100">
-        <v>3.34</v>
-      </c>
       <c r="U100">
-        <v>2.15</v>
+        <v>2.98</v>
       </c>
       <c r="V100">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="W100">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X100">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="Z100">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="AA100">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AB100">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="AC100">
-        <v>2.27</v>
+        <v>3</v>
       </c>
       <c r="AD100">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AE100">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AF100">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AG100">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK100">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="O101">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q101">
-        <v>4.42</v>
+        <v>2.91</v>
       </c>
       <c r="R101">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="S101">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T101">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="U101">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="V101">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W101">
         <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y101">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z101">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA101">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB101">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AC101">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD101">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AE101">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AF101">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG101">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK101">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="O102">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q102">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="R102">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="S102">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T102">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="U102">
-        <v>2.98</v>
+        <v>2.15</v>
       </c>
       <c r="V102">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="Z102">
-        <v>3.65</v>
+        <v>4.75</v>
       </c>
       <c r="AA102">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="AB102">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="AC102">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="AD102">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AE102">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AF102">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AG102">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK102">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -21019,10 +21019,10 @@
         <v>2.62</v>
       </c>
       <c r="Q127">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R127">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S127">
         <v>1.4</v>
@@ -21040,7 +21040,7 @@
         <v>1.04</v>
       </c>
       <c r="X127">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y127">
         <v>1.36</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="O3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
         <v>2.35</v>
       </c>
       <c r="Q3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R3">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="U3">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
+        <v>1.04</v>
+      </c>
+      <c r="X3">
         <v>1.07</v>
       </c>
-      <c r="X3">
-        <v>1.04</v>
-      </c>
       <c r="Y3">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AA3">
         <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AC3">
         <v>3.62</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
         <v>1.36</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.24</v>
+        <v>3.7</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="Q4">
         <v>4.2</v>
@@ -976,10 +976,10 @@
         <v>2.22</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T4">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="U4">
         <v>2.53</v>
@@ -988,31 +988,31 @@
         <v>1.46</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z4">
-        <v>4.12</v>
+        <v>3.82</v>
       </c>
       <c r="AA4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC4">
         <v>3</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
         <v>1.66</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.91</v>
       </c>
       <c r="AK4">
         <v>1.22</v>
@@ -2274,19 +2274,19 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
         <v>1.44</v>
@@ -2304,10 +2304,10 @@
         <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
         <v>3.16</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
         <v>2</v>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-09-11 10:40:00</t>
+          <t>2026-09-11 10:30:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hatta</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Hatta</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-11 11:00:00</t>
+          <t>2026-09-11 10:40:00</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4016,22 +4016,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lusail City</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Lusail City</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-09-11 11:30:00</t>
+          <t>2026-09-11 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4565,13 +4565,13 @@
         <v>1.22</v>
       </c>
       <c r="T26">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="U26">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W26">
         <v>1.13</v>
@@ -4589,7 +4589,7 @@
         <v>1.47</v>
       </c>
       <c r="AB26">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC26">
         <v>2.25</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="O28">
-        <v>3.66</v>
+        <v>3.51</v>
       </c>
       <c r="P28">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="Q28">
         <v>2.48</v>
@@ -4894,7 +4894,7 @@
         <v>3.08</v>
       </c>
       <c r="U28">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
         <v>1.48</v>
@@ -4915,7 +4915,7 @@
         <v>1.81</v>
       </c>
       <c r="AB28">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AC28">
         <v>2.96</v>
@@ -4930,7 +4930,7 @@
         <v>1.63</v>
       </c>
       <c r="AG28">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         <v>2.13</v>
       </c>
       <c r="O29">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="P29">
-        <v>2.8</v>
+        <v>3.29</v>
       </c>
       <c r="Q29">
         <v>3</v>
@@ -5051,10 +5051,10 @@
         <v>2.01</v>
       </c>
       <c r="S29">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U29">
         <v>2.7</v>
@@ -5066,34 +5066,34 @@
         <v>1.02</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z29">
         <v>3.1</v>
       </c>
       <c r="AA29">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC29">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD29">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE29">
         <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5365,61 +5365,61 @@
         <v>1.23</v>
       </c>
       <c r="O31">
-        <v>6.37</v>
+        <v>6.63</v>
       </c>
       <c r="P31">
-        <v>7.86</v>
+        <v>9.35</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
+        <v>3.75</v>
+      </c>
+      <c r="O32">
         <v>4</v>
       </c>
-      <c r="O32">
-        <v>4.2</v>
-      </c>
       <c r="P32">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -6524,10 +6524,10 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
         <v>0</v>
@@ -6542,25 +6542,25 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         <v>3.35</v>
       </c>
       <c r="P42">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="Q42">
         <v>2.8</v>
@@ -7194,7 +7194,7 @@
         <v>3.7</v>
       </c>
       <c r="AA42">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB42">
         <v>1.9</v>
@@ -7206,10 +7206,10 @@
         <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
         <v>2.15</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7330,19 +7330,19 @@
         <v>2.45</v>
       </c>
       <c r="R43">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T43">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="U43">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V43">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W43">
         <v>1.11</v>
@@ -7351,13 +7351,13 @@
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z43">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AA43">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB43">
         <v>2</v>
@@ -7369,13 +7369,13 @@
         <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
         <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7496,25 +7496,25 @@
         <v>2.5</v>
       </c>
       <c r="S44">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="U44">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V44">
         <v>1.68</v>
       </c>
       <c r="W44">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z44">
         <v>6</v>
@@ -7523,10 +7523,10 @@
         <v>1.4</v>
       </c>
       <c r="AB44">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC44">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AD44">
         <v>1.7</v>
@@ -7535,7 +7535,7 @@
         <v>1.28</v>
       </c>
       <c r="AF44">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG44">
         <v>2.5</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK44">
         <v>2.14</v>
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O51">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P51">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q51">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R51">
         <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T51">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="U51">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V51">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8658,19 +8658,19 @@
         <v>1.36</v>
       </c>
       <c r="Z51">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA51">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AB51">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC51">
         <v>4</v>
       </c>
       <c r="AD51">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
@@ -8679,7 +8679,7 @@
         <v>1.9</v>
       </c>
       <c r="AG51">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -9440,46 +9440,46 @@
         <v>1.57</v>
       </c>
       <c r="O56">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P56">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="Q56">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="R56">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S56">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="U56">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V56">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X56">
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>5</v>
+        <v>5.22</v>
       </c>
       <c r="AA56">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB56">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
         <v>2.27</v>
@@ -9488,13 +9488,13 @@
         <v>1.57</v>
       </c>
       <c r="AE56">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG56">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK56">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O57">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P57">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q57">
         <v>3</v>
@@ -9615,28 +9615,28 @@
         <v>2</v>
       </c>
       <c r="S57">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T57">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U57">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="V57">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W57">
         <v>1.02</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y57">
         <v>1.32</v>
       </c>
       <c r="Z57">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="AA57">
         <v>2.13</v>
@@ -9645,19 +9645,19 @@
         <v>1.65</v>
       </c>
       <c r="AC57">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="AD57">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE57">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF57">
         <v>2</v>
       </c>
       <c r="AG57">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK57">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,22 +9763,22 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="O58">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="P58">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Q58">
         <v>1.64</v>
       </c>
       <c r="R58">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T58">
         <v>3.58</v>
@@ -9787,13 +9787,13 @@
         <v>2.2</v>
       </c>
       <c r="V58">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W58">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
         <v>1.15</v>
@@ -9802,25 +9802,25 @@
         <v>5</v>
       </c>
       <c r="AA58">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB58">
         <v>2.39</v>
       </c>
       <c r="AC58">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD58">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE58">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF58">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG58">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>2.63</v>
       </c>
       <c r="R59">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S59">
         <v>1.36</v>
@@ -9956,7 +9956,7 @@
         <v>1.08</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y59">
         <v>1.24</v>
@@ -9968,7 +9968,7 @@
         <v>1.88</v>
       </c>
       <c r="AB59">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC59">
         <v>3.08</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="O62">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P62">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q62">
-        <v>4.27</v>
+        <v>5.02</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S62">
         <v>1.25</v>
@@ -10439,40 +10439,40 @@
         <v>2.2</v>
       </c>
       <c r="V62">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X62">
         <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z62">
-        <v>5.25</v>
+        <v>5.65</v>
       </c>
       <c r="AA62">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB62">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AC62">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD62">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE62">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF62">
         <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="O63">
         <v>3.6</v>
       </c>
       <c r="P63">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S63">
         <v>0</v>
@@ -10599,10 +10599,10 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
         <v>0</v>
@@ -10611,31 +10611,31 @@
         <v>0</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE63">
         <v>0</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,16 +10750,16 @@
         <v>2</v>
       </c>
       <c r="Q64">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R64">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="S64">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T64">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U64">
         <v>2.13</v>
@@ -10768,22 +10768,22 @@
         <v>1.63</v>
       </c>
       <c r="W64">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z64">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="AA64">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB64">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC64">
         <v>2.12</v>
@@ -10792,7 +10792,7 @@
         <v>1.64</v>
       </c>
       <c r="AE64">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF64">
         <v>1.44</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK64">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.42</v>
+        <v>3.5</v>
       </c>
       <c r="O65">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
-        <v>5.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q65">
-        <v>2.02</v>
+        <v>3.7</v>
       </c>
       <c r="R65">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="S65">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="U65">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V65">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z65">
-        <v>5.25</v>
+        <v>4.97</v>
       </c>
       <c r="AA65">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB65">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AC65">
-        <v>2.02</v>
+        <v>2.31</v>
       </c>
       <c r="AD65">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AE65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF65">
         <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.5</v>
+        <v>1.42</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P66">
-        <v>1.84</v>
+        <v>5.75</v>
       </c>
       <c r="Q66">
-        <v>3.35</v>
+        <v>2.02</v>
       </c>
       <c r="R66">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T66">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="U66">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="V66">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="W66">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z66">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA66">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB66">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AC66">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AD66">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE66">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AF66">
         <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.77</v>
+        <v>1.09</v>
       </c>
       <c r="AK66">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="O72">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="P72">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="Q72">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="R72">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S72">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="T72">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="U72">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="V72">
+        <v>1.36</v>
+      </c>
+      <c r="W72">
+        <v>1.08</v>
+      </c>
+      <c r="X72">
+        <v>1</v>
+      </c>
+      <c r="Y72">
+        <v>1.25</v>
+      </c>
+      <c r="Z72">
+        <v>3.3</v>
+      </c>
+      <c r="AA72">
+        <v>1.92</v>
+      </c>
+      <c r="AB72">
+        <v>1.74</v>
+      </c>
+      <c r="AC72">
+        <v>3.18</v>
+      </c>
+      <c r="AD72">
+        <v>1.25</v>
+      </c>
+      <c r="AE72">
+        <v>1.09</v>
+      </c>
+      <c r="AF72">
+        <v>1.78</v>
+      </c>
+      <c r="AG72">
+        <v>1.91</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
         <v>1.3</v>
       </c>
-      <c r="W72">
-        <v>1.05</v>
-      </c>
-      <c r="X72">
-        <v>1.04</v>
-      </c>
-      <c r="Y72">
-        <v>1.44</v>
-      </c>
-      <c r="Z72">
-        <v>2.72</v>
-      </c>
-      <c r="AA72">
-        <v>2.35</v>
-      </c>
-      <c r="AB72">
-        <v>1.57</v>
-      </c>
-      <c r="AC72">
-        <v>4.25</v>
-      </c>
-      <c r="AD72">
-        <v>1.17</v>
-      </c>
-      <c r="AE72">
-        <v>1.01</v>
-      </c>
-      <c r="AF72">
-        <v>2</v>
-      </c>
-      <c r="AG72">
-        <v>1.7</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.33</v>
-      </c>
       <c r="AK72">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.03</v>
+        <v>2.31</v>
       </c>
       <c r="O73">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="P73">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q73">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="R73">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S73">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="T73">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="U73">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="V73">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z73">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="AA73">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AB73">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC73">
-        <v>3.18</v>
+        <v>4.25</v>
       </c>
       <c r="AD73">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE73">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF73">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG73">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK73">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>4.58</v>
+        <v>5.33</v>
       </c>
       <c r="O77">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="P77">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB77">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -13023,61 +13023,61 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O78">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P78">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q78">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S78">
         <v>1.36</v>
       </c>
       <c r="T78">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="U78">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="V78">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W78">
         <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y78">
         <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA78">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB78">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AC78">
         <v>3.08</v>
       </c>
       <c r="AD78">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE78">
         <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG78">
         <v>2.05</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13349,19 +13349,19 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="O80">
-        <v>9.25</v>
+        <v>8.5</v>
       </c>
       <c r="P80">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q80">
         <v>1.37</v>
       </c>
       <c r="R80">
-        <v>3.42</v>
+        <v>3.29</v>
       </c>
       <c r="S80">
         <v>1.12</v>
@@ -13373,7 +13373,7 @@
         <v>1.8</v>
       </c>
       <c r="V80">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="W80">
         <v>1.25</v>
@@ -13382,25 +13382,25 @@
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z80">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA80">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB80">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AC80">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AD80">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE80">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AF80">
         <v>1.83</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AK80">
         <v>5</v>
@@ -13515,16 +13515,16 @@
         <v>2.3</v>
       </c>
       <c r="O81">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
         <v>2.45</v>
       </c>
       <c r="Q81">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="R81">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
         <v>1.25</v>
@@ -13533,16 +13533,16 @@
         <v>3.36</v>
       </c>
       <c r="U81">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V81">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W81">
         <v>1.13</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
         <v>1.12</v>
@@ -13551,22 +13551,22 @@
         <v>4.75</v>
       </c>
       <c r="AA81">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB81">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC81">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AD81">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE81">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF81">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG81">
         <v>2.63</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK81">
         <v>1.47</v>
@@ -13684,7 +13684,7 @@
         <v>3.6</v>
       </c>
       <c r="Q82">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R82">
         <v>2.6</v>
@@ -13693,22 +13693,22 @@
         <v>1.2</v>
       </c>
       <c r="T82">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U82">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V82">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W82">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X82">
         <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z82">
         <v>5.75</v>
@@ -13720,13 +13720,13 @@
         <v>2.7</v>
       </c>
       <c r="AC82">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD82">
         <v>1.73</v>
       </c>
       <c r="AE82">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF82">
         <v>1.4</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="O83">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P83">
         <v>2.03</v>
@@ -13853,16 +13853,16 @@
         <v>2.39</v>
       </c>
       <c r="S83">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T83">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="U83">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="V83">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W83">
         <v>1.17</v>
@@ -13871,16 +13871,16 @@
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z83">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA83">
         <v>1.4</v>
       </c>
       <c r="AB83">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC83">
         <v>2.05</v>
@@ -13892,7 +13892,7 @@
         <v>1.27</v>
       </c>
       <c r="AF83">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG83">
         <v>2.8</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="O84">
-        <v>5.1</v>
+        <v>4.05</v>
       </c>
       <c r="P84">
-        <v>5.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q84">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="R84">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="S84">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T84">
-        <v>5.1</v>
+        <v>4.25</v>
       </c>
       <c r="U84">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="V84">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="W84">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z84">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA84">
+        <v>1.3</v>
+      </c>
+      <c r="AB84">
+        <v>3.4</v>
+      </c>
+      <c r="AC84">
+        <v>1.8</v>
+      </c>
+      <c r="AD84">
+        <v>1.95</v>
+      </c>
+      <c r="AE84">
+        <v>1.38</v>
+      </c>
+      <c r="AF84">
         <v>1.28</v>
       </c>
-      <c r="AB84">
-        <v>3.2</v>
-      </c>
-      <c r="AC84">
-        <v>1.78</v>
-      </c>
-      <c r="AD84">
-        <v>1.89</v>
-      </c>
-      <c r="AE84">
-        <v>1.45</v>
-      </c>
-      <c r="AF84">
-        <v>1.4</v>
-      </c>
       <c r="AG84">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK84">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
+        <v>1.19</v>
+      </c>
+      <c r="O85">
+        <v>5.25</v>
+      </c>
+      <c r="P85">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="Q85">
+        <v>1.69</v>
+      </c>
+      <c r="R85">
+        <v>2.72</v>
+      </c>
+      <c r="S85">
+        <v>1.17</v>
+      </c>
+      <c r="T85">
+        <v>4.5</v>
+      </c>
+      <c r="U85">
+        <v>1.97</v>
+      </c>
+      <c r="V85">
+        <v>1.77</v>
+      </c>
+      <c r="W85">
+        <v>1.2</v>
+      </c>
+      <c r="X85">
+        <v>1.01</v>
+      </c>
+      <c r="Y85">
+        <v>1.1</v>
+      </c>
+      <c r="Z85">
+        <v>6.2</v>
+      </c>
+      <c r="AA85">
+        <v>1.36</v>
+      </c>
+      <c r="AB85">
+        <v>3.1</v>
+      </c>
+      <c r="AC85">
+        <v>1.89</v>
+      </c>
+      <c r="AD85">
+        <v>1.8</v>
+      </c>
+      <c r="AE85">
+        <v>1.33</v>
+      </c>
+      <c r="AF85">
+        <v>1.62</v>
+      </c>
+      <c r="AG85">
+        <v>2.2</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <v>1.14</v>
+      </c>
+      <c r="AK85">
         <v>3.4</v>
-      </c>
-      <c r="O85">
-        <v>3.75</v>
-      </c>
-      <c r="P85">
-        <v>1.9</v>
-      </c>
-      <c r="Q85">
-        <v>3.4</v>
-      </c>
-      <c r="R85">
-        <v>2.5</v>
-      </c>
-      <c r="S85">
-        <v>1.2</v>
-      </c>
-      <c r="T85">
-        <v>4</v>
-      </c>
-      <c r="U85">
-        <v>2.1</v>
-      </c>
-      <c r="V85">
-        <v>1.68</v>
-      </c>
-      <c r="W85">
-        <v>1.18</v>
-      </c>
-      <c r="X85">
-        <v>1.02</v>
-      </c>
-      <c r="Y85">
-        <v>1.09</v>
-      </c>
-      <c r="Z85">
-        <v>5.75</v>
-      </c>
-      <c r="AA85">
-        <v>1.44</v>
-      </c>
-      <c r="AB85">
-        <v>2.62</v>
-      </c>
-      <c r="AC85">
-        <v>2.1</v>
-      </c>
-      <c r="AD85">
-        <v>1.7</v>
-      </c>
-      <c r="AE85">
-        <v>1.27</v>
-      </c>
-      <c r="AF85">
-        <v>1.39</v>
-      </c>
-      <c r="AG85">
-        <v>2.8</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.21</v>
-      </c>
-      <c r="AK85">
-        <v>1.3</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="O86">
-        <v>4.05</v>
+        <v>5.1</v>
       </c>
       <c r="P86">
-        <v>2.85</v>
+        <v>5.25</v>
       </c>
       <c r="Q86">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="R86">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="S86">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T86">
-        <v>4.25</v>
+        <v>5.1</v>
       </c>
       <c r="U86">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="V86">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W86">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z86">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA86">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AB86">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AC86">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD86">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE86">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AF86">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK86">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.28</v>
+        <v>2.45</v>
       </c>
       <c r="O87">
-        <v>5.25</v>
+        <v>3.88</v>
       </c>
       <c r="P87">
-        <v>8.75</v>
+        <v>2.28</v>
       </c>
       <c r="Q87">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="R87">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="S87">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T87">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="U87">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="V87">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W87">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z87">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="AA87">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB87">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="AC87">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AD87">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AE87">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AF87">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AG87">
-        <v>2.11</v>
+        <v>2.75</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,61 +14653,61 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="O88">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P88">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="Q88">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R88">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="S88">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U88">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="V88">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W88">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z88">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA88">
         <v>1.44</v>
       </c>
       <c r="AB88">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AC88">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AD88">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE88">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF88">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG88">
         <v>2.75</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK88">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14988,40 +14988,40 @@
         <v>2.45</v>
       </c>
       <c r="Q90">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R90">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="S90">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T90">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U90">
         <v>2.2</v>
       </c>
       <c r="V90">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="W90">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X90">
         <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z90">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA90">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB90">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AC90">
         <v>2.29</v>
@@ -15030,7 +15030,7 @@
         <v>1.55</v>
       </c>
       <c r="AE90">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF90">
         <v>1.44</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK90">
         <v>1.41</v>
@@ -15803,22 +15803,22 @@
         <v>3</v>
       </c>
       <c r="Q95">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="R95">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T95">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="U95">
         <v>2.23</v>
       </c>
       <c r="V95">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W95">
         <v>1.13</v>
@@ -15827,31 +15827,31 @@
         <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z95">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA95">
         <v>1.61</v>
       </c>
       <c r="AB95">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AC95">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD95">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE95">
         <v>1.2</v>
       </c>
       <c r="AF95">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG95">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="O99">
         <v>3.7</v>
       </c>
       <c r="P99">
+        <v>4.2</v>
+      </c>
+      <c r="Q99">
+        <v>2.23</v>
+      </c>
+      <c r="R99">
+        <v>2.08</v>
+      </c>
+      <c r="S99">
+        <v>1.36</v>
+      </c>
+      <c r="T99">
+        <v>2.88</v>
+      </c>
+      <c r="U99">
+        <v>2.98</v>
+      </c>
+      <c r="V99">
+        <v>1.39</v>
+      </c>
+      <c r="W99">
+        <v>1.05</v>
+      </c>
+      <c r="X99">
+        <v>1.01</v>
+      </c>
+      <c r="Y99">
+        <v>1.32</v>
+      </c>
+      <c r="Z99">
+        <v>3.65</v>
+      </c>
+      <c r="AA99">
+        <v>1.98</v>
+      </c>
+      <c r="AB99">
+        <v>1.89</v>
+      </c>
+      <c r="AC99">
+        <v>3</v>
+      </c>
+      <c r="AD99">
+        <v>1.33</v>
+      </c>
+      <c r="AE99">
+        <v>1.04</v>
+      </c>
+      <c r="AF99">
         <v>1.85</v>
       </c>
-      <c r="Q99">
-        <v>4.42</v>
-      </c>
-      <c r="R99">
-        <v>2.42</v>
-      </c>
-      <c r="S99">
-        <v>1.3</v>
-      </c>
-      <c r="T99">
-        <v>3.15</v>
-      </c>
-      <c r="U99">
-        <v>2.4</v>
-      </c>
-      <c r="V99">
-        <v>1.49</v>
-      </c>
-      <c r="W99">
-        <v>1.08</v>
-      </c>
-      <c r="X99">
-        <v>1.04</v>
-      </c>
-      <c r="Y99">
-        <v>1.22</v>
-      </c>
-      <c r="Z99">
-        <v>4.2</v>
-      </c>
-      <c r="AA99">
-        <v>1.68</v>
-      </c>
-      <c r="AB99">
-        <v>2.14</v>
-      </c>
-      <c r="AC99">
-        <v>2.7</v>
-      </c>
-      <c r="AD99">
-        <v>1.4</v>
-      </c>
-      <c r="AE99">
-        <v>1.15</v>
-      </c>
-      <c r="AF99">
-        <v>1.62</v>
-      </c>
       <c r="AG99">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK99">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="O100">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P100">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q100">
-        <v>2.23</v>
+        <v>2.91</v>
       </c>
       <c r="R100">
         <v>2.08</v>
       </c>
       <c r="S100">
+        <v>1.38</v>
+      </c>
+      <c r="T100">
+        <v>2.9</v>
+      </c>
+      <c r="U100">
+        <v>2.95</v>
+      </c>
+      <c r="V100">
         <v>1.36</v>
       </c>
-      <c r="T100">
-        <v>2.88</v>
-      </c>
-      <c r="U100">
-        <v>2.98</v>
-      </c>
-      <c r="V100">
-        <v>1.39</v>
-      </c>
       <c r="W100">
+        <v>1.08</v>
+      </c>
+      <c r="X100">
+        <v>1.06</v>
+      </c>
+      <c r="Y100">
+        <v>1.31</v>
+      </c>
+      <c r="Z100">
+        <v>3.2</v>
+      </c>
+      <c r="AA100">
+        <v>1.95</v>
+      </c>
+      <c r="AB100">
+        <v>1.8</v>
+      </c>
+      <c r="AC100">
+        <v>3.25</v>
+      </c>
+      <c r="AD100">
+        <v>1.25</v>
+      </c>
+      <c r="AE100">
         <v>1.05</v>
       </c>
-      <c r="X100">
-        <v>1.01</v>
-      </c>
-      <c r="Y100">
-        <v>1.32</v>
-      </c>
-      <c r="Z100">
-        <v>3.65</v>
-      </c>
-      <c r="AA100">
-        <v>1.98</v>
-      </c>
-      <c r="AB100">
-        <v>1.89</v>
-      </c>
-      <c r="AC100">
-        <v>3</v>
-      </c>
-      <c r="AD100">
-        <v>1.33</v>
-      </c>
-      <c r="AE100">
-        <v>1.04</v>
-      </c>
       <c r="AF100">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AG100">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AK100">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,80 +16772,80 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="O101">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P101">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="Q101">
-        <v>2.91</v>
+        <v>4.42</v>
       </c>
       <c r="R101">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="S101">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U101">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="V101">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="W101">
         <v>1.08</v>
       </c>
       <c r="X101">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y101">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z101">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA101">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB101">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AC101">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD101">
+        <v>1.4</v>
+      </c>
+      <c r="AE101">
+        <v>1.15</v>
+      </c>
+      <c r="AF101">
+        <v>1.62</v>
+      </c>
+      <c r="AG101">
+        <v>2.1</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
         <v>1.25</v>
       </c>
-      <c r="AE101">
-        <v>1.05</v>
-      </c>
-      <c r="AF101">
-        <v>1.74</v>
-      </c>
-      <c r="AG101">
-        <v>1.95</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.38</v>
-      </c>
       <c r="AK101">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.75</v>
+        <v>1.38</v>
       </c>
       <c r="O104">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="P104">
-        <v>2.15</v>
+        <v>6.35</v>
       </c>
       <c r="Q104">
+        <v>1.83</v>
+      </c>
+      <c r="R104">
+        <v>2.5</v>
+      </c>
+      <c r="S104">
+        <v>1.27</v>
+      </c>
+      <c r="T104">
         <v>3.25</v>
       </c>
-      <c r="R104">
-        <v>2.16</v>
-      </c>
-      <c r="S104">
-        <v>1.26</v>
-      </c>
-      <c r="T104">
-        <v>3.32</v>
-      </c>
       <c r="U104">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V104">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W104">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X104">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z104">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AA104">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB104">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AC104">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AD104">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AE104">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF104">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG104">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK104">
-        <v>1.35</v>
+        <v>2.64</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="O105">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P105">
-        <v>6.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q105">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="R105">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="S105">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T105">
         <v>3.25</v>
       </c>
       <c r="U105">
+        <v>2.5</v>
+      </c>
+      <c r="V105">
+        <v>1.51</v>
+      </c>
+      <c r="W105">
+        <v>1.07</v>
+      </c>
+      <c r="X105">
+        <v>1.03</v>
+      </c>
+      <c r="Y105">
+        <v>1.2</v>
+      </c>
+      <c r="Z105">
+        <v>4.15</v>
+      </c>
+      <c r="AA105">
+        <v>1.65</v>
+      </c>
+      <c r="AB105">
+        <v>2.12</v>
+      </c>
+      <c r="AC105">
+        <v>2.7</v>
+      </c>
+      <c r="AD105">
+        <v>1.43</v>
+      </c>
+      <c r="AE105">
+        <v>1.18</v>
+      </c>
+      <c r="AF105">
+        <v>1.58</v>
+      </c>
+      <c r="AG105">
         <v>2.25</v>
-      </c>
-      <c r="V105">
-        <v>1.62</v>
-      </c>
-      <c r="W105">
-        <v>1.11</v>
-      </c>
-      <c r="X105">
-        <v>1.01</v>
-      </c>
-      <c r="Y105">
-        <v>1.18</v>
-      </c>
-      <c r="Z105">
-        <v>4.75</v>
-      </c>
-      <c r="AA105">
-        <v>1.44</v>
-      </c>
-      <c r="AB105">
-        <v>2.45</v>
-      </c>
-      <c r="AC105">
-        <v>2.1</v>
-      </c>
-      <c r="AD105">
-        <v>1.49</v>
-      </c>
-      <c r="AE105">
-        <v>1.2</v>
-      </c>
-      <c r="AF105">
-        <v>1.75</v>
-      </c>
-      <c r="AG105">
-        <v>1.97</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.2</v>
       </c>
       <c r="AK105">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,65 +17587,65 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.93</v>
+        <v>1.32</v>
       </c>
       <c r="O106">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P106">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="Q106">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="R106">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S106">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T106">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="U106">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V106">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W106">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X106">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z106">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA106">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AB106">
+        <v>2.63</v>
+      </c>
+      <c r="AC106">
+        <v>2.16</v>
+      </c>
+      <c r="AD106">
+        <v>1.62</v>
+      </c>
+      <c r="AE106">
+        <v>1.25</v>
+      </c>
+      <c r="AF106">
+        <v>1.65</v>
+      </c>
+      <c r="AG106">
         <v>2.1</v>
       </c>
-      <c r="AC106">
-        <v>2.7</v>
-      </c>
-      <c r="AD106">
-        <v>1.45</v>
-      </c>
-      <c r="AE106">
-        <v>1.12</v>
-      </c>
-      <c r="AF106">
-        <v>1.58</v>
-      </c>
-      <c r="AG106">
-        <v>2.25</v>
-      </c>
       <c r="AH106" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AK106">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.32</v>
+        <v>2.75</v>
       </c>
       <c r="O107">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P107">
-        <v>6.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q107">
-        <v>1.77</v>
+        <v>3.25</v>
       </c>
       <c r="R107">
+        <v>2.36</v>
+      </c>
+      <c r="S107">
+        <v>1.26</v>
+      </c>
+      <c r="T107">
+        <v>3.32</v>
+      </c>
+      <c r="U107">
+        <v>2.41</v>
+      </c>
+      <c r="V107">
+        <v>1.47</v>
+      </c>
+      <c r="W107">
+        <v>1.07</v>
+      </c>
+      <c r="X107">
+        <v>1.03</v>
+      </c>
+      <c r="Y107">
+        <v>1.2</v>
+      </c>
+      <c r="Z107">
+        <v>4.2</v>
+      </c>
+      <c r="AA107">
+        <v>1.64</v>
+      </c>
+      <c r="AB107">
+        <v>2.12</v>
+      </c>
+      <c r="AC107">
         <v>2.6</v>
       </c>
-      <c r="S107">
+      <c r="AD107">
+        <v>1.44</v>
+      </c>
+      <c r="AE107">
+        <v>1.17</v>
+      </c>
+      <c r="AF107">
+        <v>1.55</v>
+      </c>
+      <c r="AG107">
+        <v>2.3</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.21</v>
       </c>
-      <c r="T107">
-        <v>3.58</v>
-      </c>
-      <c r="U107">
-        <v>2.15</v>
-      </c>
-      <c r="V107">
-        <v>1.62</v>
-      </c>
-      <c r="W107">
-        <v>1.17</v>
-      </c>
-      <c r="X107">
-        <v>1.02</v>
-      </c>
-      <c r="Y107">
-        <v>1.13</v>
-      </c>
-      <c r="Z107">
-        <v>5.5</v>
-      </c>
-      <c r="AA107">
-        <v>1.44</v>
-      </c>
-      <c r="AB107">
-        <v>2.63</v>
-      </c>
-      <c r="AC107">
-        <v>2.28</v>
-      </c>
-      <c r="AD107">
-        <v>1.62</v>
-      </c>
-      <c r="AE107">
-        <v>1.25</v>
-      </c>
-      <c r="AF107">
-        <v>1.67</v>
-      </c>
-      <c r="AG107">
-        <v>2.05</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.13</v>
-      </c>
       <c r="AK107">
-        <v>3.1</v>
+        <v>1.35</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17916,40 +17916,40 @@
         <v>2.85</v>
       </c>
       <c r="O108">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q108">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="R108">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S108">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T108">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U108">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V108">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W108">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
         <v>1.25</v>
       </c>
       <c r="Z108">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA108">
         <v>1.8</v>
@@ -17961,13 +17961,13 @@
         <v>2.9</v>
       </c>
       <c r="AD108">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE108">
         <v>1.09</v>
       </c>
       <c r="AF108">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG108">
         <v>2.2</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK108">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18115,10 +18115,10 @@
         <v>0</v>
       </c>
       <c r="AA109">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB109">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC109">
         <v>0</v>
@@ -18242,28 +18242,28 @@
         <v>1.68</v>
       </c>
       <c r="O110">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P110">
-        <v>5.1</v>
+        <v>5.19</v>
       </c>
       <c r="Q110">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R110">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S110">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T110">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U110">
         <v>3.3</v>
       </c>
       <c r="V110">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W110">
         <v>1.03</v>
@@ -18272,19 +18272,19 @@
         <v>1.05</v>
       </c>
       <c r="Y110">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z110">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AA110">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB110">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC110">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
       <c r="AD110">
         <v>1.18</v>
@@ -18296,7 +18296,7 @@
         <v>2</v>
       </c>
       <c r="AG110">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK110">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="O111">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P111">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q111">
         <v>3.2</v>
@@ -18417,10 +18417,10 @@
         <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T111">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U111">
         <v>3.07</v>
@@ -18435,31 +18435,31 @@
         <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z111">
         <v>3.1</v>
       </c>
       <c r="AA111">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB111">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC111">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="AD111">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE111">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF111">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG111">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK111">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18897,58 +18897,58 @@
         <v>4.05</v>
       </c>
       <c r="P114">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q114">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="R114">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S114">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T114">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U114">
+        <v>2.3</v>
+      </c>
+      <c r="V114">
+        <v>1.57</v>
+      </c>
+      <c r="W114">
+        <v>1.09</v>
+      </c>
+      <c r="X114">
+        <v>1.04</v>
+      </c>
+      <c r="Y114">
+        <v>1.2</v>
+      </c>
+      <c r="Z114">
+        <v>4.2</v>
+      </c>
+      <c r="AA114">
+        <v>1.67</v>
+      </c>
+      <c r="AB114">
         <v>2.2</v>
       </c>
-      <c r="V114">
-        <v>1.62</v>
-      </c>
-      <c r="W114">
-        <v>1.15</v>
-      </c>
-      <c r="X114">
-        <v>1.01</v>
-      </c>
-      <c r="Y114">
+      <c r="AC114">
+        <v>2.7</v>
+      </c>
+      <c r="AD114">
+        <v>1.4</v>
+      </c>
+      <c r="AE114">
         <v>1.14</v>
       </c>
-      <c r="Z114">
-        <v>4.8</v>
-      </c>
-      <c r="AA114">
-        <v>1.57</v>
-      </c>
-      <c r="AB114">
-        <v>2.35</v>
-      </c>
-      <c r="AC114">
-        <v>2.29</v>
-      </c>
-      <c r="AD114">
-        <v>1.5</v>
-      </c>
-      <c r="AE114">
-        <v>1.2</v>
-      </c>
       <c r="AF114">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG114">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK114">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19060,58 +19060,58 @@
         <v>3.75</v>
       </c>
       <c r="P115">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q115">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R115">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S115">
+        <v>1.33</v>
+      </c>
+      <c r="T115">
+        <v>2.89</v>
+      </c>
+      <c r="U115">
+        <v>2.64</v>
+      </c>
+      <c r="V115">
         <v>1.36</v>
       </c>
-      <c r="T115">
-        <v>2.88</v>
-      </c>
-      <c r="U115">
-        <v>2.71</v>
-      </c>
-      <c r="V115">
-        <v>1.37</v>
-      </c>
       <c r="W115">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
         <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z115">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AA115">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB115">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC115">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AD115">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE115">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AG115">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK115">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19235,10 +19235,10 @@
         <v>1.36</v>
       </c>
       <c r="T116">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="U116">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="V116">
         <v>1.33</v>
@@ -19253,28 +19253,28 @@
         <v>1.28</v>
       </c>
       <c r="Z116">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA116">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AB116">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC116">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD116">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE116">
         <v>1.05</v>
       </c>
       <c r="AF116">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG116">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="O117">
         <v>3.1</v>
@@ -19389,22 +19389,22 @@
         <v>2.25</v>
       </c>
       <c r="Q117">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="R117">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S117">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T117">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U117">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="V117">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W117">
         <v>1.06</v>
@@ -19413,31 +19413,31 @@
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Z117">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AA117">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB117">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC117">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AD117">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE117">
         <v>1.02</v>
       </c>
       <c r="AF117">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG117">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O118">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P118">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20216,13 +20216,13 @@
         <v>3.6</v>
       </c>
       <c r="U122">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="V122">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W122">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X122">
         <v>1.03</v>
@@ -20234,7 +20234,7 @@
         <v>4.4</v>
       </c>
       <c r="AA122">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB122">
         <v>2.2</v>
@@ -20243,16 +20243,16 @@
         <v>2.4</v>
       </c>
       <c r="AD122">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE122">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF122">
         <v>1.6</v>
       </c>
       <c r="AG122">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.16</v>
+        <v>2.09</v>
       </c>
       <c r="AK122">
         <v>1.17</v>
@@ -22169,7 +22169,7 @@
         <v>1.25</v>
       </c>
       <c r="T134">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="U134">
         <v>2.3</v>
@@ -22178,37 +22178,37 @@
         <v>1.53</v>
       </c>
       <c r="W134">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X134">
         <v>1.03</v>
       </c>
       <c r="Y134">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z134">
         <v>4.1</v>
       </c>
       <c r="AA134">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB134">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AC134">
         <v>2.38</v>
       </c>
       <c r="AD134">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE134">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF134">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG134">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK134">
         <v>2.15</v>
@@ -22803,28 +22803,28 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="O138">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P138">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q138">
         <v>2.76</v>
       </c>
       <c r="R138">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S138">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T138">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="U138">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="V138">
         <v>1.45</v>
@@ -22845,10 +22845,10 @@
         <v>1.7</v>
       </c>
       <c r="AB138">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC138">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD138">
         <v>1.36</v>
@@ -22857,10 +22857,10 @@
         <v>1.13</v>
       </c>
       <c r="AF138">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG138">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -2274,16 +2274,16 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
         <v>2.62</v>
@@ -2295,25 +2295,25 @@
         <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.28</v>
+        <v>3.46</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB12">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AC12">
         <v>3.16</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
         <v>1.11</v>
@@ -2322,7 +2322,7 @@
         <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
         <v>2</v>
@@ -2437,55 +2437,55 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="O19">
         <v>3.5</v>
       </c>
       <c r="P19">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="Q19">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="R19">
         <v>2.4</v>
@@ -3424,62 +3424,62 @@
         <v>1.22</v>
       </c>
       <c r="T19">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="U19">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
         <v>1.65</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB19">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AC19">
         <v>2.17</v>
       </c>
       <c r="AD19">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE19">
+        <v>1.22</v>
+      </c>
+      <c r="AF19">
+        <v>1.42</v>
+      </c>
+      <c r="AG19">
+        <v>2.62</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.21</v>
       </c>
-      <c r="AF19">
-        <v>1.4</v>
-      </c>
-      <c r="AG19">
-        <v>2.64</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.29</v>
-      </c>
       <c r="AK19">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -5368,7 +5368,7 @@
         <v>3.34</v>
       </c>
       <c r="P31">
-        <v>3.29</v>
+        <v>3.05</v>
       </c>
       <c r="Q31">
         <v>3</v>
@@ -5380,7 +5380,7 @@
         <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U31">
         <v>2.7</v>
@@ -5389,7 +5389,7 @@
         <v>1.38</v>
       </c>
       <c r="W31">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
         <v>1.06</v>
@@ -5419,7 +5419,7 @@
         <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="O33">
-        <v>6.63</v>
+        <v>6.3</v>
       </c>
       <c r="P33">
-        <v>9.35</v>
+        <v>7.85</v>
       </c>
       <c r="Q33">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="R33">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S33">
         <v>1.12</v>
       </c>
       <c r="T33">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="U33">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V33">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="W33">
         <v>1.24</v>
@@ -5727,25 +5727,25 @@
         <v>6.5</v>
       </c>
       <c r="AA33">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB33">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AC33">
         <v>1.85</v>
       </c>
       <c r="AD33">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE33">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AF33">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK33">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5866,19 +5866,19 @@
         <v>2.5</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T34">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U34">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="V34">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.02</v>
@@ -5887,28 +5887,28 @@
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC34">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD34">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE34">
         <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA39">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AB39">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AD39">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AG39">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK39">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q40">
+        <v>2.12</v>
+      </c>
+      <c r="R40">
         <v>2.33</v>
       </c>
-      <c r="R40">
-        <v>2.35</v>
-      </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U40">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="V40">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA40">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB40">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="AD40">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AG40">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK40">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q41">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="R41">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U41">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="V41">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD41">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK41">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G42">
@@ -7164,55 +7164,55 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="R42">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U42">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="V42">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA42">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="AD42">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK42">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7487,13 +7487,13 @@
         <v>3.35</v>
       </c>
       <c r="P44">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q44">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="R44">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S44">
         <v>1.36</v>
@@ -7511,31 +7511,31 @@
         <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z44">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA44">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB44">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC44">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD44">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE44">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF44">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG44">
         <v>2.15</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
         <v>1.53</v>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="O45">
         <v>3.27</v>
@@ -7659,31 +7659,31 @@
         <v>2.3</v>
       </c>
       <c r="S45">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T45">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="U45">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="V45">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z45">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="AA45">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB45">
         <v>2</v>
@@ -7698,10 +7698,10 @@
         <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG45">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
         <v>1.7</v>
@@ -7813,58 +7813,58 @@
         <v>4.2</v>
       </c>
       <c r="P46">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="Q46">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T46">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="U46">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V46">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA46">
         <v>1.4</v>
       </c>
       <c r="AB46">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AC46">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AD46">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE46">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF46">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8948,55 +8948,55 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O53">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P53">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q53">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R53">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S53">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T53">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="U53">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="V53">
         <v>1.33</v>
       </c>
       <c r="W53">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y53">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z53">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA53">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB53">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC53">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="AD53">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE53">
         <v>1.04</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10264,13 +10264,13 @@
         <v>2.63</v>
       </c>
       <c r="R61">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S61">
         <v>1.36</v>
       </c>
       <c r="T61">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="U61">
         <v>2.69</v>
@@ -10291,7 +10291,7 @@
         <v>3.34</v>
       </c>
       <c r="AA61">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB61">
         <v>1.85</v>
@@ -10325,7 +10325,7 @@
         <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11070,28 +11070,28 @@
         <v>3.1</v>
       </c>
       <c r="O66">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q66">
         <v>3.4</v>
       </c>
       <c r="R66">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T66">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U66">
         <v>2.13</v>
       </c>
       <c r="V66">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W66">
         <v>1.14</v>
@@ -11100,31 +11100,31 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z66">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA66">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB66">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AC66">
         <v>2.12</v>
       </c>
       <c r="AD66">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE66">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF66">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG66">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK66">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.42</v>
+        <v>3.5</v>
       </c>
       <c r="O67">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>5.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q67">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="R67">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="S67">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.84</v>
+        <v>3.28</v>
       </c>
       <c r="U67">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V67">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="W67">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z67">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA67">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AB67">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="AC67">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AD67">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE67">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF67">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG67">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.09</v>
+        <v>1.85</v>
       </c>
       <c r="AK67">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.5</v>
+        <v>1.42</v>
       </c>
       <c r="O68">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P68">
-        <v>1.84</v>
+        <v>5.75</v>
       </c>
       <c r="Q68">
-        <v>3.7</v>
+        <v>1.93</v>
       </c>
       <c r="R68">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T68">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="U68">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="V68">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W68">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z68">
-        <v>4.97</v>
+        <v>5.25</v>
       </c>
       <c r="AA68">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB68">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AC68">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="AD68">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AE68">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF68">
         <v>1.44</v>
       </c>
       <c r="AG68">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK68">
-        <v>1.22</v>
+        <v>2.41</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11882,49 +11882,49 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="O71">
-        <v>5.95</v>
+        <v>5.1</v>
       </c>
       <c r="P71">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q71">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R71">
         <v>2.77</v>
       </c>
       <c r="S71">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T71">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="U71">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V71">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W71">
         <v>1.12</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z71">
-        <v>4.65</v>
+        <v>4.49</v>
       </c>
       <c r="AA71">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AB71">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC71">
         <v>2.37</v>
@@ -11936,10 +11936,10 @@
         <v>1.18</v>
       </c>
       <c r="AF71">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG71">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK71">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="O80">
         <v>3.7</v>
       </c>
       <c r="P80">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="O90">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="P90">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="Q90">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R90">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="S90">
+        <v>1.21</v>
+      </c>
+      <c r="T90">
+        <v>3.7</v>
+      </c>
+      <c r="U90">
+        <v>2.14</v>
+      </c>
+      <c r="V90">
+        <v>1.7</v>
+      </c>
+      <c r="W90">
         <v>1.16</v>
       </c>
-      <c r="T90">
-        <v>4.25</v>
-      </c>
-      <c r="U90">
-        <v>1.88</v>
-      </c>
-      <c r="V90">
-        <v>1.89</v>
-      </c>
-      <c r="W90">
-        <v>1.21</v>
-      </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z90">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA90">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AC90">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AD90">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AE90">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AF90">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AG90">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK90">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="O91">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="P91">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="Q91">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R91">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="S91">
+        <v>1.16</v>
+      </c>
+      <c r="T91">
+        <v>4.25</v>
+      </c>
+      <c r="U91">
+        <v>1.88</v>
+      </c>
+      <c r="V91">
+        <v>1.89</v>
+      </c>
+      <c r="W91">
         <v>1.21</v>
       </c>
-      <c r="T91">
-        <v>3.7</v>
-      </c>
-      <c r="U91">
-        <v>2.14</v>
-      </c>
-      <c r="V91">
-        <v>1.7</v>
-      </c>
-      <c r="W91">
-        <v>1.16</v>
-      </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z91">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA91">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AB91">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="AC91">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AD91">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AE91">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AF91">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AG91">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK91">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O93">
         <v>3.45</v>
       </c>
       <c r="P93">
+        <v>2.4</v>
+      </c>
+      <c r="Q93">
+        <v>3.07</v>
+      </c>
+      <c r="R93">
         <v>2.45</v>
-      </c>
-      <c r="Q93">
-        <v>3.1</v>
-      </c>
-      <c r="R93">
-        <v>2.21</v>
       </c>
       <c r="S93">
         <v>1.26</v>
       </c>
       <c r="T93">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U93">
         <v>2.2</v>
       </c>
       <c r="V93">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="W93">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z93">
-        <v>4.8</v>
+        <v>4.89</v>
       </c>
       <c r="AA93">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AB93">
         <v>2.28</v>
       </c>
       <c r="AC93">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AD93">
         <v>1.55</v>
       </c>
       <c r="AE93">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF93">
         <v>1.44</v>
       </c>
       <c r="AG93">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK93">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O98">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P98">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q98">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R98">
         <v>2.3</v>
       </c>
       <c r="S98">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T98">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="U98">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="V98">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="W98">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y98">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z98">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA98">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB98">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC98">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AD98">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE98">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF98">
         <v>1.48</v>
       </c>
       <c r="AG98">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK98">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O104">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="P104">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Q104">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="R104">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S104">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="T104">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="U104">
-        <v>2.95</v>
+        <v>2.23</v>
       </c>
       <c r="V104">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W104">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X104">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z104">
-        <v>3.18</v>
+        <v>4.75</v>
       </c>
       <c r="AA104">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="AB104">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AC104">
-        <v>3.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD104">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AE104">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AF104">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AG104">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AK104">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="P105">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q105">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R105">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S105">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U105">
-        <v>2.23</v>
+        <v>2.95</v>
       </c>
       <c r="V105">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W105">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="Z105">
-        <v>4.75</v>
+        <v>3.18</v>
       </c>
       <c r="AA105">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="AB105">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AC105">
-        <v>2.27</v>
+        <v>3.3</v>
       </c>
       <c r="AD105">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AE105">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AG105">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AK105">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18728,80 +18728,80 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="O113">
         <v>3.3</v>
       </c>
       <c r="P113">
-        <v>5.19</v>
+        <v>5</v>
       </c>
       <c r="Q113">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R113">
         <v>2.05</v>
       </c>
       <c r="S113">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="T113">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="U113">
         <v>3.3</v>
       </c>
       <c r="V113">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W113">
         <v>1.03</v>
       </c>
       <c r="X113">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y113">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z113">
         <v>2.8</v>
       </c>
       <c r="AA113">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB113">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC113">
-        <v>4.24</v>
+        <v>3.62</v>
       </c>
       <c r="AD113">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE113">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF113">
+        <v>2.1</v>
+      </c>
+      <c r="AG113">
+        <v>1.67</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
+        <v>1.25</v>
+      </c>
+      <c r="AK113">
         <v>2</v>
-      </c>
-      <c r="AG113">
-        <v>1.7</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>1.29</v>
-      </c>
-      <c r="AK113">
-        <v>1.91</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O114">
         <v>3.1</v>
       </c>
       <c r="P114">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="Q114">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R114">
         <v>2.1</v>
       </c>
       <c r="S114">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T114">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U114">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="V114">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W114">
         <v>1.05</v>
       </c>
       <c r="X114">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y114">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z114">
         <v>3.1</v>
       </c>
       <c r="AA114">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB114">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC114">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="AD114">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE114">
         <v>1.07</v>
       </c>
       <c r="AF114">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG114">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AK114">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19546,28 +19546,28 @@
         <v>1.55</v>
       </c>
       <c r="O118">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P118">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="Q118">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="R118">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="S118">
         <v>1.33</v>
       </c>
       <c r="T118">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U118">
         <v>2.64</v>
       </c>
       <c r="V118">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W118">
         <v>1.06</v>
@@ -19579,28 +19579,28 @@
         <v>1.25</v>
       </c>
       <c r="Z118">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AA118">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB118">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC118">
         <v>3.14</v>
       </c>
       <c r="AD118">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE118">
         <v>1.06</v>
       </c>
       <c r="AF118">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG118">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK118">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,34 +19706,34 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O119">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P119">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q119">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="R119">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="S119">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T119">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="U119">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V119">
         <v>1.33</v>
       </c>
       <c r="W119">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X119">
         <v>1.01</v>
@@ -19742,19 +19742,19 @@
         <v>1.28</v>
       </c>
       <c r="Z119">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA119">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB119">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC119">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AD119">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE119">
         <v>1.05</v>
@@ -19763,7 +19763,7 @@
         <v>1.75</v>
       </c>
       <c r="AG119">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK119">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="O120">
         <v>3.1</v>
       </c>
       <c r="P120">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q120">
-        <v>3.8</v>
+        <v>4.14</v>
       </c>
       <c r="R120">
         <v>1.95</v>
       </c>
       <c r="S120">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T120">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U120">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="V120">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W120">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z120">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AA120">
         <v>2.15</v>
       </c>
       <c r="AB120">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AC120">
         <v>3.8</v>
       </c>
       <c r="AD120">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE120">
         <v>1.02</v>
       </c>
       <c r="AF120">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AG120">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AK120">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20035,22 +20035,22 @@
         <v>2.37</v>
       </c>
       <c r="O121">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P121">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q121">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="R121">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S121">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T121">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="U121">
         <v>2.73</v>
@@ -20059,7 +20059,7 @@
         <v>1.36</v>
       </c>
       <c r="W121">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
         <v>1.02</v>
@@ -20074,22 +20074,22 @@
         <v>1.9</v>
       </c>
       <c r="AB121">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC121">
         <v>3.08</v>
       </c>
       <c r="AD121">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE121">
         <v>1.07</v>
       </c>
       <c r="AF121">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AG121">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>1.27</v>
       </c>
       <c r="AK121">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL123">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
         <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="U3">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
+        <v>1.05</v>
+      </c>
+      <c r="X3">
         <v>1.04</v>
       </c>
-      <c r="X3">
-        <v>1.07</v>
-      </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AA3">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB3">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC3">
-        <v>3.62</v>
+        <v>4.25</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
         <v>1.36</v>
@@ -961,34 +961,34 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.7</v>
+        <v>4.24</v>
       </c>
       <c r="O4">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q4">
         <v>4.2</v>
       </c>
       <c r="R4">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="U4">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V4">
         <v>1.46</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
         <v>1.02</v>
@@ -1003,10 +1003,10 @@
         <v>1.76</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AC4">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="AD4">
         <v>1.36</v>
@@ -1015,7 +1015,7 @@
         <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
         <v>2.05</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O25">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P25">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q25">
-        <v>4.95</v>
+        <v>5.65</v>
       </c>
       <c r="R25">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="S25">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T25">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="U25">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="V25">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="W25">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z25">
-        <v>5.3</v>
+        <v>4.85</v>
       </c>
       <c r="AA25">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AB25">
-        <v>2.52</v>
+        <v>2.37</v>
       </c>
       <c r="AC25">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AD25">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE25">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.15</v>
+        <v>2.46</v>
       </c>
       <c r="AK25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O28">
         <v>4</v>
       </c>
       <c r="P28">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q28">
         <v>2</v>
       </c>
       <c r="R28">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
         <v>1.22</v>
       </c>
       <c r="T28">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U28">
         <v>2.25</v>
@@ -4900,7 +4900,7 @@
         <v>1.57</v>
       </c>
       <c r="W28">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4909,19 +4909,19 @@
         <v>1.11</v>
       </c>
       <c r="Z28">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AA28">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB28">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC28">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD28">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE28">
         <v>1.18</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5202,16 +5202,16 @@
         <v>1.86</v>
       </c>
       <c r="O30">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>3.3</v>
+        <v>3.72</v>
       </c>
       <c r="Q30">
         <v>2.48</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S30">
         <v>1.35</v>
@@ -5220,7 +5220,7 @@
         <v>3.08</v>
       </c>
       <c r="U30">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="V30">
         <v>1.48</v>
@@ -5241,7 +5241,7 @@
         <v>1.81</v>
       </c>
       <c r="AB30">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AC30">
         <v>2.96</v>
@@ -5250,7 +5250,7 @@
         <v>1.39</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF30">
         <v>1.63</v>
@@ -5272,7 +5272,7 @@
         <v>1.31</v>
       </c>
       <c r="AK30">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5697,7 +5697,7 @@
         <v>7.85</v>
       </c>
       <c r="Q33">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R33">
         <v>3.1</v>
@@ -5706,13 +5706,13 @@
         <v>1.12</v>
       </c>
       <c r="T33">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="U33">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="V33">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W33">
         <v>1.24</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="O34">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P34">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q34">
         <v>3.75</v>
@@ -5866,10 +5866,10 @@
         <v>2.5</v>
       </c>
       <c r="S34">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="U34">
         <v>2.13</v>
@@ -5884,16 +5884,16 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AA34">
         <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC34">
         <v>2.22</v>
@@ -5902,7 +5902,7 @@
         <v>1.62</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF34">
         <v>1.44</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
         <v>1.22</v>
@@ -6014,34 +6014,34 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O35">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="P35">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q35">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S35">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
         <v>3.6</v>
       </c>
       <c r="U35">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V35">
         <v>1.57</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
         <v>1.03</v>
@@ -6053,10 +6053,10 @@
         <v>4.6</v>
       </c>
       <c r="AA35">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB35">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
         <v>2.4</v>
@@ -6071,7 +6071,7 @@
         <v>1.53</v>
       </c>
       <c r="AG35">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6503,55 +6503,55 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O38">
         <v>3.7</v>
       </c>
       <c r="P38">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q38">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="R38">
+        <v>2.28</v>
+      </c>
+      <c r="S38">
+        <v>1.25</v>
+      </c>
+      <c r="T38">
+        <v>3.45</v>
+      </c>
+      <c r="U38">
+        <v>2.33</v>
+      </c>
+      <c r="V38">
+        <v>1.61</v>
+      </c>
+      <c r="W38">
+        <v>1.11</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.14</v>
+      </c>
+      <c r="Z38">
+        <v>4.91</v>
+      </c>
+      <c r="AA38">
+        <v>1.56</v>
+      </c>
+      <c r="AB38">
+        <v>2.43</v>
+      </c>
+      <c r="AC38">
         <v>2.4</v>
       </c>
-      <c r="S38">
-        <v>1.23</v>
-      </c>
-      <c r="T38">
-        <v>3.52</v>
-      </c>
-      <c r="U38">
-        <v>2.25</v>
-      </c>
-      <c r="V38">
-        <v>1.57</v>
-      </c>
-      <c r="W38">
-        <v>1.14</v>
-      </c>
-      <c r="X38">
-        <v>1.03</v>
-      </c>
-      <c r="Y38">
-        <v>1.17</v>
-      </c>
-      <c r="Z38">
-        <v>4.8</v>
-      </c>
-      <c r="AA38">
-        <v>1.53</v>
-      </c>
-      <c r="AB38">
-        <v>2.3</v>
-      </c>
-      <c r="AC38">
-        <v>2.38</v>
-      </c>
       <c r="AD38">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE38">
         <v>1.2</v>
@@ -6560,7 +6560,7 @@
         <v>1.53</v>
       </c>
       <c r="AG38">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7982,43 +7982,43 @@
         <v>2.05</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
         <v>1.35</v>
       </c>
       <c r="T47">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="U47">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="V47">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W47">
         <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
-        <v>3.59</v>
+        <v>4.12</v>
       </c>
       <c r="AA47">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AB47">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AC47">
         <v>3.3</v>
       </c>
       <c r="AD47">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE47">
         <v>1.1</v>
@@ -8043,7 +8043,7 @@
         <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O48">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB48">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8308,37 +8308,37 @@
         <v>2.24</v>
       </c>
       <c r="R49">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S49">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="U49">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="W49">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
         <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z49">
-        <v>4.3</v>
+        <v>4.42</v>
       </c>
       <c r="AA49">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AB49">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AC49">
         <v>2.55</v>
@@ -8347,13 +8347,13 @@
         <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG49">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK49">
         <v>2</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O50">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q50">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="S50">
         <v>1.24</v>
@@ -8492,22 +8492,22 @@
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AA50">
+        <v>1.51</v>
+      </c>
+      <c r="AB50">
+        <v>2.33</v>
+      </c>
+      <c r="AC50">
+        <v>2.31</v>
+      </c>
+      <c r="AD50">
         <v>1.57</v>
-      </c>
-      <c r="AB50">
-        <v>2.5</v>
-      </c>
-      <c r="AC50">
-        <v>2.32</v>
-      </c>
-      <c r="AD50">
-        <v>1.58</v>
       </c>
       <c r="AE50">
         <v>1.19</v>
@@ -8516,7 +8516,7 @@
         <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK50">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8628,19 +8628,19 @@
         <v>3.6</v>
       </c>
       <c r="P51">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q51">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R51">
         <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
         <v>2.25</v>
@@ -8649,31 +8649,31 @@
         <v>1.57</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
         <v>4.65</v>
       </c>
       <c r="AA51">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AB51">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AC51">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="AD51">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AE51">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF51">
         <v>1.47</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK51">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
+        <v>2.5</v>
+      </c>
+      <c r="O52">
+        <v>3.75</v>
+      </c>
+      <c r="P52">
         <v>2.47</v>
-      </c>
-      <c r="O52">
-        <v>3.5</v>
-      </c>
-      <c r="P52">
-        <v>2.3</v>
       </c>
       <c r="Q52">
         <v>2.9</v>
       </c>
       <c r="R52">
-        <v>2.31</v>
+        <v>2.59</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="U52">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V52">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W52">
         <v>1.14</v>
@@ -8821,22 +8821,22 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA52">
         <v>1.5</v>
       </c>
       <c r="AB52">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AC52">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AD52">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AE52">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF52">
         <v>1.4</v>
@@ -8858,7 +8858,7 @@
         <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9120,49 +9120,49 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R54">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U54">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="V54">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W54">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA54">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AB54">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AC54">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AD54">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE54">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF54">
         <v>2.1</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK54">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9600,43 +9600,43 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q57">
         <v>3.1</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S57">
         <v>1.23</v>
       </c>
       <c r="T57">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="U57">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>5.04</v>
+        <v>4.75</v>
       </c>
       <c r="AA57">
         <v>1.53</v>
@@ -9645,13 +9645,13 @@
         <v>2.4</v>
       </c>
       <c r="AC57">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD57">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AE57">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF57">
         <v>1.37</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="O58">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P58">
-        <v>4.78</v>
+        <v>4.4</v>
       </c>
       <c r="Q58">
         <v>2.03</v>
@@ -9778,31 +9778,31 @@
         <v>2.5</v>
       </c>
       <c r="S58">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U58">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V58">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W58">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X58">
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="AA58">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB58">
         <v>2.5</v>
@@ -9817,10 +9817,10 @@
         <v>1.25</v>
       </c>
       <c r="AF58">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG58">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>3</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S59">
         <v>1.41</v>
@@ -9947,16 +9947,16 @@
         <v>2.59</v>
       </c>
       <c r="U59">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="V59">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W59">
         <v>1.02</v>
       </c>
       <c r="X59">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
         <v>1.32</v>
@@ -9968,16 +9968,16 @@
         <v>2.13</v>
       </c>
       <c r="AB59">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC59">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD59">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE59">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
         <v>2</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK59">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10092,31 +10092,31 @@
         <v>1.19</v>
       </c>
       <c r="O60">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="P60">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q60">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R60">
         <v>2.7</v>
       </c>
       <c r="S60">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="U60">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V60">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W60">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X60">
         <v>1.03</v>
@@ -10125,28 +10125,28 @@
         <v>1.15</v>
       </c>
       <c r="Z60">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA60">
         <v>1.5</v>
       </c>
       <c r="AB60">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AC60">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AD60">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE60">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF60">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG60">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK60">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O64">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P64">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="Q64">
-        <v>5.02</v>
+        <v>4.33</v>
       </c>
       <c r="R64">
         <v>2.4</v>
       </c>
       <c r="S64">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="U64">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V64">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W64">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z64">
-        <v>5.65</v>
+        <v>4.85</v>
       </c>
       <c r="AA64">
         <v>1.5</v>
       </c>
       <c r="AB64">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC64">
         <v>2.24</v>
       </c>
       <c r="AD64">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE64">
         <v>1.26</v>
       </c>
       <c r="AF64">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AG64">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11556,22 +11556,22 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O69">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P69">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q69">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="R69">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S69">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T69">
         <v>3</v>
@@ -11586,25 +11586,25 @@
         <v>1.06</v>
       </c>
       <c r="X69">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z69">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA69">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AB69">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC69">
         <v>2.8</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE69">
         <v>1.12</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11891,16 +11891,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q71">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R71">
-        <v>2.77</v>
+        <v>2.48</v>
       </c>
       <c r="S71">
         <v>1.25</v>
       </c>
       <c r="T71">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U71">
         <v>2.2</v>
@@ -11939,7 +11939,7 @@
         <v>1.87</v>
       </c>
       <c r="AG71">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O73">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P73">
         <v>3.8</v>
       </c>
       <c r="Q73">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="R73">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="S73">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T73">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="U73">
-        <v>2.64</v>
+        <v>2.81</v>
       </c>
       <c r="V73">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W73">
+        <v>1.03</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
+        <v>1.3</v>
+      </c>
+      <c r="Z73">
+        <v>3.55</v>
+      </c>
+      <c r="AA73">
+        <v>1.92</v>
+      </c>
+      <c r="AB73">
+        <v>1.8</v>
+      </c>
+      <c r="AC73">
+        <v>3.15</v>
+      </c>
+      <c r="AD73">
+        <v>1.27</v>
+      </c>
+      <c r="AE73">
         <v>1.06</v>
       </c>
-      <c r="X73">
-        <v>1.04</v>
-      </c>
-      <c r="Y73">
-        <v>1.25</v>
-      </c>
-      <c r="Z73">
-        <v>3.92</v>
-      </c>
-      <c r="AA73">
-        <v>1.72</v>
-      </c>
-      <c r="AB73">
-        <v>2.08</v>
-      </c>
-      <c r="AC73">
-        <v>2.9</v>
-      </c>
-      <c r="AD73">
-        <v>1.36</v>
-      </c>
-      <c r="AE73">
-        <v>1.13</v>
-      </c>
       <c r="AF73">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK73">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,16 +12371,16 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="O74">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>4.89</v>
+        <v>4.2</v>
       </c>
       <c r="Q74">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="R74">
         <v>2.25</v>
@@ -12389,46 +12389,46 @@
         <v>1.36</v>
       </c>
       <c r="T74">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="U74">
         <v>2.6</v>
       </c>
       <c r="V74">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W74">
         <v>1.07</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z74">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA74">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB74">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC74">
         <v>2.64</v>
       </c>
       <c r="AD74">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE74">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF74">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG74">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
         <v>2.05</v>
@@ -12534,28 +12534,28 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O75">
-        <v>3.07</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
         <v>2.85</v>
       </c>
       <c r="Q75">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R75">
         <v>2.13</v>
       </c>
       <c r="S75">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T75">
         <v>2.85</v>
       </c>
       <c r="U75">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V75">
         <v>1.39</v>
@@ -12564,31 +12564,31 @@
         <v>1.04</v>
       </c>
       <c r="X75">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z75">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA75">
         <v>1.95</v>
       </c>
       <c r="AB75">
+        <v>1.83</v>
+      </c>
+      <c r="AC75">
+        <v>3.5</v>
+      </c>
+      <c r="AD75">
+        <v>1.29</v>
+      </c>
+      <c r="AE75">
+        <v>1.06</v>
+      </c>
+      <c r="AF75">
         <v>1.75</v>
-      </c>
-      <c r="AC75">
-        <v>3.57</v>
-      </c>
-      <c r="AD75">
-        <v>1.25</v>
-      </c>
-      <c r="AE75">
-        <v>1.1</v>
-      </c>
-      <c r="AF75">
-        <v>1.8</v>
       </c>
       <c r="AG75">
         <v>1.91</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK75">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,55 +12697,55 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="O76">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P76">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="Q76">
         <v>3.45</v>
       </c>
       <c r="R76">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S76">
         <v>1.38</v>
       </c>
       <c r="T76">
-        <v>3.03</v>
+        <v>2.73</v>
       </c>
       <c r="U76">
         <v>2.75</v>
       </c>
       <c r="V76">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W76">
         <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z76">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="AA76">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AB76">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AC76">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD76">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE76">
         <v>1.09</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12866,58 +12866,58 @@
         <v>2.9</v>
       </c>
       <c r="P77">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="Q77">
         <v>3.02</v>
       </c>
       <c r="R77">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S77">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="T77">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="U77">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="V77">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W77">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
+        <v>1.1</v>
+      </c>
+      <c r="Y77">
+        <v>1.45</v>
+      </c>
+      <c r="Z77">
+        <v>2.53</v>
+      </c>
+      <c r="AA77">
+        <v>2.62</v>
+      </c>
+      <c r="AB77">
+        <v>1.51</v>
+      </c>
+      <c r="AC77">
+        <v>5.25</v>
+      </c>
+      <c r="AD77">
+        <v>1.14</v>
+      </c>
+      <c r="AE77">
         <v>1.04</v>
-      </c>
-      <c r="Y77">
-        <v>1.44</v>
-      </c>
-      <c r="Z77">
-        <v>2.5</v>
-      </c>
-      <c r="AA77">
-        <v>2.45</v>
-      </c>
-      <c r="AB77">
-        <v>1.5</v>
-      </c>
-      <c r="AC77">
-        <v>4.3</v>
-      </c>
-      <c r="AD77">
-        <v>1.15</v>
-      </c>
-      <c r="AE77">
-        <v>1.01</v>
       </c>
       <c r="AF77">
         <v>2</v>
       </c>
       <c r="AG77">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK77">
         <v>1.57</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13542,10 +13542,10 @@
         <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z81">
         <v>3.6</v>
@@ -13880,22 +13880,22 @@
         <v>1.28</v>
       </c>
       <c r="AB83">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AC83">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AD83">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AE83">
         <v>1.45</v>
       </c>
       <c r="AF83">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG83">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="O84">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q84">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="R84">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S84">
         <v>1.25</v>
@@ -14022,10 +14022,10 @@
         <v>3.36</v>
       </c>
       <c r="U84">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V84">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W84">
         <v>1.13</v>
@@ -14034,47 +14034,47 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z84">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA84">
+        <v>1.47</v>
+      </c>
+      <c r="AB84">
+        <v>2.5</v>
+      </c>
+      <c r="AC84">
+        <v>2.27</v>
+      </c>
+      <c r="AD84">
+        <v>1.6</v>
+      </c>
+      <c r="AE84">
+        <v>1.22</v>
+      </c>
+      <c r="AF84">
+        <v>1.43</v>
+      </c>
+      <c r="AG84">
+        <v>2.7</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
+        <v>1.23</v>
+      </c>
+      <c r="AK84">
         <v>1.51</v>
-      </c>
-      <c r="AB84">
-        <v>2.4</v>
-      </c>
-      <c r="AC84">
-        <v>2.19</v>
-      </c>
-      <c r="AD84">
-        <v>1.58</v>
-      </c>
-      <c r="AE84">
-        <v>1.21</v>
-      </c>
-      <c r="AF84">
-        <v>1.44</v>
-      </c>
-      <c r="AG84">
-        <v>2.63</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.44</v>
-      </c>
-      <c r="AK84">
-        <v>1.47</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O85">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q85">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R85">
         <v>2.6</v>
@@ -14182,13 +14182,13 @@
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U85">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V85">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="W85">
         <v>1.18</v>
@@ -14197,31 +14197,31 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z85">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="AA85">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB85">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC85">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AD85">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AE85">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF85">
         <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK85">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,10 +14327,10 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.61</v>
+        <v>2.95</v>
       </c>
       <c r="O86">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P86">
         <v>2.03</v>
@@ -14345,40 +14345,40 @@
         <v>1.18</v>
       </c>
       <c r="T86">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="U86">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="V86">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="W86">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z86">
-        <v>5.75</v>
+        <v>5.65</v>
       </c>
       <c r="AA86">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC86">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AD86">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AE86">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF86">
         <v>1.4</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK86">
         <v>1.33</v>
@@ -14490,19 +14490,19 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="O87">
         <v>5.25</v>
       </c>
       <c r="P87">
-        <v>8.550000000000001</v>
+        <v>7</v>
       </c>
       <c r="Q87">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="R87">
-        <v>2.72</v>
+        <v>3.03</v>
       </c>
       <c r="S87">
         <v>1.17</v>
@@ -14523,28 +14523,28 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z87">
         <v>6.2</v>
       </c>
       <c r="AA87">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB87">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC87">
         <v>1.89</v>
       </c>
       <c r="AD87">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AE87">
         <v>1.33</v>
       </c>
       <c r="AF87">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG87">
         <v>2.2</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK87">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,40 +14653,40 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O88">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="P88">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q88">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R88">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="S88">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T88">
-        <v>5.1</v>
+        <v>4.75</v>
       </c>
       <c r="U88">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V88">
         <v>1.95</v>
       </c>
       <c r="W88">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z88">
         <v>8.5</v>
@@ -14695,22 +14695,22 @@
         <v>1.28</v>
       </c>
       <c r="AB88">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC88">
         <v>1.67</v>
       </c>
       <c r="AD88">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AE88">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AF88">
         <v>1.4</v>
       </c>
       <c r="AG88">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK88">
         <v>2.7</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="O89">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="P89">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="Q89">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="R89">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S89">
         <v>1.22</v>
       </c>
       <c r="T89">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U89">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="V89">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA89">
         <v>1.44</v>
       </c>
       <c r="AB89">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AC89">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AD89">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AE89">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF89">
         <v>1.39</v>
       </c>
       <c r="AG89">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AK89">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="O90">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="P90">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="Q90">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="S90">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="U90">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V90">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W90">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X90">
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z90">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA90">
         <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AC90">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD90">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE90">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF90">
         <v>1.4</v>
       </c>
       <c r="AG90">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O91">
         <v>4.05</v>
@@ -15151,37 +15151,37 @@
         <v>2.8</v>
       </c>
       <c r="Q91">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R91">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="S91">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T91">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="U91">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V91">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="W91">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z91">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA91">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB91">
         <v>3.4</v>
@@ -15190,13 +15190,13 @@
         <v>1.8</v>
       </c>
       <c r="AD91">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE91">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF91">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AG91">
         <v>3.25</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK91">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,16 +15305,16 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
         <v>2.8</v>
       </c>
       <c r="Q92">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="R92">
         <v>2.3</v>
@@ -15362,7 +15362,7 @@
         <v>1.6</v>
       </c>
       <c r="AG92">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15634,10 +15634,10 @@
         <v>4.8</v>
       </c>
       <c r="O94">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P94">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q94">
         <v>4.75</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O95">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P95">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q95">
         <v>2.85</v>
@@ -15812,37 +15812,37 @@
         <v>1.29</v>
       </c>
       <c r="T95">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="U95">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W95">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X95">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z95">
         <v>4.2</v>
       </c>
       <c r="AA95">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AB95">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AC95">
         <v>2.6</v>
       </c>
       <c r="AD95">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE95">
         <v>1.17</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK95">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,31 +15957,31 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="O96">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P96">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Q96">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="R96">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S96">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T96">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U96">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="V96">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W96">
         <v>1.1</v>
@@ -15996,25 +15996,25 @@
         <v>3.54</v>
       </c>
       <c r="AA96">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AB96">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AC96">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD96">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE96">
         <v>1.12</v>
       </c>
       <c r="AF96">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG96">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK96">
         <v>2.15</v>
@@ -16123,25 +16123,25 @@
         <v>2.1</v>
       </c>
       <c r="O97">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P97">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="Q97">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="R97">
         <v>2.3</v>
       </c>
       <c r="S97">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T97">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="U97">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V97">
         <v>1.57</v>
@@ -16150,25 +16150,25 @@
         <v>1.12</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z97">
-        <v>4.75</v>
+        <v>5.02</v>
       </c>
       <c r="AA97">
         <v>1.56</v>
       </c>
       <c r="AB97">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AC97">
         <v>2.4</v>
       </c>
       <c r="AD97">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AE97">
         <v>1.21</v>
@@ -16177,7 +16177,7 @@
         <v>1.46</v>
       </c>
       <c r="AG97">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>1.25</v>
       </c>
       <c r="AK97">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>1.37</v>
       </c>
       <c r="T99">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U99">
         <v>2.7</v>
@@ -16473,22 +16473,22 @@
         <v>1.38</v>
       </c>
       <c r="W99">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z99">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA99">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB99">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC99">
         <v>3.28</v>
@@ -16497,7 +16497,7 @@
         <v>1.3</v>
       </c>
       <c r="AE99">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF99">
         <v>1.7</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK99">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16615,19 +16615,19 @@
         <v>4.25</v>
       </c>
       <c r="P100">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="Q100">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R100">
         <v>2.4</v>
       </c>
       <c r="S100">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T100">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U100">
         <v>2.27</v>
@@ -16639,7 +16639,7 @@
         <v>1.11</v>
       </c>
       <c r="X100">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
         <v>1.2</v>
@@ -16648,7 +16648,7 @@
         <v>4.2</v>
       </c>
       <c r="AA100">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB100">
         <v>2.2</v>
@@ -16657,13 +16657,13 @@
         <v>2.6</v>
       </c>
       <c r="AD100">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE100">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF100">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG100">
         <v>2</v>
@@ -16775,58 +16775,58 @@
         <v>2.09</v>
       </c>
       <c r="O101">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="P101">
         <v>3.15</v>
       </c>
       <c r="Q101">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R101">
         <v>2.4</v>
       </c>
       <c r="S101">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T101">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U101">
         <v>2.14</v>
       </c>
       <c r="V101">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W101">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X101">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z101">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA101">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB101">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AC101">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD101">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AE101">
         <v>1.22</v>
       </c>
       <c r="AF101">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG101">
         <v>2.6</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16947,34 +16947,34 @@
         <v>2.3</v>
       </c>
       <c r="R102">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S102">
         <v>1.36</v>
       </c>
       <c r="T102">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="V102">
         <v>1.39</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AA102">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AB102">
         <v>1.83</v>
@@ -16986,10 +16986,10 @@
         <v>1.24</v>
       </c>
       <c r="AE102">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF102">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG102">
         <v>1.85</v>
@@ -17008,7 +17008,7 @@
         <v>1.17</v>
       </c>
       <c r="AK102">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17104,7 +17104,7 @@
         <v>3.7</v>
       </c>
       <c r="P103">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="Q103">
         <v>4.42</v>
@@ -17125,16 +17125,16 @@
         <v>1.5</v>
       </c>
       <c r="W103">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
         <v>1.21</v>
       </c>
       <c r="Z103">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="AA103">
         <v>1.67</v>
@@ -17143,16 +17143,16 @@
         <v>2.15</v>
       </c>
       <c r="AC103">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD103">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE103">
         <v>1.15</v>
       </c>
       <c r="AF103">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG103">
         <v>2.1</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
         <v>1.25</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O104">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P104">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Q104">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R104">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U104">
-        <v>2.23</v>
+        <v>2.95</v>
       </c>
       <c r="V104">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="W104">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y104">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="Z104">
-        <v>4.75</v>
+        <v>3.37</v>
       </c>
       <c r="AA104">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="AB104">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AC104">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="AD104">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AE104">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF104">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AK104">
         <v>1.5</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O105">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="P105">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="Q105">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="R105">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S105">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T105">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="U105">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="V105">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z105">
-        <v>3.18</v>
+        <v>4.75</v>
       </c>
       <c r="AA105">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="AB105">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AC105">
-        <v>3.3</v>
+        <v>2.27</v>
       </c>
       <c r="AD105">
+        <v>1.62</v>
+      </c>
+      <c r="AE105">
+        <v>1.25</v>
+      </c>
+      <c r="AF105">
+        <v>1.43</v>
+      </c>
+      <c r="AG105">
+        <v>2.5</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
         <v>1.29</v>
       </c>
-      <c r="AE105">
-        <v>1.1</v>
-      </c>
-      <c r="AF105">
-        <v>1.75</v>
-      </c>
-      <c r="AG105">
-        <v>1.95</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.38</v>
-      </c>
       <c r="AK105">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O107">
         <v>4.33</v>
       </c>
       <c r="P107">
-        <v>6.35</v>
+        <v>5.75</v>
       </c>
       <c r="Q107">
         <v>1.83</v>
@@ -17765,7 +17765,7 @@
         <v>2.5</v>
       </c>
       <c r="S107">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
         <v>3.25</v>
@@ -17804,7 +17804,7 @@
         <v>1.2</v>
       </c>
       <c r="AF107">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG107">
         <v>1.95</v>
@@ -17916,37 +17916,37 @@
         <v>1.95</v>
       </c>
       <c r="O108">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
         <v>3.25</v>
       </c>
       <c r="Q108">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R108">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S108">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T108">
         <v>3.25</v>
       </c>
       <c r="U108">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V108">
         <v>1.51</v>
       </c>
       <c r="W108">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X108">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y108">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z108">
         <v>4.15</v>
@@ -17958,13 +17958,13 @@
         <v>2.12</v>
       </c>
       <c r="AC108">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AD108">
         <v>1.43</v>
       </c>
       <c r="AE108">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF108">
         <v>1.58</v>
@@ -18079,7 +18079,7 @@
         <v>2.75</v>
       </c>
       <c r="O109">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P109">
         <v>2.15</v>
@@ -18088,31 +18088,31 @@
         <v>3.25</v>
       </c>
       <c r="R109">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S109">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T109">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U109">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="V109">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W109">
         <v>1.07</v>
       </c>
       <c r="X109">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y109">
         <v>1.2</v>
       </c>
       <c r="Z109">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AA109">
         <v>1.64</v>
@@ -18121,16 +18121,16 @@
         <v>2.12</v>
       </c>
       <c r="AC109">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AD109">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE109">
         <v>1.17</v>
       </c>
       <c r="AF109">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG109">
         <v>2.3</v>
@@ -18149,7 +18149,7 @@
         <v>1.21</v>
       </c>
       <c r="AK109">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="O110">
         <v>5</v>
       </c>
       <c r="P110">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q110">
         <v>1.75</v>
@@ -18254,10 +18254,10 @@
         <v>2.63</v>
       </c>
       <c r="S110">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T110">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="U110">
         <v>2.1</v>
@@ -18272,22 +18272,22 @@
         <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z110">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA110">
         <v>1.44</v>
       </c>
       <c r="AB110">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC110">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AD110">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE110">
         <v>1.25</v>
@@ -18402,37 +18402,37 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O111">
         <v>3.4</v>
       </c>
       <c r="P111">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q111">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="R111">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T111">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U111">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V111">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W111">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X111">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y111">
         <v>1.25</v>
@@ -18450,13 +18450,13 @@
         <v>2.9</v>
       </c>
       <c r="AD111">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE111">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF111">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG111">
         <v>2.2</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AK111">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19057,16 +19057,16 @@
         <v>2.15</v>
       </c>
       <c r="O115">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P115">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="Q115">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R115">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S115">
         <v>1.4</v>
@@ -19078,10 +19078,10 @@
         <v>2.8</v>
       </c>
       <c r="V115">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
         <v>1.01</v>
@@ -19090,16 +19090,16 @@
         <v>1.3</v>
       </c>
       <c r="Z115">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA115">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AB115">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC115">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="AD115">
         <v>1.31</v>
@@ -19108,10 +19108,10 @@
         <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG115">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O116">
         <v>3.2</v>
       </c>
       <c r="P116">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q116">
         <v>2.93</v>
@@ -19235,46 +19235,46 @@
         <v>1.44</v>
       </c>
       <c r="T116">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U116">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V116">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W116">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X116">
         <v>1.1</v>
       </c>
       <c r="Y116">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z116">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="AA116">
         <v>2.3</v>
       </c>
       <c r="AB116">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC116">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AD116">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE116">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF116">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG116">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19380,58 +19380,58 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O117">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P117">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q117">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S117">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T117">
         <v>3.6</v>
       </c>
       <c r="U117">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V117">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W117">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z117">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA117">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB117">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC117">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AD117">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE117">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF117">
         <v>1.67</v>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK117">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -20195,34 +20195,34 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O122">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P122">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q122">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="R122">
         <v>2</v>
       </c>
       <c r="S122">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T122">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U122">
         <v>2.88</v>
       </c>
       <c r="V122">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W122">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
         <v>1.01</v>
@@ -20234,19 +20234,19 @@
         <v>3.14</v>
       </c>
       <c r="AA122">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB122">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AC122">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD122">
         <v>1.26</v>
       </c>
       <c r="AE122">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF122">
         <v>1.73</v>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20705,7 +20705,7 @@
         <v>3.6</v>
       </c>
       <c r="U125">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="V125">
         <v>1.53</v>
@@ -20717,25 +20717,25 @@
         <v>1.03</v>
       </c>
       <c r="Y125">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z125">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA125">
         <v>1.57</v>
       </c>
       <c r="AB125">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC125">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AD125">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE125">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF125">
         <v>1.6</v>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AK125">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,16 +20847,16 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="O126">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P126">
         <v>2.77</v>
       </c>
       <c r="Q126">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R126">
         <v>2.05</v>
@@ -20868,7 +20868,7 @@
         <v>2.5</v>
       </c>
       <c r="U126">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V126">
         <v>1.36</v>
@@ -20904,7 +20904,7 @@
         <v>1.85</v>
       </c>
       <c r="AG126">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>1.36</v>
       </c>
       <c r="AK126">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21182,7 +21182,7 @@
         <v>0</v>
       </c>
       <c r="Q128">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R128">
         <v>2.4</v>
@@ -21194,43 +21194,43 @@
         <v>3.35</v>
       </c>
       <c r="U128">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="V128">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W128">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X128">
         <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z128">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA128">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB128">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AC128">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AD128">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE128">
         <v>1.18</v>
       </c>
       <c r="AF128">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG128">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK128">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21538,10 +21538,10 @@
         <v>4.45</v>
       </c>
       <c r="AA130">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB130">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC130">
         <v>2.43</v>
@@ -21550,7 +21550,7 @@
         <v>1.44</v>
       </c>
       <c r="AE130">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF130">
         <v>1.49</v>
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O131">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P131">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="Q131">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="R131">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S131">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T131">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="U131">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="V131">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W131">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X131">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z131">
-        <v>3.72</v>
+        <v>3.39</v>
       </c>
       <c r="AA131">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB131">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC131">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD131">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE131">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF131">
         <v>1.72</v>
       </c>
       <c r="AG131">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK131">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="O132">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P132">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="Q132">
         <v>2.76</v>
@@ -21840,16 +21840,16 @@
         <v>2.16</v>
       </c>
       <c r="S132">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T132">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="U132">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V132">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W132">
         <v>1.09</v>
@@ -21858,31 +21858,31 @@
         <v>1.04</v>
       </c>
       <c r="Y132">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z132">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA132">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB132">
         <v>1.95</v>
       </c>
       <c r="AC132">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AD132">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE132">
         <v>1.13</v>
       </c>
       <c r="AF132">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG132">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK132">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL132">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="G3">
@@ -798,65 +798,65 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.8</v>
+        <v>4.24</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="Q3">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R3">
+        <v>2.3</v>
+      </c>
+      <c r="S3">
+        <v>1.32</v>
+      </c>
+      <c r="T3">
+        <v>3.27</v>
+      </c>
+      <c r="U3">
+        <v>2.45</v>
+      </c>
+      <c r="V3">
+        <v>1.46</v>
+      </c>
+      <c r="W3">
+        <v>1.07</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
+        <v>1.19</v>
+      </c>
+      <c r="Z3">
+        <v>3.82</v>
+      </c>
+      <c r="AA3">
+        <v>1.76</v>
+      </c>
+      <c r="AB3">
+        <v>2.08</v>
+      </c>
+      <c r="AC3">
+        <v>2.72</v>
+      </c>
+      <c r="AD3">
+        <v>1.36</v>
+      </c>
+      <c r="AE3">
+        <v>1.14</v>
+      </c>
+      <c r="AF3">
+        <v>1.67</v>
+      </c>
+      <c r="AG3">
         <v>2.05</v>
       </c>
-      <c r="S3">
-        <v>1.42</v>
-      </c>
-      <c r="T3">
-        <v>2.79</v>
-      </c>
-      <c r="U3">
-        <v>2.9</v>
-      </c>
-      <c r="V3">
-        <v>1.36</v>
-      </c>
-      <c r="W3">
-        <v>1.05</v>
-      </c>
-      <c r="X3">
-        <v>1.04</v>
-      </c>
-      <c r="Y3">
-        <v>1.36</v>
-      </c>
-      <c r="Z3">
-        <v>2.8</v>
-      </c>
-      <c r="AA3">
-        <v>2.04</v>
-      </c>
-      <c r="AB3">
-        <v>1.67</v>
-      </c>
-      <c r="AC3">
-        <v>4.25</v>
-      </c>
-      <c r="AD3">
-        <v>1.17</v>
-      </c>
-      <c r="AE3">
-        <v>1.05</v>
-      </c>
-      <c r="AF3">
-        <v>1.81</v>
-      </c>
-      <c r="AG3">
-        <v>1.9</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.91</v>
       </c>
       <c r="AK3">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.24</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
-        <v>3.27</v>
+        <v>2.79</v>
       </c>
       <c r="U4">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="AA4">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="AB4">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AC4">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="AD4">
+        <v>1.17</v>
+      </c>
+      <c r="AE4">
+        <v>1.05</v>
+      </c>
+      <c r="AF4">
+        <v>1.81</v>
+      </c>
+      <c r="AG4">
+        <v>1.9</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.33</v>
+      </c>
+      <c r="AK4">
         <v>1.36</v>
-      </c>
-      <c r="AE4">
-        <v>1.14</v>
-      </c>
-      <c r="AF4">
-        <v>1.67</v>
-      </c>
-      <c r="AG4">
-        <v>2.05</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.91</v>
-      </c>
-      <c r="AK4">
-        <v>1.22</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O39">
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q39">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="R39">
         <v>2.35</v>
       </c>
       <c r="S39">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T39">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="U39">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB39">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AD39">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF39">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG39">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.21</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="O40">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q40">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="R40">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S40">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T40">
-        <v>2.99</v>
+        <v>3.14</v>
       </c>
       <c r="U40">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="V40">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA40">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB40">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC40">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF40">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK40">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P41">
-        <v>2.6</v>
+        <v>4.05</v>
       </c>
       <c r="Q41">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="R41">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="S41">
         <v>1.31</v>
       </c>
       <c r="T41">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="U41">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="V41">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
         <v>1.04</v>
@@ -7028,44 +7028,44 @@
         <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA41">
         <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD41">
         <v>1.36</v>
       </c>
       <c r="AE41">
+        <v>1.13</v>
+      </c>
+      <c r="AF41">
+        <v>1.68</v>
+      </c>
+      <c r="AG41">
+        <v>2</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.12</v>
       </c>
-      <c r="AF41">
-        <v>1.57</v>
-      </c>
-      <c r="AG41">
-        <v>2.38</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.21</v>
-      </c>
       <c r="AK41">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="O66">
+        <v>3.7</v>
+      </c>
+      <c r="P66">
+        <v>1.84</v>
+      </c>
+      <c r="Q66">
         <v>3.6</v>
       </c>
-      <c r="P66">
-        <v>1.99</v>
-      </c>
-      <c r="Q66">
-        <v>3.4</v>
-      </c>
       <c r="R66">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="S66">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="U66">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="V66">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z66">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA66">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AB66">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="AC66">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="AD66">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE66">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AF66">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG66">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="AK66">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.5</v>
+        <v>1.42</v>
       </c>
       <c r="O67">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P67">
-        <v>1.84</v>
+        <v>5.75</v>
       </c>
       <c r="Q67">
-        <v>3.6</v>
+        <v>1.93</v>
       </c>
       <c r="R67">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S67">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T67">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="U67">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="V67">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="W67">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z67">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA67">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AB67">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AC67">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="AD67">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AE67">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF67">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG67">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.85</v>
+        <v>1.1</v>
       </c>
       <c r="AK67">
-        <v>1.22</v>
+        <v>2.41</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,34 +11393,34 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.42</v>
+        <v>3.1</v>
       </c>
       <c r="O68">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>5.75</v>
+        <v>1.99</v>
       </c>
       <c r="Q68">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="R68">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="S68">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="T68">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="U68">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="V68">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W68">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
         <v>1.02</v>
@@ -11429,28 +11429,28 @@
         <v>1.09</v>
       </c>
       <c r="Z68">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA68">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB68">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AC68">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AD68">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AE68">
         <v>1.28</v>
       </c>
       <c r="AF68">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>2.41</v>
+        <v>1.33</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12045,19 +12045,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="O72">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="P72">
-        <v>8</v>
+        <v>7.03</v>
       </c>
       <c r="Q72">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="R72">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S72">
         <v>1.48</v>
@@ -12069,7 +12069,7 @@
         <v>3.18</v>
       </c>
       <c r="V72">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W72">
         <v>1.05</v>
@@ -12090,7 +12090,7 @@
         <v>1.61</v>
       </c>
       <c r="AC72">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AD72">
         <v>1.18</v>
@@ -12099,7 +12099,7 @@
         <v>1.02</v>
       </c>
       <c r="AF72">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AG72">
         <v>1.46</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK72">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P78">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="R78">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
         <v>1.29</v>
       </c>
       <c r="T78">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="U78">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V78">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W78">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA78">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB78">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC78">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD78">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE78">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF78">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK78">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q79">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="R79">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S79">
         <v>1.29</v>
       </c>
       <c r="T79">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U79">
+        <v>2.36</v>
+      </c>
+      <c r="V79">
+        <v>1.49</v>
+      </c>
+      <c r="W79">
+        <v>1.08</v>
+      </c>
+      <c r="X79">
+        <v>1.03</v>
+      </c>
+      <c r="Y79">
+        <v>1.18</v>
+      </c>
+      <c r="Z79">
+        <v>4.4</v>
+      </c>
+      <c r="AA79">
+        <v>1.65</v>
+      </c>
+      <c r="AB79">
+        <v>2.2</v>
+      </c>
+      <c r="AC79">
         <v>2.5</v>
       </c>
-      <c r="V79">
-        <v>1.47</v>
-      </c>
-      <c r="W79">
-        <v>1.11</v>
-      </c>
-      <c r="X79">
-        <v>1.04</v>
-      </c>
-      <c r="Y79">
+      <c r="AD79">
+        <v>1.44</v>
+      </c>
+      <c r="AE79">
+        <v>1.18</v>
+      </c>
+      <c r="AF79">
+        <v>1.75</v>
+      </c>
+      <c r="AG79">
+        <v>1.95</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.22</v>
       </c>
-      <c r="Z79">
-        <v>3.8</v>
-      </c>
-      <c r="AA79">
-        <v>1.73</v>
-      </c>
-      <c r="AB79">
-        <v>2</v>
-      </c>
-      <c r="AC79">
-        <v>2.88</v>
-      </c>
-      <c r="AD79">
-        <v>1.36</v>
-      </c>
-      <c r="AE79">
-        <v>1.14</v>
-      </c>
-      <c r="AF79">
-        <v>1.62</v>
-      </c>
-      <c r="AG79">
-        <v>2.15</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.29</v>
-      </c>
       <c r="AK79">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,80 +14979,80 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.2</v>
+        <v>2.05</v>
       </c>
       <c r="O90">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P90">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="Q90">
+        <v>2.4</v>
+      </c>
+      <c r="R90">
+        <v>2.75</v>
+      </c>
+      <c r="S90">
+        <v>1.14</v>
+      </c>
+      <c r="T90">
+        <v>4.8</v>
+      </c>
+      <c r="U90">
+        <v>1.85</v>
+      </c>
+      <c r="V90">
+        <v>1.85</v>
+      </c>
+      <c r="W90">
+        <v>1.22</v>
+      </c>
+      <c r="X90">
+        <v>1.01</v>
+      </c>
+      <c r="Y90">
+        <v>1.07</v>
+      </c>
+      <c r="Z90">
+        <v>6.75</v>
+      </c>
+      <c r="AA90">
+        <v>1.28</v>
+      </c>
+      <c r="AB90">
         <v>3.4</v>
       </c>
-      <c r="R90">
-        <v>2.5</v>
-      </c>
-      <c r="S90">
-        <v>1.22</v>
-      </c>
-      <c r="T90">
-        <v>3.58</v>
-      </c>
-      <c r="U90">
-        <v>2.16</v>
-      </c>
-      <c r="V90">
-        <v>1.73</v>
-      </c>
-      <c r="W90">
-        <v>1.13</v>
-      </c>
-      <c r="X90">
-        <v>1.02</v>
-      </c>
-      <c r="Y90">
-        <v>1.11</v>
-      </c>
-      <c r="Z90">
-        <v>5.4</v>
-      </c>
-      <c r="AA90">
-        <v>1.44</v>
-      </c>
-      <c r="AB90">
-        <v>2.63</v>
-      </c>
       <c r="AC90">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AD90">
+        <v>2</v>
+      </c>
+      <c r="AE90">
+        <v>1.36</v>
+      </c>
+      <c r="AF90">
+        <v>1.29</v>
+      </c>
+      <c r="AG90">
+        <v>3.25</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
+        <v>1.4</v>
+      </c>
+      <c r="AK90">
         <v>1.66</v>
-      </c>
-      <c r="AE90">
-        <v>1.3</v>
-      </c>
-      <c r="AF90">
-        <v>1.4</v>
-      </c>
-      <c r="AG90">
-        <v>2.7</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.17</v>
-      </c>
-      <c r="AK90">
-        <v>1.3</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="O91">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P91">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q91">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="S91">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>4.8</v>
+        <v>3.58</v>
       </c>
       <c r="U91">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="V91">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="W91">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z91">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="AA91">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AB91">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC91">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AD91">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AE91">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF91">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AG91">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK91">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -19389,7 +19389,7 @@
         <v>5.25</v>
       </c>
       <c r="Q117">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R117">
         <v>2.38</v>
@@ -19425,13 +19425,13 @@
         <v>2.21</v>
       </c>
       <c r="AC117">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AD117">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE117">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF117">
         <v>1.67</v>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK117">
         <v>2.3</v>
@@ -20397,10 +20397,10 @@
         <v>2.97</v>
       </c>
       <c r="AA123">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB123">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC123">
         <v>3.42</v>
@@ -21339,34 +21339,34 @@
         <v>2.2</v>
       </c>
       <c r="O129">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P129">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q129">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R129">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S129">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="T129">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U129">
         <v>4</v>
       </c>
       <c r="V129">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W129">
         <v>1.03</v>
       </c>
       <c r="X129">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y129">
         <v>1.54</v>
@@ -21375,25 +21375,25 @@
         <v>2.28</v>
       </c>
       <c r="AA129">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="AB129">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AC129">
-        <v>6.38</v>
+        <v>5.9</v>
       </c>
       <c r="AD129">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE129">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF129">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG129">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK129">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL129">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O39">
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="R39">
         <v>2.35</v>
       </c>
       <c r="S39">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T39">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="U39">
-        <v>2.46</v>
+        <v>2.23</v>
       </c>
       <c r="V39">
+        <v>1.5</v>
+      </c>
+      <c r="W39">
+        <v>1.09</v>
+      </c>
+      <c r="X39">
+        <v>1.03</v>
+      </c>
+      <c r="Y39">
+        <v>1.2</v>
+      </c>
+      <c r="Z39">
+        <v>4.2</v>
+      </c>
+      <c r="AA39">
+        <v>1.58</v>
+      </c>
+      <c r="AB39">
+        <v>2.1</v>
+      </c>
+      <c r="AC39">
+        <v>2.43</v>
+      </c>
+      <c r="AD39">
         <v>1.44</v>
       </c>
-      <c r="W39">
-        <v>1.08</v>
-      </c>
-      <c r="X39">
-        <v>1.04</v>
-      </c>
-      <c r="Y39">
-        <v>1.22</v>
-      </c>
-      <c r="Z39">
-        <v>3.8</v>
-      </c>
-      <c r="AA39">
-        <v>1.75</v>
-      </c>
-      <c r="AB39">
-        <v>2.05</v>
-      </c>
-      <c r="AC39">
-        <v>2.88</v>
-      </c>
-      <c r="AD39">
-        <v>1.36</v>
-      </c>
       <c r="AE39">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF39">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG39">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.21</v>
       </c>
       <c r="AK39">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,65 +6829,65 @@
         </is>
       </c>
       <c r="N40">
+        <v>1.67</v>
+      </c>
+      <c r="O40">
+        <v>3.7</v>
+      </c>
+      <c r="P40">
+        <v>4.05</v>
+      </c>
+      <c r="Q40">
+        <v>2.12</v>
+      </c>
+      <c r="R40">
+        <v>2.33</v>
+      </c>
+      <c r="S40">
+        <v>1.31</v>
+      </c>
+      <c r="T40">
+        <v>2.99</v>
+      </c>
+      <c r="U40">
+        <v>2.39</v>
+      </c>
+      <c r="V40">
+        <v>1.46</v>
+      </c>
+      <c r="W40">
+        <v>1.1</v>
+      </c>
+      <c r="X40">
+        <v>1.04</v>
+      </c>
+      <c r="Y40">
+        <v>1.22</v>
+      </c>
+      <c r="Z40">
+        <v>3.75</v>
+      </c>
+      <c r="AA40">
+        <v>1.75</v>
+      </c>
+      <c r="AB40">
+        <v>1.95</v>
+      </c>
+      <c r="AC40">
+        <v>2.9</v>
+      </c>
+      <c r="AD40">
+        <v>1.36</v>
+      </c>
+      <c r="AE40">
+        <v>1.13</v>
+      </c>
+      <c r="AF40">
+        <v>1.68</v>
+      </c>
+      <c r="AG40">
         <v>2</v>
       </c>
-      <c r="O40">
-        <v>3.4</v>
-      </c>
-      <c r="P40">
-        <v>3.1</v>
-      </c>
-      <c r="Q40">
-        <v>2.33</v>
-      </c>
-      <c r="R40">
-        <v>2.35</v>
-      </c>
-      <c r="S40">
-        <v>1.28</v>
-      </c>
-      <c r="T40">
-        <v>3.14</v>
-      </c>
-      <c r="U40">
-        <v>2.23</v>
-      </c>
-      <c r="V40">
-        <v>1.5</v>
-      </c>
-      <c r="W40">
-        <v>1.09</v>
-      </c>
-      <c r="X40">
-        <v>1.03</v>
-      </c>
-      <c r="Y40">
-        <v>1.2</v>
-      </c>
-      <c r="Z40">
-        <v>4.2</v>
-      </c>
-      <c r="AA40">
-        <v>1.58</v>
-      </c>
-      <c r="AB40">
-        <v>2.1</v>
-      </c>
-      <c r="AC40">
-        <v>2.43</v>
-      </c>
-      <c r="AD40">
-        <v>1.44</v>
-      </c>
-      <c r="AE40">
-        <v>1.17</v>
-      </c>
-      <c r="AF40">
-        <v>1.56</v>
-      </c>
-      <c r="AG40">
-        <v>2.23</v>
-      </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK40">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="O41">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>4.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q41">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="R41">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S41">
         <v>1.31</v>
       </c>
       <c r="T41">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="U41">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="V41">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
         <v>1.04</v>
@@ -7028,28 +7028,28 @@
         <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
         <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC41">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD41">
         <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK41">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="O72">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P72">
-        <v>7.03</v>
+        <v>6.85</v>
       </c>
       <c r="Q72">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="R72">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="S72">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T72">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U72">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="V72">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W72">
         <v>1.05</v>
       </c>
       <c r="X72">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y72">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Z72">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="AA72">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AB72">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AC72">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AD72">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE72">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF72">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AG72">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK72">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.28</v>
+        <v>2.05</v>
       </c>
       <c r="O87">
-        <v>5.25</v>
+        <v>4.05</v>
       </c>
       <c r="P87">
-        <v>7</v>
+        <v>2.8</v>
       </c>
       <c r="Q87">
-        <v>1.64</v>
+        <v>2.4</v>
       </c>
       <c r="R87">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="S87">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T87">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U87">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="V87">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="W87">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z87">
-        <v>6.2</v>
+        <v>6.75</v>
       </c>
       <c r="AA87">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AB87">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AC87">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AD87">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AE87">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF87">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AG87">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="AK87">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,58 +14653,58 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.43</v>
+        <v>3.2</v>
       </c>
       <c r="O88">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="P88">
-        <v>5</v>
+        <v>1.91</v>
       </c>
       <c r="Q88">
-        <v>1.82</v>
+        <v>3.4</v>
       </c>
       <c r="R88">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S88">
+        <v>1.22</v>
+      </c>
+      <c r="T88">
+        <v>3.58</v>
+      </c>
+      <c r="U88">
+        <v>2.16</v>
+      </c>
+      <c r="V88">
+        <v>1.73</v>
+      </c>
+      <c r="W88">
+        <v>1.13</v>
+      </c>
+      <c r="X88">
+        <v>1.02</v>
+      </c>
+      <c r="Y88">
         <v>1.11</v>
       </c>
-      <c r="T88">
-        <v>4.75</v>
-      </c>
-      <c r="U88">
-        <v>1.78</v>
-      </c>
-      <c r="V88">
-        <v>1.95</v>
-      </c>
-      <c r="W88">
-        <v>1.29</v>
-      </c>
-      <c r="X88">
-        <v>1.01</v>
-      </c>
-      <c r="Y88">
-        <v>1.05</v>
-      </c>
       <c r="Z88">
-        <v>8.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA88">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AB88">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC88">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AD88">
-        <v>2.18</v>
+        <v>1.66</v>
       </c>
       <c r="AE88">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AF88">
         <v>1.4</v>
@@ -14726,7 +14726,7 @@
         <v>1.17</v>
       </c>
       <c r="AK88">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.45</v>
+        <v>1.28</v>
       </c>
       <c r="O89">
-        <v>3.55</v>
+        <v>5.25</v>
       </c>
       <c r="P89">
-        <v>2.28</v>
+        <v>7</v>
       </c>
       <c r="Q89">
-        <v>3.02</v>
+        <v>1.64</v>
       </c>
       <c r="R89">
-        <v>2.31</v>
+        <v>3.03</v>
       </c>
       <c r="S89">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T89">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U89">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="V89">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="W89">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z89">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA89">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AB89">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AC89">
-        <v>2.16</v>
+        <v>1.89</v>
       </c>
       <c r="AD89">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AE89">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF89">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AG89">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="AK89">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="O90">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="P90">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="Q90">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="R90">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="S90">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T90">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="U90">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="V90">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="W90">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z90">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA90">
         <v>1.28</v>
       </c>
       <c r="AB90">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC90">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD90">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AE90">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AF90">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AG90">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="O91">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P91">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="Q91">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="R91">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S91">
         <v>1.22</v>
       </c>
       <c r="T91">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U91">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V91">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W91">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X91">
         <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA91">
         <v>1.44</v>
       </c>
       <c r="AB91">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AC91">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AD91">
         <v>1.66</v>
       </c>
       <c r="AE91">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AF91">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG91">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.17</v>
+        <v>1.48</v>
       </c>
       <c r="AK91">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
+        <v>1.5</v>
+      </c>
+      <c r="O123">
+        <v>3.6</v>
+      </c>
+      <c r="P123">
+        <v>5.75</v>
+      </c>
+      <c r="Q123">
+        <v>2.12</v>
+      </c>
+      <c r="R123">
+        <v>2.1</v>
+      </c>
+      <c r="S123">
+        <v>1.42</v>
+      </c>
+      <c r="T123">
+        <v>2.57</v>
+      </c>
+      <c r="U123">
+        <v>3</v>
+      </c>
+      <c r="V123">
+        <v>1.35</v>
+      </c>
+      <c r="W123">
+        <v>1.06</v>
+      </c>
+      <c r="X123">
+        <v>1.08</v>
+      </c>
+      <c r="Y123">
         <v>1.36</v>
       </c>
-      <c r="O123">
-        <v>4</v>
-      </c>
-      <c r="P123">
-        <v>7.5</v>
-      </c>
-      <c r="Q123">
-        <v>1.98</v>
-      </c>
-      <c r="R123">
-        <v>2.14</v>
-      </c>
-      <c r="S123">
-        <v>1.41</v>
-      </c>
-      <c r="T123">
-        <v>2.59</v>
-      </c>
-      <c r="U123">
-        <v>2.91</v>
-      </c>
-      <c r="V123">
-        <v>1.33</v>
-      </c>
-      <c r="W123">
+      <c r="Z123">
+        <v>3.1</v>
+      </c>
+      <c r="AA123">
+        <v>2.15</v>
+      </c>
+      <c r="AB123">
+        <v>1.67</v>
+      </c>
+      <c r="AC123">
+        <v>4.1</v>
+      </c>
+      <c r="AD123">
+        <v>1.2</v>
+      </c>
+      <c r="AE123">
         <v>1.07</v>
       </c>
-      <c r="X123">
-        <v>1.02</v>
-      </c>
-      <c r="Y123">
-        <v>1.3</v>
-      </c>
-      <c r="Z123">
-        <v>2.97</v>
-      </c>
-      <c r="AA123">
-        <v>2.1</v>
-      </c>
-      <c r="AB123">
-        <v>1.72</v>
-      </c>
-      <c r="AC123">
-        <v>3.42</v>
-      </c>
-      <c r="AD123">
-        <v>1.23</v>
-      </c>
-      <c r="AE123">
-        <v>1.05</v>
-      </c>
       <c r="AF123">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AG123">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AK123">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="AL123">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.24</v>
+        <v>3.95</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P3">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Q3">
         <v>4.2</v>
@@ -816,16 +816,16 @@
         <v>1.32</v>
       </c>
       <c r="T3">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="U3">
         <v>2.45</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.02</v>
@@ -837,16 +837,16 @@
         <v>3.82</v>
       </c>
       <c r="AA3">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC3">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
         <v>1.14</v>
@@ -855,7 +855,7 @@
         <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
         <v>1.22</v>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q4">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S4">
         <v>1.42</v>
       </c>
       <c r="T4">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="U4">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
         <v>1.05</v>
@@ -994,31 +994,31 @@
         <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z4">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AA4">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC4">
-        <v>4.25</v>
+        <v>3.62</v>
       </c>
       <c r="AD4">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
         <v>1.81</v>
       </c>
       <c r="AG4">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
         <v>1.36</v>
@@ -2283,46 +2283,46 @@
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="AA12">
         <v>1.86</v>
       </c>
       <c r="AB12">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,31 +2437,31 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>6.54</v>
+        <v>6.5</v>
       </c>
       <c r="R13">
         <v>2.3</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="U13">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W13">
         <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
         <v>3.34</v>
@@ -2470,7 +2470,7 @@
         <v>1.88</v>
       </c>
       <c r="AB13">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
         <v>3.25</v>
@@ -2479,13 +2479,13 @@
         <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="O19">
         <v>3.5</v>
       </c>
       <c r="P19">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
         <v>3.3</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T19">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U19">
         <v>2.2</v>
@@ -3442,28 +3442,28 @@
         <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA19">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB19">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AC19">
         <v>2.17</v>
       </c>
       <c r="AD19">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE19">
         <v>1.22</v>
       </c>
       <c r="AF19">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG19">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,31 +5199,31 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P30">
-        <v>3.72</v>
+        <v>3.55</v>
       </c>
       <c r="Q30">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R30">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="U30">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W30">
         <v>1.09</v>
@@ -5232,31 +5232,31 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z30">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="AA30">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AB30">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AC30">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AD30">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE30">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="O31">
         <v>3.34</v>
       </c>
       <c r="P31">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q31">
         <v>3</v>
       </c>
       <c r="R31">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T31">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="U31">
         <v>2.7</v>
@@ -5389,13 +5389,13 @@
         <v>1.38</v>
       </c>
       <c r="W31">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
         <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z31">
         <v>3.1</v>
@@ -5404,22 +5404,22 @@
         <v>2</v>
       </c>
       <c r="AB31">
+        <v>1.75</v>
+      </c>
+      <c r="AC31">
+        <v>3.51</v>
+      </c>
+      <c r="AD31">
+        <v>1.25</v>
+      </c>
+      <c r="AE31">
+        <v>1.08</v>
+      </c>
+      <c r="AF31">
         <v>1.77</v>
       </c>
-      <c r="AC31">
-        <v>3.4</v>
-      </c>
-      <c r="AD31">
-        <v>1.28</v>
-      </c>
-      <c r="AE31">
-        <v>1.04</v>
-      </c>
-      <c r="AF31">
-        <v>1.7</v>
-      </c>
       <c r="AG31">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,61 +5528,61 @@
         <v>4.4</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P32">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="Q32">
-        <v>4.4</v>
+        <v>4.96</v>
       </c>
       <c r="R32">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T32">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
         <v>2.31</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z32">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB32">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC32">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD32">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE32">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG32">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O33">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="P33">
-        <v>7.85</v>
+        <v>7.9</v>
       </c>
       <c r="Q33">
         <v>1.58</v>
@@ -5724,19 +5724,19 @@
         <v>1.08</v>
       </c>
       <c r="Z33">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA33">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AB33">
         <v>2.97</v>
       </c>
       <c r="AC33">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD33">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AE33">
         <v>1.34</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK33">
-        <v>3.7</v>
+        <v>3.19</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="O34">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="P34">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q34">
-        <v>3.75</v>
+        <v>3.43</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T34">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="U34">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="V34">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W34">
         <v>1.13</v>
@@ -5884,28 +5884,28 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB34">
         <v>2.5</v>
       </c>
       <c r="AC34">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AD34">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE34">
         <v>1.21</v>
       </c>
       <c r="AF34">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG34">
         <v>2.45</v>
@@ -6017,16 +6017,16 @@
         <v>1.7</v>
       </c>
       <c r="O35">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="Q35">
+        <v>2.25</v>
+      </c>
+      <c r="R35">
         <v>2.38</v>
-      </c>
-      <c r="R35">
-        <v>2.32</v>
       </c>
       <c r="S35">
         <v>1.25</v>
@@ -6035,7 +6035,7 @@
         <v>3.6</v>
       </c>
       <c r="U35">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="V35">
         <v>1.57</v>
@@ -6050,10 +6050,10 @@
         <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>4.6</v>
+        <v>4.76</v>
       </c>
       <c r="AA35">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB35">
         <v>2.3</v>
@@ -6071,7 +6071,7 @@
         <v>1.53</v>
       </c>
       <c r="AG35">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK35">
         <v>1.95</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O38">
         <v>3.7</v>
@@ -6512,13 +6512,13 @@
         <v>3.9</v>
       </c>
       <c r="Q38">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T38">
         <v>3.45</v>
@@ -6527,40 +6527,40 @@
         <v>2.33</v>
       </c>
       <c r="V38">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W38">
         <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z38">
-        <v>4.91</v>
+        <v>4.45</v>
       </c>
       <c r="AA38">
         <v>1.56</v>
       </c>
       <c r="AB38">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AC38">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD38">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
         <v>1.53</v>
       </c>
       <c r="AG38">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>3.1</v>
+        <v>4.03</v>
       </c>
       <c r="Q39">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="R39">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
         <v>1.28</v>
       </c>
       <c r="T39">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="U39">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z39">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA39">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AB39">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC39">
-        <v>2.43</v>
+        <v>2.83</v>
       </c>
       <c r="AD39">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE39">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AG39">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="O40">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
+        <v>2.85</v>
+      </c>
+      <c r="Q40">
+        <v>2.84</v>
+      </c>
+      <c r="R40">
+        <v>2.3</v>
+      </c>
+      <c r="S40">
+        <v>1.3</v>
+      </c>
+      <c r="T40">
+        <v>3.04</v>
+      </c>
+      <c r="U40">
+        <v>2.36</v>
+      </c>
+      <c r="V40">
+        <v>1.48</v>
+      </c>
+      <c r="W40">
+        <v>1.09</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.16</v>
+      </c>
+      <c r="Z40">
         <v>4.05</v>
       </c>
-      <c r="Q40">
-        <v>2.12</v>
-      </c>
-      <c r="R40">
-        <v>2.33</v>
-      </c>
-      <c r="S40">
-        <v>1.31</v>
-      </c>
-      <c r="T40">
-        <v>2.99</v>
-      </c>
-      <c r="U40">
-        <v>2.39</v>
-      </c>
-      <c r="V40">
-        <v>1.46</v>
-      </c>
-      <c r="W40">
-        <v>1.1</v>
-      </c>
-      <c r="X40">
-        <v>1.04</v>
-      </c>
-      <c r="Y40">
-        <v>1.22</v>
-      </c>
-      <c r="Z40">
-        <v>3.75</v>
-      </c>
       <c r="AA40">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB40">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AC40">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK40">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,28 +6992,28 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="R41">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U41">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="V41">
         <v>1.44</v>
@@ -7022,34 +7022,34 @@
         <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC41">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD41">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE41">
         <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG41">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="U42">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V42">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
         <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC42">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
-        <v>1.92</v>
+        <v>1.69</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q44">
         <v>2.99</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S44">
         <v>1.36</v>
@@ -7502,7 +7502,7 @@
         <v>2.82</v>
       </c>
       <c r="U44">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="V44">
         <v>1.44</v>
@@ -7511,10 +7511,10 @@
         <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y44">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z44">
         <v>3.58</v>
@@ -7526,19 +7526,19 @@
         <v>1.93</v>
       </c>
       <c r="AC44">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD44">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE44">
         <v>1.08</v>
       </c>
       <c r="AF44">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG44">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,61 +7644,61 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="O45">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="P45">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="Q45">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R45">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S45">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="T45">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="U45">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="V45">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W45">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
         <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z45">
-        <v>3.93</v>
+        <v>3.78</v>
       </c>
       <c r="AA45">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB45">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC45">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE45">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF45">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG45">
         <v>2.18</v>
@@ -7717,7 +7717,7 @@
         <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,25 +7807,25 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="O46">
         <v>4.2</v>
       </c>
       <c r="P46">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q46">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="R46">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="S46">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="U46">
         <v>2.1</v>
@@ -7840,22 +7840,22 @@
         <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="AA46">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB46">
-        <v>2.88</v>
+        <v>2.52</v>
       </c>
       <c r="AC46">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AD46">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AE46">
         <v>1.25</v>
@@ -7880,7 +7880,7 @@
         <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,49 +7979,49 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="R47">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S47">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U47">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="V47">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="W47">
         <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>4.12</v>
+        <v>3.62</v>
       </c>
       <c r="AA47">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB47">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC47">
         <v>3.3</v>
       </c>
       <c r="AD47">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE47">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF47">
         <v>2</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB48">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8305,13 +8305,13 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R49">
         <v>2.29</v>
       </c>
       <c r="S49">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
         <v>3.35</v>
@@ -8323,16 +8323,16 @@
         <v>1.54</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
         <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="AA49">
         <v>1.61</v>
@@ -8341,16 +8341,16 @@
         <v>2.27</v>
       </c>
       <c r="AC49">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AD49">
         <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF49">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
         <v>2.23</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
         <v>2</v>
@@ -8462,22 +8462,22 @@
         <v>3.5</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q50">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R50">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="U50">
         <v>2.23</v>
@@ -8486,37 +8486,37 @@
         <v>1.6</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA50">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AB50">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AC50">
         <v>2.31</v>
       </c>
       <c r="AD50">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE50">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
         <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="O51">
         <v>3.6</v>
       </c>
       <c r="P51">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q51">
         <v>3</v>
@@ -8646,34 +8646,34 @@
         <v>2.25</v>
       </c>
       <c r="V51">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA51">
         <v>1.56</v>
       </c>
       <c r="AB51">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AC51">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="AD51">
         <v>1.52</v>
       </c>
       <c r="AE51">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF51">
         <v>1.47</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,28 +8785,28 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="O52">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P52">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="Q52">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="R52">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="S52">
         <v>1.22</v>
       </c>
       <c r="T52">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="U52">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V52">
         <v>1.67</v>
@@ -8818,22 +8818,22 @@
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>5.1</v>
+        <v>6.01</v>
       </c>
       <c r="AA52">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB52">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AC52">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD52">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AE52">
         <v>1.25</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,52 +8957,52 @@
         <v>3.7</v>
       </c>
       <c r="Q53">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="R53">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="S53">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T53">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U53">
         <v>3.04</v>
       </c>
       <c r="V53">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X53">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="Z53">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="AA53">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB53">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC53">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="AD53">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE53">
         <v>1.04</v>
       </c>
       <c r="AF53">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG53">
         <v>1.8</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK53">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9277,61 +9277,61 @@
         <v>2</v>
       </c>
       <c r="O55">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P55">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="Q55">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="R55">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S55">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T55">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="U55">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="V55">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W55">
+        <v>1.02</v>
+      </c>
+      <c r="X55">
+        <v>1.04</v>
+      </c>
+      <c r="Y55">
+        <v>1.36</v>
+      </c>
+      <c r="Z55">
+        <v>2.7</v>
+      </c>
+      <c r="AA55">
+        <v>2.25</v>
+      </c>
+      <c r="AB55">
+        <v>1.61</v>
+      </c>
+      <c r="AC55">
+        <v>3.84</v>
+      </c>
+      <c r="AD55">
+        <v>1.18</v>
+      </c>
+      <c r="AE55">
         <v>1.03</v>
       </c>
-      <c r="X55">
-        <v>1.03</v>
-      </c>
-      <c r="Y55">
-        <v>1.33</v>
-      </c>
-      <c r="Z55">
-        <v>2.83</v>
-      </c>
-      <c r="AA55">
-        <v>2.09</v>
-      </c>
-      <c r="AB55">
-        <v>1.66</v>
-      </c>
-      <c r="AC55">
-        <v>3.68</v>
-      </c>
-      <c r="AD55">
-        <v>1.2</v>
-      </c>
-      <c r="AE55">
-        <v>1.04</v>
-      </c>
       <c r="AF55">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AG55">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK55">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O57">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P57">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q57">
         <v>3.1</v>
       </c>
       <c r="R57">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
         <v>1.23</v>
@@ -9621,37 +9621,37 @@
         <v>3.42</v>
       </c>
       <c r="U57">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
         <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>4.75</v>
+        <v>5.24</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB57">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AC57">
         <v>2.25</v>
       </c>
       <c r="AD57">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE57">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF57">
         <v>1.37</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
         <v>1.4</v>
@@ -9935,25 +9935,25 @@
         <v>3.2</v>
       </c>
       <c r="Q59">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="R59">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S59">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T59">
         <v>2.59</v>
       </c>
       <c r="U59">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="V59">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W59">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X59">
         <v>1.02</v>
@@ -9962,19 +9962,19 @@
         <v>1.32</v>
       </c>
       <c r="Z59">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="AA59">
         <v>2.13</v>
       </c>
       <c r="AB59">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC59">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD59">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE59">
         <v>1.05</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,19 +10089,19 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="O60">
-        <v>5.75</v>
+        <v>5.95</v>
       </c>
       <c r="P60">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="Q60">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="R60">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="S60">
         <v>1.2</v>
@@ -10110,59 +10110,59 @@
         <v>3.66</v>
       </c>
       <c r="U60">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V60">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W60">
+        <v>1.14</v>
+      </c>
+      <c r="X60">
+        <v>1.02</v>
+      </c>
+      <c r="Y60">
+        <v>1.09</v>
+      </c>
+      <c r="Z60">
+        <v>5.3</v>
+      </c>
+      <c r="AA60">
+        <v>1.47</v>
+      </c>
+      <c r="AB60">
+        <v>2.51</v>
+      </c>
+      <c r="AC60">
+        <v>2.12</v>
+      </c>
+      <c r="AD60">
+        <v>1.65</v>
+      </c>
+      <c r="AE60">
+        <v>1.22</v>
+      </c>
+      <c r="AF60">
+        <v>1.86</v>
+      </c>
+      <c r="AG60">
+        <v>1.91</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
         <v>1.13</v>
       </c>
-      <c r="X60">
-        <v>1.03</v>
-      </c>
-      <c r="Y60">
-        <v>1.15</v>
-      </c>
-      <c r="Z60">
-        <v>5.25</v>
-      </c>
-      <c r="AA60">
-        <v>1.5</v>
-      </c>
-      <c r="AB60">
-        <v>2.45</v>
-      </c>
-      <c r="AC60">
-        <v>2.25</v>
-      </c>
-      <c r="AD60">
-        <v>1.63</v>
-      </c>
-      <c r="AE60">
-        <v>1.25</v>
-      </c>
-      <c r="AF60">
-        <v>1.76</v>
-      </c>
-      <c r="AG60">
-        <v>1.92</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.06</v>
-      </c>
       <c r="AK60">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,22 +10252,22 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q61">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="R61">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S61">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T61">
         <v>3</v>
@@ -10279,37 +10279,37 @@
         <v>1.4</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z61">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA61">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB61">
         <v>1.85</v>
       </c>
       <c r="AC61">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD61">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE61">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF61">
         <v>1.71</v>
       </c>
       <c r="AG61">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK61">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O64">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P64">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="Q64">
-        <v>4.33</v>
+        <v>5.26</v>
       </c>
       <c r="R64">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="U64">
         <v>2.1</v>
       </c>
       <c r="V64">
+        <v>1.62</v>
+      </c>
+      <c r="W64">
+        <v>1.15</v>
+      </c>
+      <c r="X64">
+        <v>1.01</v>
+      </c>
+      <c r="Y64">
+        <v>1.13</v>
+      </c>
+      <c r="Z64">
+        <v>5.87</v>
+      </c>
+      <c r="AA64">
+        <v>1.47</v>
+      </c>
+      <c r="AB64">
+        <v>2.68</v>
+      </c>
+      <c r="AC64">
+        <v>2.2</v>
+      </c>
+      <c r="AD64">
         <v>1.65</v>
       </c>
-      <c r="W64">
-        <v>1.14</v>
-      </c>
-      <c r="X64">
-        <v>1.03</v>
-      </c>
-      <c r="Y64">
-        <v>1.11</v>
-      </c>
-      <c r="Z64">
-        <v>4.85</v>
-      </c>
-      <c r="AA64">
-        <v>1.5</v>
-      </c>
-      <c r="AB64">
-        <v>2.38</v>
-      </c>
-      <c r="AC64">
-        <v>2.24</v>
-      </c>
-      <c r="AD64">
-        <v>1.67</v>
-      </c>
       <c r="AE64">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF64">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG64">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK64">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="O66">
         <v>3.7</v>
@@ -11076,37 +11076,37 @@
         <v>1.84</v>
       </c>
       <c r="Q66">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R66">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U66">
         <v>2.2</v>
       </c>
       <c r="V66">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W66">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z66">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="AA66">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB66">
         <v>2.33</v>
@@ -11118,13 +11118,13 @@
         <v>1.57</v>
       </c>
       <c r="AE66">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF66">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG66">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="AK66">
         <v>1.22</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,65 +11230,65 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.42</v>
+        <v>3.1</v>
       </c>
       <c r="O67">
-        <v>4.55</v>
+        <v>3.75</v>
       </c>
       <c r="P67">
-        <v>5.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q67">
-        <v>1.93</v>
+        <v>3.3</v>
       </c>
       <c r="R67">
-        <v>2.52</v>
+        <v>2.31</v>
       </c>
       <c r="S67">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U67">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="V67">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="W67">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z67">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="AA67">
+        <v>1.42</v>
+      </c>
+      <c r="AB67">
+        <v>2.49</v>
+      </c>
+      <c r="AC67">
+        <v>2.12</v>
+      </c>
+      <c r="AD67">
+        <v>1.64</v>
+      </c>
+      <c r="AE67">
+        <v>1.25</v>
+      </c>
+      <c r="AF67">
         <v>1.4</v>
       </c>
-      <c r="AB67">
+      <c r="AG67">
         <v>2.7</v>
       </c>
-      <c r="AC67">
-        <v>2.06</v>
-      </c>
-      <c r="AD67">
-        <v>1.78</v>
-      </c>
-      <c r="AE67">
-        <v>1.28</v>
-      </c>
-      <c r="AF67">
-        <v>1.44</v>
-      </c>
-      <c r="AG67">
-        <v>2.3</v>
-      </c>
       <c r="AH67" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AK67">
-        <v>2.41</v>
+        <v>1.27</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.1</v>
+        <v>1.47</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P68">
-        <v>1.99</v>
+        <v>5.06</v>
       </c>
       <c r="Q68">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="R68">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="S68">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="T68">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="U68">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="V68">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W68">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
+        <v>1.13</v>
+      </c>
+      <c r="Z68">
+        <v>5.25</v>
+      </c>
+      <c r="AA68">
+        <v>1.4</v>
+      </c>
+      <c r="AB68">
+        <v>2.7</v>
+      </c>
+      <c r="AC68">
+        <v>2.02</v>
+      </c>
+      <c r="AD68">
+        <v>1.69</v>
+      </c>
+      <c r="AE68">
+        <v>1.29</v>
+      </c>
+      <c r="AF68">
+        <v>1.53</v>
+      </c>
+      <c r="AG68">
+        <v>2.32</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.09</v>
       </c>
-      <c r="Z68">
-        <v>5.5</v>
-      </c>
-      <c r="AA68">
-        <v>1.42</v>
-      </c>
-      <c r="AB68">
-        <v>2.49</v>
-      </c>
-      <c r="AC68">
-        <v>2.12</v>
-      </c>
-      <c r="AD68">
-        <v>1.67</v>
-      </c>
-      <c r="AE68">
-        <v>1.28</v>
-      </c>
-      <c r="AF68">
-        <v>1.4</v>
-      </c>
-      <c r="AG68">
-        <v>2.7</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.29</v>
-      </c>
       <c r="AK68">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11559,22 +11559,22 @@
         <v>2.05</v>
       </c>
       <c r="O69">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P69">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="Q69">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R69">
         <v>2.2</v>
       </c>
       <c r="S69">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T69">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="U69">
         <v>2.62</v>
@@ -11586,19 +11586,19 @@
         <v>1.06</v>
       </c>
       <c r="X69">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>3.55</v>
+        <v>3.76</v>
       </c>
       <c r="AA69">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB69">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AC69">
         <v>2.8</v>
@@ -11607,7 +11607,7 @@
         <v>1.32</v>
       </c>
       <c r="AE69">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF69">
         <v>1.7</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK69">
         <v>1.65</v>
@@ -11882,31 +11882,31 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="O71">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="P71">
-        <v>9.199999999999999</v>
+        <v>7.21</v>
       </c>
       <c r="Q71">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R71">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="S71">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T71">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U71">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V71">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W71">
         <v>1.12</v>
@@ -11915,10 +11915,10 @@
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z71">
-        <v>4.49</v>
+        <v>5</v>
       </c>
       <c r="AA71">
         <v>1.49</v>
@@ -11936,7 +11936,7 @@
         <v>1.18</v>
       </c>
       <c r="AF71">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG71">
         <v>1.82</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK71">
-        <v>3.3</v>
+        <v>3.03</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="O72">
         <v>3.35</v>
@@ -12054,10 +12054,10 @@
         <v>6.85</v>
       </c>
       <c r="Q72">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R72">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="S72">
         <v>1.5</v>
@@ -12217,28 +12217,28 @@
         <v>3.8</v>
       </c>
       <c r="Q73">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R73">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="S73">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T73">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U73">
         <v>2.81</v>
       </c>
       <c r="V73">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W73">
+        <v>1.08</v>
+      </c>
+      <c r="X73">
         <v>1.03</v>
-      </c>
-      <c r="X73">
-        <v>1.01</v>
       </c>
       <c r="Y73">
         <v>1.3</v>
@@ -12247,16 +12247,16 @@
         <v>3.55</v>
       </c>
       <c r="AA73">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB73">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC73">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="AD73">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE73">
         <v>1.06</v>
@@ -12265,23 +12265,23 @@
         <v>1.75</v>
       </c>
       <c r="AG73">
+        <v>1.95</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>1.3</v>
+      </c>
+      <c r="AK73">
         <v>1.85</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.28</v>
-      </c>
-      <c r="AK73">
-        <v>1.92</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,19 +12371,19 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P74">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="Q74">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="R74">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S74">
         <v>1.36</v>
@@ -12401,7 +12401,7 @@
         <v>1.07</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
         <v>1.19</v>
@@ -12425,10 +12425,10 @@
         <v>1.11</v>
       </c>
       <c r="AF74">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG74">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK74">
         <v>2.05</v>
@@ -12537,61 +12537,61 @@
         <v>2.05</v>
       </c>
       <c r="O75">
+        <v>3.4</v>
+      </c>
+      <c r="P75">
         <v>3.25</v>
       </c>
-      <c r="P75">
-        <v>2.85</v>
-      </c>
       <c r="Q75">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R75">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="U75">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="V75">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W75">
+        <v>1.06</v>
+      </c>
+      <c r="X75">
         <v>1.04</v>
       </c>
-      <c r="X75">
-        <v>1.01</v>
-      </c>
       <c r="Y75">
+        <v>1.25</v>
+      </c>
+      <c r="Z75">
+        <v>3.6</v>
+      </c>
+      <c r="AA75">
+        <v>1.87</v>
+      </c>
+      <c r="AB75">
+        <v>1.9</v>
+      </c>
+      <c r="AC75">
+        <v>3.2</v>
+      </c>
+      <c r="AD75">
         <v>1.33</v>
       </c>
-      <c r="Z75">
-        <v>3.25</v>
-      </c>
-      <c r="AA75">
-        <v>1.95</v>
-      </c>
-      <c r="AB75">
-        <v>1.83</v>
-      </c>
-      <c r="AC75">
-        <v>3.5</v>
-      </c>
-      <c r="AD75">
-        <v>1.29</v>
-      </c>
       <c r="AE75">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF75">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG75">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK75">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,10 +12697,10 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="O76">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
         <v>2.25</v>
@@ -12709,46 +12709,46 @@
         <v>3.45</v>
       </c>
       <c r="R76">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="S76">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>2.73</v>
+        <v>3.03</v>
       </c>
       <c r="U76">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V76">
         <v>1.43</v>
       </c>
       <c r="W76">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X76">
         <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>3.55</v>
+        <v>3.66</v>
       </c>
       <c r="AA76">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AB76">
         <v>1.87</v>
       </c>
       <c r="AC76">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="AD76">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE76">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF76">
         <v>1.7</v>
@@ -12770,7 +12770,7 @@
         <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,46 +12869,46 @@
         <v>3</v>
       </c>
       <c r="Q77">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="R77">
         <v>1.95</v>
       </c>
       <c r="S77">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T77">
         <v>2.45</v>
       </c>
       <c r="U77">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="V77">
         <v>1.29</v>
       </c>
       <c r="W77">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X77">
         <v>1.1</v>
       </c>
       <c r="Y77">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z77">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AA77">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AB77">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AC77">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AD77">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE77">
         <v>1.04</v>
@@ -12917,7 +12917,7 @@
         <v>2</v>
       </c>
       <c r="AG77">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.33</v>
       </c>
       <c r="AK77">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,37 +13032,37 @@
         <v>0</v>
       </c>
       <c r="Q78">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T78">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U78">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="V78">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W78">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z78">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA78">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB78">
         <v>2</v>
@@ -13071,16 +13071,16 @@
         <v>2.88</v>
       </c>
       <c r="AD78">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE78">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF78">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG78">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13186,46 +13186,46 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O79">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="P79">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="Q79">
         <v>1.91</v>
       </c>
       <c r="R79">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="S79">
         <v>1.29</v>
       </c>
       <c r="T79">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U79">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="V79">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W79">
         <v>1.08</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
         <v>1.18</v>
       </c>
       <c r="Z79">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA79">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB79">
         <v>2.2</v>
@@ -13234,7 +13234,7 @@
         <v>2.5</v>
       </c>
       <c r="AD79">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE79">
         <v>1.18</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK79">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O80">
         <v>3.7</v>
       </c>
       <c r="P80">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O81">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P81">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q81">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="R81">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S81">
         <v>1.36</v>
@@ -13545,31 +13545,31 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z81">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA81">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB81">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC81">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD81">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE81">
         <v>1.11</v>
       </c>
       <c r="AF81">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG81">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="O82">
         <v>3.15</v>
@@ -13841,61 +13841,61 @@
         <v>1.17</v>
       </c>
       <c r="O83">
-        <v>8.25</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="P83">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q83">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="R83">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="S83">
         <v>1.12</v>
       </c>
       <c r="T83">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="U83">
         <v>1.8</v>
       </c>
       <c r="V83">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="W83">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z83">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA83">
         <v>1.28</v>
       </c>
       <c r="AB83">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AC83">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AD83">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE83">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AF83">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG83">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.06</v>
       </c>
       <c r="AK83">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="O84">
         <v>3.5</v>
       </c>
       <c r="P84">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q84">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R84">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S84">
         <v>1.25</v>
@@ -14025,7 +14025,7 @@
         <v>2.2</v>
       </c>
       <c r="V84">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W84">
         <v>1.13</v>
@@ -14037,19 +14037,19 @@
         <v>1.14</v>
       </c>
       <c r="Z84">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA84">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB84">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC84">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD84">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE84">
         <v>1.22</v>
@@ -14074,7 +14074,7 @@
         <v>1.23</v>
       </c>
       <c r="AK84">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O85">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P85">
         <v>3.4</v>
       </c>
       <c r="Q85">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R85">
         <v>2.6</v>
@@ -14182,10 +14182,10 @@
         <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="V85">
         <v>1.62</v>
@@ -14197,10 +14197,10 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z85">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AA85">
         <v>1.38</v>
@@ -14209,19 +14209,19 @@
         <v>2.62</v>
       </c>
       <c r="AC85">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AD85">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE85">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF85">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK85">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,40 +14327,40 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O86">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P86">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="Q86">
         <v>3.25</v>
       </c>
       <c r="R86">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="S86">
         <v>1.18</v>
       </c>
       <c r="T86">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U86">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="V86">
         <v>1.67</v>
       </c>
       <c r="W86">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z86">
         <v>5.65</v>
@@ -14372,10 +14372,10 @@
         <v>2.8</v>
       </c>
       <c r="AC86">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AD86">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AE86">
         <v>1.3</v>
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="O87">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="P87">
+        <v>2.87</v>
+      </c>
+      <c r="Q87">
+        <v>2.46</v>
+      </c>
+      <c r="R87">
         <v>2.8</v>
       </c>
-      <c r="Q87">
-        <v>2.4</v>
-      </c>
-      <c r="R87">
-        <v>2.75</v>
-      </c>
       <c r="S87">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T87">
         <v>4.8</v>
       </c>
       <c r="U87">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V87">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W87">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z87">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA87">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AB87">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="AC87">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AD87">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AE87">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AF87">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG87">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AK87">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,61 +14653,61 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.2</v>
+        <v>1.45</v>
       </c>
       <c r="O88">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="P88">
-        <v>1.91</v>
+        <v>4.85</v>
       </c>
       <c r="Q88">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="R88">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="S88">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T88">
-        <v>3.58</v>
+        <v>4.75</v>
       </c>
       <c r="U88">
-        <v>2.16</v>
+        <v>1.74</v>
       </c>
       <c r="V88">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="W88">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Z88">
-        <v>5.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA88">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AB88">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="AC88">
+        <v>1.62</v>
+      </c>
+      <c r="AD88">
         <v>2.15</v>
       </c>
-      <c r="AD88">
-        <v>1.66</v>
-      </c>
       <c r="AE88">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AF88">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AG88">
         <v>2.7</v>
@@ -14726,7 +14726,7 @@
         <v>1.17</v>
       </c>
       <c r="AK88">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14819,22 +14819,22 @@
         <v>1.28</v>
       </c>
       <c r="O89">
-        <v>5.25</v>
+        <v>5.55</v>
       </c>
       <c r="P89">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Q89">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R89">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="S89">
         <v>1.17</v>
       </c>
       <c r="T89">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="U89">
         <v>1.97</v>
@@ -14843,31 +14843,31 @@
         <v>1.77</v>
       </c>
       <c r="W89">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z89">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA89">
+        <v>1.33</v>
+      </c>
+      <c r="AB89">
+        <v>3</v>
+      </c>
+      <c r="AC89">
+        <v>1.91</v>
+      </c>
+      <c r="AD89">
+        <v>1.8</v>
+      </c>
+      <c r="AE89">
         <v>1.32</v>
-      </c>
-      <c r="AB89">
-        <v>2.88</v>
-      </c>
-      <c r="AC89">
-        <v>1.89</v>
-      </c>
-      <c r="AD89">
-        <v>1.86</v>
-      </c>
-      <c r="AE89">
-        <v>1.33</v>
       </c>
       <c r="AF89">
         <v>1.6</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK89">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.43</v>
+        <v>2.91</v>
       </c>
       <c r="O90">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="P90">
-        <v>5</v>
+        <v>1.92</v>
       </c>
       <c r="Q90">
-        <v>1.82</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S90">
+        <v>1.23</v>
+      </c>
+      <c r="T90">
+        <v>3.52</v>
+      </c>
+      <c r="U90">
+        <v>2.17</v>
+      </c>
+      <c r="V90">
+        <v>1.65</v>
+      </c>
+      <c r="W90">
+        <v>1.18</v>
+      </c>
+      <c r="X90">
+        <v>1.02</v>
+      </c>
+      <c r="Y90">
         <v>1.11</v>
       </c>
-      <c r="T90">
-        <v>4.75</v>
-      </c>
-      <c r="U90">
-        <v>1.78</v>
-      </c>
-      <c r="V90">
-        <v>1.95</v>
-      </c>
-      <c r="W90">
-        <v>1.29</v>
-      </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>1.05</v>
-      </c>
       <c r="Z90">
-        <v>8.5</v>
+        <v>5.28</v>
       </c>
       <c r="AA90">
+        <v>1.5</v>
+      </c>
+      <c r="AB90">
+        <v>2.5</v>
+      </c>
+      <c r="AC90">
+        <v>2.15</v>
+      </c>
+      <c r="AD90">
+        <v>1.66</v>
+      </c>
+      <c r="AE90">
         <v>1.28</v>
-      </c>
-      <c r="AB90">
-        <v>3.5</v>
-      </c>
-      <c r="AC90">
-        <v>1.67</v>
-      </c>
-      <c r="AD90">
-        <v>2.18</v>
-      </c>
-      <c r="AE90">
-        <v>1.51</v>
       </c>
       <c r="AF90">
         <v>1.4</v>
       </c>
       <c r="AG90">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK90">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15154,25 +15154,25 @@
         <v>3.02</v>
       </c>
       <c r="R91">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="S91">
         <v>1.22</v>
       </c>
       <c r="T91">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U91">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="V91">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W91">
         <v>1.15</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
         <v>1.13</v>
@@ -15184,22 +15184,22 @@
         <v>1.44</v>
       </c>
       <c r="AB91">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC91">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AD91">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE91">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF91">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG91">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AK91">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,22 +15305,22 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P92">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q92">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R92">
         <v>2.3</v>
       </c>
       <c r="S92">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T92">
         <v>3.02</v>
@@ -15341,7 +15341,7 @@
         <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>3.82</v>
+        <v>3.95</v>
       </c>
       <c r="AA92">
         <v>1.73</v>
@@ -15350,19 +15350,19 @@
         <v>1.99</v>
       </c>
       <c r="AC92">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD92">
         <v>1.34</v>
       </c>
       <c r="AE92">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF92">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15468,16 +15468,16 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O93">
         <v>3.45</v>
       </c>
       <c r="P93">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q93">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="R93">
         <v>2.45</v>
@@ -15492,10 +15492,10 @@
         <v>2.2</v>
       </c>
       <c r="V93">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X93">
         <v>1.01</v>
@@ -15504,22 +15504,22 @@
         <v>1.12</v>
       </c>
       <c r="Z93">
-        <v>4.89</v>
+        <v>4.65</v>
       </c>
       <c r="AA93">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB93">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AC93">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AD93">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE93">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF93">
         <v>1.44</v>
@@ -15634,13 +15634,13 @@
         <v>4.8</v>
       </c>
       <c r="O94">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P94">
         <v>1.53</v>
       </c>
       <c r="Q94">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R94">
         <v>2.4</v>
@@ -15652,37 +15652,37 @@
         <v>3.13</v>
       </c>
       <c r="U94">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="V94">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W94">
         <v>1.1</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z94">
         <v>4</v>
       </c>
       <c r="AA94">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB94">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC94">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD94">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE94">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF94">
         <v>1.73</v>
@@ -15806,13 +15806,13 @@
         <v>2.85</v>
       </c>
       <c r="R95">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S95">
         <v>1.29</v>
       </c>
       <c r="T95">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="U95">
         <v>2.46</v>
@@ -15821,37 +15821,37 @@
         <v>1.52</v>
       </c>
       <c r="W95">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y95">
         <v>1.19</v>
       </c>
       <c r="Z95">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA95">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AB95">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="AC95">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD95">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE95">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF95">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG95">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15957,55 +15957,55 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="O96">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q96">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="R96">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S96">
         <v>1.33</v>
       </c>
       <c r="T96">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U96">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="V96">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W96">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X96">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z96">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA96">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AB96">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC96">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD96">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE96">
         <v>1.12</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK96">
         <v>2.15</v>
@@ -16120,61 +16120,61 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O97">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P97">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q97">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="R97">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S97">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T97">
-        <v>3.52</v>
+        <v>3.62</v>
       </c>
       <c r="U97">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V97">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W97">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X97">
         <v>1.03</v>
       </c>
       <c r="Y97">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z97">
-        <v>5.02</v>
+        <v>4.85</v>
       </c>
       <c r="AA97">
+        <v>1.53</v>
+      </c>
+      <c r="AB97">
+        <v>2.5</v>
+      </c>
+      <c r="AC97">
+        <v>2.35</v>
+      </c>
+      <c r="AD97">
         <v>1.56</v>
       </c>
-      <c r="AB97">
-        <v>2.41</v>
-      </c>
-      <c r="AC97">
-        <v>2.4</v>
-      </c>
-      <c r="AD97">
-        <v>1.45</v>
-      </c>
       <c r="AE97">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF97">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG97">
         <v>2.5</v>
@@ -16283,10 +16283,10 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O98">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P98">
         <v>2.9</v>
@@ -16295,52 +16295,52 @@
         <v>2.8</v>
       </c>
       <c r="R98">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S98">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T98">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="U98">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V98">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="W98">
         <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z98">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA98">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB98">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AC98">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AD98">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AE98">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF98">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AG98">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16458,19 +16458,19 @@
         <v>3.6</v>
       </c>
       <c r="R99">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S99">
         <v>1.37</v>
       </c>
       <c r="T99">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="U99">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="V99">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W99">
         <v>1.06</v>
@@ -16479,47 +16479,47 @@
         <v>1.01</v>
       </c>
       <c r="Y99">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z99">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA99">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB99">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC99">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD99">
+        <v>1.28</v>
+      </c>
+      <c r="AE99">
+        <v>1.11</v>
+      </c>
+      <c r="AF99">
+        <v>1.69</v>
+      </c>
+      <c r="AG99">
+        <v>2.05</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.3</v>
       </c>
-      <c r="AE99">
-        <v>1.1</v>
-      </c>
-      <c r="AF99">
-        <v>1.7</v>
-      </c>
-      <c r="AG99">
-        <v>2.03</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.5</v>
-      </c>
       <c r="AK99">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16778,52 +16778,52 @@
         <v>3.75</v>
       </c>
       <c r="P101">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q101">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R101">
         <v>2.4</v>
       </c>
       <c r="S101">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T101">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U101">
         <v>2.14</v>
       </c>
       <c r="V101">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W101">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z101">
         <v>5</v>
       </c>
       <c r="AA101">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB101">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC101">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD101">
         <v>1.63</v>
       </c>
       <c r="AE101">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF101">
         <v>1.45</v>
@@ -16845,7 +16845,7 @@
         <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O104">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P104">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="Q104">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R104">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S104">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T104">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="U104">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="V104">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="W104">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X104">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="Z104">
-        <v>3.37</v>
+        <v>4.75</v>
       </c>
       <c r="AA104">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="AB104">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AC104">
-        <v>3.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD104">
+        <v>1.62</v>
+      </c>
+      <c r="AE104">
+        <v>1.25</v>
+      </c>
+      <c r="AF104">
+        <v>1.43</v>
+      </c>
+      <c r="AG104">
+        <v>2.5</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.29</v>
       </c>
-      <c r="AE104">
-        <v>1.08</v>
-      </c>
-      <c r="AF104">
-        <v>1.75</v>
-      </c>
-      <c r="AG104">
-        <v>1.95</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.3</v>
-      </c>
       <c r="AK104">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P105">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="Q105">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R105">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S105">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>3.34</v>
+        <v>2.8</v>
       </c>
       <c r="U105">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="V105">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="Z105">
-        <v>4.75</v>
+        <v>3.37</v>
       </c>
       <c r="AA105">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="AB105">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AC105">
-        <v>2.27</v>
+        <v>3.25</v>
       </c>
       <c r="AD105">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="AE105">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF105">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AG105">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18408,34 +18408,34 @@
         <v>3.4</v>
       </c>
       <c r="P111">
+        <v>2.21</v>
+      </c>
+      <c r="Q111">
+        <v>3.4</v>
+      </c>
+      <c r="R111">
         <v>2.25</v>
       </c>
-      <c r="Q111">
-        <v>3.5</v>
-      </c>
-      <c r="R111">
-        <v>2.1</v>
-      </c>
       <c r="S111">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T111">
         <v>2.96</v>
       </c>
       <c r="U111">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="V111">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W111">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X111">
         <v>1.05</v>
       </c>
       <c r="Y111">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z111">
         <v>3.9</v>
@@ -18444,10 +18444,10 @@
         <v>1.8</v>
       </c>
       <c r="AB111">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AC111">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD111">
         <v>1.36</v>
@@ -18459,7 +18459,7 @@
         <v>1.62</v>
       </c>
       <c r="AG111">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK111">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O113">
         <v>3.3</v>
@@ -18737,10 +18737,10 @@
         <v>5</v>
       </c>
       <c r="Q113">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R113">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S113">
         <v>1.42</v>
@@ -18752,13 +18752,13 @@
         <v>3.3</v>
       </c>
       <c r="V113">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W113">
         <v>1.03</v>
       </c>
       <c r="X113">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y113">
         <v>1.4</v>
@@ -18767,25 +18767,25 @@
         <v>2.8</v>
       </c>
       <c r="AA113">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB113">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC113">
-        <v>3.62</v>
+        <v>4.5</v>
       </c>
       <c r="AD113">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF113">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG113">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK113">
         <v>2</v>
@@ -18891,19 +18891,19 @@
         </is>
       </c>
       <c r="N114">
+        <v>2.69</v>
+      </c>
+      <c r="O114">
+        <v>3</v>
+      </c>
+      <c r="P114">
         <v>2.65</v>
       </c>
-      <c r="O114">
-        <v>3.1</v>
-      </c>
-      <c r="P114">
-        <v>2.55</v>
-      </c>
       <c r="Q114">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R114">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S114">
         <v>1.44</v>
@@ -18915,19 +18915,19 @@
         <v>3.06</v>
       </c>
       <c r="V114">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W114">
         <v>1.05</v>
       </c>
       <c r="X114">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y114">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z114">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA114">
         <v>2</v>
@@ -18936,13 +18936,13 @@
         <v>1.8</v>
       </c>
       <c r="AC114">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="AD114">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE114">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF114">
         <v>1.75</v>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK114">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         <v>3.5</v>
       </c>
       <c r="Q116">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="R116">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S116">
         <v>1.44</v>
@@ -19241,7 +19241,7 @@
         <v>3.25</v>
       </c>
       <c r="V116">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W116">
         <v>1.03</v>
@@ -19250,22 +19250,22 @@
         <v>1.1</v>
       </c>
       <c r="Y116">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="Z116">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AA116">
         <v>2.3</v>
       </c>
       <c r="AB116">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC116">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD116">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE116">
         <v>1.03</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AK116">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19386,16 +19386,16 @@
         <v>4.2</v>
       </c>
       <c r="P117">
-        <v>5.25</v>
+        <v>5.02</v>
       </c>
       <c r="Q117">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R117">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S117">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T117">
         <v>3.6</v>
@@ -19413,10 +19413,10 @@
         <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z117">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AA117">
         <v>1.64</v>
@@ -19425,13 +19425,13 @@
         <v>2.21</v>
       </c>
       <c r="AC117">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AD117">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE117">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF117">
         <v>1.67</v>
@@ -19543,80 +19543,80 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="O118">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P118">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="Q118">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="R118">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S118">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T118">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U118">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="V118">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z118">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AA118">
+        <v>1.9</v>
+      </c>
+      <c r="AB118">
+        <v>1.77</v>
+      </c>
+      <c r="AC118">
+        <v>3.5</v>
+      </c>
+      <c r="AD118">
+        <v>1.3</v>
+      </c>
+      <c r="AE118">
+        <v>1.05</v>
+      </c>
+      <c r="AF118">
+        <v>1.8</v>
+      </c>
+      <c r="AG118">
+        <v>1.85</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
+        <v>1.22</v>
+      </c>
+      <c r="AK118">
         <v>1.95</v>
-      </c>
-      <c r="AB118">
-        <v>1.85</v>
-      </c>
-      <c r="AC118">
-        <v>3.14</v>
-      </c>
-      <c r="AD118">
-        <v>1.27</v>
-      </c>
-      <c r="AE118">
-        <v>1.06</v>
-      </c>
-      <c r="AF118">
-        <v>1.85</v>
-      </c>
-      <c r="AG118">
-        <v>1.82</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.21</v>
-      </c>
-      <c r="AK118">
-        <v>2.3</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,80 +19706,80 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="O119">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P119">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="Q119">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="R119">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S119">
         <v>1.4</v>
       </c>
       <c r="T119">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U119">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V119">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W119">
+        <v>1.04</v>
+      </c>
+      <c r="X119">
         <v>1.03</v>
       </c>
-      <c r="X119">
-        <v>1.01</v>
-      </c>
       <c r="Y119">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z119">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA119">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AB119">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC119">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD119">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE119">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF119">
+        <v>1.76</v>
+      </c>
+      <c r="AG119">
+        <v>1.93</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
+        <v>1.3</v>
+      </c>
+      <c r="AK119">
         <v>1.75</v>
-      </c>
-      <c r="AG119">
-        <v>1.9</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.27</v>
-      </c>
-      <c r="AK119">
-        <v>1.52</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="O120">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P120">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q120">
-        <v>4.14</v>
+        <v>4.62</v>
       </c>
       <c r="R120">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S120">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="T120">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U120">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="V120">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X120">
         <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z120">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="AA120">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AB120">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC120">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD120">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE120">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF120">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG120">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AK120">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O121">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P121">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q121">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="R121">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S121">
+        <v>1.36</v>
+      </c>
+      <c r="T121">
+        <v>2.81</v>
+      </c>
+      <c r="U121">
+        <v>2.5</v>
+      </c>
+      <c r="V121">
+        <v>1.45</v>
+      </c>
+      <c r="W121">
+        <v>1.07</v>
+      </c>
+      <c r="X121">
+        <v>1.01</v>
+      </c>
+      <c r="Y121">
+        <v>1.22</v>
+      </c>
+      <c r="Z121">
+        <v>3.7</v>
+      </c>
+      <c r="AA121">
+        <v>1.77</v>
+      </c>
+      <c r="AB121">
+        <v>1.92</v>
+      </c>
+      <c r="AC121">
+        <v>2.78</v>
+      </c>
+      <c r="AD121">
+        <v>1.34</v>
+      </c>
+      <c r="AE121">
+        <v>1.13</v>
+      </c>
+      <c r="AF121">
+        <v>1.6</v>
+      </c>
+      <c r="AG121">
+        <v>2.15</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
         <v>1.33</v>
       </c>
-      <c r="T121">
-        <v>3</v>
-      </c>
-      <c r="U121">
-        <v>2.73</v>
-      </c>
-      <c r="V121">
-        <v>1.36</v>
-      </c>
-      <c r="W121">
-        <v>1.08</v>
-      </c>
-      <c r="X121">
-        <v>1.02</v>
-      </c>
-      <c r="Y121">
-        <v>1.26</v>
-      </c>
-      <c r="Z121">
-        <v>3.2</v>
-      </c>
-      <c r="AA121">
-        <v>1.9</v>
-      </c>
-      <c r="AB121">
-        <v>1.9</v>
-      </c>
-      <c r="AC121">
-        <v>3.08</v>
-      </c>
-      <c r="AD121">
-        <v>1.26</v>
-      </c>
-      <c r="AE121">
-        <v>1.07</v>
-      </c>
-      <c r="AF121">
-        <v>1.69</v>
-      </c>
-      <c r="AG121">
-        <v>2</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.27</v>
-      </c>
       <c r="AK121">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20198,25 +20198,25 @@
         <v>2.3</v>
       </c>
       <c r="O122">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P122">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="Q122">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R122">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S122">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T122">
         <v>2.75</v>
       </c>
       <c r="U122">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V122">
         <v>1.38</v>
@@ -20225,25 +20225,25 @@
         <v>1.08</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y122">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z122">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA122">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB122">
         <v>1.78</v>
       </c>
       <c r="AC122">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD122">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE122">
         <v>1.08</v>
@@ -20268,7 +20268,7 @@
         <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20364,16 +20364,16 @@
         <v>3.6</v>
       </c>
       <c r="P123">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="Q123">
         <v>2.12</v>
       </c>
       <c r="R123">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S123">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T123">
         <v>2.57</v>
@@ -20391,31 +20391,31 @@
         <v>1.08</v>
       </c>
       <c r="Y123">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z123">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AA123">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB123">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC123">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD123">
         <v>1.2</v>
       </c>
       <c r="AE123">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG123">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK123">
         <v>2.22</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>4.8</v>
+        <v>5.54</v>
       </c>
       <c r="O25">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="P25">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Q25">
-        <v>5.65</v>
+        <v>5.33</v>
       </c>
       <c r="R25">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="S25">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V25">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W25">
         <v>1.14</v>
@@ -4417,31 +4417,31 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z25">
-        <v>4.85</v>
+        <v>5.5</v>
       </c>
       <c r="AA25">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB25">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD25">
         <v>1.57</v>
       </c>
       <c r="AE25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>2.46</v>
+        <v>1.14</v>
       </c>
       <c r="AK25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4879,19 +4879,19 @@
         <v>4</v>
       </c>
       <c r="P28">
-        <v>4.2</v>
+        <v>4.08</v>
       </c>
       <c r="Q28">
         <v>2</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S28">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="U28">
         <v>2.25</v>
@@ -4900,7 +4900,7 @@
         <v>1.57</v>
       </c>
       <c r="W28">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4909,7 +4909,7 @@
         <v>1.11</v>
       </c>
       <c r="Z28">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA28">
         <v>1.53</v>
@@ -4921,13 +4921,13 @@
         <v>2.29</v>
       </c>
       <c r="AD28">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE28">
         <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
         <v>2.29</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK28">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O53">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P53">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q53">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="R53">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S53">
         <v>1.46</v>
@@ -8972,37 +8972,37 @@
         <v>3.04</v>
       </c>
       <c r="V53">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W53">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
         <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z53">
         <v>2.89</v>
       </c>
       <c r="AA53">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB53">
         <v>1.7</v>
       </c>
       <c r="AC53">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD53">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE53">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG53">
         <v>1.8</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,52 +9120,52 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R54">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U54">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="V54">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W54">
         <v>1.12</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA54">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB54">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AC54">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="AD54">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE54">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG54">
         <v>1.67</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="O57">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
         <v>2.2</v>
       </c>
       <c r="Q57">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S57">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="U57">
         <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W57">
+        <v>1.15</v>
+      </c>
+      <c r="X57">
+        <v>1.03</v>
+      </c>
+      <c r="Y57">
         <v>1.1</v>
       </c>
-      <c r="X57">
-        <v>1.01</v>
-      </c>
-      <c r="Y57">
-        <v>1.11</v>
-      </c>
       <c r="Z57">
-        <v>5.24</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
         <v>1.5</v>
       </c>
       <c r="AB57">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="AC57">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD57">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE57">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AK57">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>4.1</v>
       </c>
       <c r="P58">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="Q58">
         <v>2.03</v>
@@ -9778,13 +9778,13 @@
         <v>2.5</v>
       </c>
       <c r="S58">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T58">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="U58">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="V58">
         <v>1.61</v>
@@ -9793,19 +9793,19 @@
         <v>1.13</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z58">
         <v>5</v>
       </c>
       <c r="AA58">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB58">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC58">
         <v>2.27</v>
@@ -9814,10 +9814,10 @@
         <v>1.57</v>
       </c>
       <c r="AE58">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF58">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG58">
         <v>2.25</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10907,61 +10907,61 @@
         <v>1.9</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.47</v>
       </c>
       <c r="P65">
-        <v>3.49</v>
+        <v>3.57</v>
       </c>
       <c r="Q65">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R65">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U65">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="V65">
         <v>1.5</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z65">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AA65">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB65">
         <v>2.1</v>
       </c>
       <c r="AC65">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AD65">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG65">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK65">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
+        <v>1.87</v>
+      </c>
+      <c r="O70">
+        <v>3.1</v>
+      </c>
+      <c r="P70">
+        <v>3.8</v>
+      </c>
+      <c r="Q70">
+        <v>2.45</v>
+      </c>
+      <c r="R70">
+        <v>1.97</v>
+      </c>
+      <c r="S70">
+        <v>1.46</v>
+      </c>
+      <c r="T70">
+        <v>2.54</v>
+      </c>
+      <c r="U70">
+        <v>3.18</v>
+      </c>
+      <c r="V70">
+        <v>1.31</v>
+      </c>
+      <c r="W70">
+        <v>1.03</v>
+      </c>
+      <c r="X70">
+        <v>1.06</v>
+      </c>
+      <c r="Y70">
+        <v>1.36</v>
+      </c>
+      <c r="Z70">
+        <v>2.7</v>
+      </c>
+      <c r="AA70">
+        <v>2.17</v>
+      </c>
+      <c r="AB70">
+        <v>1.61</v>
+      </c>
+      <c r="AC70">
+        <v>3.82</v>
+      </c>
+      <c r="AD70">
+        <v>1.19</v>
+      </c>
+      <c r="AE70">
+        <v>1.06</v>
+      </c>
+      <c r="AF70">
+        <v>1.83</v>
+      </c>
+      <c r="AG70">
         <v>1.84</v>
       </c>
-      <c r="O70">
-        <v>3.25</v>
-      </c>
-      <c r="P70">
-        <v>4</v>
-      </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
-      </c>
-      <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
-      </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70">
-        <v>0</v>
-      </c>
-      <c r="Y70">
-        <v>0</v>
-      </c>
-      <c r="Z70">
-        <v>0</v>
-      </c>
-      <c r="AA70">
-        <v>0</v>
-      </c>
-      <c r="AB70">
-        <v>0</v>
-      </c>
-      <c r="AC70">
-        <v>0</v>
-      </c>
-      <c r="AD70">
-        <v>0</v>
-      </c>
-      <c r="AE70">
-        <v>0</v>
-      </c>
-      <c r="AF70">
-        <v>0</v>
-      </c>
-      <c r="AG70">
-        <v>0</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P76">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="Q76">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="R76">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="S76">
+        <v>1.49</v>
+      </c>
+      <c r="T76">
+        <v>2.45</v>
+      </c>
+      <c r="U76">
+        <v>3.28</v>
+      </c>
+      <c r="V76">
+        <v>1.29</v>
+      </c>
+      <c r="W76">
+        <v>1.03</v>
+      </c>
+      <c r="X76">
+        <v>1.1</v>
+      </c>
+      <c r="Y76">
+        <v>1.47</v>
+      </c>
+      <c r="Z76">
+        <v>2.63</v>
+      </c>
+      <c r="AA76">
+        <v>2.66</v>
+      </c>
+      <c r="AB76">
+        <v>1.48</v>
+      </c>
+      <c r="AC76">
+        <v>5</v>
+      </c>
+      <c r="AD76">
+        <v>1.17</v>
+      </c>
+      <c r="AE76">
+        <v>1.04</v>
+      </c>
+      <c r="AF76">
+        <v>2</v>
+      </c>
+      <c r="AG76">
+        <v>1.73</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.33</v>
       </c>
-      <c r="T76">
-        <v>3.03</v>
-      </c>
-      <c r="U76">
-        <v>2.62</v>
-      </c>
-      <c r="V76">
-        <v>1.43</v>
-      </c>
-      <c r="W76">
-        <v>1.06</v>
-      </c>
-      <c r="X76">
-        <v>1.03</v>
-      </c>
-      <c r="Y76">
-        <v>1.25</v>
-      </c>
-      <c r="Z76">
-        <v>3.66</v>
-      </c>
-      <c r="AA76">
-        <v>1.88</v>
-      </c>
-      <c r="AB76">
-        <v>1.87</v>
-      </c>
-      <c r="AC76">
-        <v>3.13</v>
-      </c>
-      <c r="AD76">
-        <v>1.36</v>
-      </c>
-      <c r="AE76">
-        <v>1.11</v>
-      </c>
-      <c r="AF76">
-        <v>1.7</v>
-      </c>
-      <c r="AG76">
-        <v>2.05</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.3</v>
-      </c>
       <c r="AK76">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
+        <v>2.92</v>
+      </c>
+      <c r="O77">
+        <v>3.2</v>
+      </c>
+      <c r="P77">
         <v>2.25</v>
       </c>
-      <c r="O77">
-        <v>2.9</v>
-      </c>
-      <c r="P77">
-        <v>3</v>
-      </c>
       <c r="Q77">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="R77">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="S77">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="T77">
-        <v>2.45</v>
+        <v>3.03</v>
       </c>
       <c r="U77">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="V77">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
+        <v>1.06</v>
+      </c>
+      <c r="X77">
         <v>1.03</v>
       </c>
-      <c r="X77">
-        <v>1.1</v>
-      </c>
       <c r="Y77">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>2.63</v>
+        <v>3.66</v>
       </c>
       <c r="AA77">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="AB77">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AC77">
-        <v>5</v>
+        <v>3.13</v>
       </c>
       <c r="AD77">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AE77">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,80 +14490,80 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.93</v>
+        <v>2.91</v>
       </c>
       <c r="O87">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="P87">
-        <v>2.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q87">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="R87">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="S87">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="T87">
-        <v>4.8</v>
+        <v>3.52</v>
       </c>
       <c r="U87">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="V87">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="W87">
+        <v>1.18</v>
+      </c>
+      <c r="X87">
+        <v>1.02</v>
+      </c>
+      <c r="Y87">
+        <v>1.11</v>
+      </c>
+      <c r="Z87">
+        <v>5.28</v>
+      </c>
+      <c r="AA87">
+        <v>1.5</v>
+      </c>
+      <c r="AB87">
+        <v>2.5</v>
+      </c>
+      <c r="AC87">
+        <v>2.15</v>
+      </c>
+      <c r="AD87">
+        <v>1.66</v>
+      </c>
+      <c r="AE87">
+        <v>1.28</v>
+      </c>
+      <c r="AF87">
+        <v>1.4</v>
+      </c>
+      <c r="AG87">
+        <v>2.69</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
         <v>1.25</v>
       </c>
-      <c r="X87">
-        <v>1.01</v>
-      </c>
-      <c r="Y87">
-        <v>1.03</v>
-      </c>
-      <c r="Z87">
-        <v>7.5</v>
-      </c>
-      <c r="AA87">
-        <v>1.23</v>
-      </c>
-      <c r="AB87">
-        <v>3.69</v>
-      </c>
-      <c r="AC87">
-        <v>1.69</v>
-      </c>
-      <c r="AD87">
-        <v>2.13</v>
-      </c>
-      <c r="AE87">
-        <v>1.43</v>
-      </c>
-      <c r="AF87">
+      <c r="AK87">
         <v>1.3</v>
-      </c>
-      <c r="AG87">
-        <v>3.42</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.19</v>
-      </c>
-      <c r="AK87">
-        <v>1.7</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.28</v>
+        <v>2.45</v>
       </c>
       <c r="O89">
-        <v>5.55</v>
+        <v>3.55</v>
       </c>
       <c r="P89">
-        <v>7.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q89">
-        <v>1.6</v>
+        <v>3.02</v>
       </c>
       <c r="R89">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="U89">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="V89">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="W89">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA89">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AB89">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC89">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AD89">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE89">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF89">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AG89">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="AK89">
-        <v>3.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.91</v>
+        <v>1.28</v>
       </c>
       <c r="O90">
-        <v>3.88</v>
+        <v>5.55</v>
       </c>
       <c r="P90">
-        <v>1.92</v>
+        <v>7.2</v>
       </c>
       <c r="Q90">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="R90">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="S90">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T90">
-        <v>3.52</v>
+        <v>4.05</v>
       </c>
       <c r="U90">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="V90">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="W90">
         <v>1.18</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z90">
-        <v>5.28</v>
+        <v>6.5</v>
       </c>
       <c r="AA90">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AB90">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC90">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD90">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AE90">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF90">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG90">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK90">
-        <v>1.3</v>
+        <v>3.38</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="O91">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="P91">
-        <v>2.28</v>
+        <v>2.87</v>
       </c>
       <c r="Q91">
-        <v>3.02</v>
+        <v>2.46</v>
       </c>
       <c r="R91">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T91">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="U91">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="V91">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z91">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA91">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AB91">
-        <v>2.5</v>
+        <v>3.69</v>
       </c>
       <c r="AC91">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AD91">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="AE91">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AF91">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG91">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AK91">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16612,13 +16612,13 @@
         <v>1.44</v>
       </c>
       <c r="O100">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P100">
-        <v>6</v>
+        <v>5.31</v>
       </c>
       <c r="Q100">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R100">
         <v>2.4</v>
@@ -16627,7 +16627,7 @@
         <v>1.29</v>
       </c>
       <c r="T100">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U100">
         <v>2.27</v>
@@ -16639,7 +16639,7 @@
         <v>1.11</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
         <v>1.2</v>
@@ -16648,25 +16648,25 @@
         <v>4.2</v>
       </c>
       <c r="AA100">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB100">
+        <v>2.16</v>
+      </c>
+      <c r="AC100">
         <v>2.2</v>
       </c>
-      <c r="AC100">
-        <v>2.6</v>
-      </c>
       <c r="AD100">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE100">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF100">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG100">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK100">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16944,56 +16944,56 @@
         <v>4.2</v>
       </c>
       <c r="Q102">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R102">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="S102">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T102">
         <v>2.88</v>
       </c>
       <c r="U102">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="V102">
         <v>1.39</v>
       </c>
       <c r="W102">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y102">
         <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA102">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB102">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC102">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AD102">
         <v>1.24</v>
       </c>
       <c r="AE102">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF102">
+        <v>1.85</v>
+      </c>
+      <c r="AG102">
         <v>1.83</v>
       </c>
-      <c r="AG102">
-        <v>1.85</v>
-      </c>
       <c r="AH102" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK102">
         <v>2</v>
@@ -17101,61 +17101,61 @@
         <v>3.5</v>
       </c>
       <c r="O103">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P103">
         <v>1.76</v>
       </c>
       <c r="Q103">
-        <v>4.42</v>
+        <v>3.8</v>
       </c>
       <c r="R103">
-        <v>2.42</v>
+        <v>2.19</v>
       </c>
       <c r="S103">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T103">
         <v>3.3</v>
       </c>
       <c r="U103">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V103">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W103">
         <v>1.08</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z103">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA103">
         <v>1.67</v>
       </c>
       <c r="AB103">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC103">
         <v>2.7</v>
       </c>
       <c r="AD103">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE103">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF103">
         <v>1.6</v>
       </c>
       <c r="AG103">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="O104">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P104">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="Q104">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="R104">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="T104">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="U104">
-        <v>2.15</v>
+        <v>2.73</v>
       </c>
       <c r="V104">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="W104">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
         <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z104">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA104">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="AB104">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="AC104">
-        <v>2.27</v>
+        <v>3.6</v>
       </c>
       <c r="AD104">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AE104">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF104">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.29</v>
       </c>
       <c r="AK104">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O105">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P105">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="Q105">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="R105">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="S105">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T105">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="U105">
-        <v>2.95</v>
+        <v>2.23</v>
       </c>
       <c r="V105">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="Z105">
-        <v>3.37</v>
+        <v>4.75</v>
       </c>
       <c r="AA105">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="AB105">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AC105">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="AD105">
+        <v>1.58</v>
+      </c>
+      <c r="AE105">
+        <v>1.21</v>
+      </c>
+      <c r="AF105">
+        <v>1.53</v>
+      </c>
+      <c r="AG105">
+        <v>2.5</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
         <v>1.29</v>
       </c>
-      <c r="AE105">
-        <v>1.08</v>
-      </c>
-      <c r="AF105">
-        <v>1.75</v>
-      </c>
-      <c r="AG105">
-        <v>1.95</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.3</v>
-      </c>
       <c r="AK105">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17753,7 +17753,7 @@
         <v>1.4</v>
       </c>
       <c r="O107">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P107">
         <v>5.75</v>
@@ -17765,13 +17765,13 @@
         <v>2.5</v>
       </c>
       <c r="S107">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T107">
         <v>3.25</v>
       </c>
       <c r="U107">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V107">
         <v>1.53</v>
@@ -17783,10 +17783,10 @@
         <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z107">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA107">
         <v>1.44</v>
@@ -17798,16 +17798,16 @@
         <v>2.1</v>
       </c>
       <c r="AD107">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE107">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF107">
         <v>1.73</v>
       </c>
       <c r="AG107">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK107">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,10 +17913,10 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O108">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P108">
         <v>3.25</v>
@@ -17931,43 +17931,43 @@
         <v>1.3</v>
       </c>
       <c r="T108">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U108">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V108">
         <v>1.51</v>
       </c>
       <c r="W108">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X108">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z108">
         <v>4.15</v>
       </c>
       <c r="AA108">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB108">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AC108">
         <v>2.61</v>
       </c>
       <c r="AD108">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE108">
         <v>1.17</v>
       </c>
       <c r="AF108">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG108">
         <v>2.25</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18079,7 +18079,7 @@
         <v>2.75</v>
       </c>
       <c r="O109">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P109">
         <v>2.15</v>
@@ -18088,10 +18088,10 @@
         <v>3.25</v>
       </c>
       <c r="R109">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S109">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T109">
         <v>3.25</v>
@@ -18103,28 +18103,28 @@
         <v>1.51</v>
       </c>
       <c r="W109">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X109">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
         <v>1.2</v>
       </c>
       <c r="Z109">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AA109">
         <v>1.64</v>
       </c>
       <c r="AB109">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC109">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AD109">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE109">
         <v>1.17</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18242,28 +18242,28 @@
         <v>1.35</v>
       </c>
       <c r="O110">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P110">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q110">
         <v>1.75</v>
       </c>
       <c r="R110">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="S110">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T110">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="U110">
         <v>2.1</v>
       </c>
       <c r="V110">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="W110">
         <v>1.17</v>
@@ -18272,22 +18272,22 @@
         <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z110">
         <v>5</v>
       </c>
       <c r="AA110">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB110">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AC110">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD110">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE110">
         <v>1.25</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AK110">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18737,28 +18737,28 @@
         <v>5</v>
       </c>
       <c r="Q113">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R113">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S113">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T113">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="U113">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V113">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W113">
         <v>1.03</v>
       </c>
       <c r="X113">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y113">
         <v>1.4</v>
@@ -18767,25 +18767,25 @@
         <v>2.8</v>
       </c>
       <c r="AA113">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB113">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC113">
-        <v>4.5</v>
+        <v>3.62</v>
       </c>
       <c r="AD113">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE113">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF113">
         <v>2</v>
       </c>
       <c r="AG113">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AK113">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="O114">
         <v>3</v>
@@ -18900,55 +18900,55 @@
         <v>2.65</v>
       </c>
       <c r="Q114">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="R114">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S114">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T114">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U114">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="V114">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X114">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y114">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z114">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="AA114">
         <v>2</v>
       </c>
       <c r="AB114">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC114">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="AD114">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE114">
         <v>1.08</v>
       </c>
       <c r="AF114">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG114">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>1.34</v>
       </c>
       <c r="AK114">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,34 +19054,34 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="Q115">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R115">
         <v>2.15</v>
       </c>
       <c r="S115">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T115">
         <v>2.77</v>
       </c>
       <c r="U115">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="V115">
         <v>1.38</v>
       </c>
       <c r="W115">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
         <v>1.01</v>
@@ -19090,25 +19090,25 @@
         <v>1.3</v>
       </c>
       <c r="Z115">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA115">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB115">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC115">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AD115">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE115">
         <v>1.06</v>
       </c>
       <c r="AF115">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG115">
         <v>1.95</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="O124">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P124">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20693,10 +20693,10 @@
         <v>0</v>
       </c>
       <c r="Q125">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="R125">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S125">
         <v>1.25</v>
@@ -20705,10 +20705,10 @@
         <v>3.6</v>
       </c>
       <c r="U125">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="V125">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W125">
         <v>1.13</v>
@@ -20717,7 +20717,7 @@
         <v>1.03</v>
       </c>
       <c r="Y125">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z125">
         <v>4.5</v>
@@ -20726,22 +20726,22 @@
         <v>1.57</v>
       </c>
       <c r="AB125">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC125">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AD125">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE125">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF125">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AG125">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK125">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="O126">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P126">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="Q126">
         <v>3.6</v>
@@ -20862,19 +20862,19 @@
         <v>2.05</v>
       </c>
       <c r="S126">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T126">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U126">
-        <v>3.04</v>
+        <v>3.24</v>
       </c>
       <c r="V126">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W126">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X126">
         <v>1.08</v>
@@ -20898,13 +20898,13 @@
         <v>1.22</v>
       </c>
       <c r="AE126">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF126">
         <v>1.85</v>
       </c>
       <c r="AG126">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>1.36</v>
       </c>
       <c r="AK126">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O127">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P127">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21182,7 +21182,7 @@
         <v>0</v>
       </c>
       <c r="Q128">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="R128">
         <v>2.4</v>
@@ -21197,7 +21197,7 @@
         <v>2.15</v>
       </c>
       <c r="V128">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W128">
         <v>1.14</v>
@@ -21206,31 +21206,31 @@
         <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z128">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA128">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AB128">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AC128">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="AD128">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AE128">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF128">
         <v>1.53</v>
       </c>
       <c r="AG128">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK128">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="O130">
         <v>3.5</v>
@@ -21532,19 +21532,19 @@
         <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z130">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA130">
         <v>1.61</v>
       </c>
       <c r="AB130">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AC130">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AD130">
         <v>1.44</v>
@@ -21553,10 +21553,10 @@
         <v>1.14</v>
       </c>
       <c r="AF130">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AG130">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK130">
         <v>1.57</v>
@@ -21662,49 +21662,49 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="O131">
         <v>3.35</v>
       </c>
       <c r="P131">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q131">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R131">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S131">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T131">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U131">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="V131">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W131">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X131">
         <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z131">
-        <v>3.39</v>
+        <v>3.46</v>
       </c>
       <c r="AA131">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB131">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC131">
         <v>3.2</v>
@@ -21716,7 +21716,7 @@
         <v>1.11</v>
       </c>
       <c r="AF131">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG131">
         <v>1.91</v>
@@ -21735,7 +21735,7 @@
         <v>1.25</v>
       </c>
       <c r="AK131">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21834,7 +21834,7 @@
         <v>2.42</v>
       </c>
       <c r="Q132">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R132">
         <v>2.16</v>
@@ -21849,7 +21849,7 @@
         <v>2.5</v>
       </c>
       <c r="V132">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W132">
         <v>1.09</v>
@@ -21861,28 +21861,28 @@
         <v>1.2</v>
       </c>
       <c r="Z132">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AA132">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB132">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC132">
         <v>2.83</v>
       </c>
       <c r="AD132">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE132">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF132">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AG132">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK132">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL132">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -12051,7 +12051,7 @@
         <v>3.35</v>
       </c>
       <c r="P72">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="Q72">
         <v>2.18</v>
@@ -12063,7 +12063,7 @@
         <v>1.5</v>
       </c>
       <c r="T72">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="U72">
         <v>3.4</v>
@@ -12075,28 +12075,28 @@
         <v>1.05</v>
       </c>
       <c r="X72">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y72">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z72">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AA72">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AB72">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AC72">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD72">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE72">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF72">
         <v>2.5</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
+        <v>2.92</v>
+      </c>
+      <c r="O76">
+        <v>3.2</v>
+      </c>
+      <c r="P76">
         <v>2.25</v>
       </c>
-      <c r="O76">
-        <v>2.9</v>
-      </c>
-      <c r="P76">
-        <v>3</v>
-      </c>
       <c r="Q76">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="R76">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="S76">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>2.45</v>
+        <v>3.03</v>
       </c>
       <c r="U76">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="V76">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W76">
+        <v>1.06</v>
+      </c>
+      <c r="X76">
         <v>1.03</v>
       </c>
-      <c r="X76">
-        <v>1.1</v>
-      </c>
       <c r="Y76">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>2.63</v>
+        <v>3.66</v>
       </c>
       <c r="AA76">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="AB76">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AC76">
-        <v>5</v>
+        <v>3.13</v>
       </c>
       <c r="AD76">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AE76">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF76">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG76">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P77">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="Q77">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="R77">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="S77">
+        <v>1.49</v>
+      </c>
+      <c r="T77">
+        <v>2.45</v>
+      </c>
+      <c r="U77">
+        <v>3.28</v>
+      </c>
+      <c r="V77">
+        <v>1.29</v>
+      </c>
+      <c r="W77">
+        <v>1.03</v>
+      </c>
+      <c r="X77">
+        <v>1.1</v>
+      </c>
+      <c r="Y77">
+        <v>1.47</v>
+      </c>
+      <c r="Z77">
+        <v>2.63</v>
+      </c>
+      <c r="AA77">
+        <v>2.66</v>
+      </c>
+      <c r="AB77">
+        <v>1.48</v>
+      </c>
+      <c r="AC77">
+        <v>5</v>
+      </c>
+      <c r="AD77">
+        <v>1.17</v>
+      </c>
+      <c r="AE77">
+        <v>1.04</v>
+      </c>
+      <c r="AF77">
+        <v>2</v>
+      </c>
+      <c r="AG77">
+        <v>1.73</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
         <v>1.33</v>
       </c>
-      <c r="T77">
-        <v>3.03</v>
-      </c>
-      <c r="U77">
-        <v>2.62</v>
-      </c>
-      <c r="V77">
-        <v>1.43</v>
-      </c>
-      <c r="W77">
-        <v>1.06</v>
-      </c>
-      <c r="X77">
-        <v>1.03</v>
-      </c>
-      <c r="Y77">
-        <v>1.25</v>
-      </c>
-      <c r="Z77">
-        <v>3.66</v>
-      </c>
-      <c r="AA77">
-        <v>1.88</v>
-      </c>
-      <c r="AB77">
-        <v>1.87</v>
-      </c>
-      <c r="AC77">
-        <v>3.13</v>
-      </c>
-      <c r="AD77">
-        <v>1.36</v>
-      </c>
-      <c r="AE77">
-        <v>1.11</v>
-      </c>
-      <c r="AF77">
-        <v>1.7</v>
-      </c>
-      <c r="AG77">
-        <v>2.05</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.3</v>
-      </c>
       <c r="AK77">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.45</v>
+        <v>1.28</v>
       </c>
       <c r="O89">
-        <v>3.55</v>
+        <v>5.55</v>
       </c>
       <c r="P89">
-        <v>2.28</v>
+        <v>7.2</v>
       </c>
       <c r="Q89">
-        <v>3.02</v>
+        <v>1.6</v>
       </c>
       <c r="R89">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="S89">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T89">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="U89">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="V89">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="W89">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z89">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA89">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AB89">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC89">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD89">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AF89">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG89">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AK89">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="O90">
-        <v>5.55</v>
+        <v>4.25</v>
       </c>
       <c r="P90">
-        <v>7.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q90">
-        <v>1.6</v>
+        <v>2.46</v>
       </c>
       <c r="R90">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="S90">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T90">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="U90">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="V90">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="W90">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Z90">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA90">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AB90">
-        <v>3</v>
+        <v>3.69</v>
       </c>
       <c r="AC90">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AD90">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="AE90">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AF90">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AG90">
-        <v>2.2</v>
+        <v>3.42</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK90">
-        <v>3.38</v>
+        <v>1.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="O91">
-        <v>4.25</v>
+        <v>3.55</v>
       </c>
       <c r="P91">
-        <v>2.87</v>
+        <v>2.28</v>
       </c>
       <c r="Q91">
-        <v>2.46</v>
+        <v>3.02</v>
       </c>
       <c r="R91">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="S91">
+        <v>1.22</v>
+      </c>
+      <c r="T91">
+        <v>3.9</v>
+      </c>
+      <c r="U91">
+        <v>2.09</v>
+      </c>
+      <c r="V91">
+        <v>1.68</v>
+      </c>
+      <c r="W91">
         <v>1.15</v>
-      </c>
-      <c r="T91">
-        <v>4.8</v>
-      </c>
-      <c r="U91">
-        <v>1.8</v>
-      </c>
-      <c r="V91">
-        <v>1.91</v>
-      </c>
-      <c r="W91">
-        <v>1.25</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA91">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AB91">
-        <v>3.69</v>
+        <v>2.5</v>
       </c>
       <c r="AC91">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="AD91">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="AE91">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AF91">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG91">
-        <v>3.42</v>
+        <v>2.88</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AK91">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -20364,10 +20364,10 @@
         <v>3.6</v>
       </c>
       <c r="P123">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q123">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="R123">
         <v>2.02</v>
@@ -20388,34 +20388,34 @@
         <v>1.06</v>
       </c>
       <c r="X123">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y123">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z123">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AA123">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB123">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC123">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AD123">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE123">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AG123">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.92</v>
+        <v>2.25</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P76">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="Q76">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="R76">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="S76">
+        <v>1.49</v>
+      </c>
+      <c r="T76">
+        <v>2.45</v>
+      </c>
+      <c r="U76">
+        <v>3.28</v>
+      </c>
+      <c r="V76">
+        <v>1.29</v>
+      </c>
+      <c r="W76">
+        <v>1.03</v>
+      </c>
+      <c r="X76">
+        <v>1.1</v>
+      </c>
+      <c r="Y76">
+        <v>1.47</v>
+      </c>
+      <c r="Z76">
+        <v>2.63</v>
+      </c>
+      <c r="AA76">
+        <v>2.66</v>
+      </c>
+      <c r="AB76">
+        <v>1.48</v>
+      </c>
+      <c r="AC76">
+        <v>5</v>
+      </c>
+      <c r="AD76">
+        <v>1.17</v>
+      </c>
+      <c r="AE76">
+        <v>1.04</v>
+      </c>
+      <c r="AF76">
+        <v>2</v>
+      </c>
+      <c r="AG76">
+        <v>1.73</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.33</v>
       </c>
-      <c r="T76">
-        <v>3.03</v>
-      </c>
-      <c r="U76">
-        <v>2.62</v>
-      </c>
-      <c r="V76">
-        <v>1.43</v>
-      </c>
-      <c r="W76">
-        <v>1.06</v>
-      </c>
-      <c r="X76">
-        <v>1.03</v>
-      </c>
-      <c r="Y76">
-        <v>1.25</v>
-      </c>
-      <c r="Z76">
-        <v>3.66</v>
-      </c>
-      <c r="AA76">
-        <v>1.88</v>
-      </c>
-      <c r="AB76">
-        <v>1.87</v>
-      </c>
-      <c r="AC76">
-        <v>3.13</v>
-      </c>
-      <c r="AD76">
-        <v>1.36</v>
-      </c>
-      <c r="AE76">
-        <v>1.11</v>
-      </c>
-      <c r="AF76">
-        <v>1.7</v>
-      </c>
-      <c r="AG76">
-        <v>2.05</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.3</v>
-      </c>
       <c r="AK76">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
+        <v>2.92</v>
+      </c>
+      <c r="O77">
+        <v>3.2</v>
+      </c>
+      <c r="P77">
         <v>2.25</v>
       </c>
-      <c r="O77">
-        <v>2.9</v>
-      </c>
-      <c r="P77">
-        <v>3</v>
-      </c>
       <c r="Q77">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="R77">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="S77">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="T77">
-        <v>2.45</v>
+        <v>3.03</v>
       </c>
       <c r="U77">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="V77">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
+        <v>1.06</v>
+      </c>
+      <c r="X77">
         <v>1.03</v>
       </c>
-      <c r="X77">
-        <v>1.1</v>
-      </c>
       <c r="Y77">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>2.63</v>
+        <v>3.66</v>
       </c>
       <c r="AA77">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="AB77">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AC77">
-        <v>5</v>
+        <v>3.13</v>
       </c>
       <c r="AD77">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AE77">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,46 +14490,46 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="O87">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="P87">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="Q87">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="R87">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S87">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T87">
-        <v>3.52</v>
+        <v>3.9</v>
       </c>
       <c r="U87">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="V87">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W87">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z87">
-        <v>5.28</v>
+        <v>5.5</v>
       </c>
       <c r="AA87">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB87">
         <v>2.5</v>
@@ -14538,16 +14538,16 @@
         <v>2.15</v>
       </c>
       <c r="AD87">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE87">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF87">
         <v>1.4</v>
       </c>
       <c r="AG87">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK87">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,80 +14653,80 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.45</v>
+        <v>2.91</v>
       </c>
       <c r="O88">
-        <v>4.9</v>
+        <v>3.88</v>
       </c>
       <c r="P88">
-        <v>4.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q88">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="R88">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S88">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="T88">
-        <v>4.75</v>
+        <v>3.52</v>
       </c>
       <c r="U88">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="V88">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="W88">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Z88">
-        <v>8.699999999999999</v>
+        <v>5.28</v>
       </c>
       <c r="AA88">
+        <v>1.5</v>
+      </c>
+      <c r="AB88">
+        <v>2.5</v>
+      </c>
+      <c r="AC88">
+        <v>2.15</v>
+      </c>
+      <c r="AD88">
+        <v>1.66</v>
+      </c>
+      <c r="AE88">
+        <v>1.28</v>
+      </c>
+      <c r="AF88">
+        <v>1.4</v>
+      </c>
+      <c r="AG88">
+        <v>2.69</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
         <v>1.25</v>
       </c>
-      <c r="AB88">
-        <v>3.75</v>
-      </c>
-      <c r="AC88">
-        <v>1.62</v>
-      </c>
-      <c r="AD88">
-        <v>2.15</v>
-      </c>
-      <c r="AE88">
-        <v>1.5</v>
-      </c>
-      <c r="AF88">
-        <v>1.35</v>
-      </c>
-      <c r="AG88">
-        <v>2.7</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.17</v>
-      </c>
       <c r="AK88">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="O90">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="P90">
-        <v>2.87</v>
+        <v>4.85</v>
       </c>
       <c r="Q90">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="R90">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S90">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="T90">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="U90">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V90">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="W90">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Z90">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA90">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AB90">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="AC90">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AD90">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AE90">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AF90">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AG90">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="O91">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="P91">
-        <v>2.28</v>
+        <v>2.87</v>
       </c>
       <c r="Q91">
-        <v>3.02</v>
+        <v>2.46</v>
       </c>
       <c r="R91">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T91">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="U91">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="V91">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Z91">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA91">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AB91">
-        <v>2.5</v>
+        <v>3.69</v>
       </c>
       <c r="AC91">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AD91">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="AE91">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AF91">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG91">
-        <v>2.88</v>
+        <v>3.42</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AK91">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O104">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="Q104">
-        <v>2.99</v>
+        <v>2.83</v>
       </c>
       <c r="R104">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="S104">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="T104">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="U104">
-        <v>2.73</v>
+        <v>2.23</v>
       </c>
       <c r="V104">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="W104">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X104">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z104">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA104">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="AC104">
-        <v>3.6</v>
+        <v>2.26</v>
       </c>
       <c r="AD104">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AE104">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="AF104">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG104">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.29</v>
       </c>
       <c r="AK104">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O105">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P105">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="Q105">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="R105">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="S105">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="T105">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="U105">
-        <v>2.23</v>
+        <v>2.73</v>
       </c>
       <c r="V105">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z105">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA105">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="AB105">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="AC105">
-        <v>2.26</v>
+        <v>3.6</v>
       </c>
       <c r="AD105">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AE105">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AF105">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG105">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL105">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -3741,55 +3741,55 @@
         <v>1.84</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5691,16 +5691,16 @@
         <v>1.22</v>
       </c>
       <c r="O33">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="P33">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="Q33">
         <v>1.57</v>
       </c>
       <c r="R33">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="S33">
         <v>1.13</v>
@@ -5733,10 +5733,10 @@
         <v>3</v>
       </c>
       <c r="AC33">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD33">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE33">
         <v>1.36</v>
@@ -5745,7 +5745,7 @@
         <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.07</v>
       </c>
       <c r="AK33">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,31 +5854,31 @@
         <v>4.2</v>
       </c>
       <c r="O34">
-        <v>4.02</v>
+        <v>4.15</v>
       </c>
       <c r="P34">
         <v>1.73</v>
       </c>
       <c r="Q34">
-        <v>4.54</v>
+        <v>4.68</v>
       </c>
       <c r="R34">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="S34">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V34">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5896,7 +5896,7 @@
         <v>2.43</v>
       </c>
       <c r="AC34">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD34">
         <v>1.58</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
         <v>1.2</v>
@@ -6186,55 +6186,55 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q40">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R40">
         <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="U40">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="V40">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W40">
         <v>1.11</v>
@@ -6862,31 +6862,31 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB40">
         <v>2.05</v>
       </c>
       <c r="AC40">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="AD40">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="O41">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="Q41">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="U41">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="V41">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
         <v>1.11</v>
@@ -7025,31 +7025,31 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z41">
         <v>4</v>
       </c>
       <c r="AA41">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB41">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC41">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
         <v>1.29</v>
       </c>
       <c r="T42">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U42">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V42">
         <v>1.48</v>
@@ -7188,31 +7188,31 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA42">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AB42">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC42">
         <v>2.79</v>
       </c>
       <c r="AD42">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE42">
         <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -9763,43 +9763,43 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="O58">
         <v>4.1</v>
       </c>
       <c r="P58">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="Q58">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="R58">
         <v>2.5</v>
       </c>
       <c r="S58">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="U58">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="V58">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W58">
         <v>1.13</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z58">
-        <v>5</v>
+        <v>5.21</v>
       </c>
       <c r="AA58">
         <v>1.53</v>
@@ -9814,13 +9814,13 @@
         <v>1.57</v>
       </c>
       <c r="AE58">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AF58">
         <v>1.6</v>
       </c>
       <c r="AG58">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK58">
         <v>2.22</v>
@@ -10418,61 +10418,61 @@
         <v>2.6</v>
       </c>
       <c r="O62">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="P62">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="Q62">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="R62">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S62">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="T62">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="U62">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="V62">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W62">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X62">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y62">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Z62">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AA62">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AB62">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC62">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AD62">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AE62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF62">
         <v>2.15</v>
       </c>
       <c r="AG62">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK62">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10907,61 +10907,61 @@
         <v>1.9</v>
       </c>
       <c r="O65">
-        <v>3.47</v>
+        <v>3.55</v>
       </c>
       <c r="P65">
-        <v>3.57</v>
+        <v>3.21</v>
       </c>
       <c r="Q65">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S65">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U65">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W65">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA65">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB65">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC65">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD65">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG65">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.47</v>
+        <v>3.44</v>
       </c>
       <c r="O66">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>5.06</v>
+        <v>1.84</v>
       </c>
       <c r="Q66">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="R66">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U66">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V66">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W66">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z66">
-        <v>5.25</v>
+        <v>5.03</v>
       </c>
       <c r="AA66">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB66">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AC66">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="AD66">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AE66">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF66">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG66">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK66">
-        <v>2.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="O67">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="Q67">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R67">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S67">
+        <v>1.19</v>
+      </c>
+      <c r="T67">
+        <v>3.9</v>
+      </c>
+      <c r="U67">
+        <v>2.02</v>
+      </c>
+      <c r="V67">
+        <v>1.68</v>
+      </c>
+      <c r="W67">
+        <v>1.14</v>
+      </c>
+      <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
+        <v>1.07</v>
+      </c>
+      <c r="Z67">
+        <v>5.5</v>
+      </c>
+      <c r="AA67">
+        <v>1.37</v>
+      </c>
+      <c r="AB67">
+        <v>2.66</v>
+      </c>
+      <c r="AC67">
+        <v>2.1</v>
+      </c>
+      <c r="AD67">
+        <v>1.67</v>
+      </c>
+      <c r="AE67">
         <v>1.25</v>
       </c>
-      <c r="T67">
-        <v>3.55</v>
-      </c>
-      <c r="U67">
-        <v>2.1</v>
-      </c>
-      <c r="V67">
-        <v>1.65</v>
-      </c>
-      <c r="W67">
-        <v>1.12</v>
-      </c>
-      <c r="X67">
-        <v>1.03</v>
-      </c>
-      <c r="Y67">
-        <v>1.12</v>
-      </c>
-      <c r="Z67">
-        <v>5.03</v>
-      </c>
-      <c r="AA67">
-        <v>1.53</v>
-      </c>
-      <c r="AB67">
-        <v>2.45</v>
-      </c>
-      <c r="AC67">
-        <v>2.32</v>
-      </c>
-      <c r="AD67">
-        <v>1.62</v>
-      </c>
-      <c r="AE67">
-        <v>1.22</v>
-      </c>
       <c r="AF67">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AG67">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.21</v>
+        <v>1.79</v>
       </c>
       <c r="AK67">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,25 +11393,25 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.45</v>
+        <v>1.47</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P68">
-        <v>1.96</v>
+        <v>5.06</v>
       </c>
       <c r="Q68">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="R68">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="S68">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U68">
         <v>2.02</v>
@@ -11420,37 +11420,37 @@
         <v>1.68</v>
       </c>
       <c r="W68">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z68">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA68">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB68">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AC68">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD68">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE68">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF68">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.79</v>
+        <v>1.12</v>
       </c>
       <c r="AK68">
-        <v>1.23</v>
+        <v>2.28</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11891,19 +11891,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="Q71">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="R71">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S71">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T71">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U71">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V71">
         <v>1.6</v>
@@ -11921,25 +11921,25 @@
         <v>5.5</v>
       </c>
       <c r="AA71">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB71">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC71">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD71">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE71">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AF71">
         <v>1.9</v>
       </c>
       <c r="AG71">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.12</v>
       </c>
       <c r="AK71">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O72">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P72">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="Q72">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="R72">
         <v>2</v>
@@ -12075,7 +12075,7 @@
         <v>1.04</v>
       </c>
       <c r="X72">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y72">
         <v>1.49</v>
@@ -12084,25 +12084,25 @@
         <v>2.3</v>
       </c>
       <c r="AA72">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AB72">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AC72">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AD72">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE72">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF72">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AG72">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="AK72">
         <v>2.3</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>3.78</v>
+      </c>
+      <c r="R78">
+        <v>2.24</v>
+      </c>
+      <c r="S78">
+        <v>1.28</v>
+      </c>
+      <c r="T78">
+        <v>3.18</v>
+      </c>
+      <c r="U78">
+        <v>2.61</v>
+      </c>
+      <c r="V78">
         <v>1.44</v>
       </c>
-      <c r="O78">
-        <v>4.2</v>
-      </c>
-      <c r="P78">
-        <v>5.5</v>
-      </c>
-      <c r="Q78">
-        <v>1.91</v>
-      </c>
-      <c r="R78">
-        <v>2.38</v>
-      </c>
-      <c r="S78">
-        <v>1.29</v>
-      </c>
-      <c r="T78">
-        <v>3.32</v>
-      </c>
-      <c r="U78">
-        <v>2.29</v>
-      </c>
-      <c r="V78">
-        <v>1.53</v>
-      </c>
       <c r="W78">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z78">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="AA78">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB78">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AC78">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="AD78">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE78">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q79">
-        <v>3.78</v>
+        <v>1.91</v>
       </c>
       <c r="R79">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S79">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="U79">
-        <v>2.61</v>
+        <v>2.29</v>
       </c>
       <c r="V79">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z79">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="AA79">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB79">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AC79">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="AD79">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE79">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF79">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG79">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O86">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P86">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q86">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="R86">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="S86">
+        <v>1.22</v>
+      </c>
+      <c r="T86">
+        <v>4</v>
+      </c>
+      <c r="U86">
+        <v>2.02</v>
+      </c>
+      <c r="V86">
+        <v>1.68</v>
+      </c>
+      <c r="W86">
         <v>1.17</v>
       </c>
-      <c r="T86">
-        <v>4.6</v>
-      </c>
-      <c r="U86">
-        <v>1.8</v>
-      </c>
-      <c r="V86">
-        <v>1.91</v>
-      </c>
-      <c r="W86">
+      <c r="X86">
+        <v>1.02</v>
+      </c>
+      <c r="Y86">
+        <v>1.12</v>
+      </c>
+      <c r="Z86">
+        <v>5.84</v>
+      </c>
+      <c r="AA86">
+        <v>1.43</v>
+      </c>
+      <c r="AB86">
+        <v>2.73</v>
+      </c>
+      <c r="AC86">
+        <v>2.05</v>
+      </c>
+      <c r="AD86">
+        <v>1.74</v>
+      </c>
+      <c r="AE86">
         <v>1.25</v>
       </c>
-      <c r="X86">
-        <v>1.01</v>
-      </c>
-      <c r="Y86">
-        <v>1.07</v>
-      </c>
-      <c r="Z86">
-        <v>6.75</v>
-      </c>
-      <c r="AA86">
-        <v>1.29</v>
-      </c>
-      <c r="AB86">
-        <v>3.5</v>
-      </c>
-      <c r="AC86">
-        <v>1.8</v>
-      </c>
-      <c r="AD86">
-        <v>2</v>
-      </c>
-      <c r="AE86">
-        <v>1.36</v>
-      </c>
       <c r="AF86">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG86">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK86">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O87">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P87">
-        <v>3.5</v>
+        <v>2.06</v>
       </c>
       <c r="Q87">
-        <v>2.13</v>
+        <v>3.38</v>
       </c>
       <c r="R87">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S87">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T87">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U87">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V87">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W87">
         <v>1.17</v>
@@ -14523,31 +14523,31 @@
         <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>5.84</v>
+        <v>5.7</v>
       </c>
       <c r="AA87">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB87">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="AC87">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD87">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AE87">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF87">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG87">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.8</v>
+        <v>1.19</v>
       </c>
       <c r="O88">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="P88">
-        <v>2.06</v>
+        <v>7.5</v>
       </c>
       <c r="Q88">
-        <v>3.38</v>
+        <v>1.64</v>
       </c>
       <c r="R88">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="S88">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T88">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V88">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="W88">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
         <v>1.08</v>
       </c>
       <c r="Z88">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA88">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB88">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AC88">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AD88">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AE88">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AF88">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG88">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK88">
-        <v>1.35</v>
+        <v>3.38</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.19</v>
+        <v>2.45</v>
       </c>
       <c r="O90">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="P90">
-        <v>7.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q90">
+        <v>3.1</v>
+      </c>
+      <c r="R90">
+        <v>2.31</v>
+      </c>
+      <c r="S90">
+        <v>1.21</v>
+      </c>
+      <c r="T90">
+        <v>3.7</v>
+      </c>
+      <c r="U90">
+        <v>2.1</v>
+      </c>
+      <c r="V90">
+        <v>1.65</v>
+      </c>
+      <c r="W90">
+        <v>1.14</v>
+      </c>
+      <c r="X90">
+        <v>1.02</v>
+      </c>
+      <c r="Y90">
+        <v>1.13</v>
+      </c>
+      <c r="Z90">
+        <v>5.2</v>
+      </c>
+      <c r="AA90">
+        <v>1.48</v>
+      </c>
+      <c r="AB90">
+        <v>2.5</v>
+      </c>
+      <c r="AC90">
+        <v>2.16</v>
+      </c>
+      <c r="AD90">
         <v>1.64</v>
       </c>
-      <c r="R90">
-        <v>3.05</v>
-      </c>
-      <c r="S90">
-        <v>1.18</v>
-      </c>
-      <c r="T90">
-        <v>4.05</v>
-      </c>
-      <c r="U90">
-        <v>1.98</v>
-      </c>
-      <c r="V90">
-        <v>1.81</v>
-      </c>
-      <c r="W90">
-        <v>1.2</v>
-      </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>1.08</v>
-      </c>
-      <c r="Z90">
-        <v>7.5</v>
-      </c>
-      <c r="AA90">
-        <v>1.36</v>
-      </c>
-      <c r="AB90">
-        <v>3.1</v>
-      </c>
-      <c r="AC90">
-        <v>1.9</v>
-      </c>
-      <c r="AD90">
-        <v>1.9</v>
-      </c>
       <c r="AE90">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AF90">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AG90">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="AK90">
-        <v>3.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,80 +15142,80 @@
         </is>
       </c>
       <c r="N91">
+        <v>1.9</v>
+      </c>
+      <c r="O91">
+        <v>4.15</v>
+      </c>
+      <c r="P91">
+        <v>2.9</v>
+      </c>
+      <c r="Q91">
         <v>2.45</v>
       </c>
-      <c r="O91">
-        <v>3.75</v>
-      </c>
-      <c r="P91">
-        <v>2.28</v>
-      </c>
-      <c r="Q91">
-        <v>3.1</v>
-      </c>
       <c r="R91">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="S91">
+        <v>1.17</v>
+      </c>
+      <c r="T91">
+        <v>4.6</v>
+      </c>
+      <c r="U91">
+        <v>1.8</v>
+      </c>
+      <c r="V91">
+        <v>1.91</v>
+      </c>
+      <c r="W91">
+        <v>1.25</v>
+      </c>
+      <c r="X91">
+        <v>1.01</v>
+      </c>
+      <c r="Y91">
+        <v>1.07</v>
+      </c>
+      <c r="Z91">
+        <v>6.75</v>
+      </c>
+      <c r="AA91">
+        <v>1.29</v>
+      </c>
+      <c r="AB91">
+        <v>3.5</v>
+      </c>
+      <c r="AC91">
+        <v>1.8</v>
+      </c>
+      <c r="AD91">
+        <v>2</v>
+      </c>
+      <c r="AE91">
+        <v>1.36</v>
+      </c>
+      <c r="AF91">
+        <v>1.3</v>
+      </c>
+      <c r="AG91">
+        <v>3.25</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
         <v>1.21</v>
       </c>
-      <c r="T91">
-        <v>3.7</v>
-      </c>
-      <c r="U91">
-        <v>2.1</v>
-      </c>
-      <c r="V91">
-        <v>1.65</v>
-      </c>
-      <c r="W91">
-        <v>1.14</v>
-      </c>
-      <c r="X91">
-        <v>1.02</v>
-      </c>
-      <c r="Y91">
-        <v>1.13</v>
-      </c>
-      <c r="Z91">
-        <v>5.2</v>
-      </c>
-      <c r="AA91">
-        <v>1.48</v>
-      </c>
-      <c r="AB91">
-        <v>2.5</v>
-      </c>
-      <c r="AC91">
-        <v>2.16</v>
-      </c>
-      <c r="AD91">
-        <v>1.64</v>
-      </c>
-      <c r="AE91">
-        <v>1.21</v>
-      </c>
-      <c r="AF91">
-        <v>1.39</v>
-      </c>
-      <c r="AG91">
-        <v>2.8</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>1.48</v>
-      </c>
       <c r="AK91">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P102">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q102">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="R102">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="S102">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="T102">
-        <v>3.34</v>
+        <v>2.66</v>
       </c>
       <c r="U102">
-        <v>2.23</v>
+        <v>2.73</v>
       </c>
       <c r="V102">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>4.75</v>
+        <v>3.24</v>
       </c>
       <c r="AA102">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB102">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AC102">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="AD102">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AE102">
+        <v>1.05</v>
+      </c>
+      <c r="AF102">
+        <v>1.85</v>
+      </c>
+      <c r="AG102">
+        <v>1.85</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
         <v>1.21</v>
       </c>
-      <c r="AF102">
-        <v>1.53</v>
-      </c>
-      <c r="AG102">
-        <v>2.5</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.29</v>
-      </c>
       <c r="AK102">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.7</v>
+        <v>3.65</v>
       </c>
       <c r="O103">
         <v>3.7</v>
       </c>
       <c r="P103">
+        <v>1.76</v>
+      </c>
+      <c r="Q103">
+        <v>3.8</v>
+      </c>
+      <c r="R103">
+        <v>2.3</v>
+      </c>
+      <c r="S103">
+        <v>1.3</v>
+      </c>
+      <c r="T103">
+        <v>3.15</v>
+      </c>
+      <c r="U103">
+        <v>2.47</v>
+      </c>
+      <c r="V103">
+        <v>1.48</v>
+      </c>
+      <c r="W103">
+        <v>1.12</v>
+      </c>
+      <c r="X103">
+        <v>1.02</v>
+      </c>
+      <c r="Y103">
+        <v>1.17</v>
+      </c>
+      <c r="Z103">
         <v>4.2</v>
       </c>
-      <c r="Q103">
-        <v>2.25</v>
-      </c>
-      <c r="R103">
-        <v>2.24</v>
-      </c>
-      <c r="S103">
-        <v>1.39</v>
-      </c>
-      <c r="T103">
-        <v>2.88</v>
-      </c>
-      <c r="U103">
-        <v>2.77</v>
-      </c>
-      <c r="V103">
-        <v>1.39</v>
-      </c>
-      <c r="W103">
-        <v>1.05</v>
-      </c>
-      <c r="X103">
-        <v>1.03</v>
-      </c>
-      <c r="Y103">
-        <v>1.3</v>
-      </c>
-      <c r="Z103">
-        <v>3.2</v>
-      </c>
       <c r="AA103">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="AB103">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC103">
-        <v>3.5</v>
+        <v>2.71</v>
       </c>
       <c r="AD103">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AE103">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF103">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG103">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AK103">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.5</v>
+        <v>2.26</v>
       </c>
       <c r="O104">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P104">
-        <v>1.76</v>
+        <v>2.58</v>
       </c>
       <c r="Q104">
+        <v>2.88</v>
+      </c>
+      <c r="R104">
+        <v>2.29</v>
+      </c>
+      <c r="S104">
+        <v>1.22</v>
+      </c>
+      <c r="T104">
         <v>3.8</v>
       </c>
-      <c r="R104">
-        <v>2.19</v>
-      </c>
-      <c r="S104">
-        <v>1.31</v>
-      </c>
-      <c r="T104">
-        <v>3.3</v>
-      </c>
       <c r="U104">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="V104">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="W104">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA104">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AC104">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="AD104">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AE104">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF104">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AG104">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17430,58 +17430,58 @@
         <v>3.4</v>
       </c>
       <c r="P105">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="Q105">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="R105">
         <v>2.1</v>
       </c>
       <c r="S105">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U105">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V105">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W105">
         <v>1.06</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y105">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z105">
         <v>3.4</v>
       </c>
       <c r="AA105">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AB105">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC105">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD105">
         <v>1.25</v>
       </c>
       <c r="AE105">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF105">
         <v>1.73</v>
       </c>
       <c r="AG105">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17750,10 +17750,10 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="O107">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="P107">
         <v>5.75</v>
@@ -17762,31 +17762,31 @@
         <v>1.83</v>
       </c>
       <c r="R107">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S107">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U107">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="V107">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W107">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z107">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="AA107">
         <v>1.44</v>
@@ -17798,16 +17798,16 @@
         <v>2.1</v>
       </c>
       <c r="AD107">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE107">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF107">
         <v>1.73</v>
       </c>
       <c r="AG107">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O108">
         <v>3.5</v>
@@ -17922,25 +17922,25 @@
         <v>3.25</v>
       </c>
       <c r="Q108">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="R108">
         <v>2.3</v>
       </c>
       <c r="S108">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T108">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U108">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V108">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W108">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X108">
         <v>1.02</v>
@@ -17949,16 +17949,16 @@
         <v>1.2</v>
       </c>
       <c r="Z108">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="AA108">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB108">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC108">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AD108">
         <v>1.47</v>
@@ -17967,10 +17967,10 @@
         <v>1.17</v>
       </c>
       <c r="AF108">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG108">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK108">
         <v>1.86</v>
@@ -18082,13 +18082,13 @@
         <v>4.6</v>
       </c>
       <c r="P109">
-        <v>6</v>
+        <v>6.32</v>
       </c>
       <c r="Q109">
         <v>1.75</v>
       </c>
       <c r="R109">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="S109">
         <v>1.21</v>
@@ -18100,40 +18100,40 @@
         <v>2.1</v>
       </c>
       <c r="V109">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="W109">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X109">
         <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z109">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA109">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB109">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="AC109">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD109">
         <v>1.62</v>
       </c>
       <c r="AE109">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF109">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG109">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AK109">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18251,46 +18251,46 @@
         <v>3.25</v>
       </c>
       <c r="R110">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T110">
         <v>3.25</v>
       </c>
       <c r="U110">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="V110">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W110">
         <v>1.12</v>
       </c>
       <c r="X110">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z110">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA110">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB110">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC110">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD110">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE110">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF110">
         <v>1.53</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK110">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O115">
         <v>3.2</v>
@@ -19063,10 +19063,10 @@
         <v>3.21</v>
       </c>
       <c r="Q115">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="R115">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S115">
         <v>1.38</v>
@@ -19075,43 +19075,43 @@
         <v>2.77</v>
       </c>
       <c r="U115">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="V115">
         <v>1.38</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z115">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="AA115">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB115">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC115">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD115">
         <v>1.29</v>
       </c>
       <c r="AE115">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG115">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>1.33</v>
       </c>
       <c r="AK115">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19389,16 +19389,16 @@
         <v>5.3</v>
       </c>
       <c r="Q117">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="R117">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="S117">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T117">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U117">
         <v>2.4</v>
@@ -19407,7 +19407,7 @@
         <v>1.5</v>
       </c>
       <c r="W117">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
         <v>1.02</v>
@@ -19425,19 +19425,19 @@
         <v>2.28</v>
       </c>
       <c r="AC117">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AD117">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE117">
         <v>1.15</v>
       </c>
       <c r="AF117">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG117">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>1.18</v>
       </c>
       <c r="AK117">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="O118">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P118">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q118">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="R118">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T118">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="U118">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="V118">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y118">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z118">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA118">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB118">
+        <v>1.76</v>
+      </c>
+      <c r="AC118">
+        <v>3.34</v>
+      </c>
+      <c r="AD118">
+        <v>1.24</v>
+      </c>
+      <c r="AE118">
+        <v>1.08</v>
+      </c>
+      <c r="AF118">
         <v>1.73</v>
       </c>
-      <c r="AC118">
-        <v>3.4</v>
-      </c>
-      <c r="AD118">
-        <v>1.25</v>
-      </c>
-      <c r="AE118">
-        <v>1.05</v>
-      </c>
-      <c r="AF118">
-        <v>1.81</v>
-      </c>
       <c r="AG118">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="O119">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P119">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="Q119">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="R119">
         <v>2.1</v>
       </c>
       <c r="S119">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T119">
         <v>2.88</v>
       </c>
       <c r="U119">
-        <v>2.92</v>
+        <v>2.47</v>
       </c>
       <c r="V119">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W119">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X119">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z119">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AA119">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AB119">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC119">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AD119">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE119">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF119">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG119">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>1.29</v>
       </c>
       <c r="AK119">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,80 +20032,80 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="O121">
         <v>3.3</v>
       </c>
       <c r="P121">
-        <v>3.18</v>
+        <v>4.25</v>
       </c>
       <c r="Q121">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="R121">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S121">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T121">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="U121">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="V121">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W121">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X121">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z121">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA121">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB121">
+        <v>1.73</v>
+      </c>
+      <c r="AC121">
+        <v>3.4</v>
+      </c>
+      <c r="AD121">
+        <v>1.25</v>
+      </c>
+      <c r="AE121">
+        <v>1.05</v>
+      </c>
+      <c r="AF121">
+        <v>1.81</v>
+      </c>
+      <c r="AG121">
+        <v>1.86</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
+        <v>1.2</v>
+      </c>
+      <c r="AK121">
         <v>1.91</v>
-      </c>
-      <c r="AC121">
-        <v>3.1</v>
-      </c>
-      <c r="AD121">
-        <v>1.33</v>
-      </c>
-      <c r="AE121">
-        <v>1.11</v>
-      </c>
-      <c r="AF121">
-        <v>1.6</v>
-      </c>
-      <c r="AG121">
-        <v>2.17</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.29</v>
-      </c>
-      <c r="AK121">
-        <v>1.62</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20367,25 +20367,25 @@
         <v>5.75</v>
       </c>
       <c r="Q123">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="R123">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="S123">
         <v>1.44</v>
       </c>
       <c r="T123">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="U123">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V123">
         <v>1.35</v>
       </c>
       <c r="W123">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X123">
         <v>1.06</v>
@@ -20394,16 +20394,16 @@
         <v>1.36</v>
       </c>
       <c r="Z123">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA123">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB123">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC123">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AD123">
         <v>1.22</v>
@@ -20412,10 +20412,10 @@
         <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AG123">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>1.2</v>
       </c>
       <c r="AK123">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20684,34 +20684,34 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q125">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="R125">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S125">
         <v>1.25</v>
       </c>
       <c r="T125">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="U125">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="V125">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W125">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X125">
         <v>1.03</v>
@@ -20720,25 +20720,25 @@
         <v>1.13</v>
       </c>
       <c r="Z125">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA125">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB125">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC125">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="AD125">
+        <v>1.5</v>
+      </c>
+      <c r="AE125">
+        <v>1.15</v>
+      </c>
+      <c r="AF125">
         <v>1.44</v>
-      </c>
-      <c r="AE125">
-        <v>1.13</v>
-      </c>
-      <c r="AF125">
-        <v>1.45</v>
       </c>
       <c r="AG125">
         <v>1.95</v>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="AK125">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,34 +20847,34 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="O126">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P126">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="Q126">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R126">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S126">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T126">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U126">
-        <v>3.24</v>
+        <v>3.04</v>
       </c>
       <c r="V126">
         <v>1.33</v>
       </c>
       <c r="W126">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X126">
         <v>1.08</v>
@@ -20889,7 +20889,7 @@
         <v>2.15</v>
       </c>
       <c r="AB126">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC126">
         <v>3.9</v>
@@ -20904,7 +20904,7 @@
         <v>1.85</v>
       </c>
       <c r="AG126">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AK126">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21182,25 +21182,25 @@
         <v>0</v>
       </c>
       <c r="Q128">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R128">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S128">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T128">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="U128">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="V128">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W128">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X128">
         <v>1.03</v>
@@ -21209,19 +21209,19 @@
         <v>1.11</v>
       </c>
       <c r="Z128">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="AA128">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB128">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AC128">
-        <v>1.99</v>
+        <v>2.31</v>
       </c>
       <c r="AD128">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AE128">
         <v>1.14</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AK128">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21336,22 +21336,22 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O129">
         <v>2.8</v>
       </c>
       <c r="P129">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="Q129">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R129">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S129">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="T129">
         <v>2.2</v>
@@ -21360,13 +21360,13 @@
         <v>4</v>
       </c>
       <c r="V129">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W129">
         <v>1.03</v>
       </c>
       <c r="X129">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y129">
         <v>1.54</v>
@@ -21375,16 +21375,16 @@
         <v>2.28</v>
       </c>
       <c r="AA129">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AB129">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC129">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AD129">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE129">
         <v>1.03</v>
@@ -21409,7 +21409,7 @@
         <v>1.44</v>
       </c>
       <c r="AK129">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,34 +21499,34 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="O130">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="P130">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Q130">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R130">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S130">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T130">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U130">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="V130">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W130">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X130">
         <v>1.01</v>
@@ -21535,28 +21535,28 @@
         <v>1.18</v>
       </c>
       <c r="Z130">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA130">
         <v>1.61</v>
       </c>
       <c r="AB130">
+        <v>2.21</v>
+      </c>
+      <c r="AC130">
         <v>2.35</v>
-      </c>
-      <c r="AC130">
-        <v>2.4</v>
       </c>
       <c r="AD130">
         <v>1.44</v>
       </c>
       <c r="AE130">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF130">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG130">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK130">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21662,25 +21662,25 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="O131">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="P131">
-        <v>3.8</v>
+        <v>3.03</v>
       </c>
       <c r="Q131">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R131">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S131">
         <v>1.35</v>
       </c>
       <c r="T131">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U131">
         <v>2.82</v>
@@ -21692,34 +21692,34 @@
         <v>1.04</v>
       </c>
       <c r="X131">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y131">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z131">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="AA131">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AB131">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC131">
         <v>3.2</v>
       </c>
       <c r="AD131">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AE131">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF131">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG131">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK131">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21825,7 +21825,7 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="O132">
         <v>3.35</v>
@@ -21834,43 +21834,43 @@
         <v>2.42</v>
       </c>
       <c r="Q132">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="R132">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S132">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T132">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="U132">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V132">
         <v>1.43</v>
       </c>
       <c r="W132">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X132">
         <v>1.04</v>
       </c>
       <c r="Y132">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z132">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AA132">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB132">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AC132">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD132">
         <v>1.36</v>
@@ -21879,7 +21879,7 @@
         <v>1.1</v>
       </c>
       <c r="AF132">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AG132">
         <v>2.2</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>4.95</v>
+        <v>1.64</v>
       </c>
       <c r="R21">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="S21">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="T21">
-        <v>2.56</v>
+        <v>3.7</v>
       </c>
       <c r="U21">
-        <v>2.92</v>
+        <v>2.26</v>
       </c>
       <c r="V21">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>3.08</v>
+        <v>4.9</v>
       </c>
       <c r="AA21">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AB21">
+        <v>2.33</v>
+      </c>
+      <c r="AC21">
+        <v>2.35</v>
+      </c>
+      <c r="AD21">
+        <v>1.55</v>
+      </c>
+      <c r="AE21">
+        <v>1.18</v>
+      </c>
+      <c r="AF21">
+        <v>1.96</v>
+      </c>
+      <c r="AG21">
         <v>1.73</v>
       </c>
-      <c r="AC21">
-        <v>3.52</v>
-      </c>
-      <c r="AD21">
-        <v>1.24</v>
-      </c>
-      <c r="AE21">
-        <v>1.04</v>
-      </c>
-      <c r="AF21">
-        <v>1.85</v>
-      </c>
-      <c r="AG21">
-        <v>1.82</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AK21">
-        <v>1.17</v>
+        <v>3.9</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q22">
-        <v>1.64</v>
+        <v>4.95</v>
       </c>
       <c r="R22">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="S22">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="T22">
-        <v>3.7</v>
+        <v>2.56</v>
       </c>
       <c r="U22">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="V22">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z22">
-        <v>4.9</v>
+        <v>3.08</v>
       </c>
       <c r="AA22">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AB22">
-        <v>2.33</v>
+        <v>1.73</v>
       </c>
       <c r="AC22">
-        <v>2.35</v>
+        <v>3.52</v>
       </c>
       <c r="AD22">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="AE22">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG22">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>3.9</v>
+        <v>1.17</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q35">
         <v>2.38</v>
       </c>
       <c r="R35">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U35">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V35">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
         <v>1.11</v>
@@ -6050,22 +6050,22 @@
         <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>4.63</v>
+        <v>4.68</v>
       </c>
       <c r="AA35">
         <v>1.6</v>
       </c>
       <c r="AB35">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AC35">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AD35">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
         <v>1.53</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Q39">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
         <v>1.3</v>
       </c>
       <c r="T39">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="U39">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="V39">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
         <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AA39">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB39">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="AD39">
         <v>1.4</v>
       </c>
       <c r="AE39">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="O40">
-        <v>3.7</v>
+        <v>3.24</v>
       </c>
       <c r="P40">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="Q40">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T40">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="U40">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="V40">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W40">
         <v>1.11</v>
@@ -6862,31 +6862,31 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z40">
         <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB40">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC40">
-        <v>2.56</v>
+        <v>2.79</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE40">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="O41">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P41">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="U41">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W41">
         <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AA41">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB41">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="AC41">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="AD41">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,55 +8296,55 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q49">
-        <v>2.21</v>
+        <v>3.58</v>
       </c>
       <c r="R49">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="S49">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T49">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="U49">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
         <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA49">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AB49">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AC49">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AD49">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE49">
         <v>1.2</v>
@@ -8353,7 +8353,7 @@
         <v>1.5</v>
       </c>
       <c r="AG49">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK49">
-        <v>2.05</v>
+        <v>1.17</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,55 +8459,55 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>3.58</v>
+        <v>2.21</v>
       </c>
       <c r="R50">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T50">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="U50">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA50">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AB50">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AC50">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AD50">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE50">
         <v>1.2</v>
@@ -8516,7 +8516,7 @@
         <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AK50">
-        <v>1.17</v>
+        <v>2.05</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,25 +11230,25 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.45</v>
+        <v>1.47</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P67">
-        <v>1.96</v>
+        <v>5.06</v>
       </c>
       <c r="Q67">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="R67">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="S67">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T67">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U67">
         <v>2.02</v>
@@ -11257,37 +11257,37 @@
         <v>1.68</v>
       </c>
       <c r="W67">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA67">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB67">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AC67">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD67">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE67">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF67">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.79</v>
+        <v>1.12</v>
       </c>
       <c r="AK67">
-        <v>1.23</v>
+        <v>2.28</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,25 +11393,25 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.47</v>
+        <v>3.45</v>
       </c>
       <c r="O68">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>5.06</v>
+        <v>1.96</v>
       </c>
       <c r="Q68">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="R68">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="S68">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T68">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U68">
         <v>2.02</v>
@@ -11420,37 +11420,37 @@
         <v>1.68</v>
       </c>
       <c r="W68">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
         <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z68">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA68">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB68">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AC68">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD68">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE68">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF68">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AG68">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.12</v>
+        <v>1.79</v>
       </c>
       <c r="AK68">
-        <v>2.28</v>
+        <v>1.23</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,65 +12534,65 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="O75">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
-        <v>2.77</v>
+        <v>3.51</v>
       </c>
       <c r="Q75">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="R75">
-        <v>1.84</v>
+        <v>2.29</v>
       </c>
       <c r="S75">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="T75">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="U75">
-        <v>3.22</v>
+        <v>2.56</v>
       </c>
       <c r="V75">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W75">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y75">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="Z75">
-        <v>2.43</v>
+        <v>3.35</v>
       </c>
       <c r="AA75">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="AB75">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AC75">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="AD75">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AE75">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF75">
+        <v>1.75</v>
+      </c>
+      <c r="AG75">
         <v>2</v>
       </c>
-      <c r="AG75">
-        <v>1.78</v>
-      </c>
       <c r="AH75" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK75">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="O76">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P76">
-        <v>3.51</v>
+        <v>2.25</v>
       </c>
       <c r="Q76">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="R76">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="S76">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U76">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="V76">
         <v>1.4</v>
       </c>
       <c r="W76">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
         <v>1</v>
       </c>
       <c r="Y76">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z76">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AA76">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB76">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC76">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AD76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE76">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF76">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.79</v>
+        <v>1.36</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="O77">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P77">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="Q77">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="R77">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="S77">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="T77">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="U77">
-        <v>2.73</v>
+        <v>3.22</v>
       </c>
       <c r="V77">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W77">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Z77">
-        <v>3.38</v>
+        <v>2.43</v>
       </c>
       <c r="AA77">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="AB77">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AC77">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AD77">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AE77">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF77">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AG77">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK77">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q78">
-        <v>3.78</v>
+        <v>1.91</v>
       </c>
       <c r="R78">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="S78">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T78">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="U78">
-        <v>2.61</v>
+        <v>2.29</v>
       </c>
       <c r="V78">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z78">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="AA78">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB78">
-        <v>1.98</v>
+        <v>2.13</v>
       </c>
       <c r="AC78">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="AD78">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AE78">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF78">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG78">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK78">
-        <v>1.23</v>
+        <v>2.5</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>3.78</v>
+      </c>
+      <c r="R79">
+        <v>2.24</v>
+      </c>
+      <c r="S79">
+        <v>1.28</v>
+      </c>
+      <c r="T79">
+        <v>3.18</v>
+      </c>
+      <c r="U79">
+        <v>2.61</v>
+      </c>
+      <c r="V79">
         <v>1.44</v>
       </c>
-      <c r="O79">
-        <v>4.2</v>
-      </c>
-      <c r="P79">
-        <v>5.5</v>
-      </c>
-      <c r="Q79">
-        <v>1.91</v>
-      </c>
-      <c r="R79">
-        <v>2.38</v>
-      </c>
-      <c r="S79">
-        <v>1.29</v>
-      </c>
-      <c r="T79">
-        <v>3.32</v>
-      </c>
-      <c r="U79">
-        <v>2.29</v>
-      </c>
-      <c r="V79">
-        <v>1.53</v>
-      </c>
       <c r="W79">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z79">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="AA79">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB79">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AC79">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="AD79">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE79">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF79">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.91</v>
+        <v>1.8</v>
       </c>
       <c r="O85">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P85">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="Q85">
-        <v>3.4</v>
+        <v>2.13</v>
       </c>
       <c r="R85">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="S85">
         <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U85">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="V85">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="W85">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z85">
-        <v>5.49</v>
+        <v>5.84</v>
       </c>
       <c r="AA85">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB85">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="AC85">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD85">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AE85">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF85">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK85">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,31 +14327,31 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O86">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>3.5</v>
+        <v>2.06</v>
       </c>
       <c r="Q86">
-        <v>2.13</v>
+        <v>3.38</v>
       </c>
       <c r="R86">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S86">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T86">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U86">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V86">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W86">
         <v>1.17</v>
@@ -14360,31 +14360,31 @@
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z86">
-        <v>5.84</v>
+        <v>5.7</v>
       </c>
       <c r="AA86">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AB86">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="AC86">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD86">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AE86">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF86">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK86">
-        <v>1.97</v>
+        <v>1.35</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.8</v>
+        <v>1.19</v>
       </c>
       <c r="O87">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="P87">
-        <v>2.06</v>
+        <v>7.5</v>
       </c>
       <c r="Q87">
-        <v>3.38</v>
+        <v>1.64</v>
       </c>
       <c r="R87">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="S87">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T87">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="U87">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V87">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="W87">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
         <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA87">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB87">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AC87">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AD87">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AE87">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AF87">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG87">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK87">
-        <v>1.35</v>
+        <v>3.38</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="O88">
         <v>5.5</v>
       </c>
       <c r="P88">
-        <v>7.5</v>
+        <v>5.97</v>
       </c>
       <c r="Q88">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="R88">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="S88">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T88">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="U88">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="V88">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="W88">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z88">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA88">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AB88">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="AC88">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AD88">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AE88">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AF88">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AG88">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK88">
-        <v>3.38</v>
+        <v>2.92</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,80 +14816,80 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="O89">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="P89">
-        <v>5.97</v>
+        <v>2.28</v>
       </c>
       <c r="Q89">
-        <v>1.76</v>
+        <v>3.1</v>
       </c>
       <c r="R89">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="S89">
+        <v>1.21</v>
+      </c>
+      <c r="T89">
+        <v>3.7</v>
+      </c>
+      <c r="U89">
+        <v>2.1</v>
+      </c>
+      <c r="V89">
+        <v>1.65</v>
+      </c>
+      <c r="W89">
         <v>1.14</v>
       </c>
-      <c r="T89">
-        <v>5</v>
-      </c>
-      <c r="U89">
-        <v>1.79</v>
-      </c>
-      <c r="V89">
-        <v>2</v>
-      </c>
-      <c r="W89">
-        <v>1.29</v>
-      </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA89">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AB89">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC89">
+        <v>2.16</v>
+      </c>
+      <c r="AD89">
         <v>1.64</v>
       </c>
-      <c r="AD89">
-        <v>2.2</v>
-      </c>
       <c r="AE89">
+        <v>1.21</v>
+      </c>
+      <c r="AF89">
+        <v>1.39</v>
+      </c>
+      <c r="AG89">
+        <v>2.8</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
         <v>1.48</v>
       </c>
-      <c r="AF89">
-        <v>1.4</v>
-      </c>
-      <c r="AG89">
-        <v>2.88</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>1.13</v>
-      </c>
       <c r="AK89">
-        <v>2.92</v>
+        <v>1.44</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="O90">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P90">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="Q90">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.31</v>
+        <v>2.58</v>
       </c>
       <c r="S90">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="V90">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="W90">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X90">
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z90">
-        <v>5.2</v>
+        <v>5.49</v>
       </c>
       <c r="AA90">
         <v>1.48</v>
       </c>
       <c r="AB90">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AC90">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AD90">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AE90">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AF90">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG90">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AK90">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -16458,31 +16458,31 @@
         <v>3.75</v>
       </c>
       <c r="R99">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S99">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U99">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="V99">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W99">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
         <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z99">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA99">
         <v>1.91</v>
@@ -16491,13 +16491,13 @@
         <v>1.77</v>
       </c>
       <c r="AC99">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD99">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE99">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF99">
         <v>1.7</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O104">
         <v>3.4</v>
       </c>
       <c r="P104">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="Q104">
         <v>2.88</v>
       </c>
       <c r="R104">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="U104">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="V104">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W104">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y104">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="Z104">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AA104">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AB104">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AC104">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="AD104">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AE104">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AF104">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK104">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="O105">
         <v>3.4</v>
       </c>
       <c r="P105">
-        <v>2.85</v>
+        <v>2.58</v>
       </c>
       <c r="Q105">
         <v>2.88</v>
       </c>
       <c r="R105">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S105">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T105">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="U105">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="V105">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X105">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="Z105">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA105">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AB105">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AC105">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="AD105">
+        <v>1.6</v>
+      </c>
+      <c r="AE105">
         <v>1.25</v>
       </c>
-      <c r="AE105">
-        <v>1.08</v>
-      </c>
       <c r="AF105">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AG105">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.75</v>
+        <v>2.77</v>
       </c>
       <c r="O113">
+        <v>3</v>
+      </c>
+      <c r="P113">
+        <v>2.5</v>
+      </c>
+      <c r="Q113">
         <v>3.2</v>
       </c>
-      <c r="P113">
-        <v>5</v>
-      </c>
-      <c r="Q113">
-        <v>2.34</v>
-      </c>
       <c r="R113">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S113">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T113">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U113">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="V113">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W113">
+        <v>1.05</v>
+      </c>
+      <c r="X113">
         <v>1.03</v>
       </c>
-      <c r="X113">
-        <v>1.07</v>
-      </c>
       <c r="Y113">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z113">
-        <v>2.8</v>
+        <v>3.32</v>
       </c>
       <c r="AA113">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB113">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC113">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="AD113">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF113">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AK113">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.77</v>
+        <v>1.75</v>
       </c>
       <c r="O114">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P114">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="Q114">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="R114">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S114">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T114">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U114">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="V114">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X114">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y114">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Z114">
-        <v>3.32</v>
+        <v>2.8</v>
       </c>
       <c r="AA114">
+        <v>2.3</v>
+      </c>
+      <c r="AB114">
+        <v>1.62</v>
+      </c>
+      <c r="AC114">
+        <v>3.62</v>
+      </c>
+      <c r="AD114">
+        <v>1.2</v>
+      </c>
+      <c r="AE114">
+        <v>1.04</v>
+      </c>
+      <c r="AF114">
         <v>2</v>
       </c>
-      <c r="AB114">
-        <v>1.76</v>
-      </c>
-      <c r="AC114">
-        <v>3.7</v>
-      </c>
-      <c r="AD114">
-        <v>1.27</v>
-      </c>
-      <c r="AE114">
-        <v>1.08</v>
-      </c>
-      <c r="AF114">
-        <v>1.7</v>
-      </c>
       <c r="AG114">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="AK114">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AL114">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -635,31 +635,31 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q2">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="R2">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T2">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="U2">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
         <v>1.08</v>
@@ -668,31 +668,31 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>4.08</v>
+        <v>3.75</v>
       </c>
       <c r="AA2">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AD2">
         <v>1.4</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK2">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="O3">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R3">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="U3">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
         <v>1.07</v>
@@ -831,13 +831,13 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z3">
         <v>3.8</v>
       </c>
       <c r="AA3">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
         <v>1.96</v>
@@ -846,7 +846,7 @@
         <v>2.95</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
         <v>1.1</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.27</v>
+        <v>1.91</v>
       </c>
       <c r="AK3">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="O4">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
         <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>3.63</v>
+        <v>3.58</v>
       </c>
       <c r="R4">
         <v>2</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T4">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="U4">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
         <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
         <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>2.86</v>
+        <v>2.99</v>
       </c>
       <c r="AA4">
         <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AC4">
-        <v>3.54</v>
+        <v>3.87</v>
       </c>
       <c r="AD4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE4">
         <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
         <v>1.9</v>
@@ -1034,7 +1034,7 @@
         <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.4</v>
+        <v>1.31</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="P6">
-        <v>1.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q6">
-        <v>5.29</v>
+        <v>1.75</v>
       </c>
       <c r="R6">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
+        <v>3.5</v>
+      </c>
+      <c r="U6">
+        <v>2.25</v>
+      </c>
+      <c r="V6">
+        <v>1.57</v>
+      </c>
+      <c r="W6">
+        <v>1.09</v>
+      </c>
+      <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
+        <v>1.17</v>
+      </c>
+      <c r="Z6">
+        <v>4.6</v>
+      </c>
+      <c r="AA6">
+        <v>1.53</v>
+      </c>
+      <c r="AB6">
+        <v>2.3</v>
+      </c>
+      <c r="AC6">
+        <v>2.38</v>
+      </c>
+      <c r="AD6">
+        <v>1.53</v>
+      </c>
+      <c r="AE6">
+        <v>1.2</v>
+      </c>
+      <c r="AF6">
+        <v>1.85</v>
+      </c>
+      <c r="AG6">
+        <v>1.85</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.17</v>
+      </c>
+      <c r="AK6">
         <v>3.2</v>
-      </c>
-      <c r="U6">
-        <v>2.41</v>
-      </c>
-      <c r="V6">
-        <v>1.46</v>
-      </c>
-      <c r="W6">
-        <v>1.07</v>
-      </c>
-      <c r="X6">
-        <v>1.02</v>
-      </c>
-      <c r="Y6">
-        <v>1.16</v>
-      </c>
-      <c r="Z6">
-        <v>4.1</v>
-      </c>
-      <c r="AA6">
-        <v>1.67</v>
-      </c>
-      <c r="AB6">
-        <v>2.14</v>
-      </c>
-      <c r="AC6">
-        <v>2.59</v>
-      </c>
-      <c r="AD6">
-        <v>1.39</v>
-      </c>
-      <c r="AE6">
-        <v>1.11</v>
-      </c>
-      <c r="AF6">
-        <v>1.68</v>
-      </c>
-      <c r="AG6">
-        <v>2.02</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.16</v>
-      </c>
-      <c r="AK6">
-        <v>1.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
+        <v>4.97</v>
+      </c>
+      <c r="O7">
+        <v>3.8</v>
+      </c>
+      <c r="P7">
+        <v>1.56</v>
+      </c>
+      <c r="Q7">
+        <v>5.1</v>
+      </c>
+      <c r="R7">
+        <v>2.23</v>
+      </c>
+      <c r="S7">
+        <v>1.29</v>
+      </c>
+      <c r="T7">
+        <v>3.25</v>
+      </c>
+      <c r="U7">
+        <v>2.37</v>
+      </c>
+      <c r="V7">
+        <v>1.5</v>
+      </c>
+      <c r="W7">
+        <v>1.11</v>
+      </c>
+      <c r="X7">
+        <v>1.04</v>
+      </c>
+      <c r="Y7">
+        <v>1.22</v>
+      </c>
+      <c r="Z7">
+        <v>3.98</v>
+      </c>
+      <c r="AA7">
+        <v>1.71</v>
+      </c>
+      <c r="AB7">
+        <v>2.08</v>
+      </c>
+      <c r="AC7">
+        <v>2.76</v>
+      </c>
+      <c r="AD7">
         <v>1.36</v>
       </c>
-      <c r="O7">
-        <v>4.33</v>
-      </c>
-      <c r="P7">
-        <v>7</v>
-      </c>
-      <c r="Q7">
-        <v>1.89</v>
-      </c>
-      <c r="R7">
-        <v>2.18</v>
-      </c>
-      <c r="S7">
-        <v>1.33</v>
-      </c>
-      <c r="T7">
-        <v>2.88</v>
-      </c>
-      <c r="U7">
-        <v>2.34</v>
-      </c>
-      <c r="V7">
-        <v>1.49</v>
-      </c>
-      <c r="W7">
-        <v>1.09</v>
-      </c>
-      <c r="X7">
-        <v>1.02</v>
-      </c>
-      <c r="Y7">
+      <c r="AE7">
         <v>1.14</v>
       </c>
-      <c r="Z7">
-        <v>4.4</v>
-      </c>
-      <c r="AA7">
-        <v>1.57</v>
-      </c>
-      <c r="AB7">
-        <v>2.23</v>
-      </c>
-      <c r="AC7">
-        <v>2.28</v>
-      </c>
-      <c r="AD7">
-        <v>1.5</v>
-      </c>
-      <c r="AE7">
+      <c r="AF7">
+        <v>1.67</v>
+      </c>
+      <c r="AG7">
+        <v>1.96</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.17</v>
       </c>
-      <c r="AF7">
-        <v>1.8</v>
-      </c>
-      <c r="AG7">
-        <v>1.87</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.15</v>
-      </c>
       <c r="AK7">
-        <v>2.78</v>
+        <v>1.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
+        <v>1.1</v>
+      </c>
+      <c r="O8">
+        <v>6.85</v>
+      </c>
+      <c r="P8">
+        <v>15.5</v>
+      </c>
+      <c r="Q8">
+        <v>1.48</v>
+      </c>
+      <c r="R8">
+        <v>3.14</v>
+      </c>
+      <c r="S8">
+        <v>1.22</v>
+      </c>
+      <c r="T8">
+        <v>3.8</v>
+      </c>
+      <c r="U8">
+        <v>2.1</v>
+      </c>
+      <c r="V8">
+        <v>1.67</v>
+      </c>
+      <c r="W8">
         <v>1.17</v>
       </c>
-      <c r="O8">
-        <v>6.5</v>
-      </c>
-      <c r="P8">
-        <v>11</v>
-      </c>
-      <c r="Q8">
-        <v>1.51</v>
-      </c>
-      <c r="R8">
-        <v>2.78</v>
-      </c>
-      <c r="S8">
-        <v>1.18</v>
-      </c>
-      <c r="T8">
-        <v>3.85</v>
-      </c>
-      <c r="U8">
-        <v>2.08</v>
-      </c>
-      <c r="V8">
-        <v>1.7</v>
-      </c>
-      <c r="W8">
-        <v>1.13</v>
-      </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z8">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="AA8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB8">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AC8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD8">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AE8">
         <v>1.25</v>
       </c>
       <c r="AF8">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK8">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="O9">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="Q9">
         <v>1.7</v>
@@ -1797,22 +1797,22 @@
         <v>3.2</v>
       </c>
       <c r="U9">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V9">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W9">
         <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
         <v>1.57</v>
@@ -1821,19 +1821,19 @@
         <v>2.35</v>
       </c>
       <c r="AC9">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AD9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE9">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="O10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="P10">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="Q10">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="R10">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="S10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T10">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="U10">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V10">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="W10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1975,28 +1975,28 @@
         <v>1.03</v>
       </c>
       <c r="Z10">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB10">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AC10">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AD10">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF10">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG10">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK10">
         <v>3.3</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O11">
+        <v>3.33</v>
+      </c>
+      <c r="P11">
+        <v>2.38</v>
+      </c>
+      <c r="Q11">
+        <v>2.91</v>
+      </c>
+      <c r="R11">
+        <v>2.24</v>
+      </c>
+      <c r="S11">
+        <v>1.33</v>
+      </c>
+      <c r="T11">
+        <v>2.9</v>
+      </c>
+      <c r="U11">
+        <v>2.63</v>
+      </c>
+      <c r="V11">
+        <v>1.39</v>
+      </c>
+      <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
+        <v>1.04</v>
+      </c>
+      <c r="Y11">
+        <v>1.25</v>
+      </c>
+      <c r="Z11">
+        <v>3.5</v>
+      </c>
+      <c r="AA11">
+        <v>1.8</v>
+      </c>
+      <c r="AB11">
+        <v>1.89</v>
+      </c>
+      <c r="AC11">
         <v>3</v>
       </c>
-      <c r="P11">
-        <v>2.8</v>
-      </c>
-      <c r="Q11">
-        <v>2.7</v>
-      </c>
-      <c r="R11">
-        <v>2.2</v>
-      </c>
-      <c r="S11">
-        <v>1.29</v>
-      </c>
-      <c r="T11">
-        <v>2.35</v>
-      </c>
-      <c r="U11">
-        <v>2.56</v>
-      </c>
-      <c r="V11">
-        <v>1.41</v>
-      </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1.21</v>
-      </c>
-      <c r="Z11">
-        <v>3.58</v>
-      </c>
-      <c r="AA11">
-        <v>1.75</v>
-      </c>
-      <c r="AB11">
-        <v>1.94</v>
-      </c>
-      <c r="AC11">
-        <v>2.74</v>
-      </c>
       <c r="AD11">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AK11">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,28 +2265,28 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="O12">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="Q12">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
         <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="V12">
         <v>1.41</v>
@@ -2301,28 +2301,28 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA12">
         <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC12">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG12">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2428,34 +2428,34 @@
         </is>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P13">
         <v>1.44</v>
       </c>
       <c r="Q13">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
         <v>2.75</v>
       </c>
       <c r="U13">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V13">
         <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
         <v>1.05</v>
@@ -2464,16 +2464,16 @@
         <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA13">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB13">
         <v>1.85</v>
       </c>
       <c r="AC13">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD13">
         <v>1.3</v>
@@ -2482,7 +2482,7 @@
         <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG13">
         <v>1.75</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2.46</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="O14">
-        <v>13</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="P14">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="Q14">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="R14">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA14">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AB14">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AC14">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AD14">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AE14">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK14">
         <v>8.4</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="R15">
         <v>2</v>
       </c>
       <c r="S15">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="U15">
-        <v>3.14</v>
+        <v>2.89</v>
       </c>
       <c r="V15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2790,28 +2790,28 @@
         <v>1.34</v>
       </c>
       <c r="Z15">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="AA15">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC15">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AD15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE15">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
         <v>1.87</v>
       </c>
       <c r="AG15">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AK15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,55 +2917,55 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="O16">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="Q16">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="R16">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S16">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T16">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U16">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="V16">
         <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z16">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB16">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC16">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
         <v>1.05</v>
@@ -2974,7 +2974,7 @@
         <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,52 +3080,52 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="Q17">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="R17">
         <v>2</v>
       </c>
       <c r="S17">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="U17">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="V17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
         <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AA17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB17">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC17">
-        <v>3.88</v>
+        <v>4.5</v>
       </c>
       <c r="AD17">
         <v>1.18</v>
@@ -3134,10 +3134,10 @@
         <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q18">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S18">
         <v>1.43</v>
       </c>
       <c r="T18">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U18">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z18">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AA18">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB18">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC18">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AD18">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AE18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O19">
         <v>3.68</v>
       </c>
       <c r="P19">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q19">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="S19">
         <v>1.22</v>
@@ -3442,19 +3442,19 @@
         <v>1.13</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AA19">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AB19">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="AC19">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD19">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AE19">
         <v>1.2</v>
@@ -3572,10 +3572,10 @@
         <v>2.8</v>
       </c>
       <c r="O20">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="P20">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q20">
         <v>3.4</v>
@@ -3587,46 +3587,46 @@
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
         <v>1.2</v>
       </c>
       <c r="Z20">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AA20">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB20">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC20">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AD20">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
         <v>1.36</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O24">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA24">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB24">
         <v>1.75</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="O26">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="P26">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4710,65 +4710,65 @@
         </is>
       </c>
       <c r="N27">
+        <v>1.75</v>
+      </c>
+      <c r="O27">
+        <v>3.25</v>
+      </c>
+      <c r="P27">
+        <v>4.1</v>
+      </c>
+      <c r="Q27">
+        <v>2.25</v>
+      </c>
+      <c r="R27">
+        <v>2.1</v>
+      </c>
+      <c r="S27">
+        <v>1.45</v>
+      </c>
+      <c r="T27">
+        <v>2.49</v>
+      </c>
+      <c r="U27">
+        <v>3.08</v>
+      </c>
+      <c r="V27">
+        <v>1.31</v>
+      </c>
+      <c r="W27">
+        <v>1.04</v>
+      </c>
+      <c r="X27">
+        <v>1.05</v>
+      </c>
+      <c r="Y27">
+        <v>1.37</v>
+      </c>
+      <c r="Z27">
+        <v>2.83</v>
+      </c>
+      <c r="AA27">
+        <v>1.98</v>
+      </c>
+      <c r="AB27">
+        <v>1.67</v>
+      </c>
+      <c r="AC27">
+        <v>3.45</v>
+      </c>
+      <c r="AD27">
+        <v>1.23</v>
+      </c>
+      <c r="AE27">
+        <v>1.07</v>
+      </c>
+      <c r="AF27">
+        <v>2</v>
+      </c>
+      <c r="AG27">
         <v>1.7</v>
       </c>
-      <c r="O27">
-        <v>3.7</v>
-      </c>
-      <c r="P27">
-        <v>4.5</v>
-      </c>
-      <c r="Q27">
-        <v>2.23</v>
-      </c>
-      <c r="R27">
-        <v>2.09</v>
-      </c>
-      <c r="S27">
-        <v>1.36</v>
-      </c>
-      <c r="T27">
-        <v>2.75</v>
-      </c>
-      <c r="U27">
-        <v>2.84</v>
-      </c>
-      <c r="V27">
-        <v>1.34</v>
-      </c>
-      <c r="W27">
-        <v>1.06</v>
-      </c>
-      <c r="X27">
-        <v>1.02</v>
-      </c>
-      <c r="Y27">
-        <v>1.3</v>
-      </c>
-      <c r="Z27">
-        <v>2.97</v>
-      </c>
-      <c r="AA27">
-        <v>2.04</v>
-      </c>
-      <c r="AB27">
-        <v>1.68</v>
-      </c>
-      <c r="AC27">
-        <v>3.72</v>
-      </c>
-      <c r="AD27">
-        <v>1.2</v>
-      </c>
-      <c r="AE27">
-        <v>1.08</v>
-      </c>
-      <c r="AF27">
-        <v>1.95</v>
-      </c>
-      <c r="AG27">
-        <v>1.74</v>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="O29">
         <v>5.75</v>
       </c>
       <c r="P29">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q29">
         <v>1.57</v>
       </c>
       <c r="R29">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T29">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="V29">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="W29">
         <v>1.17</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z29">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA29">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB29">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC29">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AD29">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE29">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG29">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK29">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,28 +5202,28 @@
         <v>1.86</v>
       </c>
       <c r="O30">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P30">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="Q30">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="R30">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="U30">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="V30">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W30">
         <v>1.09</v>
@@ -5232,31 +5232,31 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z30">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="AA30">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AB30">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AC30">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="AD30">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE30">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF30">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG30">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK30">
         <v>1.89</v>
@@ -5362,22 +5362,22 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P31">
-        <v>2.9</v>
+        <v>3.29</v>
       </c>
       <c r="Q31">
         <v>3</v>
       </c>
       <c r="R31">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
         <v>2.69</v>
@@ -5395,31 +5395,31 @@
         <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="Z31">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB31">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC31">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AD31">
         <v>1.28</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
         <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
         <v>1.57</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="O32">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q32">
-        <v>4.96</v>
+        <v>5.25</v>
       </c>
       <c r="R32">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U32">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="V32">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA32">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB32">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="AC32">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AD32">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK32">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="O33">
-        <v>6.45</v>
+        <v>6.57</v>
       </c>
       <c r="P33">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="R33">
         <v>3.1</v>
@@ -5730,7 +5730,7 @@
         <v>1.3</v>
       </c>
       <c r="AB33">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AC33">
         <v>1.91</v>
@@ -5745,7 +5745,7 @@
         <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK33">
         <v>3.75</v>
@@ -5851,25 +5851,25 @@
         </is>
       </c>
       <c r="N34">
+        <v>4.55</v>
+      </c>
+      <c r="O34">
         <v>4.2</v>
       </c>
-      <c r="O34">
-        <v>4.15</v>
-      </c>
       <c r="P34">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q34">
-        <v>4.68</v>
+        <v>4.33</v>
       </c>
       <c r="R34">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
         <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U34">
         <v>2.18</v>
@@ -5884,7 +5884,7 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
         <v>5.1</v>
@@ -5896,16 +5896,16 @@
         <v>2.43</v>
       </c>
       <c r="AC34">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AD34">
         <v>1.58</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF34">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG34">
         <v>2.3</v>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
         <v>3.6</v>
@@ -6041,7 +6041,7 @@
         <v>1.48</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
         <v>1.03</v>
@@ -6050,13 +6050,13 @@
         <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>4.68</v>
+        <v>4.5</v>
       </c>
       <c r="AA35">
         <v>1.6</v>
       </c>
       <c r="AB35">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AC35">
         <v>2.55</v>
@@ -6340,28 +6340,28 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
         <v>3.1</v>
       </c>
       <c r="P37">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q37">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="R37">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T37">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="U37">
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="V37">
         <v>1.34</v>
@@ -6370,34 +6370,34 @@
         <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y37">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z37">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="AA37">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB37">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC37">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD37">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE37">
         <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG37">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P38">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="Q38">
         <v>2.3</v>
       </c>
       <c r="R38">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U38">
         <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W38">
         <v>1.14</v>
@@ -6539,25 +6539,25 @@
         <v>1.13</v>
       </c>
       <c r="Z38">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA38">
+        <v>1.5</v>
+      </c>
+      <c r="AB38">
+        <v>2.24</v>
+      </c>
+      <c r="AC38">
+        <v>2.4</v>
+      </c>
+      <c r="AD38">
         <v>1.53</v>
       </c>
-      <c r="AB38">
-        <v>2.3</v>
-      </c>
-      <c r="AC38">
-        <v>2.38</v>
-      </c>
-      <c r="AD38">
-        <v>1.54</v>
-      </c>
       <c r="AE38">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG38">
         <v>2.45</v>
@@ -6576,7 +6576,7 @@
         <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O39">
         <v>3.7</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q39">
         <v>2.15</v>
@@ -6684,10 +6684,10 @@
         <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U39">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="V39">
         <v>1.46</v>
@@ -6696,10 +6696,10 @@
         <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
         <v>4</v>
@@ -6708,38 +6708,38 @@
         <v>1.7</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC39">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD39">
         <v>1.4</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG39">
+        <v>2.08</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.18</v>
+      </c>
+      <c r="AK39">
         <v>2.05</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.2</v>
-      </c>
-      <c r="AK39">
-        <v>1.98</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="O40">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q40">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R40">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
         <v>1.29</v>
       </c>
       <c r="T40">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="U40">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="V40">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA40">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB40">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC40">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="AD40">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
         <v>1.17</v>
       </c>
       <c r="AF40">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="O41">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
         <v>2.33</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="U41">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
         <v>1.11</v>
@@ -7028,28 +7028,28 @@
         <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC41">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
         <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7170,22 +7170,22 @@
         <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="V42">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
         <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
         <v>1.2</v>
@@ -7194,25 +7194,25 @@
         <v>4.33</v>
       </c>
       <c r="AA42">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC42">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AD42">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
         <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="O43">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P43">
         <v>3.6</v>
       </c>
       <c r="Q43">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
         <v>1.4</v>
@@ -7339,43 +7339,43 @@
         <v>2.75</v>
       </c>
       <c r="U43">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V43">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
         <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z43">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA43">
         <v>2.1</v>
       </c>
       <c r="AB43">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC43">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD43">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE43">
         <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG43">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="P44">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="Q44">
         <v>2.8</v>
@@ -7511,34 +7511,34 @@
         <v>1.11</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
         <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="AA44">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB44">
         <v>1.92</v>
       </c>
       <c r="AC44">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AD44">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE44">
         <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG44">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="O45">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="P45">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q45">
         <v>2.6</v>
@@ -7659,34 +7659,34 @@
         <v>2.16</v>
       </c>
       <c r="S45">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T45">
         <v>3.2</v>
       </c>
       <c r="U45">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V45">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W45">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z45">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AA45">
         <v>1.72</v>
       </c>
       <c r="AB45">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC45">
         <v>2.74</v>
@@ -7695,13 +7695,13 @@
         <v>1.36</v>
       </c>
       <c r="AE45">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF45">
         <v>1.57</v>
       </c>
       <c r="AG45">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,22 +7807,22 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="O46">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P46">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q46">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R46">
         <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
         <v>3.58</v>
@@ -7840,25 +7840,25 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.59</v>
+        <v>5.67</v>
       </c>
       <c r="AA46">
         <v>1.45</v>
       </c>
       <c r="AB46">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AC46">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AD46">
         <v>1.71</v>
       </c>
       <c r="AE46">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF46">
         <v>1.44</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="O47">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="Q47">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R47">
         <v>2.21</v>
@@ -7997,10 +7997,10 @@
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
         <v>1.24</v>
@@ -8009,25 +8009,25 @@
         <v>3.5</v>
       </c>
       <c r="AA47">
+        <v>1.7</v>
+      </c>
+      <c r="AB47">
         <v>1.9</v>
-      </c>
-      <c r="AB47">
-        <v>1.67</v>
       </c>
       <c r="AC47">
         <v>3.3</v>
       </c>
       <c r="AD47">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE47">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AG47">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O48">
-        <v>3.77</v>
+        <v>3.89</v>
       </c>
       <c r="P48">
-        <v>3.86</v>
+        <v>4.04</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.58</v>
+        <v>2.19</v>
       </c>
       <c r="R49">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="S49">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T49">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V49">
+        <v>1.59</v>
+      </c>
+      <c r="W49">
+        <v>1.11</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
+        <v>1.17</v>
+      </c>
+      <c r="Z49">
+        <v>4.94</v>
+      </c>
+      <c r="AA49">
+        <v>1.62</v>
+      </c>
+      <c r="AB49">
+        <v>2.35</v>
+      </c>
+      <c r="AC49">
+        <v>2.33</v>
+      </c>
+      <c r="AD49">
         <v>1.6</v>
-      </c>
-      <c r="W49">
-        <v>1.13</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.14</v>
-      </c>
-      <c r="Z49">
-        <v>5.5</v>
-      </c>
-      <c r="AA49">
-        <v>1.52</v>
-      </c>
-      <c r="AB49">
-        <v>2.55</v>
-      </c>
-      <c r="AC49">
-        <v>2.23</v>
-      </c>
-      <c r="AD49">
-        <v>1.57</v>
       </c>
       <c r="AE49">
         <v>1.2</v>
       </c>
       <c r="AF49">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AK49">
-        <v>1.17</v>
+        <v>2.05</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,55 +8459,55 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q50">
-        <v>2.21</v>
+        <v>3.57</v>
       </c>
       <c r="R50">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T50">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AB50">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="AC50">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AD50">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE50">
         <v>1.2</v>
@@ -8516,7 +8516,7 @@
         <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.21</v>
+        <v>1.93</v>
       </c>
       <c r="AK50">
-        <v>2.05</v>
+        <v>1.26</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,55 +8622,55 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q51">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="R51">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U51">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="V51">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z51">
-        <v>4.75</v>
+        <v>4.93</v>
       </c>
       <c r="AA51">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB51">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AC51">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AD51">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE51">
         <v>1.2</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AK51">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O52">
         <v>3.75</v>
       </c>
       <c r="P52">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q52">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R52">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
         <v>1.23</v>
@@ -8806,7 +8806,7 @@
         <v>3.58</v>
       </c>
       <c r="U52">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
         <v>1.67</v>
@@ -8815,25 +8815,25 @@
         <v>1.18</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA52">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB52">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AC52">
         <v>2.17</v>
       </c>
       <c r="AD52">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE52">
         <v>1.24</v>
@@ -8842,7 +8842,7 @@
         <v>1.4</v>
       </c>
       <c r="AG52">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
         <v>1.48</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="O53">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P53">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q53">
         <v>2.4</v>
       </c>
       <c r="R53">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S53">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T53">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="U53">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V53">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W53">
         <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y53">
         <v>1.36</v>
       </c>
       <c r="Z53">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="AA53">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AB53">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC53">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AD53">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE53">
         <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG53">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,22 +9114,22 @@
         <v>1.13</v>
       </c>
       <c r="O54">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="P54">
         <v>13</v>
       </c>
       <c r="Q54">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="R54">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="U54">
         <v>2.4</v>
@@ -9144,31 +9144,31 @@
         <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z54">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA54">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AB54">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AC54">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AD54">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF54">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG54">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK54">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,31 +9274,31 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="O55">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P55">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
       </c>
       <c r="R55">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S55">
         <v>1.4</v>
       </c>
       <c r="T55">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U55">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="V55">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W55">
         <v>1.05</v>
@@ -9310,7 +9310,7 @@
         <v>1.38</v>
       </c>
       <c r="Z55">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AA55">
         <v>2.17</v>
@@ -9319,19 +9319,19 @@
         <v>1.61</v>
       </c>
       <c r="AC55">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="AD55">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE55">
         <v>1.03</v>
       </c>
       <c r="AF55">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG55">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
         <v>1.67</v>
@@ -9600,34 +9600,34 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P57">
         <v>2.2</v>
       </c>
       <c r="Q57">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R57">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="S57">
         <v>1.25</v>
       </c>
       <c r="T57">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="U57">
         <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
         <v>1.03</v>
@@ -9639,13 +9639,13 @@
         <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB57">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC57">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AD57">
         <v>1.6</v>
@@ -9654,10 +9654,10 @@
         <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AK57">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9932,13 +9932,13 @@
         <v>3.25</v>
       </c>
       <c r="P59">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q59">
         <v>3</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S59">
         <v>1.41</v>
@@ -9947,25 +9947,25 @@
         <v>2.75</v>
       </c>
       <c r="U59">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="V59">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W59">
         <v>1.02</v>
       </c>
       <c r="X59">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y59">
         <v>1.32</v>
       </c>
       <c r="Z59">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="AA59">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB59">
         <v>1.7</v>
@@ -9974,16 +9974,16 @@
         <v>3.8</v>
       </c>
       <c r="AD59">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE59">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF59">
         <v>1.8</v>
       </c>
       <c r="AG59">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK59">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,31 +10089,31 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="O60">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="P60">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Q60">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R60">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="S60">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T60">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U60">
         <v>2.08</v>
       </c>
       <c r="V60">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W60">
         <v>1.17</v>
@@ -10122,31 +10122,31 @@
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z60">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="AA60">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB60">
-        <v>2.45</v>
+        <v>2.68</v>
       </c>
       <c r="AC60">
         <v>2.25</v>
       </c>
       <c r="AD60">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE60">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF60">
         <v>1.9</v>
       </c>
       <c r="AG60">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AK60">
         <v>3.75</v>
@@ -10252,49 +10252,49 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O61">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P61">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q61">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="R61">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S61">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T61">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U61">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="V61">
         <v>1.4</v>
       </c>
       <c r="W61">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X61">
         <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z61">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AA61">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB61">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC61">
         <v>3.2</v>
@@ -10306,10 +10306,10 @@
         <v>1.11</v>
       </c>
       <c r="AF61">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG61">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK61">
         <v>1.75</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O62">
+        <v>2.83</v>
+      </c>
+      <c r="P62">
         <v>2.65</v>
-      </c>
-      <c r="P62">
-        <v>2.96</v>
       </c>
       <c r="Q62">
         <v>3.1</v>
@@ -10454,7 +10454,7 @@
         <v>2.3</v>
       </c>
       <c r="AA62">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AB62">
         <v>1.4</v>
@@ -10469,7 +10469,7 @@
         <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG62">
         <v>1.62</v>
@@ -10741,49 +10741,49 @@
         </is>
       </c>
       <c r="N64">
-        <v>4.75</v>
+        <v>5.95</v>
       </c>
       <c r="O64">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="P64">
         <v>1.45</v>
       </c>
       <c r="Q64">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="R64">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S64">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T64">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U64">
         <v>2.1</v>
       </c>
       <c r="V64">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W64">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X64">
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z64">
-        <v>6</v>
+        <v>5.05</v>
       </c>
       <c r="AA64">
         <v>1.47</v>
       </c>
       <c r="AB64">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AC64">
         <v>2.14</v>
@@ -10795,26 +10795,26 @@
         <v>1.23</v>
       </c>
       <c r="AF64">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
+        <v>2.45</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>2.4</v>
       </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>2.3</v>
-      </c>
       <c r="AK64">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.44</v>
+        <v>3.15</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P66">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q66">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R66">
         <v>2.35</v>
@@ -11088,10 +11088,10 @@
         <v>3.55</v>
       </c>
       <c r="U66">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V66">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W66">
         <v>1.12</v>
@@ -11100,31 +11100,31 @@
         <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>5.03</v>
+        <v>5.25</v>
       </c>
       <c r="AA66">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB66">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC66">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AD66">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE66">
         <v>1.22</v>
       </c>
       <c r="AF66">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG66">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O67">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P67">
-        <v>5.06</v>
+        <v>5.75</v>
       </c>
       <c r="Q67">
         <v>2.02</v>
       </c>
       <c r="R67">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="S67">
         <v>1.2</v>
@@ -11254,25 +11254,25 @@
         <v>2.02</v>
       </c>
       <c r="V67">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W67">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X67">
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z67">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA67">
         <v>1.4</v>
       </c>
       <c r="AB67">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC67">
         <v>2</v>
@@ -11287,7 +11287,7 @@
         <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,34 +11393,34 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O68">
         <v>3.6</v>
       </c>
       <c r="P68">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q68">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R68">
         <v>2.36</v>
       </c>
       <c r="S68">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U68">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V68">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W68">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X68">
         <v>1.02</v>
@@ -11429,13 +11429,13 @@
         <v>1.07</v>
       </c>
       <c r="Z68">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA68">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AB68">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC68">
         <v>2.1</v>
@@ -11444,13 +11444,13 @@
         <v>1.67</v>
       </c>
       <c r="AE68">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF68">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG68">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.79</v>
+        <v>1.19</v>
       </c>
       <c r="AK68">
         <v>1.23</v>
@@ -11556,43 +11556,43 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O69">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="Q69">
         <v>2.6</v>
       </c>
       <c r="R69">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S69">
         <v>1.36</v>
       </c>
       <c r="T69">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="U69">
         <v>2.75</v>
       </c>
       <c r="V69">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W69">
         <v>1.06</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
         <v>1.22</v>
       </c>
       <c r="Z69">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA69">
         <v>1.73</v>
@@ -11604,10 +11604,10 @@
         <v>2.8</v>
       </c>
       <c r="AD69">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF69">
         <v>1.7</v>
@@ -11629,7 +11629,7 @@
         <v>1.3</v>
       </c>
       <c r="AK69">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11722,46 +11722,46 @@
         <v>2.15</v>
       </c>
       <c r="O70">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P70">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="Q70">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="R70">
         <v>2</v>
       </c>
       <c r="S70">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="T70">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="U70">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="V70">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W70">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X70">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y70">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z70">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA70">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB70">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC70">
         <v>4.33</v>
@@ -11773,10 +11773,10 @@
         <v>1.02</v>
       </c>
       <c r="AF70">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG70">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AK70">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11894,7 +11894,7 @@
         <v>1.58</v>
       </c>
       <c r="R71">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="S71">
         <v>1.21</v>
@@ -11903,34 +11903,34 @@
         <v>4</v>
       </c>
       <c r="U71">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="V71">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W71">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X71">
         <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z71">
         <v>5.5</v>
       </c>
       <c r="AA71">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AB71">
         <v>2.5</v>
       </c>
       <c r="AC71">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AD71">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE71">
         <v>1.24</v>
@@ -11939,7 +11939,7 @@
         <v>1.9</v>
       </c>
       <c r="AG71">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AK71">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12048,10 +12048,10 @@
         <v>1.53</v>
       </c>
       <c r="O72">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -12060,16 +12060,16 @@
         <v>2</v>
       </c>
       <c r="S72">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="T72">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="U72">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="V72">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W72">
         <v>1.04</v>
@@ -12078,16 +12078,16 @@
         <v>1.11</v>
       </c>
       <c r="Y72">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z72">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA72">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="AB72">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC72">
         <v>5.5</v>
@@ -12217,28 +12217,28 @@
         <v>3.8</v>
       </c>
       <c r="Q73">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R73">
         <v>2.15</v>
       </c>
       <c r="S73">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T73">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U73">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V73">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W73">
+        <v>1.08</v>
+      </c>
+      <c r="X73">
         <v>1.03</v>
-      </c>
-      <c r="X73">
-        <v>1.06</v>
       </c>
       <c r="Y73">
         <v>1.3</v>
@@ -12247,13 +12247,13 @@
         <v>3.25</v>
       </c>
       <c r="AA73">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB73">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC73">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD73">
         <v>1.3</v>
@@ -12265,7 +12265,7 @@
         <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12371,25 +12371,25 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="O74">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q74">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R74">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="S74">
         <v>1.35</v>
       </c>
       <c r="T74">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U74">
         <v>2.6</v>
@@ -12401,7 +12401,7 @@
         <v>1.07</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
         <v>1.21</v>
@@ -12410,25 +12410,25 @@
         <v>3.85</v>
       </c>
       <c r="AA74">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB74">
         <v>1.9</v>
       </c>
       <c r="AC74">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AD74">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE74">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF74">
         <v>1.75</v>
       </c>
       <c r="AG74">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK74">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,49 +12534,49 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O75">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="P75">
-        <v>3.51</v>
+        <v>3.65</v>
       </c>
       <c r="Q75">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R75">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="S75">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T75">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U75">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V75">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z75">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AA75">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB75">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AC75">
         <v>3.35</v>
@@ -12585,7 +12585,7 @@
         <v>1.33</v>
       </c>
       <c r="AE75">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF75">
         <v>1.75</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="O76">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P76">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q76">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="R76">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="S76">
+        <v>1.48</v>
+      </c>
+      <c r="T76">
+        <v>2.47</v>
+      </c>
+      <c r="U76">
+        <v>3.16</v>
+      </c>
+      <c r="V76">
+        <v>1.31</v>
+      </c>
+      <c r="W76">
+        <v>1.03</v>
+      </c>
+      <c r="X76">
+        <v>1.04</v>
+      </c>
+      <c r="Y76">
+        <v>1.48</v>
+      </c>
+      <c r="Z76">
+        <v>2.71</v>
+      </c>
+      <c r="AA76">
+        <v>2.23</v>
+      </c>
+      <c r="AB76">
+        <v>1.53</v>
+      </c>
+      <c r="AC76">
+        <v>4.8</v>
+      </c>
+      <c r="AD76">
+        <v>1.15</v>
+      </c>
+      <c r="AE76">
+        <v>1.05</v>
+      </c>
+      <c r="AF76">
+        <v>2</v>
+      </c>
+      <c r="AG76">
+        <v>1.78</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.36</v>
       </c>
-      <c r="T76">
-        <v>2.9</v>
-      </c>
-      <c r="U76">
-        <v>2.73</v>
-      </c>
-      <c r="V76">
-        <v>1.4</v>
-      </c>
-      <c r="W76">
-        <v>1.08</v>
-      </c>
-      <c r="X76">
-        <v>1</v>
-      </c>
-      <c r="Y76">
-        <v>1.24</v>
-      </c>
-      <c r="Z76">
-        <v>3.38</v>
-      </c>
-      <c r="AA76">
-        <v>1.88</v>
-      </c>
-      <c r="AB76">
-        <v>1.85</v>
-      </c>
-      <c r="AC76">
-        <v>3.5</v>
-      </c>
-      <c r="AD76">
-        <v>1.3</v>
-      </c>
-      <c r="AE76">
-        <v>1.12</v>
-      </c>
-      <c r="AF76">
-        <v>1.67</v>
-      </c>
-      <c r="AG76">
-        <v>2.08</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.3</v>
-      </c>
       <c r="AK76">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="O77">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>2.77</v>
+        <v>2.06</v>
       </c>
       <c r="Q77">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="R77">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="T77">
-        <v>2.47</v>
+        <v>2.68</v>
       </c>
       <c r="U77">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="V77">
+        <v>1.4</v>
+      </c>
+      <c r="W77">
+        <v>1.05</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+      <c r="Y77">
+        <v>1.24</v>
+      </c>
+      <c r="Z77">
+        <v>3.3</v>
+      </c>
+      <c r="AA77">
+        <v>1.88</v>
+      </c>
+      <c r="AB77">
+        <v>1.77</v>
+      </c>
+      <c r="AC77">
+        <v>3.35</v>
+      </c>
+      <c r="AD77">
+        <v>1.29</v>
+      </c>
+      <c r="AE77">
+        <v>1.07</v>
+      </c>
+      <c r="AF77">
+        <v>1.67</v>
+      </c>
+      <c r="AG77">
+        <v>2.05</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
         <v>1.3</v>
       </c>
-      <c r="W77">
-        <v>1.03</v>
-      </c>
-      <c r="X77">
-        <v>1.04</v>
-      </c>
-      <c r="Y77">
-        <v>1.46</v>
-      </c>
-      <c r="Z77">
-        <v>2.43</v>
-      </c>
-      <c r="AA77">
-        <v>2.55</v>
-      </c>
-      <c r="AB77">
-        <v>1.51</v>
-      </c>
-      <c r="AC77">
-        <v>5</v>
-      </c>
-      <c r="AD77">
-        <v>1.16</v>
-      </c>
-      <c r="AE77">
-        <v>1.05</v>
-      </c>
-      <c r="AF77">
-        <v>2</v>
-      </c>
-      <c r="AG77">
-        <v>1.78</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.35</v>
-      </c>
       <c r="AK77">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13029,25 +13029,25 @@
         <v>4.2</v>
       </c>
       <c r="P78">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q78">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R78">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T78">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U78">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="V78">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W78">
         <v>1.08</v>
@@ -13056,47 +13056,47 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z78">
         <v>4.5</v>
       </c>
       <c r="AA78">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB78">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC78">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AD78">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE78">
+        <v>1.2</v>
+      </c>
+      <c r="AF78">
+        <v>1.75</v>
+      </c>
+      <c r="AG78">
+        <v>2</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
         <v>1.13</v>
       </c>
-      <c r="AF78">
-        <v>1.73</v>
-      </c>
-      <c r="AG78">
-        <v>1.94</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.2</v>
-      </c>
       <c r="AK78">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,10 +13195,10 @@
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="R79">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S79">
         <v>1.28</v>
@@ -13207,7 +13207,7 @@
         <v>3.18</v>
       </c>
       <c r="U79">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="V79">
         <v>1.44</v>
@@ -13216,28 +13216,28 @@
         <v>1.06</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
         <v>1.18</v>
       </c>
       <c r="Z79">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AA79">
         <v>1.75</v>
       </c>
       <c r="AB79">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AC79">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="AD79">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE79">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF79">
         <v>1.62</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P80">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q81">
         <v>2.44</v>
@@ -13533,13 +13533,13 @@
         <v>2.73</v>
       </c>
       <c r="U81">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="V81">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X81">
         <v>1.03</v>
@@ -13554,13 +13554,13 @@
         <v>1.84</v>
       </c>
       <c r="AB81">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC81">
         <v>3.04</v>
       </c>
       <c r="AD81">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE81">
         <v>1.1</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O82">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P82">
         <v>3.5</v>
@@ -13687,52 +13687,52 @@
         <v>2.57</v>
       </c>
       <c r="R82">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S82">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U82">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V82">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X82">
         <v>1.03</v>
       </c>
       <c r="Y82">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z82">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA82">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AB82">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC82">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD82">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE82">
         <v>1.06</v>
       </c>
       <c r="AF82">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG82">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.29</v>
       </c>
       <c r="AK82">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13844,19 +13844,19 @@
         <v>8.5</v>
       </c>
       <c r="P83">
-        <v>13.37</v>
+        <v>13</v>
       </c>
       <c r="Q83">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R83">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="S83">
         <v>1.11</v>
       </c>
       <c r="T83">
-        <v>5.15</v>
+        <v>5.3</v>
       </c>
       <c r="U83">
         <v>1.75</v>
@@ -13865,7 +13865,7 @@
         <v>2</v>
       </c>
       <c r="W83">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13880,22 +13880,22 @@
         <v>1.22</v>
       </c>
       <c r="AB83">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AC83">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD83">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AE83">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AF83">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG83">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.06</v>
       </c>
       <c r="AK83">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="O84">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P84">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q84">
         <v>2.8</v>
       </c>
       <c r="R84">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
         <v>1.25</v>
@@ -14037,19 +14037,19 @@
         <v>1.17</v>
       </c>
       <c r="Z84">
-        <v>5</v>
+        <v>5.36</v>
       </c>
       <c r="AA84">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB84">
         <v>2.5</v>
       </c>
       <c r="AC84">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD84">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AE84">
         <v>1.25</v>
@@ -14058,7 +14058,7 @@
         <v>1.43</v>
       </c>
       <c r="AG84">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,31 +14164,31 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O85">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q85">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="R85">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
         <v>4</v>
       </c>
       <c r="U85">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="V85">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W85">
         <v>1.17</v>
@@ -14197,31 +14197,31 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>5.84</v>
+        <v>6</v>
       </c>
       <c r="AA85">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AB85">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="AC85">
         <v>2.05</v>
       </c>
       <c r="AD85">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE85">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF85">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AG85">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14336,22 +14336,22 @@
         <v>2.06</v>
       </c>
       <c r="Q86">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="R86">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S86">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T86">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U86">
         <v>2</v>
       </c>
       <c r="V86">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W86">
         <v>1.17</v>
@@ -14363,28 +14363,28 @@
         <v>1.08</v>
       </c>
       <c r="Z86">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA86">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB86">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AC86">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AD86">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AE86">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF86">
         <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK86">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,10 +14490,10 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="O87">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P87">
         <v>7.5</v>
@@ -14502,16 +14502,16 @@
         <v>1.64</v>
       </c>
       <c r="R87">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="S87">
         <v>1.18</v>
       </c>
       <c r="T87">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="U87">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V87">
         <v>1.81</v>
@@ -14523,31 +14523,31 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z87">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA87">
         <v>1.36</v>
       </c>
       <c r="AB87">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AC87">
         <v>1.9</v>
       </c>
       <c r="AD87">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AE87">
         <v>1.36</v>
       </c>
       <c r="AF87">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG87">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,58 +14653,58 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.34</v>
+        <v>2.55</v>
       </c>
       <c r="O88">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="P88">
-        <v>5.97</v>
+        <v>2.35</v>
       </c>
       <c r="Q88">
-        <v>1.76</v>
+        <v>3.12</v>
       </c>
       <c r="R88">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="S88">
+        <v>1.2</v>
+      </c>
+      <c r="T88">
+        <v>4</v>
+      </c>
+      <c r="U88">
+        <v>2.1</v>
+      </c>
+      <c r="V88">
+        <v>1.65</v>
+      </c>
+      <c r="W88">
         <v>1.14</v>
       </c>
-      <c r="T88">
-        <v>5</v>
-      </c>
-      <c r="U88">
-        <v>1.79</v>
-      </c>
-      <c r="V88">
-        <v>2</v>
-      </c>
-      <c r="W88">
-        <v>1.29</v>
-      </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y88">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z88">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA88">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AB88">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="AC88">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="AD88">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="AE88">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AF88">
         <v>1.4</v>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AK88">
-        <v>2.92</v>
+        <v>1.44</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
+        <v>1.89</v>
+      </c>
+      <c r="O89">
+        <v>4.35</v>
+      </c>
+      <c r="P89">
+        <v>3.34</v>
+      </c>
+      <c r="Q89">
         <v>2.45</v>
       </c>
-      <c r="O89">
-        <v>3.75</v>
-      </c>
-      <c r="P89">
-        <v>2.28</v>
-      </c>
-      <c r="Q89">
-        <v>3.1</v>
-      </c>
       <c r="R89">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="S89">
+        <v>1.17</v>
+      </c>
+      <c r="T89">
+        <v>4.4</v>
+      </c>
+      <c r="U89">
+        <v>1.94</v>
+      </c>
+      <c r="V89">
+        <v>1.88</v>
+      </c>
+      <c r="W89">
         <v>1.21</v>
       </c>
-      <c r="T89">
-        <v>3.7</v>
-      </c>
-      <c r="U89">
-        <v>2.1</v>
-      </c>
-      <c r="V89">
-        <v>1.65</v>
-      </c>
-      <c r="W89">
-        <v>1.14</v>
-      </c>
       <c r="X89">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z89">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AA89">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AB89">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AC89">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="AD89">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AE89">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AF89">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AG89">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AK89">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,25 +14979,25 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="O90">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P90">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q90">
         <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="S90">
         <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U90">
         <v>2.03</v>
@@ -15012,25 +15012,25 @@
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z90">
-        <v>5.49</v>
+        <v>5.5</v>
       </c>
       <c r="AA90">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AB90">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AC90">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AD90">
         <v>1.69</v>
       </c>
       <c r="AE90">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF90">
         <v>1.4</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK90">
         <v>1.25</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="O91">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="P91">
+        <v>5.97</v>
+      </c>
+      <c r="Q91">
+        <v>1.75</v>
+      </c>
+      <c r="R91">
         <v>2.9</v>
       </c>
-      <c r="Q91">
-        <v>2.45</v>
-      </c>
-      <c r="R91">
-        <v>2.75</v>
-      </c>
       <c r="S91">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T91">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="U91">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="V91">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="W91">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Z91">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA91">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB91">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AC91">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AD91">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AE91">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AF91">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AG91">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK91">
-        <v>1.77</v>
+        <v>2.92</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,22 +15305,22 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O92">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="P92">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="Q92">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R92">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="S92">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T92">
         <v>3.28</v>
@@ -15329,7 +15329,7 @@
         <v>2.45</v>
       </c>
       <c r="V92">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
         <v>1.11</v>
@@ -15341,16 +15341,16 @@
         <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AA92">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB92">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC92">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD92">
         <v>1.4</v>
@@ -15362,7 +15362,7 @@
         <v>1.6</v>
       </c>
       <c r="AG92">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK92">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O93">
         <v>3.4</v>
@@ -15477,31 +15477,31 @@
         <v>2.4</v>
       </c>
       <c r="Q93">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="R93">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="S93">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U93">
         <v>2.2</v>
       </c>
       <c r="V93">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W93">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
         <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z93">
         <v>4.7</v>
@@ -15516,10 +15516,10 @@
         <v>2.5</v>
       </c>
       <c r="AD93">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AE93">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF93">
         <v>1.43</v>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK93">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15649,31 +15649,31 @@
         <v>1.25</v>
       </c>
       <c r="T94">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="U94">
         <v>2.43</v>
       </c>
       <c r="V94">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W94">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
         <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z94">
         <v>4.33</v>
       </c>
       <c r="AA94">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB94">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AC94">
         <v>2.7</v>
@@ -15688,7 +15688,7 @@
         <v>1.73</v>
       </c>
       <c r="AG94">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15794,31 +15794,31 @@
         </is>
       </c>
       <c r="N95">
+        <v>2.45</v>
+      </c>
+      <c r="O95">
+        <v>3.35</v>
+      </c>
+      <c r="P95">
+        <v>2.75</v>
+      </c>
+      <c r="Q95">
+        <v>2.75</v>
+      </c>
+      <c r="R95">
         <v>2.3</v>
-      </c>
-      <c r="O95">
-        <v>3.4</v>
-      </c>
-      <c r="P95">
-        <v>2.6</v>
-      </c>
-      <c r="Q95">
-        <v>2.85</v>
-      </c>
-      <c r="R95">
-        <v>2.21</v>
       </c>
       <c r="S95">
         <v>1.29</v>
       </c>
       <c r="T95">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="U95">
         <v>2.38</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
         <v>1.11</v>
@@ -15833,16 +15833,16 @@
         <v>4.4</v>
       </c>
       <c r="AA95">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB95">
         <v>2.15</v>
       </c>
       <c r="AC95">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD95">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE95">
         <v>1.12</v>
@@ -15851,7 +15851,7 @@
         <v>1.53</v>
       </c>
       <c r="AG95">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK95">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,31 +15957,31 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O96">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P96">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="Q96">
+        <v>2.2</v>
+      </c>
+      <c r="R96">
         <v>2.22</v>
       </c>
-      <c r="R96">
-        <v>2.17</v>
-      </c>
       <c r="S96">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T96">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="U96">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="V96">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W96">
         <v>1.08</v>
@@ -15990,31 +15990,31 @@
         <v>1.05</v>
       </c>
       <c r="Y96">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z96">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AA96">
         <v>1.85</v>
       </c>
       <c r="AB96">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC96">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="AD96">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE96">
         <v>1.12</v>
       </c>
       <c r="AF96">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG96">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK96">
         <v>2.1</v>
@@ -16123,16 +16123,16 @@
         <v>2.2</v>
       </c>
       <c r="O97">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P97">
         <v>2.7</v>
       </c>
       <c r="Q97">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R97">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="S97">
         <v>1.22</v>
@@ -16141,10 +16141,10 @@
         <v>3.5</v>
       </c>
       <c r="U97">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V97">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W97">
         <v>1.13</v>
@@ -16153,22 +16153,22 @@
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z97">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA97">
         <v>1.53</v>
       </c>
       <c r="AB97">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="AC97">
         <v>2.45</v>
       </c>
       <c r="AD97">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE97">
         <v>1.2</v>
@@ -16193,7 +16193,7 @@
         <v>1.4</v>
       </c>
       <c r="AK97">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,34 +16283,34 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O98">
         <v>3.6</v>
       </c>
       <c r="P98">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q98">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="R98">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S98">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T98">
         <v>3.5</v>
       </c>
       <c r="U98">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V98">
         <v>1.57</v>
       </c>
       <c r="W98">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
         <v>1.01</v>
@@ -16319,28 +16319,28 @@
         <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA98">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB98">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AC98">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AD98">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE98">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF98">
         <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK98">
         <v>1.65</v>
@@ -16455,49 +16455,49 @@
         <v>0</v>
       </c>
       <c r="Q99">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R99">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S99">
         <v>1.33</v>
       </c>
       <c r="T99">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U99">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="V99">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W99">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X99">
         <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z99">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA99">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB99">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC99">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="AD99">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE99">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF99">
         <v>1.7</v>
@@ -16519,7 +16519,7 @@
         <v>1.27</v>
       </c>
       <c r="AK99">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17587,61 +17587,61 @@
         </is>
       </c>
       <c r="N106">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="O106">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P106">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Q106">
-        <v>7.55</v>
+        <v>7.5</v>
       </c>
       <c r="R106">
         <v>2.63</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T106">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U106">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V106">
         <v>1.57</v>
       </c>
       <c r="W106">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X106">
         <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z106">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="AA106">
+        <v>1.5</v>
+      </c>
+      <c r="AB106">
+        <v>2.28</v>
+      </c>
+      <c r="AC106">
+        <v>2.27</v>
+      </c>
+      <c r="AD106">
         <v>1.54</v>
       </c>
-      <c r="AB106">
-        <v>2.29</v>
-      </c>
-      <c r="AC106">
-        <v>2.33</v>
-      </c>
-      <c r="AD106">
-        <v>1.51</v>
-      </c>
       <c r="AE106">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF106">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG106">
         <v>1.75</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK106">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18405,31 +18405,31 @@
         <v>2.85</v>
       </c>
       <c r="O111">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P111">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q111">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="R111">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S111">
         <v>1.36</v>
       </c>
       <c r="T111">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="U111">
         <v>2.65</v>
       </c>
       <c r="V111">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="W111">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X111">
         <v>1.02</v>
@@ -18438,13 +18438,13 @@
         <v>1.22</v>
       </c>
       <c r="Z111">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA111">
         <v>1.8</v>
       </c>
       <c r="AB111">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC111">
         <v>2.95</v>
@@ -18453,7 +18453,7 @@
         <v>1.39</v>
       </c>
       <c r="AE111">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF111">
         <v>1.67</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK111">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="O112">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="P112">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB112">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="O113">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P113">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -18749,37 +18749,37 @@
         <v>2.7</v>
       </c>
       <c r="U113">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V113">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W113">
         <v>1.05</v>
       </c>
       <c r="X113">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y113">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z113">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="AA113">
         <v>2</v>
       </c>
       <c r="AB113">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AC113">
         <v>3.7</v>
       </c>
       <c r="AD113">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE113">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF113">
         <v>1.7</v>
@@ -18801,7 +18801,7 @@
         <v>1.34</v>
       </c>
       <c r="AK113">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,19 +18891,19 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O114">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P114">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q114">
         <v>2.34</v>
       </c>
       <c r="R114">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S114">
         <v>1.48</v>
@@ -18918,16 +18918,16 @@
         <v>1.35</v>
       </c>
       <c r="W114">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X114">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y114">
         <v>1.41</v>
       </c>
       <c r="Z114">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AA114">
         <v>2.3</v>
@@ -18936,7 +18936,7 @@
         <v>1.62</v>
       </c>
       <c r="AC114">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AD114">
         <v>1.2</v>
@@ -18945,10 +18945,10 @@
         <v>1.04</v>
       </c>
       <c r="AF114">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG114">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK114">
         <v>2</v>
@@ -19226,7 +19226,7 @@
         <v>3.8</v>
       </c>
       <c r="Q116">
-        <v>2.79</v>
+        <v>2.59</v>
       </c>
       <c r="R116">
         <v>2.09</v>
@@ -19235,13 +19235,13 @@
         <v>1.48</v>
       </c>
       <c r="T116">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U116">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="V116">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W116">
         <v>1.05</v>
@@ -19250,16 +19250,16 @@
         <v>1.08</v>
       </c>
       <c r="Y116">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z116">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AA116">
         <v>2.3</v>
       </c>
       <c r="AB116">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC116">
         <v>4.15</v>
@@ -19271,7 +19271,7 @@
         <v>1.03</v>
       </c>
       <c r="AF116">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG116">
         <v>1.75</v>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK116">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O117">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P117">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q117">
         <v>2.08</v>
@@ -19395,10 +19395,10 @@
         <v>2.22</v>
       </c>
       <c r="S117">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T117">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U117">
         <v>2.4</v>
@@ -19422,22 +19422,22 @@
         <v>1.65</v>
       </c>
       <c r="AB117">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AC117">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="AD117">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE117">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF117">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG117">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O118">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P118">
         <v>3.4</v>
       </c>
       <c r="Q118">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R118">
         <v>2.1</v>
       </c>
       <c r="S118">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T118">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U118">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="V118">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W118">
         <v>1.05</v>
       </c>
       <c r="X118">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z118">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA118">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AB118">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC118">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AD118">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE118">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF118">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG118">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK118">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19724,16 +19724,16 @@
         <v>1.33</v>
       </c>
       <c r="T119">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U119">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="V119">
         <v>1.44</v>
       </c>
       <c r="W119">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X119">
         <v>1.02</v>
@@ -19742,28 +19742,28 @@
         <v>1.22</v>
       </c>
       <c r="Z119">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="AA119">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB119">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC119">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD119">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE119">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF119">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG119">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>1.29</v>
       </c>
       <c r="AK119">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>3.7</v>
+        <v>1.83</v>
       </c>
       <c r="O120">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P120">
-        <v>1.98</v>
+        <v>4.25</v>
       </c>
       <c r="Q120">
-        <v>4.46</v>
+        <v>2.33</v>
       </c>
       <c r="R120">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="S120">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T120">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="U120">
+        <v>2.79</v>
+      </c>
+      <c r="V120">
+        <v>1.36</v>
+      </c>
+      <c r="W120">
+        <v>1.08</v>
+      </c>
+      <c r="X120">
+        <v>1.06</v>
+      </c>
+      <c r="Y120">
+        <v>1.3</v>
+      </c>
+      <c r="Z120">
         <v>3.25</v>
       </c>
-      <c r="V120">
+      <c r="AA120">
+        <v>2</v>
+      </c>
+      <c r="AB120">
+        <v>1.7</v>
+      </c>
+      <c r="AC120">
+        <v>3.5</v>
+      </c>
+      <c r="AD120">
         <v>1.29</v>
       </c>
-      <c r="W120">
+      <c r="AE120">
         <v>1.05</v>
       </c>
-      <c r="X120">
-        <v>1.03</v>
-      </c>
-      <c r="Y120">
-        <v>1.43</v>
-      </c>
-      <c r="Z120">
-        <v>2.59</v>
-      </c>
-      <c r="AA120">
-        <v>2.23</v>
-      </c>
-      <c r="AB120">
-        <v>1.54</v>
-      </c>
-      <c r="AC120">
-        <v>4.4</v>
-      </c>
-      <c r="AD120">
-        <v>1.14</v>
-      </c>
-      <c r="AE120">
-        <v>1.01</v>
-      </c>
       <c r="AF120">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AG120">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="AK120">
-        <v>1.21</v>
+        <v>1.83</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.75</v>
+        <v>3.8</v>
       </c>
       <c r="O121">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="P121">
-        <v>4.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q121">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="R121">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="S121">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T121">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="U121">
-        <v>2.69</v>
+        <v>3.42</v>
       </c>
       <c r="V121">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="W121">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y121">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Z121">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="AA121">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="AB121">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC121">
-        <v>3.4</v>
+        <v>4.65</v>
       </c>
       <c r="AD121">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE121">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF121">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="AG121">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="AK121">
-        <v>1.91</v>
+        <v>1.16</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20201,19 +20201,19 @@
         <v>3.1</v>
       </c>
       <c r="P122">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
       </c>
       <c r="R122">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S122">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T122">
-        <v>2.59</v>
+        <v>2.93</v>
       </c>
       <c r="U122">
         <v>2.88</v>
@@ -20222,19 +20222,19 @@
         <v>1.36</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y122">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z122">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="AA122">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB122">
         <v>1.75</v>
@@ -20361,19 +20361,19 @@
         <v>1.5</v>
       </c>
       <c r="O123">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P123">
         <v>5.75</v>
       </c>
       <c r="Q123">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="R123">
         <v>2.03</v>
       </c>
       <c r="S123">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T123">
         <v>2.63</v>
@@ -20400,7 +20400,7 @@
         <v>2.11</v>
       </c>
       <c r="AB123">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC123">
         <v>3.58</v>
@@ -20431,7 +20431,7 @@
         <v>1.2</v>
       </c>
       <c r="AK123">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL123">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -2920,7 +2920,7 @@
         <v>2.05</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
         <v>3.1</v>
@@ -3083,19 +3083,19 @@
         <v>2.05</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q17">
-        <v>2.77</v>
+        <v>2.92</v>
       </c>
       <c r="R17">
         <v>2</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
         <v>2.6</v>
@@ -3113,7 +3113,7 @@
         <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z17">
         <v>2.88</v>
@@ -3128,10 +3128,10 @@
         <v>4.5</v>
       </c>
       <c r="AD17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
         <v>2</v>
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="Q21">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="R21">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="S21">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="T21">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="U21">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="V21">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
         <v>1.14</v>
@@ -3768,28 +3768,28 @@
         <v>1.13</v>
       </c>
       <c r="Z21">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD21">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE21">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF21">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG21">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK21">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.19</v>
+        <v>3.68</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q22">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="R22">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
         <v>1.41</v>
       </c>
       <c r="T22">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U22">
         <v>2.92</v>
       </c>
       <c r="V22">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W22">
         <v>1.05</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA22">
         <v>2.03</v>
       </c>
       <c r="AB22">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC22">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="AD22">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE22">
         <v>1.04</v>
       </c>
       <c r="AF22">
+        <v>1.87</v>
+      </c>
+      <c r="AG22">
+        <v>1.87</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.85</v>
       </c>
-      <c r="AG22">
-        <v>1.82</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.28</v>
-      </c>
       <c r="AK22">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>3.82</v>
       </c>
       <c r="O25">
-        <v>4.2</v>
+        <v>3.79</v>
       </c>
       <c r="P25">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="Q25">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S25">
         <v>1.22</v>
       </c>
       <c r="T25">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="U25">
         <v>2.25</v>
@@ -4414,7 +4414,7 @@
         <v>1.14</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
         <v>1.14</v>
@@ -4423,25 +4423,25 @@
         <v>5.5</v>
       </c>
       <c r="AA25">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB25">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="AC25">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="AD25">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AE25">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF25">
         <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
+        <v>1.17</v>
+      </c>
+      <c r="AK25">
         <v>1.14</v>
-      </c>
-      <c r="AK25">
-        <v>1.12</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="O28">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="P28">
-        <v>6.72</v>
+        <v>6.1</v>
       </c>
       <c r="Q28">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S28">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="U28">
+        <v>2.1</v>
+      </c>
+      <c r="V28">
+        <v>1.67</v>
+      </c>
+      <c r="W28">
+        <v>1.17</v>
+      </c>
+      <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.11</v>
+      </c>
+      <c r="Z28">
+        <v>4.95</v>
+      </c>
+      <c r="AA28">
+        <v>1.5</v>
+      </c>
+      <c r="AB28">
+        <v>2.5</v>
+      </c>
+      <c r="AC28">
         <v>2.25</v>
       </c>
-      <c r="V28">
-        <v>1.57</v>
-      </c>
-      <c r="W28">
-        <v>1.14</v>
-      </c>
-      <c r="X28">
-        <v>1.02</v>
-      </c>
-      <c r="Y28">
-        <v>1.1</v>
-      </c>
-      <c r="Z28">
-        <v>5.15</v>
-      </c>
-      <c r="AA28">
-        <v>1.44</v>
-      </c>
-      <c r="AB28">
-        <v>2.43</v>
-      </c>
-      <c r="AC28">
-        <v>2.17</v>
-      </c>
       <c r="AD28">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE28">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK28">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O35">
         <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q35">
         <v>2.38</v>
@@ -6087,7 +6087,7 @@
         <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q36">
         <v>7.5</v>
       </c>
       <c r="R36">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S36">
         <v>1.22</v>
@@ -6201,13 +6201,13 @@
         <v>2.1</v>
       </c>
       <c r="V36">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W36">
         <v>1.17</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.13</v>
@@ -6222,19 +6222,19 @@
         <v>2.6</v>
       </c>
       <c r="AC36">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD36">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE36">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG36">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK36">
         <v>1.05</v>
@@ -6521,13 +6521,13 @@
         <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="U38">
         <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W38">
         <v>1.14</v>
@@ -6545,10 +6545,10 @@
         <v>1.5</v>
       </c>
       <c r="AB38">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AC38">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD38">
         <v>1.53</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="O46">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P46">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -7822,16 +7822,16 @@
         <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T46">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="U46">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="V46">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W46">
         <v>1.17</v>
@@ -7840,31 +7840,31 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z46">
-        <v>5.67</v>
+        <v>5.31</v>
       </c>
       <c r="AA46">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AB46">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AC46">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AD46">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE46">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF46">
         <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.56</v>
+        <v>2.32</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q49">
-        <v>2.19</v>
+        <v>3.57</v>
       </c>
       <c r="R49">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T49">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U49">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V49">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>4.94</v>
+        <v>5.5</v>
       </c>
       <c r="AA49">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AB49">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AC49">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD49">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE49">
         <v>1.2</v>
       </c>
       <c r="AF49">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG49">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.21</v>
+        <v>1.93</v>
       </c>
       <c r="AK49">
-        <v>2.05</v>
+        <v>1.26</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>3.57</v>
+        <v>2.19</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T50">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
+        <v>1.59</v>
+      </c>
+      <c r="W50">
+        <v>1.11</v>
+      </c>
+      <c r="X50">
+        <v>1.03</v>
+      </c>
+      <c r="Y50">
+        <v>1.17</v>
+      </c>
+      <c r="Z50">
+        <v>4.94</v>
+      </c>
+      <c r="AA50">
         <v>1.62</v>
       </c>
-      <c r="W50">
-        <v>1.13</v>
-      </c>
-      <c r="X50">
-        <v>1.01</v>
-      </c>
-      <c r="Y50">
-        <v>1.14</v>
-      </c>
-      <c r="Z50">
-        <v>5.5</v>
-      </c>
-      <c r="AA50">
-        <v>1.51</v>
-      </c>
       <c r="AB50">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AC50">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD50">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE50">
         <v>1.2</v>
       </c>
       <c r="AF50">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG50">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.93</v>
+        <v>1.21</v>
       </c>
       <c r="AK50">
-        <v>1.26</v>
+        <v>2.05</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,16 +8622,16 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="O51">
         <v>3.7</v>
       </c>
       <c r="P51">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q51">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="R51">
         <v>2.3</v>
@@ -8658,7 +8658,7 @@
         <v>1.19</v>
       </c>
       <c r="Z51">
-        <v>4.93</v>
+        <v>4.98</v>
       </c>
       <c r="AA51">
         <v>1.56</v>
@@ -8667,7 +8667,7 @@
         <v>2.29</v>
       </c>
       <c r="AC51">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AD51">
         <v>1.5</v>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O52">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P52">
         <v>2.37</v>
@@ -8800,19 +8800,19 @@
         <v>2.4</v>
       </c>
       <c r="S52">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="U52">
         <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8821,28 +8821,28 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA52">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AB52">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="AC52">
         <v>2.17</v>
       </c>
       <c r="AD52">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE52">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF52">
         <v>1.4</v>
       </c>
       <c r="AG52">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O58">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="P58">
-        <v>4.25</v>
+        <v>4.95</v>
       </c>
       <c r="Q58">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="R58">
         <v>2.5</v>
@@ -9781,7 +9781,7 @@
         <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="U58">
         <v>2.15</v>
@@ -9796,31 +9796,31 @@
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z58">
-        <v>5.21</v>
+        <v>4.8</v>
       </c>
       <c r="AA58">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB58">
         <v>2.4</v>
       </c>
       <c r="AC58">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AD58">
         <v>1.57</v>
       </c>
       <c r="AE58">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF58">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG58">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O65">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="Q65">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="R65">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S65">
         <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U65">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V65">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W65">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
         <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA65">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB65">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC65">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD65">
         <v>1.36</v>
       </c>
       <c r="AE65">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF65">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.15</v>
+        <v>1.48</v>
       </c>
       <c r="O66">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="P66">
-        <v>1.85</v>
+        <v>5.75</v>
       </c>
       <c r="Q66">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="R66">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T66">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U66">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="V66">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="W66">
+        <v>1.2</v>
+      </c>
+      <c r="X66">
+        <v>1.02</v>
+      </c>
+      <c r="Y66">
+        <v>1.1</v>
+      </c>
+      <c r="Z66">
+        <v>6</v>
+      </c>
+      <c r="AA66">
+        <v>1.4</v>
+      </c>
+      <c r="AB66">
+        <v>2.75</v>
+      </c>
+      <c r="AC66">
+        <v>2</v>
+      </c>
+      <c r="AD66">
+        <v>1.73</v>
+      </c>
+      <c r="AE66">
+        <v>1.3</v>
+      </c>
+      <c r="AF66">
+        <v>1.53</v>
+      </c>
+      <c r="AG66">
+        <v>2.32</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.12</v>
       </c>
-      <c r="X66">
-        <v>1.03</v>
-      </c>
-      <c r="Y66">
-        <v>1.13</v>
-      </c>
-      <c r="Z66">
-        <v>5.25</v>
-      </c>
-      <c r="AA66">
-        <v>1.48</v>
-      </c>
-      <c r="AB66">
-        <v>2.5</v>
-      </c>
-      <c r="AC66">
-        <v>2.2</v>
-      </c>
-      <c r="AD66">
-        <v>1.57</v>
-      </c>
-      <c r="AE66">
-        <v>1.22</v>
-      </c>
-      <c r="AF66">
-        <v>1.47</v>
-      </c>
-      <c r="AG66">
-        <v>2.42</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.25</v>
-      </c>
       <c r="AK66">
-        <v>1.18</v>
+        <v>2.28</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.48</v>
+        <v>3.2</v>
       </c>
       <c r="O67">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>5.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q67">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="R67">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="S67">
         <v>1.2</v>
@@ -11251,10 +11251,10 @@
         <v>4</v>
       </c>
       <c r="U67">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V67">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W67">
         <v>1.2</v>
@@ -11263,31 +11263,31 @@
         <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z67">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA67">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB67">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC67">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD67">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE67">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF67">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AG67">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>2.28</v>
+        <v>1.23</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P68">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q68">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R68">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S68">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U68">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="V68">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="W68">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z68">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA68">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AB68">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC68">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD68">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE68">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF68">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG68">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="O88">
+        <v>4.35</v>
+      </c>
+      <c r="P88">
+        <v>3.34</v>
+      </c>
+      <c r="Q88">
+        <v>2.45</v>
+      </c>
+      <c r="R88">
+        <v>2.75</v>
+      </c>
+      <c r="S88">
+        <v>1.17</v>
+      </c>
+      <c r="T88">
+        <v>4.4</v>
+      </c>
+      <c r="U88">
+        <v>1.94</v>
+      </c>
+      <c r="V88">
+        <v>1.88</v>
+      </c>
+      <c r="W88">
+        <v>1.21</v>
+      </c>
+      <c r="X88">
+        <v>1.01</v>
+      </c>
+      <c r="Y88">
+        <v>1.04</v>
+      </c>
+      <c r="Z88">
+        <v>6.8</v>
+      </c>
+      <c r="AA88">
+        <v>1.29</v>
+      </c>
+      <c r="AB88">
         <v>3.5</v>
       </c>
-      <c r="P88">
-        <v>2.35</v>
-      </c>
-      <c r="Q88">
-        <v>3.12</v>
-      </c>
-      <c r="R88">
-        <v>2.57</v>
-      </c>
-      <c r="S88">
-        <v>1.2</v>
-      </c>
-      <c r="T88">
-        <v>4</v>
-      </c>
-      <c r="U88">
-        <v>2.1</v>
-      </c>
-      <c r="V88">
-        <v>1.65</v>
-      </c>
-      <c r="W88">
-        <v>1.14</v>
-      </c>
-      <c r="X88">
-        <v>1.02</v>
-      </c>
-      <c r="Y88">
-        <v>1.13</v>
-      </c>
-      <c r="Z88">
-        <v>5.25</v>
-      </c>
-      <c r="AA88">
-        <v>1.48</v>
-      </c>
-      <c r="AB88">
-        <v>2.6</v>
-      </c>
       <c r="AC88">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AD88">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AE88">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AF88">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG88">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AK88">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.89</v>
+        <v>1.34</v>
       </c>
       <c r="O89">
-        <v>4.35</v>
+        <v>5.5</v>
       </c>
       <c r="P89">
-        <v>3.34</v>
+        <v>5.97</v>
       </c>
       <c r="Q89">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="R89">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T89">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="U89">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="V89">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="W89">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Z89">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA89">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB89">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AC89">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AD89">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AE89">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AF89">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AG89">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AK89">
-        <v>1.75</v>
+        <v>2.92</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.34</v>
+        <v>2.55</v>
       </c>
       <c r="O91">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="P91">
-        <v>5.97</v>
+        <v>2.35</v>
       </c>
       <c r="Q91">
-        <v>1.75</v>
+        <v>3.12</v>
       </c>
       <c r="R91">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="S91">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T91">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="U91">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="V91">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="W91">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA91">
+        <v>1.48</v>
+      </c>
+      <c r="AB91">
+        <v>2.6</v>
+      </c>
+      <c r="AC91">
+        <v>2.12</v>
+      </c>
+      <c r="AD91">
+        <v>1.58</v>
+      </c>
+      <c r="AE91">
         <v>1.25</v>
       </c>
-      <c r="AB91">
-        <v>4.2</v>
-      </c>
-      <c r="AC91">
-        <v>1.63</v>
-      </c>
-      <c r="AD91">
-        <v>2.17</v>
-      </c>
-      <c r="AE91">
-        <v>1.48</v>
-      </c>
       <c r="AF91">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG91">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AK91">
-        <v>2.92</v>
+        <v>1.44</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16129,7 +16129,7 @@
         <v>2.7</v>
       </c>
       <c r="Q97">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="R97">
         <v>2.53</v>
@@ -16283,28 +16283,28 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O98">
         <v>3.6</v>
       </c>
       <c r="P98">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q98">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="R98">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S98">
         <v>1.32</v>
       </c>
       <c r="T98">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U98">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="V98">
         <v>1.57</v>
@@ -16322,22 +16322,22 @@
         <v>5</v>
       </c>
       <c r="AA98">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB98">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC98">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD98">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE98">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF98">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG98">
         <v>2.63</v>
@@ -16356,7 +16356,7 @@
         <v>1.3</v>
       </c>
       <c r="AK98">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,19 +16446,19 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
       </c>
       <c r="R99">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="S99">
         <v>1.33</v>
@@ -16485,13 +16485,13 @@
         <v>3.25</v>
       </c>
       <c r="AA99">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB99">
         <v>1.8</v>
       </c>
       <c r="AC99">
-        <v>3.51</v>
+        <v>3.56</v>
       </c>
       <c r="AD99">
         <v>1.28</v>
@@ -16519,7 +16519,7 @@
         <v>1.27</v>
       </c>
       <c r="AK99">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,10 +16609,10 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O100">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P100">
         <v>5.5</v>
@@ -16627,7 +16627,7 @@
         <v>1.22</v>
       </c>
       <c r="T100">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="U100">
         <v>2.27</v>
@@ -16636,37 +16636,37 @@
         <v>1.53</v>
       </c>
       <c r="W100">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z100">
         <v>3.13</v>
       </c>
       <c r="AA100">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AB100">
-        <v>2.16</v>
+        <v>1.88</v>
       </c>
       <c r="AC100">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AD100">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE100">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF100">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
         <v>2.5</v>
@@ -16772,16 +16772,16 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="O101">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="P101">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q101">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="R101">
         <v>2.45</v>
@@ -16790,16 +16790,16 @@
         <v>1.25</v>
       </c>
       <c r="T101">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U101">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="V101">
         <v>1.65</v>
       </c>
       <c r="W101">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X101">
         <v>1.01</v>
@@ -16811,19 +16811,19 @@
         <v>5.25</v>
       </c>
       <c r="AA101">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AB101">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AC101">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AD101">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE101">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF101">
         <v>1.44</v>
@@ -16845,7 +16845,7 @@
         <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16938,28 +16938,28 @@
         <v>1.7</v>
       </c>
       <c r="O102">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P102">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
       <c r="Q102">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="R102">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S102">
         <v>1.36</v>
       </c>
       <c r="T102">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>2.73</v>
+        <v>2.98</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W102">
         <v>1.06</v>
@@ -16974,41 +16974,41 @@
         <v>3.24</v>
       </c>
       <c r="AA102">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB102">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC102">
         <v>3.3</v>
       </c>
       <c r="AD102">
+        <v>1.3</v>
+      </c>
+      <c r="AE102">
+        <v>1.1</v>
+      </c>
+      <c r="AF102">
+        <v>1.9</v>
+      </c>
+      <c r="AG102">
+        <v>1.87</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
         <v>1.29</v>
       </c>
-      <c r="AE102">
-        <v>1.05</v>
-      </c>
-      <c r="AF102">
-        <v>1.85</v>
-      </c>
-      <c r="AG102">
-        <v>1.85</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.21</v>
-      </c>
       <c r="AK102">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,61 +17098,61 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O103">
         <v>3.7</v>
       </c>
       <c r="P103">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q103">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="R103">
         <v>2.3</v>
       </c>
       <c r="S103">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T103">
         <v>3.15</v>
       </c>
       <c r="U103">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V103">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W103">
         <v>1.12</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z103">
         <v>4.2</v>
       </c>
       <c r="AA103">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB103">
         <v>2.15</v>
       </c>
       <c r="AC103">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AD103">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE103">
         <v>1.17</v>
       </c>
       <c r="AF103">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG103">
         <v>2.1</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O104">
         <v>3.4</v>
       </c>
       <c r="P104">
-        <v>2.85</v>
+        <v>2.58</v>
       </c>
       <c r="Q104">
         <v>2.88</v>
       </c>
       <c r="R104">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S104">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T104">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="U104">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="V104">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W104">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="Z104">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA104">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AC104">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="AD104">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AE104">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AF104">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK104">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="O105">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P105">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="Q105">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R105">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S105">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="U105">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="V105">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y105">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="Z105">
-        <v>5</v>
+        <v>3.39</v>
       </c>
       <c r="AA105">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB105">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AC105">
-        <v>2.26</v>
+        <v>3.57</v>
       </c>
       <c r="AD105">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE105">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AF105">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG105">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="O107">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P107">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q107">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R107">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="S107">
         <v>1.25</v>
@@ -17777,16 +17777,16 @@
         <v>1.57</v>
       </c>
       <c r="W107">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X107">
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z107">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA107">
         <v>1.44</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK107">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17916,16 +17916,16 @@
         <v>1.95</v>
       </c>
       <c r="O108">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P108">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q108">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="R108">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S108">
         <v>1.29</v>
@@ -17934,10 +17934,10 @@
         <v>3.25</v>
       </c>
       <c r="U108">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V108">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W108">
         <v>1.13</v>
@@ -17946,16 +17946,16 @@
         <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z108">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA108">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB108">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC108">
         <v>2.63</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK108">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18082,16 +18082,16 @@
         <v>4.6</v>
       </c>
       <c r="P109">
-        <v>6.32</v>
+        <v>7.1</v>
       </c>
       <c r="Q109">
         <v>1.75</v>
       </c>
       <c r="R109">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="S109">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T109">
         <v>3.58</v>
@@ -18103,7 +18103,7 @@
         <v>1.62</v>
       </c>
       <c r="W109">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X109">
         <v>1.02</v>
@@ -18121,7 +18121,7 @@
         <v>2.46</v>
       </c>
       <c r="AC109">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AD109">
         <v>1.62</v>
@@ -18130,10 +18130,10 @@
         <v>1.22</v>
       </c>
       <c r="AF109">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AG109">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18239,10 +18239,10 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="O110">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
         <v>2.15</v>
@@ -18260,13 +18260,13 @@
         <v>3.25</v>
       </c>
       <c r="U110">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="V110">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X110">
         <v>1.02</v>
@@ -18278,7 +18278,7 @@
         <v>4.5</v>
       </c>
       <c r="AA110">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB110">
         <v>2.2</v>
@@ -18287,7 +18287,7 @@
         <v>2.7</v>
       </c>
       <c r="AD110">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE110">
         <v>1.18</v>
@@ -19057,58 +19057,58 @@
         <v>2.15</v>
       </c>
       <c r="O115">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P115">
-        <v>3.21</v>
+        <v>3.05</v>
       </c>
       <c r="Q115">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="R115">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S115">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U115">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="V115">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W115">
         <v>1.05</v>
       </c>
       <c r="X115">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
         <v>1.29</v>
       </c>
       <c r="Z115">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="AA115">
         <v>1.9</v>
       </c>
       <c r="AB115">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AC115">
         <v>3.5</v>
       </c>
       <c r="AD115">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE115">
         <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG115">
         <v>2</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK115">
         <v>1.62</v>
@@ -19217,19 +19217,19 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O116">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P116">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q116">
         <v>2.59</v>
       </c>
       <c r="R116">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S116">
         <v>1.48</v>
@@ -19241,7 +19241,7 @@
         <v>3.2</v>
       </c>
       <c r="V116">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W116">
         <v>1.05</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="O118">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P118">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="Q118">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="R118">
         <v>2.1</v>
       </c>
       <c r="S118">
+        <v>1.33</v>
+      </c>
+      <c r="T118">
+        <v>3.2</v>
+      </c>
+      <c r="U118">
+        <v>2.63</v>
+      </c>
+      <c r="V118">
+        <v>1.44</v>
+      </c>
+      <c r="W118">
+        <v>1.08</v>
+      </c>
+      <c r="X118">
+        <v>1.02</v>
+      </c>
+      <c r="Y118">
+        <v>1.22</v>
+      </c>
+      <c r="Z118">
+        <v>3.72</v>
+      </c>
+      <c r="AA118">
+        <v>1.75</v>
+      </c>
+      <c r="AB118">
+        <v>2</v>
+      </c>
+      <c r="AC118">
+        <v>2.75</v>
+      </c>
+      <c r="AD118">
         <v>1.36</v>
       </c>
-      <c r="T118">
-        <v>2.63</v>
-      </c>
-      <c r="U118">
-        <v>2.79</v>
-      </c>
-      <c r="V118">
-        <v>1.35</v>
-      </c>
-      <c r="W118">
-        <v>1.05</v>
-      </c>
-      <c r="X118">
-        <v>1.01</v>
-      </c>
-      <c r="Y118">
-        <v>1.26</v>
-      </c>
-      <c r="Z118">
-        <v>3.2</v>
-      </c>
-      <c r="AA118">
-        <v>1.9</v>
-      </c>
-      <c r="AB118">
-        <v>1.79</v>
-      </c>
-      <c r="AC118">
-        <v>3.14</v>
-      </c>
-      <c r="AD118">
-        <v>1.27</v>
-      </c>
       <c r="AE118">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF118">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG118">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,80 +19706,80 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="O119">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P119">
-        <v>3.18</v>
+        <v>4.25</v>
       </c>
       <c r="Q119">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="R119">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S119">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T119">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="U119">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="V119">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W119">
         <v>1.08</v>
       </c>
       <c r="X119">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y119">
+        <v>1.3</v>
+      </c>
+      <c r="Z119">
+        <v>3.25</v>
+      </c>
+      <c r="AA119">
+        <v>2</v>
+      </c>
+      <c r="AB119">
+        <v>1.7</v>
+      </c>
+      <c r="AC119">
+        <v>3.5</v>
+      </c>
+      <c r="AD119">
+        <v>1.29</v>
+      </c>
+      <c r="AE119">
+        <v>1.05</v>
+      </c>
+      <c r="AF119">
+        <v>1.8</v>
+      </c>
+      <c r="AG119">
+        <v>1.85</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
         <v>1.22</v>
       </c>
-      <c r="Z119">
-        <v>3.72</v>
-      </c>
-      <c r="AA119">
-        <v>1.75</v>
-      </c>
-      <c r="AB119">
-        <v>2</v>
-      </c>
-      <c r="AC119">
-        <v>2.75</v>
-      </c>
-      <c r="AD119">
-        <v>1.36</v>
-      </c>
-      <c r="AE119">
-        <v>1.12</v>
-      </c>
-      <c r="AF119">
-        <v>1.62</v>
-      </c>
-      <c r="AG119">
-        <v>2.15</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.29</v>
-      </c>
       <c r="AK119">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,80 +19869,80 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="O120">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P120">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q120">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="R120">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S120">
         <v>1.36</v>
       </c>
       <c r="T120">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="U120">
         <v>2.79</v>
       </c>
       <c r="V120">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W120">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X120">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z120">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA120">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB120">
+        <v>1.79</v>
+      </c>
+      <c r="AC120">
+        <v>3.14</v>
+      </c>
+      <c r="AD120">
+        <v>1.27</v>
+      </c>
+      <c r="AE120">
+        <v>1.1</v>
+      </c>
+      <c r="AF120">
+        <v>1.75</v>
+      </c>
+      <c r="AG120">
+        <v>1.93</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
+        <v>1.25</v>
+      </c>
+      <c r="AK120">
         <v>1.7</v>
-      </c>
-      <c r="AC120">
-        <v>3.5</v>
-      </c>
-      <c r="AD120">
-        <v>1.29</v>
-      </c>
-      <c r="AE120">
-        <v>1.05</v>
-      </c>
-      <c r="AF120">
-        <v>1.8</v>
-      </c>
-      <c r="AG120">
-        <v>1.85</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.22</v>
-      </c>
-      <c r="AK120">
-        <v>1.83</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O124">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P124">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q124">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="R124">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S124">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T124">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="U124">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="V124">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W124">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X124">
         <v>1.01</v>
       </c>
       <c r="Y124">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z124">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="AA124">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AB124">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AC124">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AD124">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AE124">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AF124">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG124">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK124">
         <v>1.5</v>
@@ -20693,7 +20693,7 @@
         <v>1.45</v>
       </c>
       <c r="Q125">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="R125">
         <v>2.4</v>
@@ -20720,28 +20720,28 @@
         <v>1.13</v>
       </c>
       <c r="Z125">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA125">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB125">
         <v>2.25</v>
       </c>
       <c r="AC125">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AD125">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE125">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF125">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG125">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AK125">
         <v>1.09</v>
@@ -20847,16 +20847,16 @@
         </is>
       </c>
       <c r="N126">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="O126">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P126">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="Q126">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="R126">
         <v>2</v>
@@ -20865,7 +20865,7 @@
         <v>1.42</v>
       </c>
       <c r="T126">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U126">
         <v>3.04</v>
@@ -20877,7 +20877,7 @@
         <v>1.07</v>
       </c>
       <c r="X126">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y126">
         <v>1.36</v>
@@ -20889,19 +20889,19 @@
         <v>2.15</v>
       </c>
       <c r="AB126">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC126">
         <v>3.9</v>
       </c>
       <c r="AD126">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE126">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF126">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG126">
         <v>1.84</v>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AK126">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21010,34 +21010,34 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="O127">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P127">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="Q127">
         <v>2.05</v>
       </c>
       <c r="R127">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S127">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T127">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U127">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V127">
         <v>1.57</v>
       </c>
       <c r="W127">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X127">
         <v>1.01</v>
@@ -21049,25 +21049,25 @@
         <v>5</v>
       </c>
       <c r="AA127">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB127">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AC127">
         <v>2.29</v>
       </c>
       <c r="AD127">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AE127">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF127">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG127">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21185,7 +21185,7 @@
         <v>2</v>
       </c>
       <c r="R128">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S128">
         <v>1.18</v>
@@ -21206,7 +21206,7 @@
         <v>1.03</v>
       </c>
       <c r="Y128">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z128">
         <v>4.7</v>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK128">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21499,19 +21499,19 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O130">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="P130">
         <v>2.45</v>
       </c>
       <c r="Q130">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R130">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S130">
         <v>1.25</v>
@@ -21523,7 +21523,7 @@
         <v>2.21</v>
       </c>
       <c r="V130">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W130">
         <v>1.11</v>
@@ -21550,13 +21550,13 @@
         <v>1.44</v>
       </c>
       <c r="AE130">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF130">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG130">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK130">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21662,40 +21662,40 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O131">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="P131">
-        <v>3.03</v>
+        <v>3.48</v>
       </c>
       <c r="Q131">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R131">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S131">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T131">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="U131">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V131">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W131">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X131">
         <v>1.03</v>
       </c>
       <c r="Y131">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z131">
         <v>3.4</v>
@@ -21704,22 +21704,22 @@
         <v>1.78</v>
       </c>
       <c r="AB131">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC131">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD131">
         <v>1.32</v>
       </c>
       <c r="AE131">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF131">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG131">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK131">
         <v>1.83</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O132">
         <v>3.35</v>
       </c>
       <c r="P132">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="Q132">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R132">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="S132">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T132">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="U132">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="V132">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W132">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
         <v>1.04</v>
       </c>
       <c r="Y132">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z132">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="AA132">
         <v>1.7</v>
       </c>
       <c r="AB132">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AC132">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD132">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE132">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF132">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG132">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AK132">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AL132">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -615,33 +615,33 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P2">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
         <v>2.51</v>
@@ -650,10 +650,10 @@
         <v>2.18</v>
       </c>
       <c r="S2">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U2">
         <v>2.4</v>
@@ -662,7 +662,7 @@
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
         <v>1.02</v>
@@ -692,7 +692,7 @@
         <v>1.54</v>
       </c>
       <c r="AG2">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -701,11 +701,11 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "76"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
         <v>1.62</v>
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.98</v>
+        <v>4.68</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P3">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
         <v>4.1</v>
@@ -816,7 +816,7 @@
         <v>1.34</v>
       </c>
       <c r="T3">
-        <v>3.18</v>
+        <v>2.85</v>
       </c>
       <c r="U3">
         <v>2.6</v>
@@ -831,10 +831,10 @@
         <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="AA3">
         <v>1.75</v>
@@ -849,7 +849,7 @@
         <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
         <v>1.67</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -950,33 +950,33 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
         <v>3.1</v>
       </c>
       <c r="P4">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="R4">
         <v>2</v>
       </c>
       <c r="S4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
         <v>2.65</v>
@@ -985,34 +985,34 @@
         <v>2.9</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AA4">
         <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC4">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.87</v>
@@ -1022,34 +1022,34 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "77"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ4">
         <v>0</v>
@@ -2271,19 +2271,19 @@
         <v>3.5</v>
       </c>
       <c r="P12">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q12">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U12">
         <v>2.57</v>
@@ -2304,7 +2304,7 @@
         <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
         <v>1.86</v>
@@ -2313,13 +2313,13 @@
         <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
         <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
         <v>1.88</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="O19">
         <v>3.68</v>
       </c>
       <c r="P19">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>3.36</v>
+        <v>3.18</v>
       </c>
       <c r="R19">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
         <v>1.22</v>
@@ -3430,7 +3430,7 @@
         <v>2.2</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W19">
         <v>1.14</v>
@@ -3448,10 +3448,10 @@
         <v>1.55</v>
       </c>
       <c r="AB19">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD19">
         <v>1.48</v>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="O20">
-        <v>3.13</v>
+        <v>3.24</v>
       </c>
       <c r="P20">
         <v>2.08</v>
@@ -3602,7 +3602,7 @@
         <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
         <v>3.75</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,28 +6992,28 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R41">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U41">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="V41">
         <v>1.44</v>
@@ -7022,34 +7022,34 @@
         <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA41">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC41">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD41">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U42">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="V42">
         <v>1.44</v>
@@ -7185,34 +7185,34 @@
         <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC42">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG42">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="O44">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="P44">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="Q44">
         <v>2.8</v>
@@ -7499,10 +7499,10 @@
         <v>1.33</v>
       </c>
       <c r="T44">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="U44">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="V44">
         <v>1.44</v>
@@ -7520,13 +7520,13 @@
         <v>3.65</v>
       </c>
       <c r="AA44">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB44">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC44">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="AD44">
         <v>1.36</v>
@@ -7647,16 +7647,16 @@
         <v>1.93</v>
       </c>
       <c r="O45">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="P45">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q45">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R45">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S45">
         <v>1.3</v>
@@ -7677,25 +7677,25 @@
         <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z45">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AA45">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB45">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC45">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AD45">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE45">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF45">
         <v>1.57</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>3.57</v>
+        <v>2.19</v>
       </c>
       <c r="R49">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S49">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T49">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U49">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V49">
+        <v>1.59</v>
+      </c>
+      <c r="W49">
+        <v>1.11</v>
+      </c>
+      <c r="X49">
+        <v>1.03</v>
+      </c>
+      <c r="Y49">
+        <v>1.17</v>
+      </c>
+      <c r="Z49">
+        <v>4.94</v>
+      </c>
+      <c r="AA49">
         <v>1.62</v>
       </c>
-      <c r="W49">
-        <v>1.13</v>
-      </c>
-      <c r="X49">
-        <v>1.01</v>
-      </c>
-      <c r="Y49">
-        <v>1.14</v>
-      </c>
-      <c r="Z49">
-        <v>5.5</v>
-      </c>
-      <c r="AA49">
-        <v>1.51</v>
-      </c>
       <c r="AB49">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AC49">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD49">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE49">
         <v>1.2</v>
       </c>
       <c r="AF49">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG49">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.93</v>
+        <v>1.21</v>
       </c>
       <c r="AK49">
-        <v>1.26</v>
+        <v>2.05</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q50">
-        <v>2.19</v>
+        <v>3.57</v>
       </c>
       <c r="R50">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>4.94</v>
+        <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AB50">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AC50">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD50">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE50">
         <v>1.2</v>
       </c>
       <c r="AF50">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.21</v>
+        <v>1.93</v>
       </c>
       <c r="AK50">
-        <v>2.05</v>
+        <v>1.26</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.48</v>
+        <v>3.2</v>
       </c>
       <c r="O66">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>5.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q66">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="R66">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="S66">
         <v>1.2</v>
@@ -11088,10 +11088,10 @@
         <v>4</v>
       </c>
       <c r="U66">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V66">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W66">
         <v>1.2</v>
@@ -11100,31 +11100,31 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z66">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA66">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB66">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC66">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD66">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE66">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF66">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AG66">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>2.28</v>
+        <v>1.23</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P67">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q67">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R67">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S67">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U67">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="V67">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="W67">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA67">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AB67">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC67">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD67">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE67">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF67">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG67">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.15</v>
+        <v>1.48</v>
       </c>
       <c r="O68">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="P68">
-        <v>1.85</v>
+        <v>5.75</v>
       </c>
       <c r="Q68">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="R68">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U68">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="V68">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="W68">
+        <v>1.2</v>
+      </c>
+      <c r="X68">
+        <v>1.02</v>
+      </c>
+      <c r="Y68">
+        <v>1.1</v>
+      </c>
+      <c r="Z68">
+        <v>6</v>
+      </c>
+      <c r="AA68">
+        <v>1.4</v>
+      </c>
+      <c r="AB68">
+        <v>2.75</v>
+      </c>
+      <c r="AC68">
+        <v>2</v>
+      </c>
+      <c r="AD68">
+        <v>1.73</v>
+      </c>
+      <c r="AE68">
+        <v>1.3</v>
+      </c>
+      <c r="AF68">
+        <v>1.53</v>
+      </c>
+      <c r="AG68">
+        <v>2.32</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.12</v>
       </c>
-      <c r="X68">
-        <v>1.03</v>
-      </c>
-      <c r="Y68">
-        <v>1.13</v>
-      </c>
-      <c r="Z68">
-        <v>5.25</v>
-      </c>
-      <c r="AA68">
-        <v>1.48</v>
-      </c>
-      <c r="AB68">
-        <v>2.5</v>
-      </c>
-      <c r="AC68">
-        <v>2.2</v>
-      </c>
-      <c r="AD68">
-        <v>1.57</v>
-      </c>
-      <c r="AE68">
-        <v>1.22</v>
-      </c>
-      <c r="AF68">
-        <v>1.47</v>
-      </c>
-      <c r="AG68">
-        <v>2.42</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.25</v>
-      </c>
       <c r="AK68">
-        <v>1.18</v>
+        <v>2.28</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>3.79</v>
+      </c>
+      <c r="R78">
+        <v>2.2</v>
+      </c>
+      <c r="S78">
+        <v>1.28</v>
+      </c>
+      <c r="T78">
+        <v>3.18</v>
+      </c>
+      <c r="U78">
+        <v>2.48</v>
+      </c>
+      <c r="V78">
         <v>1.44</v>
       </c>
-      <c r="O78">
-        <v>4.2</v>
-      </c>
-      <c r="P78">
-        <v>6</v>
-      </c>
-      <c r="Q78">
-        <v>1.85</v>
-      </c>
-      <c r="R78">
-        <v>2.4</v>
-      </c>
-      <c r="S78">
+      <c r="W78">
+        <v>1.06</v>
+      </c>
+      <c r="X78">
+        <v>1.04</v>
+      </c>
+      <c r="Y78">
+        <v>1.18</v>
+      </c>
+      <c r="Z78">
+        <v>3.88</v>
+      </c>
+      <c r="AA78">
+        <v>1.75</v>
+      </c>
+      <c r="AB78">
+        <v>2.02</v>
+      </c>
+      <c r="AC78">
+        <v>2.74</v>
+      </c>
+      <c r="AD78">
+        <v>1.35</v>
+      </c>
+      <c r="AE78">
+        <v>1.13</v>
+      </c>
+      <c r="AF78">
+        <v>1.62</v>
+      </c>
+      <c r="AG78">
+        <v>2.14</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.25</v>
+      </c>
+      <c r="AK78">
         <v>1.27</v>
-      </c>
-      <c r="T78">
-        <v>3.3</v>
-      </c>
-      <c r="U78">
-        <v>2.33</v>
-      </c>
-      <c r="V78">
-        <v>1.5</v>
-      </c>
-      <c r="W78">
-        <v>1.08</v>
-      </c>
-      <c r="X78">
-        <v>1.01</v>
-      </c>
-      <c r="Y78">
-        <v>1.2</v>
-      </c>
-      <c r="Z78">
-        <v>4.5</v>
-      </c>
-      <c r="AA78">
-        <v>1.57</v>
-      </c>
-      <c r="AB78">
-        <v>2.2</v>
-      </c>
-      <c r="AC78">
-        <v>2.46</v>
-      </c>
-      <c r="AD78">
-        <v>1.48</v>
-      </c>
-      <c r="AE78">
-        <v>1.2</v>
-      </c>
-      <c r="AF78">
-        <v>1.75</v>
-      </c>
-      <c r="AG78">
-        <v>2</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.13</v>
-      </c>
-      <c r="AK78">
-        <v>2.47</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q79">
-        <v>3.79</v>
+        <v>1.85</v>
       </c>
       <c r="R79">
+        <v>2.4</v>
+      </c>
+      <c r="S79">
+        <v>1.27</v>
+      </c>
+      <c r="T79">
+        <v>3.3</v>
+      </c>
+      <c r="U79">
+        <v>2.33</v>
+      </c>
+      <c r="V79">
+        <v>1.5</v>
+      </c>
+      <c r="W79">
+        <v>1.08</v>
+      </c>
+      <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>1.2</v>
+      </c>
+      <c r="Z79">
+        <v>4.5</v>
+      </c>
+      <c r="AA79">
+        <v>1.57</v>
+      </c>
+      <c r="AB79">
         <v>2.2</v>
       </c>
-      <c r="S79">
-        <v>1.28</v>
-      </c>
-      <c r="T79">
-        <v>3.18</v>
-      </c>
-      <c r="U79">
-        <v>2.48</v>
-      </c>
-      <c r="V79">
-        <v>1.44</v>
-      </c>
-      <c r="W79">
-        <v>1.06</v>
-      </c>
-      <c r="X79">
-        <v>1.04</v>
-      </c>
-      <c r="Y79">
-        <v>1.18</v>
-      </c>
-      <c r="Z79">
-        <v>3.88</v>
-      </c>
-      <c r="AA79">
+      <c r="AC79">
+        <v>2.46</v>
+      </c>
+      <c r="AD79">
+        <v>1.48</v>
+      </c>
+      <c r="AE79">
+        <v>1.2</v>
+      </c>
+      <c r="AF79">
         <v>1.75</v>
       </c>
-      <c r="AB79">
-        <v>2.02</v>
-      </c>
-      <c r="AC79">
-        <v>2.74</v>
-      </c>
-      <c r="AD79">
-        <v>1.35</v>
-      </c>
-      <c r="AE79">
+      <c r="AG79">
+        <v>2</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.13</v>
       </c>
-      <c r="AF79">
-        <v>1.62</v>
-      </c>
-      <c r="AG79">
-        <v>2.14</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.25</v>
-      </c>
       <c r="AK79">
-        <v>1.27</v>
+        <v>2.47</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,65 +14653,65 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.89</v>
+        <v>3.05</v>
       </c>
       <c r="O88">
-        <v>4.35</v>
+        <v>3.65</v>
       </c>
       <c r="P88">
-        <v>3.34</v>
+        <v>1.92</v>
       </c>
       <c r="Q88">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="R88">
+        <v>2.6</v>
+      </c>
+      <c r="S88">
+        <v>1.22</v>
+      </c>
+      <c r="T88">
+        <v>4</v>
+      </c>
+      <c r="U88">
+        <v>2.03</v>
+      </c>
+      <c r="V88">
+        <v>1.79</v>
+      </c>
+      <c r="W88">
+        <v>1.13</v>
+      </c>
+      <c r="X88">
+        <v>1.02</v>
+      </c>
+      <c r="Y88">
+        <v>1.08</v>
+      </c>
+      <c r="Z88">
+        <v>5.5</v>
+      </c>
+      <c r="AA88">
+        <v>1.4</v>
+      </c>
+      <c r="AB88">
+        <v>2.7</v>
+      </c>
+      <c r="AC88">
+        <v>2.1</v>
+      </c>
+      <c r="AD88">
+        <v>1.69</v>
+      </c>
+      <c r="AE88">
+        <v>1.3</v>
+      </c>
+      <c r="AF88">
+        <v>1.4</v>
+      </c>
+      <c r="AG88">
         <v>2.75</v>
       </c>
-      <c r="S88">
-        <v>1.17</v>
-      </c>
-      <c r="T88">
-        <v>4.4</v>
-      </c>
-      <c r="U88">
-        <v>1.94</v>
-      </c>
-      <c r="V88">
-        <v>1.88</v>
-      </c>
-      <c r="W88">
-        <v>1.21</v>
-      </c>
-      <c r="X88">
-        <v>1.01</v>
-      </c>
-      <c r="Y88">
-        <v>1.04</v>
-      </c>
-      <c r="Z88">
-        <v>6.8</v>
-      </c>
-      <c r="AA88">
-        <v>1.29</v>
-      </c>
-      <c r="AB88">
-        <v>3.5</v>
-      </c>
-      <c r="AC88">
-        <v>1.8</v>
-      </c>
-      <c r="AD88">
-        <v>1.95</v>
-      </c>
-      <c r="AE88">
-        <v>1.42</v>
-      </c>
-      <c r="AF88">
-        <v>1.3</v>
-      </c>
-      <c r="AG88">
-        <v>3.25</v>
-      </c>
       <c r="AH88" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK88">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.34</v>
+        <v>2.55</v>
       </c>
       <c r="O89">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="P89">
-        <v>5.97</v>
+        <v>2.35</v>
       </c>
       <c r="Q89">
-        <v>1.75</v>
+        <v>3.12</v>
       </c>
       <c r="R89">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="S89">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T89">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="U89">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="V89">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="W89">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA89">
+        <v>1.48</v>
+      </c>
+      <c r="AB89">
+        <v>2.6</v>
+      </c>
+      <c r="AC89">
+        <v>2.12</v>
+      </c>
+      <c r="AD89">
+        <v>1.58</v>
+      </c>
+      <c r="AE89">
         <v>1.25</v>
       </c>
-      <c r="AB89">
-        <v>4.2</v>
-      </c>
-      <c r="AC89">
-        <v>1.63</v>
-      </c>
-      <c r="AD89">
-        <v>2.17</v>
-      </c>
-      <c r="AE89">
-        <v>1.48</v>
-      </c>
       <c r="AF89">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG89">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AK89">
-        <v>2.92</v>
+        <v>1.44</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.05</v>
+        <v>1.34</v>
       </c>
       <c r="O90">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="P90">
-        <v>1.92</v>
+        <v>5.97</v>
       </c>
       <c r="Q90">
-        <v>3.4</v>
+        <v>1.75</v>
       </c>
       <c r="R90">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="S90">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T90">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="U90">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="V90">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="W90">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="X90">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Z90">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA90">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AB90">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="AC90">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AD90">
-        <v>1.69</v>
+        <v>2.17</v>
       </c>
       <c r="AE90">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF90">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG90">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK90">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="O91">
+        <v>4.35</v>
+      </c>
+      <c r="P91">
+        <v>3.34</v>
+      </c>
+      <c r="Q91">
+        <v>2.45</v>
+      </c>
+      <c r="R91">
+        <v>2.75</v>
+      </c>
+      <c r="S91">
+        <v>1.17</v>
+      </c>
+      <c r="T91">
+        <v>4.4</v>
+      </c>
+      <c r="U91">
+        <v>1.94</v>
+      </c>
+      <c r="V91">
+        <v>1.88</v>
+      </c>
+      <c r="W91">
+        <v>1.21</v>
+      </c>
+      <c r="X91">
+        <v>1.01</v>
+      </c>
+      <c r="Y91">
+        <v>1.04</v>
+      </c>
+      <c r="Z91">
+        <v>6.8</v>
+      </c>
+      <c r="AA91">
+        <v>1.29</v>
+      </c>
+      <c r="AB91">
         <v>3.5</v>
       </c>
-      <c r="P91">
-        <v>2.35</v>
-      </c>
-      <c r="Q91">
-        <v>3.12</v>
-      </c>
-      <c r="R91">
-        <v>2.57</v>
-      </c>
-      <c r="S91">
-        <v>1.2</v>
-      </c>
-      <c r="T91">
-        <v>4</v>
-      </c>
-      <c r="U91">
-        <v>2.1</v>
-      </c>
-      <c r="V91">
-        <v>1.65</v>
-      </c>
-      <c r="W91">
-        <v>1.14</v>
-      </c>
-      <c r="X91">
-        <v>1.02</v>
-      </c>
-      <c r="Y91">
-        <v>1.13</v>
-      </c>
-      <c r="Z91">
-        <v>5.25</v>
-      </c>
-      <c r="AA91">
-        <v>1.48</v>
-      </c>
-      <c r="AB91">
-        <v>2.6</v>
-      </c>
       <c r="AC91">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AD91">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AE91">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AF91">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG91">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AK91">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O109">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P109">
-        <v>7.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q109">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="R109">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S109">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T109">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="U109">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="V109">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X109">
         <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z109">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA109">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AB109">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AC109">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AD109">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AE109">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF109">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AG109">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AK109">
-        <v>2.9</v>
+        <v>1.35</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O110">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P110">
-        <v>2.15</v>
+        <v>7.1</v>
       </c>
       <c r="Q110">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="R110">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S110">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T110">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="U110">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="V110">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W110">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X110">
         <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z110">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA110">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB110">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AC110">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="AD110">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AE110">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF110">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AG110">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AK110">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,80 +18728,80 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.75</v>
+        <v>1.72</v>
       </c>
       <c r="O113">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P113">
-        <v>2.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q113">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="R113">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S113">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T113">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U113">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V113">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W113">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X113">
         <v>1.06</v>
       </c>
       <c r="Y113">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="Z113">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="AA113">
+        <v>2.3</v>
+      </c>
+      <c r="AB113">
+        <v>1.62</v>
+      </c>
+      <c r="AC113">
+        <v>3.54</v>
+      </c>
+      <c r="AD113">
+        <v>1.2</v>
+      </c>
+      <c r="AE113">
+        <v>1.04</v>
+      </c>
+      <c r="AF113">
+        <v>2.01</v>
+      </c>
+      <c r="AG113">
+        <v>1.7</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
+        <v>1.11</v>
+      </c>
+      <c r="AK113">
         <v>2</v>
-      </c>
-      <c r="AB113">
-        <v>1.68</v>
-      </c>
-      <c r="AC113">
-        <v>3.7</v>
-      </c>
-      <c r="AD113">
-        <v>1.25</v>
-      </c>
-      <c r="AE113">
-        <v>1.1</v>
-      </c>
-      <c r="AF113">
-        <v>1.7</v>
-      </c>
-      <c r="AG113">
-        <v>2.1</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>1.34</v>
-      </c>
-      <c r="AK113">
-        <v>1.36</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.72</v>
+        <v>2.75</v>
       </c>
       <c r="O114">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P114">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q114">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="R114">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S114">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T114">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U114">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V114">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W114">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
         <v>1.06</v>
       </c>
       <c r="Y114">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="Z114">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="AA114">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB114">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC114">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD114">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE114">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AG114">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AK114">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,80 +19543,80 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="O118">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P118">
-        <v>3.18</v>
+        <v>4.25</v>
       </c>
       <c r="Q118">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="R118">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S118">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T118">
-        <v>3.2</v>
+        <v>2.73</v>
       </c>
       <c r="U118">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="V118">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
         <v>1.08</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y118">
+        <v>1.3</v>
+      </c>
+      <c r="Z118">
+        <v>3.25</v>
+      </c>
+      <c r="AA118">
+        <v>2</v>
+      </c>
+      <c r="AB118">
+        <v>1.7</v>
+      </c>
+      <c r="AC118">
+        <v>3.5</v>
+      </c>
+      <c r="AD118">
+        <v>1.29</v>
+      </c>
+      <c r="AE118">
+        <v>1.05</v>
+      </c>
+      <c r="AF118">
+        <v>1.8</v>
+      </c>
+      <c r="AG118">
+        <v>1.85</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
         <v>1.22</v>
       </c>
-      <c r="Z118">
-        <v>3.72</v>
-      </c>
-      <c r="AA118">
-        <v>1.75</v>
-      </c>
-      <c r="AB118">
-        <v>2</v>
-      </c>
-      <c r="AC118">
-        <v>2.75</v>
-      </c>
-      <c r="AD118">
-        <v>1.36</v>
-      </c>
-      <c r="AE118">
-        <v>1.12</v>
-      </c>
-      <c r="AF118">
-        <v>1.62</v>
-      </c>
-      <c r="AG118">
-        <v>2.15</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.29</v>
-      </c>
       <c r="AK118">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,80 +19706,80 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="O119">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P119">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q119">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="R119">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S119">
         <v>1.36</v>
       </c>
       <c r="T119">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="U119">
         <v>2.79</v>
       </c>
       <c r="V119">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W119">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X119">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z119">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA119">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB119">
+        <v>1.79</v>
+      </c>
+      <c r="AC119">
+        <v>3.14</v>
+      </c>
+      <c r="AD119">
+        <v>1.27</v>
+      </c>
+      <c r="AE119">
+        <v>1.1</v>
+      </c>
+      <c r="AF119">
+        <v>1.75</v>
+      </c>
+      <c r="AG119">
+        <v>1.93</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
+        <v>1.25</v>
+      </c>
+      <c r="AK119">
         <v>1.7</v>
-      </c>
-      <c r="AC119">
-        <v>3.5</v>
-      </c>
-      <c r="AD119">
-        <v>1.29</v>
-      </c>
-      <c r="AE119">
-        <v>1.05</v>
-      </c>
-      <c r="AF119">
-        <v>1.8</v>
-      </c>
-      <c r="AG119">
-        <v>1.85</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.22</v>
-      </c>
-      <c r="AK119">
-        <v>1.83</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="O120">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P120">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="Q120">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="R120">
         <v>2.1</v>
       </c>
       <c r="S120">
+        <v>1.33</v>
+      </c>
+      <c r="T120">
+        <v>3.2</v>
+      </c>
+      <c r="U120">
+        <v>2.63</v>
+      </c>
+      <c r="V120">
+        <v>1.44</v>
+      </c>
+      <c r="W120">
+        <v>1.08</v>
+      </c>
+      <c r="X120">
+        <v>1.02</v>
+      </c>
+      <c r="Y120">
+        <v>1.22</v>
+      </c>
+      <c r="Z120">
+        <v>3.72</v>
+      </c>
+      <c r="AA120">
+        <v>1.75</v>
+      </c>
+      <c r="AB120">
+        <v>2</v>
+      </c>
+      <c r="AC120">
+        <v>2.75</v>
+      </c>
+      <c r="AD120">
         <v>1.36</v>
       </c>
-      <c r="T120">
-        <v>2.63</v>
-      </c>
-      <c r="U120">
-        <v>2.79</v>
-      </c>
-      <c r="V120">
-        <v>1.35</v>
-      </c>
-      <c r="W120">
-        <v>1.05</v>
-      </c>
-      <c r="X120">
-        <v>1.01</v>
-      </c>
-      <c r="Y120">
-        <v>1.26</v>
-      </c>
-      <c r="Z120">
-        <v>3.2</v>
-      </c>
-      <c r="AA120">
-        <v>1.9</v>
-      </c>
-      <c r="AB120">
-        <v>1.79</v>
-      </c>
-      <c r="AC120">
-        <v>3.14</v>
-      </c>
-      <c r="AD120">
-        <v>1.27</v>
-      </c>
       <c r="AE120">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF120">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG120">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK120">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -21517,16 +21517,16 @@
         <v>1.25</v>
       </c>
       <c r="T130">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U130">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="V130">
         <v>1.57</v>
       </c>
       <c r="W130">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X130">
         <v>1.01</v>
@@ -21535,10 +21535,10 @@
         <v>1.18</v>
       </c>
       <c r="Z130">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA130">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB130">
         <v>2.21</v>
@@ -21547,7 +21547,7 @@
         <v>2.35</v>
       </c>
       <c r="AD130">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE130">
         <v>1.14</v>
@@ -21556,7 +21556,7 @@
         <v>1.48</v>
       </c>
       <c r="AG130">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21695,7 +21695,7 @@
         <v>1.03</v>
       </c>
       <c r="Y131">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z131">
         <v>3.4</v>
@@ -21707,7 +21707,7 @@
         <v>1.9</v>
       </c>
       <c r="AC131">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD131">
         <v>1.32</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -790,11 +790,11 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "33"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "67", "71"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1120,20 +1120,20 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O5">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P5">
         <v>2.4</v>
       </c>
       <c r="Q5">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="R5">
         <v>1.91</v>
@@ -1145,10 +1145,10 @@
         <v>2.36</v>
       </c>
       <c r="U5">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W5">
         <v>1.04</v>
@@ -1169,7 +1169,7 @@
         <v>1.5</v>
       </c>
       <c r="AC5">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD5">
         <v>1.14</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1197,34 +1197,34 @@
         <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1279,21 +1279,21 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
         <v>1.31</v>
       </c>
       <c r="O6">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="P6">
-        <v>9.699999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q6">
         <v>1.75</v>
@@ -1314,7 +1314,7 @@
         <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
         <v>1.03</v>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "37"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1439,30 +1439,30 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>4.97</v>
+        <v>4.57</v>
       </c>
       <c r="O7">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="P7">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
         <v>1.29</v>
@@ -1471,7 +1471,7 @@
         <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="V7">
         <v>1.5</v>
@@ -1486,32 +1486,32 @@
         <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AA7">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AC7">
         <v>2.76</v>
       </c>
       <c r="AD7">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE7">
         <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG7">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "64", "75"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1520,37 +1520,37 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1605,30 +1605,30 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="O8">
-        <v>6.85</v>
+        <v>7.25</v>
       </c>
       <c r="P8">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Q8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R8">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T8">
         <v>3.8</v>
@@ -1640,13 +1640,13 @@
         <v>1.67</v>
       </c>
       <c r="W8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X8">
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z8">
         <v>5.5</v>
@@ -1674,46 +1674,46 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AJ8">
         <v>1.03</v>
       </c>
       <c r="AK8">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,36 +1753,36 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
         <v>1.27</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P9">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="Q9">
         <v>1.7</v>
@@ -1791,16 +1791,16 @@
         <v>2.5</v>
       </c>
       <c r="S9">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W9">
         <v>1.1</v>
@@ -1809,10 +1809,10 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA9">
         <v>1.57</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "77"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,16 +1855,16 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ9">
         <v>0</v>
@@ -1916,36 +1916,36 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="O10">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P10">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q10">
         <v>1.62</v>
@@ -1954,10 +1954,10 @@
         <v>2.9</v>
       </c>
       <c r="S10">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T10">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="U10">
         <v>1.8</v>
@@ -1966,13 +1966,13 @@
         <v>1.91</v>
       </c>
       <c r="W10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z10">
         <v>7</v>
@@ -1984,13 +1984,13 @@
         <v>3.28</v>
       </c>
       <c r="AC10">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AE10">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AF10">
         <v>1.5</v>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "87"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK10">
         <v>3.3</v>
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="O11">
         <v>3.33</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="Q11">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="R11">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U11">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W11">
         <v>1.08</v>
@@ -2141,10 +2141,10 @@
         <v>3.5</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB11">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AC11">
         <v>3</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AK11">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2242,39 +2242,39 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q12">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="R12">
         <v>2.2</v>
@@ -2283,28 +2283,28 @@
         <v>1.36</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
         <v>3.5</v>
       </c>
       <c r="AA12">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB12">
         <v>1.86</v>
@@ -2313,7 +2313,7 @@
         <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
         <v>1.11</v>
@@ -2322,50 +2322,50 @@
         <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "85"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "45+5"]</t>
         </is>
       </c>
       <c r="AJ12">
         <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,30 +2405,30 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O13">
         <v>4</v>
@@ -2437,25 +2437,25 @@
         <v>1.44</v>
       </c>
       <c r="Q13">
-        <v>6.6</v>
+        <v>5.75</v>
       </c>
       <c r="R13">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U13">
-        <v>2.67</v>
+        <v>2.18</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.05</v>
@@ -2467,7 +2467,7 @@
         <v>3.4</v>
       </c>
       <c r="AA13">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="AB13">
         <v>1.85</v>
@@ -2482,23 +2482,23 @@
         <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG13">
         <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "45+7"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "28", "80"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
         <v>1.04</v>
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,72 +2568,72 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
         <v>1.01</v>
       </c>
       <c r="O14">
-        <v>9.449999999999999</v>
+        <v>21</v>
       </c>
       <c r="P14">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="Q14">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="R14">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="S14">
+        <v>1.1</v>
+      </c>
+      <c r="T14">
+        <v>6</v>
+      </c>
+      <c r="U14">
+        <v>1.59</v>
+      </c>
+      <c r="V14">
+        <v>2.15</v>
+      </c>
+      <c r="W14">
+        <v>1.4</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>1.02</v>
+      </c>
+      <c r="Z14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA14">
         <v>1.08</v>
       </c>
-      <c r="T14">
-        <v>6.1</v>
-      </c>
-      <c r="U14">
-        <v>1.5</v>
-      </c>
-      <c r="V14">
-        <v>2.45</v>
-      </c>
-      <c r="W14">
-        <v>1.47</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>1.01</v>
-      </c>
-      <c r="Z14">
-        <v>10.5</v>
-      </c>
-      <c r="AA14">
-        <v>1.09</v>
-      </c>
       <c r="AB14">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AC14">
         <v>1.35</v>
@@ -2645,14 +2645,14 @@
         <v>1.82</v>
       </c>
       <c r="AF14">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="AG14">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "31", "66"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -2670,16 +2670,16 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ14">
         <v>0</v>
@@ -2778,7 +2778,7 @@
         <v>2.89</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2885,22 +2885,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2909,115 +2909,115 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P16">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="Q16">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="R16">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T16">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U16">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
         <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="AA16">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AB16">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC16">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG16">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "42"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75", "88", "90+4"]</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3048,25 +3048,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3076,111 +3076,111 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
         <v>2.05</v>
       </c>
       <c r="O17">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="V17">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AA17">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB17">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC17">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD17">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "41"]</t>
         </is>
       </c>
       <c r="AJ17">
         <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,68 +3239,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="P18">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="Q18">
         <v>2.86</v>
       </c>
       <c r="R18">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
       <c r="AA18">
+        <v>1.55</v>
+      </c>
+      <c r="AB18">
         <v>2.2</v>
       </c>
-      <c r="AB18">
-        <v>1.66</v>
-      </c>
       <c r="AC18">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
+        <v>1.48</v>
+      </c>
+      <c r="AE18">
         <v>1.2</v>
       </c>
-      <c r="AE18">
-        <v>1.06</v>
-      </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AG18">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,22 +3316,22 @@
         <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ18">
         <v>0</v>
@@ -3374,22 +3374,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Hatta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3398,115 +3398,115 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="O19">
-        <v>3.68</v>
+        <v>3.13</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q19">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R19">
         <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
+        <v>3.2</v>
+      </c>
+      <c r="U19">
+        <v>2.63</v>
+      </c>
+      <c r="V19">
+        <v>1.44</v>
+      </c>
+      <c r="W19">
+        <v>1.11</v>
+      </c>
+      <c r="X19">
+        <v>1.04</v>
+      </c>
+      <c r="Y19">
+        <v>1.17</v>
+      </c>
+      <c r="Z19">
         <v>3.75</v>
       </c>
-      <c r="U19">
-        <v>2.2</v>
-      </c>
-      <c r="V19">
+      <c r="AA19">
+        <v>1.75</v>
+      </c>
+      <c r="AB19">
+        <v>1.95</v>
+      </c>
+      <c r="AC19">
+        <v>2.9</v>
+      </c>
+      <c r="AD19">
+        <v>1.36</v>
+      </c>
+      <c r="AE19">
+        <v>1.13</v>
+      </c>
+      <c r="AF19">
         <v>1.62</v>
       </c>
-      <c r="W19">
-        <v>1.14</v>
-      </c>
-      <c r="X19">
-        <v>1.01</v>
-      </c>
-      <c r="Y19">
-        <v>1.13</v>
-      </c>
-      <c r="Z19">
-        <v>5.25</v>
-      </c>
-      <c r="AA19">
-        <v>1.55</v>
-      </c>
-      <c r="AB19">
-        <v>2.2</v>
-      </c>
-      <c r="AC19">
-        <v>2.25</v>
-      </c>
-      <c r="AD19">
-        <v>1.48</v>
-      </c>
-      <c r="AE19">
-        <v>1.2</v>
-      </c>
-      <c r="AF19">
-        <v>1.42</v>
-      </c>
       <c r="AG19">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "84"]</t>
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hatta</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,81 +3569,81 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.73</v>
+        <v>1.28</v>
       </c>
       <c r="O20">
-        <v>3.24</v>
+        <v>5.25</v>
       </c>
       <c r="P20">
-        <v>2.08</v>
+        <v>7.75</v>
       </c>
       <c r="Q20">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="U20">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
+        <v>5.5</v>
+      </c>
+      <c r="AA20">
+        <v>1.5</v>
+      </c>
+      <c r="AB20">
+        <v>2.5</v>
+      </c>
+      <c r="AC20">
+        <v>2.21</v>
+      </c>
+      <c r="AD20">
+        <v>1.58</v>
+      </c>
+      <c r="AE20">
+        <v>1.22</v>
+      </c>
+      <c r="AF20">
+        <v>1.95</v>
+      </c>
+      <c r="AG20">
+        <v>1.8</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.09</v>
+      </c>
+      <c r="AK20">
         <v>3.75</v>
       </c>
-      <c r="AA20">
-        <v>1.75</v>
-      </c>
-      <c r="AB20">
-        <v>1.95</v>
-      </c>
-      <c r="AC20">
-        <v>2.9</v>
-      </c>
-      <c r="AD20">
-        <v>1.36</v>
-      </c>
-      <c r="AE20">
-        <v>1.13</v>
-      </c>
-      <c r="AF20">
-        <v>1.62</v>
-      </c>
-      <c r="AG20">
-        <v>2.15</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.3</v>
-      </c>
-      <c r="AK20">
-        <v>1.36</v>
-      </c>
       <c r="AL20">
         <v>0</v>
       </c>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-11 10:40:00</t>
+          <t>2026-09-11 11:00:00</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
+        <v>3.8</v>
+      </c>
+      <c r="O21">
+        <v>3.2</v>
+      </c>
+      <c r="P21">
+        <v>1.83</v>
+      </c>
+      <c r="Q21">
+        <v>4.4</v>
+      </c>
+      <c r="R21">
+        <v>1.97</v>
+      </c>
+      <c r="S21">
+        <v>1.4</v>
+      </c>
+      <c r="T21">
+        <v>2.8</v>
+      </c>
+      <c r="U21">
+        <v>3</v>
+      </c>
+      <c r="V21">
+        <v>1.37</v>
+      </c>
+      <c r="W21">
+        <v>1.05</v>
+      </c>
+      <c r="X21">
+        <v>1.06</v>
+      </c>
+      <c r="Y21">
+        <v>1.33</v>
+      </c>
+      <c r="Z21">
+        <v>3.25</v>
+      </c>
+      <c r="AA21">
+        <v>2.02</v>
+      </c>
+      <c r="AB21">
+        <v>1.75</v>
+      </c>
+      <c r="AC21">
+        <v>3.34</v>
+      </c>
+      <c r="AD21">
         <v>1.25</v>
       </c>
-      <c r="O21">
-        <v>5</v>
-      </c>
-      <c r="P21">
-        <v>9.25</v>
-      </c>
-      <c r="Q21">
-        <v>1.62</v>
-      </c>
-      <c r="R21">
-        <v>2.75</v>
-      </c>
-      <c r="S21">
-        <v>1.26</v>
-      </c>
-      <c r="T21">
-        <v>3.28</v>
-      </c>
-      <c r="U21">
-        <v>2.33</v>
-      </c>
-      <c r="V21">
-        <v>1.57</v>
-      </c>
-      <c r="W21">
-        <v>1.14</v>
-      </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>1.13</v>
-      </c>
-      <c r="Z21">
-        <v>5.5</v>
-      </c>
-      <c r="AA21">
-        <v>1.57</v>
-      </c>
-      <c r="AB21">
-        <v>2.35</v>
-      </c>
-      <c r="AC21">
-        <v>2.38</v>
-      </c>
-      <c r="AD21">
-        <v>1.5</v>
-      </c>
       <c r="AE21">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG21">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>3.35</v>
+        <v>1.18</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.68</v>
+        <v>6.1</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="P22">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="Q22">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>1.7</v>
+      </c>
+      <c r="AB22">
         <v>2.1</v>
       </c>
-      <c r="S22">
-        <v>1.41</v>
-      </c>
-      <c r="T22">
-        <v>2.8</v>
-      </c>
-      <c r="U22">
-        <v>2.92</v>
-      </c>
-      <c r="V22">
-        <v>1.37</v>
-      </c>
-      <c r="W22">
-        <v>1.05</v>
-      </c>
-      <c r="X22">
-        <v>1.06</v>
-      </c>
-      <c r="Y22">
-        <v>1.33</v>
-      </c>
-      <c r="Z22">
-        <v>3.25</v>
-      </c>
-      <c r="AA22">
-        <v>2.03</v>
-      </c>
-      <c r="AB22">
-        <v>1.75</v>
-      </c>
       <c r="AC22">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>1.36</v>
+        <v>2.35</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA23">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB23">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4179,149 +4179,149 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>2.7</v>
+        <v>3.81</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3.84</v>
       </c>
       <c r="P24">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="Q24">
+        <v>4.6</v>
+      </c>
+      <c r="R24">
+        <v>2.45</v>
+      </c>
+      <c r="S24">
+        <v>1.22</v>
+      </c>
+      <c r="T24">
         <v>3.6</v>
       </c>
-      <c r="R24">
-        <v>2.1</v>
-      </c>
-      <c r="S24">
-        <v>1.38</v>
-      </c>
-      <c r="T24">
-        <v>2.67</v>
-      </c>
       <c r="U24">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V24">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA24">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AB24">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC24">
-        <v>3.42</v>
+        <v>2.3</v>
       </c>
       <c r="AD24">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "50"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79", "90+9"]</t>
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Lusail City</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,68 +4380,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
-        <v>3.82</v>
+        <v>1.8</v>
       </c>
       <c r="O25">
-        <v>3.79</v>
+        <v>3.95</v>
       </c>
       <c r="P25">
-        <v>1.63</v>
+        <v>3.5</v>
       </c>
       <c r="Q25">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T25">
         <v>3.85</v>
       </c>
       <c r="U25">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="V25">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z25">
         <v>5.5</v>
       </c>
       <c r="AA25">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB25">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AC25">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD25">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AE25">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF25">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG25">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,37 +4454,37 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.14</v>
+        <v>1.95</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lusail City</t>
+          <t>Al Musannah</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="O26">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA26">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="AB26">
-        <v>2.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-11 11:00:00</t>
+          <t>2026-09-11 11:55:00</t>
         </is>
       </c>
     </row>
@@ -4663,27 +4663,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Musannah</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="O27">
-        <v>3.25</v>
+        <v>4.65</v>
       </c>
       <c r="P27">
-        <v>4.1</v>
+        <v>5.89</v>
       </c>
       <c r="Q27">
+        <v>1.73</v>
+      </c>
+      <c r="R27">
+        <v>2.7</v>
+      </c>
+      <c r="S27">
+        <v>1.19</v>
+      </c>
+      <c r="T27">
+        <v>3.75</v>
+      </c>
+      <c r="U27">
+        <v>2.1</v>
+      </c>
+      <c r="V27">
+        <v>1.67</v>
+      </c>
+      <c r="W27">
+        <v>1.17</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.1</v>
+      </c>
+      <c r="Z27">
+        <v>4.95</v>
+      </c>
+      <c r="AA27">
+        <v>1.5</v>
+      </c>
+      <c r="AB27">
+        <v>2.5</v>
+      </c>
+      <c r="AC27">
         <v>2.25</v>
       </c>
-      <c r="R27">
-        <v>2.1</v>
-      </c>
-      <c r="S27">
-        <v>1.45</v>
-      </c>
-      <c r="T27">
-        <v>2.49</v>
-      </c>
-      <c r="U27">
-        <v>3.08</v>
-      </c>
-      <c r="V27">
-        <v>1.31</v>
-      </c>
-      <c r="W27">
-        <v>1.04</v>
-      </c>
-      <c r="X27">
-        <v>1.05</v>
-      </c>
-      <c r="Y27">
-        <v>1.37</v>
-      </c>
-      <c r="Z27">
-        <v>2.83</v>
-      </c>
-      <c r="AA27">
-        <v>1.98</v>
-      </c>
-      <c r="AB27">
-        <v>1.67</v>
-      </c>
-      <c r="AC27">
-        <v>3.45</v>
-      </c>
       <c r="AD27">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AE27">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AF27">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK27">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-09-11 11:55:00</t>
+          <t>2026-09-11 12:00:00</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="O28">
-        <v>4.65</v>
+        <v>6.5</v>
       </c>
       <c r="P28">
-        <v>6.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q28">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="R28">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="S28">
         <v>1.2</v>
       </c>
       <c r="T28">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V28">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W28">
         <v>1.17</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z28">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA28">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB28">
         <v>2.5</v>
       </c>
       <c r="AC28">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD28">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE28">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF28">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG28">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK28">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
       <c r="O29">
-        <v>5.75</v>
+        <v>3.65</v>
       </c>
       <c r="P29">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
-        <v>1.57</v>
+        <v>2.27</v>
       </c>
       <c r="R29">
-        <v>2.65</v>
+        <v>2.23</v>
       </c>
       <c r="S29">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T29">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="V29">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="AA29">
-        <v>1.44</v>
+        <v>1.74</v>
       </c>
       <c r="AB29">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AC29">
-        <v>2.2</v>
+        <v>2.69</v>
       </c>
       <c r="AD29">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AF29">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AG29">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK29">
-        <v>3.85</v>
+        <v>1.89</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="O30">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="P30">
+        <v>3.29</v>
+      </c>
+      <c r="Q30">
+        <v>3</v>
+      </c>
+      <c r="R30">
+        <v>2.03</v>
+      </c>
+      <c r="S30">
+        <v>1.36</v>
+      </c>
+      <c r="T30">
+        <v>2.69</v>
+      </c>
+      <c r="U30">
+        <v>2.8</v>
+      </c>
+      <c r="V30">
+        <v>1.37</v>
+      </c>
+      <c r="W30">
+        <v>1.07</v>
+      </c>
+      <c r="X30">
+        <v>1.06</v>
+      </c>
+      <c r="Y30">
+        <v>1.26</v>
+      </c>
+      <c r="Z30">
+        <v>3.45</v>
+      </c>
+      <c r="AA30">
+        <v>1.88</v>
+      </c>
+      <c r="AB30">
+        <v>1.8</v>
+      </c>
+      <c r="AC30">
         <v>3.5</v>
       </c>
-      <c r="Q30">
-        <v>2.27</v>
-      </c>
-      <c r="R30">
-        <v>2.23</v>
-      </c>
-      <c r="S30">
-        <v>1.35</v>
-      </c>
-      <c r="T30">
-        <v>3.16</v>
-      </c>
-      <c r="U30">
-        <v>2.57</v>
-      </c>
-      <c r="V30">
-        <v>1.48</v>
-      </c>
-      <c r="W30">
-        <v>1.09</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.24</v>
-      </c>
-      <c r="Z30">
-        <v>4.15</v>
-      </c>
-      <c r="AA30">
-        <v>1.74</v>
-      </c>
-      <c r="AB30">
-        <v>2.13</v>
-      </c>
-      <c r="AC30">
-        <v>2.69</v>
-      </c>
       <c r="AD30">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AG30">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="O31">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="P31">
-        <v>3.29</v>
+        <v>1.55</v>
       </c>
       <c r="Q31">
-        <v>3</v>
+        <v>5.25</v>
       </c>
       <c r="R31">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
+        <v>1.29</v>
+      </c>
+      <c r="T31">
+        <v>3.04</v>
+      </c>
+      <c r="U31">
+        <v>2.39</v>
+      </c>
+      <c r="V31">
+        <v>1.49</v>
+      </c>
+      <c r="W31">
+        <v>1.08</v>
+      </c>
+      <c r="X31">
+        <v>1</v>
+      </c>
+      <c r="Y31">
+        <v>1.22</v>
+      </c>
+      <c r="Z31">
+        <v>3.8</v>
+      </c>
+      <c r="AA31">
+        <v>1.73</v>
+      </c>
+      <c r="AB31">
+        <v>2.11</v>
+      </c>
+      <c r="AC31">
+        <v>2.62</v>
+      </c>
+      <c r="AD31">
         <v>1.36</v>
       </c>
-      <c r="T31">
-        <v>2.69</v>
-      </c>
-      <c r="U31">
-        <v>2.8</v>
-      </c>
-      <c r="V31">
-        <v>1.37</v>
-      </c>
-      <c r="W31">
-        <v>1.07</v>
-      </c>
-      <c r="X31">
-        <v>1.06</v>
-      </c>
-      <c r="Y31">
-        <v>1.26</v>
-      </c>
-      <c r="Z31">
-        <v>3.45</v>
-      </c>
-      <c r="AA31">
-        <v>1.88</v>
-      </c>
-      <c r="AB31">
-        <v>1.8</v>
-      </c>
-      <c r="AC31">
-        <v>3.5</v>
-      </c>
-      <c r="AD31">
-        <v>1.28</v>
-      </c>
       <c r="AE31">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
         <v>1.7</v>
       </c>
       <c r="AG31">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.75</v>
+        <v>1.23</v>
       </c>
       <c r="O32">
-        <v>4.1</v>
+        <v>6.57</v>
       </c>
       <c r="P32">
-        <v>1.55</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>5.25</v>
+        <v>1.59</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="T32">
-        <v>3.04</v>
+        <v>4.5</v>
       </c>
       <c r="U32">
-        <v>2.39</v>
+        <v>1.93</v>
       </c>
       <c r="V32">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="W32">
+        <v>1.2</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
         <v>1.08</v>
       </c>
-      <c r="X32">
-        <v>1</v>
-      </c>
-      <c r="Y32">
-        <v>1.22</v>
-      </c>
       <c r="Z32">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="AA32">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AB32">
-        <v>2.11</v>
+        <v>2.97</v>
       </c>
       <c r="AC32">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD32">
+        <v>1.89</v>
+      </c>
+      <c r="AE32">
         <v>1.36</v>
       </c>
-      <c r="AE32">
-        <v>1.14</v>
-      </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AK32">
-        <v>1.09</v>
+        <v>3.75</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-11 12:00:00</t>
+          <t>2026-09-11 12:25:00</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.23</v>
+        <v>4.55</v>
       </c>
       <c r="O33">
-        <v>6.57</v>
+        <v>4.2</v>
       </c>
       <c r="P33">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="Q33">
-        <v>1.59</v>
+        <v>4.33</v>
       </c>
       <c r="R33">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="S33">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="U33">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="V33">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AA33">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AB33">
-        <v>2.97</v>
+        <v>2.43</v>
       </c>
       <c r="AC33">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AD33">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AE33">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AF33">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AG33">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>3.75</v>
+        <v>1.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-11 12:25:00</t>
+          <t>2026-09-11 12:45:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,61 +5851,61 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.55</v>
+        <v>1.85</v>
       </c>
       <c r="O34">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P34">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q34">
-        <v>4.33</v>
+        <v>2.38</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
+        <v>1.61</v>
+      </c>
+      <c r="AB34">
+        <v>2.07</v>
+      </c>
+      <c r="AC34">
+        <v>2.55</v>
+      </c>
+      <c r="AD34">
+        <v>1.44</v>
+      </c>
+      <c r="AE34">
+        <v>1.18</v>
+      </c>
+      <c r="AF34">
         <v>1.53</v>
-      </c>
-      <c r="AB34">
-        <v>2.43</v>
-      </c>
-      <c r="AC34">
-        <v>2.3</v>
-      </c>
-      <c r="AD34">
-        <v>1.58</v>
-      </c>
-      <c r="AE34">
-        <v>1.19</v>
-      </c>
-      <c r="AF34">
-        <v>1.51</v>
       </c>
       <c r="AG34">
         <v>2.3</v>
@@ -5924,7 +5924,7 @@
         <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-11 12:45:00</t>
+          <t>2026-09-11 13:00:00</t>
         </is>
       </c>
     </row>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.91</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="P35">
-        <v>3.5</v>
+        <v>1.11</v>
       </c>
       <c r="Q35">
-        <v>2.38</v>
+        <v>7.5</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W35">
+        <v>1.17</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
         <v>1.13</v>
       </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.18</v>
-      </c>
       <c r="Z35">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA35">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB35">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="AC35">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="AD35">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AG35">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK35">
-        <v>1.76</v>
+        <v>1.05</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>9.800000000000001</v>
+        <v>3.1</v>
       </c>
       <c r="O36">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="P36">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q36">
-        <v>7.5</v>
+        <v>4.05</v>
       </c>
       <c r="R36">
-        <v>2.8</v>
+        <v>1.94</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>2.53</v>
       </c>
       <c r="U36">
-        <v>2.1</v>
+        <v>2.91</v>
       </c>
       <c r="V36">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="W36">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>2.84</v>
       </c>
       <c r="AA36">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB36">
-        <v>2.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC36">
-        <v>2.06</v>
+        <v>4.33</v>
       </c>
       <c r="AD36">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
         <v>1.87</v>
       </c>
       <c r="AG36">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.05</v>
+        <v>1.29</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,52 +6340,52 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P37">
-        <v>2.1</v>
+        <v>3.72</v>
       </c>
       <c r="Q37">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="R37">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S37">
         <v>1.44</v>
       </c>
       <c r="T37">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U37">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="V37">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W37">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1.06</v>
       </c>
       <c r="Y37">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z37">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AA37">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB37">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC37">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD37">
         <v>1.2</v>
@@ -6394,10 +6394,10 @@
         <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,28 +6992,28 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U41">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
         <v>1.44</v>
@@ -7022,34 +7022,34 @@
         <v>1.11</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC41">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD41">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R42">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="V42">
         <v>1.44</v>
@@ -7185,34 +7185,34 @@
         <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA42">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC42">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD42">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE42">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="O43">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P43">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="Q43">
         <v>2.5</v>
@@ -7481,34 +7481,34 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.36</v>
+        <v>2.72</v>
       </c>
       <c r="O44">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="P44">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="Q44">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S44">
         <v>1.33</v>
       </c>
       <c r="T44">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="U44">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="V44">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
         <v>1.03</v>
@@ -7520,13 +7520,13 @@
         <v>3.65</v>
       </c>
       <c r="AA44">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB44">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC44">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="AD44">
         <v>1.36</v>
@@ -7554,7 +7554,7 @@
         <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="O45">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="P45">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q45">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="R45">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S45">
         <v>1.3</v>
@@ -7671,25 +7671,25 @@
         <v>1.5</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
         <v>1.23</v>
       </c>
       <c r="Z45">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="AA45">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB45">
         <v>2.01</v>
       </c>
       <c r="AC45">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD45">
         <v>1.4</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
         <v>1.7</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="O46">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P46">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -7822,34 +7822,34 @@
         <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="V46">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.31</v>
+        <v>5.64</v>
       </c>
       <c r="AA46">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB46">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC46">
         <v>2.05</v>
@@ -7864,7 +7864,7 @@
         <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA63">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB63">
         <v>2</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="O76">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P76">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q76">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="R76">
+        <v>2.1</v>
+      </c>
+      <c r="S76">
+        <v>1.39</v>
+      </c>
+      <c r="T76">
+        <v>2.68</v>
+      </c>
+      <c r="U76">
+        <v>2.73</v>
+      </c>
+      <c r="V76">
+        <v>1.4</v>
+      </c>
+      <c r="W76">
+        <v>1.05</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="Y76">
+        <v>1.24</v>
+      </c>
+      <c r="Z76">
+        <v>3.3</v>
+      </c>
+      <c r="AA76">
         <v>1.88</v>
       </c>
-      <c r="S76">
-        <v>1.48</v>
-      </c>
-      <c r="T76">
-        <v>2.47</v>
-      </c>
-      <c r="U76">
-        <v>3.16</v>
-      </c>
-      <c r="V76">
-        <v>1.31</v>
-      </c>
-      <c r="W76">
-        <v>1.03</v>
-      </c>
-      <c r="X76">
-        <v>1.04</v>
-      </c>
-      <c r="Y76">
-        <v>1.48</v>
-      </c>
-      <c r="Z76">
-        <v>2.71</v>
-      </c>
-      <c r="AA76">
-        <v>2.23</v>
-      </c>
       <c r="AB76">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC76">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="AD76">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AE76">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF76">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG76">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
+        <v>1.3</v>
+      </c>
+      <c r="AK76">
         <v>1.36</v>
-      </c>
-      <c r="AK76">
-        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
+        <v>2.37</v>
+      </c>
+      <c r="O77">
         <v>2.9</v>
       </c>
-      <c r="O77">
-        <v>3.2</v>
-      </c>
       <c r="P77">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="Q77">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="S77">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="T77">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="U77">
-        <v>2.73</v>
+        <v>3.16</v>
       </c>
       <c r="V77">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W77">
+        <v>1.03</v>
+      </c>
+      <c r="X77">
+        <v>1.04</v>
+      </c>
+      <c r="Y77">
+        <v>1.48</v>
+      </c>
+      <c r="Z77">
+        <v>2.71</v>
+      </c>
+      <c r="AA77">
+        <v>2.23</v>
+      </c>
+      <c r="AB77">
+        <v>1.53</v>
+      </c>
+      <c r="AC77">
+        <v>4.8</v>
+      </c>
+      <c r="AD77">
+        <v>1.15</v>
+      </c>
+      <c r="AE77">
         <v>1.05</v>
       </c>
-      <c r="X77">
-        <v>1</v>
-      </c>
-      <c r="Y77">
-        <v>1.24</v>
-      </c>
-      <c r="Z77">
-        <v>3.3</v>
-      </c>
-      <c r="AA77">
-        <v>1.88</v>
-      </c>
-      <c r="AB77">
-        <v>1.77</v>
-      </c>
-      <c r="AC77">
-        <v>3.35</v>
-      </c>
-      <c r="AD77">
-        <v>1.29</v>
-      </c>
-      <c r="AE77">
-        <v>1.07</v>
-      </c>
       <c r="AF77">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AG77">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK77">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13675,25 +13675,25 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="O82">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P82">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q82">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S82">
         <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U82">
         <v>3</v>
@@ -13714,10 +13714,10 @@
         <v>3.2</v>
       </c>
       <c r="AA82">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB82">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC82">
         <v>3.8</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.05</v>
+        <v>1.89</v>
       </c>
       <c r="O88">
-        <v>3.65</v>
+        <v>4.35</v>
       </c>
       <c r="P88">
-        <v>1.92</v>
+        <v>3.34</v>
       </c>
       <c r="Q88">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="R88">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S88">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T88">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U88">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="V88">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="W88">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="X88">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z88">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA88">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AB88">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AC88">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD88">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AE88">
+        <v>1.42</v>
+      </c>
+      <c r="AF88">
         <v>1.3</v>
       </c>
-      <c r="AF88">
-        <v>1.4</v>
-      </c>
       <c r="AG88">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK88">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="O89">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P89">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="Q89">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="R89">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="S89">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
         <v>4</v>
       </c>
       <c r="U89">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="V89">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
         <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z89">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA89">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AB89">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC89">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AD89">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF89">
         <v>1.4</v>
       </c>
       <c r="AG89">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AK89">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="O91">
-        <v>4.35</v>
+        <v>3.5</v>
       </c>
       <c r="P91">
-        <v>3.34</v>
+        <v>2.35</v>
       </c>
       <c r="Q91">
-        <v>2.45</v>
+        <v>3.12</v>
       </c>
       <c r="R91">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="S91">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T91">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U91">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="V91">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="W91">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y91">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>6.8</v>
+        <v>5.25</v>
       </c>
       <c r="AA91">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AB91">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC91">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="AD91">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AE91">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AF91">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG91">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AK91">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="O99">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P99">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q99">
         <v>3.4</v>
@@ -16467,16 +16467,16 @@
         <v>3</v>
       </c>
       <c r="U99">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V99">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W99">
         <v>1.08</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y99">
         <v>1.25</v>
@@ -16485,7 +16485,7 @@
         <v>3.25</v>
       </c>
       <c r="AA99">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB99">
         <v>1.8</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O109">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P109">
-        <v>2.15</v>
+        <v>7.1</v>
       </c>
       <c r="Q109">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="R109">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S109">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T109">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="U109">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="V109">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X109">
         <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z109">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA109">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB109">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AC109">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="AD109">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AE109">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF109">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AG109">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AK109">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O110">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
-        <v>7.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q110">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="R110">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S110">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T110">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="U110">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="V110">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W110">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X110">
         <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z110">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA110">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AB110">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AC110">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AD110">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AE110">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF110">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AG110">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AK110">
-        <v>2.9</v>
+        <v>1.35</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.83</v>
+        <v>3.8</v>
       </c>
       <c r="O118">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P118">
-        <v>4.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q118">
-        <v>2.33</v>
+        <v>4.33</v>
       </c>
       <c r="R118">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="S118">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T118">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="U118">
-        <v>2.79</v>
+        <v>3.42</v>
       </c>
       <c r="V118">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="W118">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X118">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y118">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Z118">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="AA118">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AB118">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC118">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="AD118">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AE118">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF118">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AG118">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.22</v>
+        <v>1.76</v>
       </c>
       <c r="AK118">
-        <v>1.83</v>
+        <v>1.16</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="O119">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P119">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="Q119">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="R119">
         <v>2.1</v>
       </c>
       <c r="S119">
+        <v>1.33</v>
+      </c>
+      <c r="T119">
+        <v>3.2</v>
+      </c>
+      <c r="U119">
+        <v>2.63</v>
+      </c>
+      <c r="V119">
+        <v>1.44</v>
+      </c>
+      <c r="W119">
+        <v>1.08</v>
+      </c>
+      <c r="X119">
+        <v>1.02</v>
+      </c>
+      <c r="Y119">
+        <v>1.22</v>
+      </c>
+      <c r="Z119">
+        <v>3.72</v>
+      </c>
+      <c r="AA119">
+        <v>1.75</v>
+      </c>
+      <c r="AB119">
+        <v>2</v>
+      </c>
+      <c r="AC119">
+        <v>2.75</v>
+      </c>
+      <c r="AD119">
         <v>1.36</v>
       </c>
-      <c r="T119">
-        <v>2.63</v>
-      </c>
-      <c r="U119">
-        <v>2.79</v>
-      </c>
-      <c r="V119">
-        <v>1.35</v>
-      </c>
-      <c r="W119">
-        <v>1.05</v>
-      </c>
-      <c r="X119">
-        <v>1.01</v>
-      </c>
-      <c r="Y119">
-        <v>1.26</v>
-      </c>
-      <c r="Z119">
-        <v>3.2</v>
-      </c>
-      <c r="AA119">
-        <v>1.9</v>
-      </c>
-      <c r="AB119">
-        <v>1.79</v>
-      </c>
-      <c r="AC119">
-        <v>3.14</v>
-      </c>
-      <c r="AD119">
-        <v>1.27</v>
-      </c>
       <c r="AE119">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF119">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG119">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK119">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="O120">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P120">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="Q120">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="R120">
         <v>2.1</v>
       </c>
       <c r="S120">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T120">
+        <v>2.63</v>
+      </c>
+      <c r="U120">
+        <v>2.79</v>
+      </c>
+      <c r="V120">
+        <v>1.35</v>
+      </c>
+      <c r="W120">
+        <v>1.05</v>
+      </c>
+      <c r="X120">
+        <v>1.01</v>
+      </c>
+      <c r="Y120">
+        <v>1.26</v>
+      </c>
+      <c r="Z120">
         <v>3.2</v>
       </c>
-      <c r="U120">
-        <v>2.63</v>
-      </c>
-      <c r="V120">
-        <v>1.44</v>
-      </c>
-      <c r="W120">
-        <v>1.08</v>
-      </c>
-      <c r="X120">
-        <v>1.02</v>
-      </c>
-      <c r="Y120">
-        <v>1.22</v>
-      </c>
-      <c r="Z120">
-        <v>3.72</v>
-      </c>
       <c r="AA120">
+        <v>1.9</v>
+      </c>
+      <c r="AB120">
+        <v>1.79</v>
+      </c>
+      <c r="AC120">
+        <v>3.14</v>
+      </c>
+      <c r="AD120">
+        <v>1.27</v>
+      </c>
+      <c r="AE120">
+        <v>1.1</v>
+      </c>
+      <c r="AF120">
         <v>1.75</v>
       </c>
-      <c r="AB120">
-        <v>2</v>
-      </c>
-      <c r="AC120">
-        <v>2.75</v>
-      </c>
-      <c r="AD120">
-        <v>1.36</v>
-      </c>
-      <c r="AE120">
-        <v>1.12</v>
-      </c>
-      <c r="AF120">
-        <v>1.62</v>
-      </c>
       <c r="AG120">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.8</v>
+        <v>1.83</v>
       </c>
       <c r="O121">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P121">
-        <v>1.95</v>
+        <v>4.25</v>
       </c>
       <c r="Q121">
-        <v>4.33</v>
+        <v>2.33</v>
       </c>
       <c r="R121">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="S121">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T121">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="U121">
-        <v>3.42</v>
+        <v>2.79</v>
       </c>
       <c r="V121">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="W121">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X121">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y121">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z121">
-        <v>2.52</v>
+        <v>3.25</v>
       </c>
       <c r="AA121">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AB121">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC121">
-        <v>4.65</v>
+        <v>3.5</v>
       </c>
       <c r="AD121">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AE121">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AG121">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.76</v>
+        <v>1.22</v>
       </c>
       <c r="AK121">
-        <v>1.16</v>
+        <v>1.83</v>
       </c>
       <c r="AL121">
         <v>0</v>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2181,16 +2181,16 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ11">
         <v>0</v>
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2746,11 +2746,11 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "61", "86"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "69", "78", "88"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,36 +3872,36 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>6.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O22">
-        <v>4.25</v>
+        <v>4.9</v>
       </c>
       <c r="P22">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "80"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "30"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,36 +4035,36 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O23">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q23">
         <v>3.6</v>
@@ -4073,16 +4073,16 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T23">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="U23">
         <v>2.88</v>
       </c>
       <c r="V23">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W23">
         <v>1.06</v>
@@ -4103,7 +4103,7 @@
         <v>1.75</v>
       </c>
       <c r="AC23">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD23">
         <v>1.25</v>
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "87"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "43"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26">
@@ -4687,26 +4687,26 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "65"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76", "90+3"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5025,21 +5025,21 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="O29">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P29">
         <v>3.5</v>
@@ -5048,65 +5048,65 @@
         <v>2.27</v>
       </c>
       <c r="R29">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S29">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="U29">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="V29">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z29">
-        <v>4.15</v>
+        <v>3.68</v>
       </c>
       <c r="AA29">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB29">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="AC29">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AE29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG29">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64", "88"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AJ29">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
         <v>1.89</v>
@@ -5115,16 +5115,16 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ29">
         <v>0</v>
@@ -5176,57 +5176,57 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="O30">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
         <v>3.29</v>
       </c>
       <c r="Q30">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R30">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
         <v>2.8</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
         <v>1.06</v>
@@ -5244,7 +5244,7 @@
         <v>1.8</v>
       </c>
       <c r="AC30">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD30">
         <v>1.28</v>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "20", "44", "57"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "87"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,16 +5278,16 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ30">
         <v>0</v>
@@ -5339,36 +5339,36 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="O31">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="P31">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q31">
         <v>5.25</v>
@@ -5380,19 +5380,19 @@
         <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V31">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
         <v>1.22</v>
@@ -5404,10 +5404,10 @@
         <v>1.73</v>
       </c>
       <c r="AB31">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AC31">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AD31">
         <v>1.36</v>
@@ -5416,19 +5416,19 @@
         <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62", "79", "88"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "39"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,39 +5502,39 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O32">
-        <v>6.57</v>
+        <v>6.75</v>
       </c>
       <c r="P32">
-        <v>9</v>
+        <v>8.65</v>
       </c>
       <c r="Q32">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R32">
         <v>3.1</v>
@@ -5564,34 +5564,34 @@
         <v>8</v>
       </c>
       <c r="AA32">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB32">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AC32">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AD32">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AE32">
         <v>1.36</v>
       </c>
       <c r="AF32">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG32">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "15", "81"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "64", "85"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ32">
         <v>0</v>
@@ -5665,36 +5665,36 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
-        <v>4.55</v>
+        <v>5.75</v>
       </c>
       <c r="O33">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P33">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="Q33">
         <v>4.33</v>
@@ -5709,10 +5709,10 @@
         <v>3.55</v>
       </c>
       <c r="U33">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W33">
         <v>1.11</v>
@@ -5739,44 +5739,44 @@
         <v>1.58</v>
       </c>
       <c r="AE33">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "43", "59"]</t>
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ33">
         <v>0</v>
@@ -5828,45 +5828,45 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="Q34">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="R34">
         <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
         <v>3.4</v>
@@ -5878,7 +5878,7 @@
         <v>1.48</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.03</v>
@@ -5890,7 +5890,7 @@
         <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
         <v>2.07</v>
@@ -5912,46 +5912,46 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "89"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48", "75"]</t>
         </is>
       </c>
       <c r="AJ34">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK34">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,36 +5991,36 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="O35">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="P35">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Q35">
         <v>7.5</v>
@@ -6029,22 +6029,22 @@
         <v>2.8</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U35">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="V35">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="W35">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.13</v>
@@ -6059,28 +6059,28 @@
         <v>2.6</v>
       </c>
       <c r="AC35">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AD35">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE35">
         <v>1.22</v>
       </c>
       <c r="AF35">
+        <v>1.72</v>
+      </c>
+      <c r="AG35">
         <v>1.87</v>
       </c>
-      <c r="AG35">
-        <v>1.83</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "21", "72"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "37", "45+2", "69", "79", "83"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.1</v>
+        <v>1.93</v>
       </c>
       <c r="O36">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P36">
-        <v>2.1</v>
+        <v>3.72</v>
       </c>
       <c r="Q36">
-        <v>4.05</v>
+        <v>2.63</v>
       </c>
       <c r="R36">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S36">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T36">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U36">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="V36">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
         <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z36">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AA36">
         <v>2.2</v>
       </c>
       <c r="AB36">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC36">
         <v>4.33</v>
       </c>
       <c r="AD36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,63 +6308,63 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>1.93</v>
+        <v>2.85</v>
       </c>
       <c r="O37">
         <v>3</v>
       </c>
       <c r="P37">
-        <v>3.72</v>
+        <v>2.25</v>
       </c>
       <c r="Q37">
-        <v>2.61</v>
+        <v>3.65</v>
       </c>
       <c r="R37">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="S37">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T37">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U37">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="V37">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W37">
         <v>1.06</v>
@@ -6373,19 +6373,19 @@
         <v>1.06</v>
       </c>
       <c r="Y37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA37">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB37">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC37">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD37">
         <v>1.2</v>
@@ -6394,7 +6394,7 @@
         <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG37">
         <v>1.83</v>
@@ -6406,41 +6406,41 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "56"]</t>
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6480,36 +6480,36 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="P38">
-        <v>3.72</v>
+        <v>2.91</v>
       </c>
       <c r="Q38">
         <v>2.3</v>
@@ -6527,10 +6527,10 @@
         <v>2.25</v>
       </c>
       <c r="V38">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X38">
         <v>1.01</v>
@@ -6548,7 +6548,7 @@
         <v>2.35</v>
       </c>
       <c r="AC38">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD38">
         <v>1.53</v>
@@ -6564,12 +6564,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "77"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AJ38">
@@ -6582,28 +6582,28 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6643,36 +6643,36 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="O39">
         <v>3.7</v>
       </c>
       <c r="P39">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="Q39">
         <v>2.15</v>
@@ -6681,7 +6681,7 @@
         <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T39">
         <v>3.25</v>
@@ -6705,7 +6705,7 @@
         <v>4</v>
       </c>
       <c r="AA39">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB39">
         <v>2.1</v>
@@ -6720,19 +6720,19 @@
         <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "71", "76"]</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "44", "45+2"]</t>
         </is>
       </c>
       <c r="AJ39">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6797,139 +6797,139 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>2.95</v>
+        <v>3.71</v>
       </c>
       <c r="Q40">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="R40">
         <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V40">
         <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA40">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB40">
         <v>2.15</v>
       </c>
       <c r="AC40">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE40">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "57", "62"]</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6969,16 +6969,16 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -6988,17 +6988,17 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O41">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q41">
         <v>2.33</v>
@@ -7010,7 +7010,7 @@
         <v>1.33</v>
       </c>
       <c r="T41">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U41">
         <v>2.63</v>
@@ -7019,7 +7019,7 @@
         <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
         <v>1</v>
@@ -7034,65 +7034,65 @@
         <v>1.75</v>
       </c>
       <c r="AB41">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC41">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD41">
         <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG41">
         <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "44"]</t>
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK41">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL41">
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7123,139 +7123,139 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="R42">
         <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
         <v>3.25</v>
       </c>
       <c r="U42">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="V42">
         <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "36", "56"]</t>
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AL42">
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7295,26 +7295,26 @@
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "32", "35", "56", "90+2"]</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
@@ -7397,28 +7397,28 @@
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7784,26 +7784,26 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "36", "74"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7970,40 +7970,40 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="P47">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="Q47">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R47">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S47">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T47">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="U47">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V47">
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
         <v>3.5</v>
@@ -8018,16 +8018,16 @@
         <v>3.3</v>
       </c>
       <c r="AD47">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE47">
         <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG47">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O48">
-        <v>3.89</v>
+        <v>3.55</v>
       </c>
       <c r="P48">
-        <v>4.04</v>
+        <v>3.4</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA48">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q49">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S49">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="T49">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="U49">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V49">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W49">
         <v>1.11</v>
@@ -8329,44 +8329,44 @@
         <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z49">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="AA49">
         <v>1.62</v>
       </c>
       <c r="AB49">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC49">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AD49">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AE49">
+        <v>1.22</v>
+      </c>
+      <c r="AF49">
+        <v>1.57</v>
+      </c>
+      <c r="AG49">
+        <v>2.15</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.2</v>
-      </c>
-      <c r="AF49">
-        <v>1.51</v>
-      </c>
-      <c r="AG49">
-        <v>2.35</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.21</v>
       </c>
       <c r="AK49">
         <v>2.05</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.36</v>
+        <v>3.65</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P50">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q50">
         <v>3.57</v>
@@ -8474,7 +8474,7 @@
         <v>2.38</v>
       </c>
       <c r="S50">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
         <v>3.75</v>
@@ -8486,7 +8486,7 @@
         <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8498,10 +8498,10 @@
         <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB50">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AC50">
         <v>2.38</v>
@@ -8510,7 +8510,7 @@
         <v>1.57</v>
       </c>
       <c r="AE50">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF50">
         <v>1.5</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.93</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.73</v>
+        <v>3.01</v>
       </c>
       <c r="O51">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q51">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R51">
         <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
         <v>2.2</v>
@@ -8649,7 +8649,7 @@
         <v>1.6</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8664,7 +8664,7 @@
         <v>1.56</v>
       </c>
       <c r="AB51">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AC51">
         <v>2.54</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O52">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="Q52">
         <v>2.88</v>
@@ -8803,16 +8803,16 @@
         <v>1.2</v>
       </c>
       <c r="T52">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="U52">
         <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="W52">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X52">
         <v>1.01</v>
@@ -8824,10 +8824,10 @@
         <v>7</v>
       </c>
       <c r="AA52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB52">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AC52">
         <v>2.17</v>
@@ -8836,13 +8836,13 @@
         <v>1.67</v>
       </c>
       <c r="AE52">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF52">
         <v>1.4</v>
       </c>
       <c r="AG52">
-        <v>3.04</v>
+        <v>3.32</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,34 +8948,34 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="O53">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P53">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q53">
         <v>2.4</v>
       </c>
       <c r="R53">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S53">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T53">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="U53">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V53">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
         <v>1.08</v>
@@ -8984,28 +8984,28 @@
         <v>1.36</v>
       </c>
       <c r="Z53">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AA53">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AB53">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AC53">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AD53">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE53">
         <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG53">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="O54">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="P54">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q54">
         <v>1.51</v>
@@ -9129,7 +9129,7 @@
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U54">
         <v>2.4</v>
@@ -9147,13 +9147,13 @@
         <v>1.2</v>
       </c>
       <c r="Z54">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA54">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB54">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AC54">
         <v>2.35</v>
@@ -9274,16 +9274,16 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="O55">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P55">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q55">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R55">
         <v>1.94</v>
@@ -9313,10 +9313,10 @@
         <v>2.85</v>
       </c>
       <c r="AA55">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AB55">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC55">
         <v>3.95</v>
@@ -9347,7 +9347,7 @@
         <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O56">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="P56">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O57">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
         <v>2.2</v>
@@ -9612,7 +9612,7 @@
         <v>3.1</v>
       </c>
       <c r="R57">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9624,22 +9624,22 @@
         <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z57">
         <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AB57">
         <v>2.55</v>
@@ -9926,34 +9926,34 @@
         </is>
       </c>
       <c r="N59">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O59">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q59">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R59">
         <v>2.05</v>
       </c>
       <c r="S59">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T59">
         <v>2.75</v>
       </c>
       <c r="U59">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="V59">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W59">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X59">
         <v>1.06</v>
@@ -9962,13 +9962,13 @@
         <v>1.32</v>
       </c>
       <c r="Z59">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AA59">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB59">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC59">
         <v>3.8</v>
@@ -9983,7 +9983,7 @@
         <v>1.8</v>
       </c>
       <c r="AG59">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10066,81 +10066,81 @@
         </is>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N60">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="O60">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="P60">
         <v>12</v>
       </c>
       <c r="Q60">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="R60">
         <v>2.7</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T60">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U60">
         <v>2.08</v>
       </c>
       <c r="V60">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W60">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AA60">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AB60">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="AC60">
         <v>2.25</v>
       </c>
       <c r="AD60">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AE60">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF60">
         <v>1.9</v>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "49"]</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
@@ -10168,28 +10168,28 @@
         <v>0</v>
       </c>
       <c r="AM60">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN60">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO60">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP60">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR60">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS60">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
@@ -10255,46 +10255,46 @@
         <v>2.05</v>
       </c>
       <c r="O61">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P61">
         <v>3.25</v>
       </c>
       <c r="Q61">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="R61">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="S61">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T61">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U61">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V61">
         <v>1.4</v>
       </c>
       <c r="W61">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
         <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z61">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AA61">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AB61">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AC61">
         <v>3.2</v>
@@ -10306,7 +10306,7 @@
         <v>1.11</v>
       </c>
       <c r="AF61">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AG61">
         <v>2.05</v>
@@ -10454,7 +10454,7 @@
         <v>2.3</v>
       </c>
       <c r="AA62">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AB62">
         <v>1.4</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>5.95</v>
+        <v>6.15</v>
       </c>
       <c r="O64">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P64">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Q64">
         <v>4.5</v>
@@ -10756,34 +10756,34 @@
         <v>2.46</v>
       </c>
       <c r="S64">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="U64">
         <v>2.1</v>
       </c>
       <c r="V64">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W64">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X64">
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z64">
-        <v>5.05</v>
+        <v>6</v>
       </c>
       <c r="AA64">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB64">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AC64">
         <v>2.14</v>
@@ -10900,26 +10900,26 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N65">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P65">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="Q65">
         <v>2.44</v>
       </c>
       <c r="R65">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T65">
         <v>3.2</v>
@@ -10943,7 +10943,7 @@
         <v>4.2</v>
       </c>
       <c r="AA65">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB65">
         <v>2.07</v>
@@ -10955,7 +10955,7 @@
         <v>1.36</v>
       </c>
       <c r="AE65">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF65">
         <v>1.62</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="Q66">
         <v>3.4</v>
@@ -11085,13 +11085,13 @@
         <v>1.2</v>
       </c>
       <c r="T66">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U66">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V66">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="W66">
         <v>1.2</v>
@@ -11100,16 +11100,16 @@
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z66">
-        <v>5.75</v>
+        <v>6.3</v>
       </c>
       <c r="AA66">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB66">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC66">
         <v>2.1</v>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.19</v>
+        <v>1.85</v>
       </c>
       <c r="AK66">
         <v>1.23</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.15</v>
+        <v>1.48</v>
       </c>
       <c r="O67">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="P67">
-        <v>1.85</v>
+        <v>5.25</v>
       </c>
       <c r="Q67">
-        <v>3.65</v>
+        <v>2.02</v>
       </c>
       <c r="R67">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="S67">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T67">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U67">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="V67">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W67">
+        <v>1.18</v>
+      </c>
+      <c r="X67">
+        <v>1.02</v>
+      </c>
+      <c r="Y67">
+        <v>1.1</v>
+      </c>
+      <c r="Z67">
+        <v>6</v>
+      </c>
+      <c r="AA67">
+        <v>1.44</v>
+      </c>
+      <c r="AB67">
+        <v>2.75</v>
+      </c>
+      <c r="AC67">
+        <v>2</v>
+      </c>
+      <c r="AD67">
+        <v>1.73</v>
+      </c>
+      <c r="AE67">
+        <v>1.3</v>
+      </c>
+      <c r="AF67">
+        <v>1.52</v>
+      </c>
+      <c r="AG67">
+        <v>2.34</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
         <v>1.12</v>
       </c>
-      <c r="X67">
-        <v>1.03</v>
-      </c>
-      <c r="Y67">
-        <v>1.13</v>
-      </c>
-      <c r="Z67">
-        <v>5.25</v>
-      </c>
-      <c r="AA67">
-        <v>1.48</v>
-      </c>
-      <c r="AB67">
-        <v>2.5</v>
-      </c>
-      <c r="AC67">
-        <v>2.2</v>
-      </c>
-      <c r="AD67">
-        <v>1.57</v>
-      </c>
-      <c r="AE67">
-        <v>1.22</v>
-      </c>
-      <c r="AF67">
-        <v>1.47</v>
-      </c>
-      <c r="AG67">
-        <v>2.42</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.25</v>
-      </c>
       <c r="AK67">
-        <v>1.18</v>
+        <v>2.28</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.48</v>
+        <v>3.4</v>
       </c>
       <c r="O68">
-        <v>4.55</v>
+        <v>3.8</v>
       </c>
       <c r="P68">
-        <v>5.75</v>
+        <v>1.87</v>
       </c>
       <c r="Q68">
-        <v>2.02</v>
+        <v>3.65</v>
       </c>
       <c r="R68">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="S68">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U68">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="V68">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="W68">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z68">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AA68">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB68">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC68">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD68">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AE68">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF68">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG68">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>2.28</v>
+        <v>1.18</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="O69">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="P69">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q69">
         <v>2.6</v>
@@ -11574,13 +11574,13 @@
         <v>1.36</v>
       </c>
       <c r="T69">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="U69">
         <v>2.75</v>
       </c>
       <c r="V69">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W69">
         <v>1.06</v>
@@ -11604,16 +11604,16 @@
         <v>2.8</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AE69">
         <v>1.13</v>
       </c>
       <c r="AF69">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG69">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK69">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O70">
         <v>3</v>
       </c>
       <c r="P70">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -11737,16 +11737,16 @@
         <v>1.38</v>
       </c>
       <c r="T70">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="U70">
         <v>3.2</v>
       </c>
       <c r="V70">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W70">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
         <v>1.07</v>
@@ -11758,10 +11758,10 @@
         <v>2.88</v>
       </c>
       <c r="AA70">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="AB70">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AC70">
         <v>4.33</v>
@@ -11770,7 +11770,7 @@
         <v>1.2</v>
       </c>
       <c r="AE70">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF70">
         <v>1.81</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK70">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,19 +11882,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="O71">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="P71">
-        <v>9.119999999999999</v>
+        <v>11</v>
       </c>
       <c r="Q71">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R71">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="S71">
         <v>1.21</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="O72">
         <v>3.3</v>
       </c>
       <c r="P72">
-        <v>7.5</v>
+        <v>7.46</v>
       </c>
       <c r="Q72">
         <v>2.1</v>
@@ -12060,7 +12060,7 @@
         <v>2</v>
       </c>
       <c r="S72">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="T72">
         <v>2.5</v>
@@ -12078,16 +12078,16 @@
         <v>1.11</v>
       </c>
       <c r="Y72">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Z72">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA72">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="AB72">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AC72">
         <v>5.5</v>
@@ -12217,7 +12217,7 @@
         <v>3.8</v>
       </c>
       <c r="Q73">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R73">
         <v>2.15</v>
@@ -12232,13 +12232,13 @@
         <v>3</v>
       </c>
       <c r="V73">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X73">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y73">
         <v>1.3</v>
@@ -12247,13 +12247,13 @@
         <v>3.25</v>
       </c>
       <c r="AA73">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB73">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC73">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD73">
         <v>1.3</v>
@@ -12371,22 +12371,22 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P74">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q74">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="R74">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="S74">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T74">
         <v>3.3</v>
@@ -12401,7 +12401,7 @@
         <v>1.07</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y74">
         <v>1.21</v>
@@ -12410,7 +12410,7 @@
         <v>3.85</v>
       </c>
       <c r="AA74">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB74">
         <v>1.9</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,55 +12534,55 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O75">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="P75">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q75">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="R75">
         <v>2.05</v>
       </c>
       <c r="S75">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T75">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="U75">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W75">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
         <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
         <v>3.8</v>
       </c>
       <c r="AA75">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB75">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC75">
         <v>3.35</v>
       </c>
       <c r="AD75">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE75">
         <v>1.13</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="O76">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P76">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="Q76">
+        <v>3.5</v>
+      </c>
+      <c r="R76">
+        <v>1.88</v>
+      </c>
+      <c r="S76">
+        <v>1.43</v>
+      </c>
+      <c r="T76">
+        <v>2.85</v>
+      </c>
+      <c r="U76">
         <v>3.6</v>
       </c>
-      <c r="R76">
-        <v>2.1</v>
-      </c>
-      <c r="S76">
-        <v>1.39</v>
-      </c>
-      <c r="T76">
-        <v>2.68</v>
-      </c>
-      <c r="U76">
-        <v>2.73</v>
-      </c>
       <c r="V76">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W76">
+        <v>1.07</v>
+      </c>
+      <c r="X76">
         <v>1.05</v>
       </c>
-      <c r="X76">
-        <v>1</v>
-      </c>
       <c r="Y76">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Z76">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="AA76">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="AB76">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AC76">
-        <v>3.35</v>
+        <v>5</v>
       </c>
       <c r="AD76">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AE76">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF76">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AG76">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK76">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.37</v>
+        <v>3.11</v>
       </c>
       <c r="O77">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="P77">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q77">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="R77">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T77">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U77">
-        <v>3.16</v>
+        <v>2.69</v>
       </c>
       <c r="V77">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="W77">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="Z77">
-        <v>2.71</v>
+        <v>3.3</v>
       </c>
       <c r="AA77">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="AB77">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AC77">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="AD77">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AE77">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF77">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AG77">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
+        <v>1.3</v>
+      </c>
+      <c r="AK77">
         <v>1.36</v>
-      </c>
-      <c r="AK77">
-        <v>1.53</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,25 +13023,25 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q78">
-        <v>3.79</v>
+        <v>3.65</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="U78">
         <v>2.48</v>
@@ -13050,37 +13050,37 @@
         <v>1.44</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
         <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="AA78">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB78">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AC78">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AD78">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE78">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF78">
         <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13201,40 +13201,40 @@
         <v>2.4</v>
       </c>
       <c r="S79">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T79">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U79">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="V79">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X79">
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z79">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA79">
         <v>1.57</v>
       </c>
       <c r="AB79">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC79">
         <v>2.46</v>
       </c>
       <c r="AD79">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE79">
         <v>1.2</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK79">
         <v>2.47</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="O80">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P80">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AA80">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB80">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,34 +13512,34 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P81">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q81">
         <v>2.44</v>
       </c>
       <c r="R81">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S81">
         <v>1.35</v>
       </c>
       <c r="T81">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U81">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="V81">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W81">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
         <v>1.03</v>
@@ -13557,7 +13557,7 @@
         <v>1.85</v>
       </c>
       <c r="AC81">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD81">
         <v>1.32</v>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK81">
         <v>1.72</v>
@@ -13838,34 +13838,34 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="O83">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="P83">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R83">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="S83">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T83">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="U83">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V83">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="W83">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13886,10 +13886,10 @@
         <v>1.65</v>
       </c>
       <c r="AD83">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AE83">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AF83">
         <v>1.75</v>
@@ -13911,7 +13911,7 @@
         <v>1.06</v>
       </c>
       <c r="AK83">
-        <v>5.9</v>
+        <v>6.35</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,25 +14001,25 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="O84">
         <v>3.55</v>
       </c>
       <c r="P84">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q84">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S84">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T84">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="U84">
         <v>2.2</v>
@@ -14031,13 +14031,13 @@
         <v>1.13</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
         <v>1.17</v>
       </c>
       <c r="Z84">
-        <v>5.36</v>
+        <v>5</v>
       </c>
       <c r="AA84">
         <v>1.5</v>
@@ -14049,13 +14049,13 @@
         <v>2.3</v>
       </c>
       <c r="AD84">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE84">
         <v>1.25</v>
       </c>
       <c r="AF84">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
         <v>2.6</v>
@@ -14074,7 +14074,7 @@
         <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,10 +14173,10 @@
         <v>3.4</v>
       </c>
       <c r="Q85">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="R85">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="S85">
         <v>1.2</v>
@@ -14188,19 +14188,19 @@
         <v>2.03</v>
       </c>
       <c r="V85">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="W85">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z85">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA85">
         <v>1.39</v>
@@ -14212,16 +14212,16 @@
         <v>2.05</v>
       </c>
       <c r="AD85">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE85">
         <v>1.3</v>
       </c>
       <c r="AF85">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK85">
         <v>1.97</v>
@@ -14327,19 +14327,19 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P86">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q86">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="R86">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S86">
         <v>1.2</v>
@@ -14351,7 +14351,7 @@
         <v>2</v>
       </c>
       <c r="V86">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W86">
         <v>1.17</v>
@@ -14360,7 +14360,7 @@
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z86">
         <v>5.75</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK86">
         <v>1.36</v>
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O87">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="P87">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q87">
         <v>1.64</v>
       </c>
       <c r="R87">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="S87">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T87">
         <v>4.5</v>
       </c>
       <c r="U87">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V87">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W87">
         <v>1.2</v>
@@ -14523,16 +14523,16 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z87">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA87">
         <v>1.36</v>
       </c>
       <c r="AB87">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC87">
         <v>1.9</v>
@@ -14544,10 +14544,10 @@
         <v>1.36</v>
       </c>
       <c r="AF87">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG87">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK87">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,25 +14653,25 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="O88">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P88">
-        <v>3.34</v>
+        <v>4.12</v>
       </c>
       <c r="Q88">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="R88">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="S88">
         <v>1.17</v>
       </c>
       <c r="T88">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="U88">
         <v>1.94</v>
@@ -14680,16 +14680,16 @@
         <v>1.88</v>
       </c>
       <c r="W88">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z88">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AA88">
         <v>1.29</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.05</v>
+        <v>1.28</v>
       </c>
       <c r="O89">
-        <v>3.65</v>
+        <v>6.05</v>
       </c>
       <c r="P89">
-        <v>1.92</v>
+        <v>7.28</v>
       </c>
       <c r="Q89">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="R89">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="S89">
+        <v>1.15</v>
+      </c>
+      <c r="T89">
+        <v>5.5</v>
+      </c>
+      <c r="U89">
+        <v>1.72</v>
+      </c>
+      <c r="V89">
+        <v>1.95</v>
+      </c>
+      <c r="W89">
+        <v>1.3</v>
+      </c>
+      <c r="X89">
+        <v>1</v>
+      </c>
+      <c r="Y89">
+        <v>1.05</v>
+      </c>
+      <c r="Z89">
+        <v>8.5</v>
+      </c>
+      <c r="AA89">
         <v>1.22</v>
       </c>
-      <c r="T89">
-        <v>4</v>
-      </c>
-      <c r="U89">
-        <v>2.03</v>
-      </c>
-      <c r="V89">
-        <v>1.79</v>
-      </c>
-      <c r="W89">
-        <v>1.13</v>
-      </c>
-      <c r="X89">
-        <v>1.02</v>
-      </c>
-      <c r="Y89">
-        <v>1.08</v>
-      </c>
-      <c r="Z89">
-        <v>5.5</v>
-      </c>
-      <c r="AA89">
-        <v>1.4</v>
-      </c>
       <c r="AB89">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="AC89">
+        <v>1.54</v>
+      </c>
+      <c r="AD89">
         <v>2.1</v>
       </c>
-      <c r="AD89">
-        <v>1.69</v>
-      </c>
       <c r="AE89">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AF89">
         <v>1.4</v>
       </c>
       <c r="AG89">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK89">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,80 +14979,80 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.34</v>
+        <v>3.05</v>
       </c>
       <c r="O90">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="P90">
-        <v>5.97</v>
+        <v>1.97</v>
       </c>
       <c r="Q90">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="R90">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="S90">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T90">
-        <v>5.5</v>
+        <v>4.05</v>
       </c>
       <c r="U90">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="V90">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="W90">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z90">
-        <v>8.5</v>
+        <v>6.65</v>
       </c>
       <c r="AA90">
+        <v>1.4</v>
+      </c>
+      <c r="AB90">
+        <v>3.4</v>
+      </c>
+      <c r="AC90">
+        <v>2.1</v>
+      </c>
+      <c r="AD90">
+        <v>1.87</v>
+      </c>
+      <c r="AE90">
+        <v>1.3</v>
+      </c>
+      <c r="AF90">
+        <v>1.4</v>
+      </c>
+      <c r="AG90">
+        <v>2.75</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
+        <v>1.18</v>
+      </c>
+      <c r="AK90">
         <v>1.25</v>
-      </c>
-      <c r="AB90">
-        <v>4.2</v>
-      </c>
-      <c r="AC90">
-        <v>1.63</v>
-      </c>
-      <c r="AD90">
-        <v>2.17</v>
-      </c>
-      <c r="AE90">
-        <v>1.48</v>
-      </c>
-      <c r="AF90">
-        <v>1.38</v>
-      </c>
-      <c r="AG90">
-        <v>2.8</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.15</v>
-      </c>
-      <c r="AK90">
-        <v>2.92</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,22 +15142,22 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O91">
         <v>3.5</v>
       </c>
       <c r="P91">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q91">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="R91">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="S91">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T91">
         <v>4</v>
@@ -15184,10 +15184,10 @@
         <v>1.48</v>
       </c>
       <c r="AB91">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC91">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD91">
         <v>1.58</v>
@@ -15215,7 +15215,7 @@
         <v>1.47</v>
       </c>
       <c r="AK91">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,10 +15305,10 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O92">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="P92">
         <v>2.8</v>
@@ -15320,7 +15320,7 @@
         <v>2.2</v>
       </c>
       <c r="S92">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T92">
         <v>3.28</v>
@@ -15332,7 +15332,7 @@
         <v>1.44</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X92">
         <v>1.03</v>
@@ -15341,10 +15341,10 @@
         <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AA92">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB92">
         <v>2</v>
@@ -15359,10 +15359,10 @@
         <v>1.14</v>
       </c>
       <c r="AF92">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG92">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P93">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="Q93">
         <v>2.88</v>
@@ -15486,25 +15486,25 @@
         <v>1.22</v>
       </c>
       <c r="T93">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U93">
         <v>2.2</v>
       </c>
       <c r="V93">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z93">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="AA93">
         <v>1.61</v>
@@ -15519,10 +15519,10 @@
         <v>1.42</v>
       </c>
       <c r="AE93">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AF93">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG93">
         <v>2.5</v>
@@ -15541,7 +15541,7 @@
         <v>1.3</v>
       </c>
       <c r="AK93">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O94">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P94">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q94">
         <v>5</v>
@@ -15646,16 +15646,16 @@
         <v>2.4</v>
       </c>
       <c r="S94">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T94">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="U94">
         <v>2.43</v>
       </c>
       <c r="V94">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W94">
         <v>1.08</v>
@@ -15673,7 +15673,7 @@
         <v>1.7</v>
       </c>
       <c r="AB94">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC94">
         <v>2.7</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O95">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="P95">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q95">
         <v>2.75</v>
@@ -15815,7 +15815,7 @@
         <v>3.2</v>
       </c>
       <c r="U95">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V95">
         <v>1.5</v>
@@ -15827,28 +15827,28 @@
         <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z95">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA95">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB95">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AC95">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD95">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE95">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF95">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG95">
         <v>2.38</v>
@@ -15957,31 +15957,31 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="O96">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P96">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="Q96">
         <v>2.2</v>
       </c>
       <c r="R96">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="S96">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T96">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="U96">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="V96">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W96">
         <v>1.08</v>
@@ -15990,31 +15990,31 @@
         <v>1.05</v>
       </c>
       <c r="Y96">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z96">
         <v>3.5</v>
       </c>
       <c r="AA96">
+        <v>2.05</v>
+      </c>
+      <c r="AB96">
         <v>1.85</v>
       </c>
-      <c r="AB96">
-        <v>2.05</v>
-      </c>
       <c r="AC96">
-        <v>2.76</v>
+        <v>3.18</v>
       </c>
       <c r="AD96">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE96">
         <v>1.12</v>
       </c>
       <c r="AF96">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG96">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16120,19 +16120,19 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O97">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P97">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q97">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R97">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="S97">
         <v>1.22</v>
@@ -16283,16 +16283,16 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="O98">
         <v>3.6</v>
       </c>
       <c r="P98">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q98">
-        <v>2.92</v>
+        <v>2.54</v>
       </c>
       <c r="R98">
         <v>2.3</v>
@@ -16331,7 +16331,7 @@
         <v>2.55</v>
       </c>
       <c r="AD98">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE98">
         <v>1.2</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="O100">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="P100">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q100">
         <v>1.91</v>
       </c>
       <c r="R100">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="S100">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T100">
         <v>3.25</v>
       </c>
       <c r="U100">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="V100">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W100">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X100">
         <v>1.03</v>
       </c>
       <c r="Y100">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z100">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AA100">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB100">
-        <v>1.88</v>
+        <v>2.23</v>
       </c>
       <c r="AC100">
         <v>2.6</v>
       </c>
       <c r="AD100">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE100">
         <v>1.18</v>
       </c>
       <c r="AF100">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG100">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK100">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,34 +16772,34 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O101">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="P101">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q101">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="R101">
         <v>2.45</v>
       </c>
       <c r="S101">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T101">
         <v>4</v>
       </c>
       <c r="U101">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="V101">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W101">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X101">
         <v>1.01</v>
@@ -16808,13 +16808,13 @@
         <v>1.14</v>
       </c>
       <c r="Z101">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA101">
         <v>1.5</v>
       </c>
       <c r="AB101">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="AC101">
         <v>2.28</v>
@@ -16823,10 +16823,10 @@
         <v>1.6</v>
       </c>
       <c r="AE101">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF101">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG101">
         <v>2.6</v>
@@ -16845,7 +16845,7 @@
         <v>1.22</v>
       </c>
       <c r="AK101">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O104">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P104">
-        <v>2.58</v>
+        <v>2.86</v>
       </c>
       <c r="Q104">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R104">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="S104">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T104">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="U104">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="V104">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W104">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y104">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="Z104">
-        <v>5</v>
+        <v>3.39</v>
       </c>
       <c r="AA104">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AB104">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AC104">
-        <v>2.26</v>
+        <v>3.57</v>
       </c>
       <c r="AD104">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AE104">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AF104">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>1.29</v>
       </c>
       <c r="AK104">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O105">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P105">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="Q105">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="R105">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="S105">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T105">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="U105">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="V105">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X105">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="Z105">
-        <v>3.39</v>
+        <v>5</v>
       </c>
       <c r="AA105">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="AB105">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AC105">
-        <v>3.57</v>
+        <v>2.26</v>
       </c>
       <c r="AD105">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AE105">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AF105">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AG105">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="O106">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="P106">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q106">
         <v>7.5</v>
@@ -17626,25 +17626,25 @@
         <v>4.55</v>
       </c>
       <c r="AA106">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB106">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="AC106">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD106">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE106">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF106">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG106">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.35</v>
+        <v>2.85</v>
       </c>
       <c r="O109">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P109">
-        <v>7.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q109">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="R109">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S109">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T109">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="U109">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="V109">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X109">
         <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z109">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA109">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AB109">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AC109">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AD109">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AE109">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF109">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AG109">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AK109">
-        <v>2.9</v>
+        <v>1.35</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="O110">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P110">
-        <v>2.15</v>
+        <v>7.1</v>
       </c>
       <c r="Q110">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="R110">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S110">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T110">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="U110">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="V110">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W110">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X110">
         <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z110">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA110">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AB110">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AC110">
-        <v>2.7</v>
+        <v>2.16</v>
       </c>
       <c r="AD110">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AE110">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF110">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AG110">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AK110">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,16 +18402,16 @@
         </is>
       </c>
       <c r="N111">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="O111">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P111">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q111">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="R111">
         <v>2.2</v>
@@ -18435,22 +18435,22 @@
         <v>1.02</v>
       </c>
       <c r="Y111">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z111">
         <v>3.9</v>
       </c>
       <c r="AA111">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB111">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC111">
         <v>2.95</v>
       </c>
       <c r="AD111">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE111">
         <v>1.12</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK111">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="O112">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P112">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18604,10 +18604,10 @@
         <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB112">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.72</v>
+        <v>2.85</v>
       </c>
       <c r="O113">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P113">
-        <v>5.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q113">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="R113">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S113">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T113">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U113">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V113">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W113">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X113">
         <v>1.06</v>
       </c>
       <c r="Y113">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="Z113">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="AA113">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB113">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC113">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD113">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE113">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF113">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="AG113">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AK113">
-        <v>2</v>
+        <v>1.42</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.75</v>
+        <v>1.72</v>
       </c>
       <c r="O114">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P114">
-        <v>2.3</v>
+        <v>4.75</v>
       </c>
       <c r="Q114">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="R114">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S114">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T114">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="U114">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V114">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W114">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X114">
         <v>1.06</v>
       </c>
       <c r="Y114">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z114">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="AA114">
+        <v>2.19</v>
+      </c>
+      <c r="AB114">
+        <v>1.62</v>
+      </c>
+      <c r="AC114">
+        <v>3.38</v>
+      </c>
+      <c r="AD114">
+        <v>1.2</v>
+      </c>
+      <c r="AE114">
+        <v>1.05</v>
+      </c>
+      <c r="AF114">
         <v>2</v>
       </c>
-      <c r="AB114">
-        <v>1.68</v>
-      </c>
-      <c r="AC114">
-        <v>3.7</v>
-      </c>
-      <c r="AD114">
-        <v>1.25</v>
-      </c>
-      <c r="AE114">
-        <v>1.1</v>
-      </c>
-      <c r="AF114">
-        <v>1.7</v>
-      </c>
       <c r="AG114">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AK114">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19217,19 +19217,19 @@
         </is>
       </c>
       <c r="N116">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O116">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q116">
         <v>2.59</v>
       </c>
       <c r="R116">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S116">
         <v>1.48</v>
@@ -19259,7 +19259,7 @@
         <v>2.3</v>
       </c>
       <c r="AB116">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC116">
         <v>4.15</v>
@@ -19268,7 +19268,7 @@
         <v>1.2</v>
       </c>
       <c r="AE116">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF116">
         <v>2</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O117">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P117">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q117">
         <v>2.08</v>
@@ -19407,7 +19407,7 @@
         <v>1.5</v>
       </c>
       <c r="W117">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X117">
         <v>1.02</v>
@@ -19422,22 +19422,22 @@
         <v>1.65</v>
       </c>
       <c r="AB117">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AC117">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="AD117">
         <v>1.5</v>
       </c>
       <c r="AE117">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF117">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG117">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="O118">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P118">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q118">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="R118">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
         <v>1.44</v>
       </c>
       <c r="T118">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="U118">
-        <v>3.42</v>
+        <v>2.97</v>
       </c>
       <c r="V118">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="W118">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y118">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="Z118">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="AA118">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="AB118">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC118">
-        <v>4.65</v>
+        <v>3.25</v>
       </c>
       <c r="AD118">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AE118">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AF118">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="AG118">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AK118">
-        <v>1.16</v>
+        <v>1.7</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
+        <v>4.05</v>
+      </c>
+      <c r="O119">
+        <v>3.1</v>
+      </c>
+      <c r="P119">
+        <v>1.85</v>
+      </c>
+      <c r="Q119">
+        <v>4.33</v>
+      </c>
+      <c r="R119">
+        <v>1.93</v>
+      </c>
+      <c r="S119">
+        <v>1.44</v>
+      </c>
+      <c r="T119">
+        <v>2.63</v>
+      </c>
+      <c r="U119">
+        <v>3.25</v>
+      </c>
+      <c r="V119">
+        <v>1.29</v>
+      </c>
+      <c r="W119">
+        <v>1.04</v>
+      </c>
+      <c r="X119">
+        <v>1.03</v>
+      </c>
+      <c r="Y119">
+        <v>1.37</v>
+      </c>
+      <c r="Z119">
+        <v>2.59</v>
+      </c>
+      <c r="AA119">
+        <v>2.31</v>
+      </c>
+      <c r="AB119">
+        <v>1.53</v>
+      </c>
+      <c r="AC119">
+        <v>4.45</v>
+      </c>
+      <c r="AD119">
+        <v>1.19</v>
+      </c>
+      <c r="AE119">
+        <v>1.01</v>
+      </c>
+      <c r="AF119">
         <v>2.04</v>
       </c>
-      <c r="O119">
-        <v>3.3</v>
-      </c>
-      <c r="P119">
-        <v>3.18</v>
-      </c>
-      <c r="Q119">
-        <v>2.61</v>
-      </c>
-      <c r="R119">
-        <v>2.1</v>
-      </c>
-      <c r="S119">
-        <v>1.33</v>
-      </c>
-      <c r="T119">
-        <v>3.2</v>
-      </c>
-      <c r="U119">
-        <v>2.63</v>
-      </c>
-      <c r="V119">
-        <v>1.44</v>
-      </c>
-      <c r="W119">
-        <v>1.08</v>
-      </c>
-      <c r="X119">
-        <v>1.02</v>
-      </c>
-      <c r="Y119">
-        <v>1.22</v>
-      </c>
-      <c r="Z119">
-        <v>3.72</v>
-      </c>
-      <c r="AA119">
-        <v>1.75</v>
-      </c>
-      <c r="AB119">
-        <v>2</v>
-      </c>
-      <c r="AC119">
-        <v>2.75</v>
-      </c>
-      <c r="AD119">
-        <v>1.36</v>
-      </c>
-      <c r="AE119">
-        <v>1.12</v>
-      </c>
-      <c r="AF119">
-        <v>1.62</v>
-      </c>
       <c r="AG119">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK119">
-        <v>1.65</v>
+        <v>1.16</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="O120">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P120">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="Q120">
         <v>2.6</v>
       </c>
       <c r="R120">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S120">
+        <v>1.32</v>
+      </c>
+      <c r="T120">
+        <v>3.25</v>
+      </c>
+      <c r="U120">
+        <v>2.63</v>
+      </c>
+      <c r="V120">
+        <v>1.44</v>
+      </c>
+      <c r="W120">
+        <v>1.11</v>
+      </c>
+      <c r="X120">
+        <v>1.02</v>
+      </c>
+      <c r="Y120">
+        <v>1.22</v>
+      </c>
+      <c r="Z120">
+        <v>4.2</v>
+      </c>
+      <c r="AA120">
+        <v>1.75</v>
+      </c>
+      <c r="AB120">
+        <v>2.19</v>
+      </c>
+      <c r="AC120">
+        <v>2.75</v>
+      </c>
+      <c r="AD120">
         <v>1.36</v>
       </c>
-      <c r="T120">
-        <v>2.63</v>
-      </c>
-      <c r="U120">
-        <v>2.79</v>
-      </c>
-      <c r="V120">
-        <v>1.35</v>
-      </c>
-      <c r="W120">
-        <v>1.05</v>
-      </c>
-      <c r="X120">
-        <v>1.01</v>
-      </c>
-      <c r="Y120">
-        <v>1.26</v>
-      </c>
-      <c r="Z120">
-        <v>3.2</v>
-      </c>
-      <c r="AA120">
-        <v>1.9</v>
-      </c>
-      <c r="AB120">
-        <v>1.79</v>
-      </c>
-      <c r="AC120">
-        <v>3.14</v>
-      </c>
-      <c r="AD120">
-        <v>1.27</v>
-      </c>
       <c r="AE120">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF120">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG120">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK120">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20038,28 +20038,28 @@
         <v>3.25</v>
       </c>
       <c r="P121">
-        <v>4.25</v>
+        <v>3.72</v>
       </c>
       <c r="Q121">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="R121">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S121">
         <v>1.36</v>
       </c>
       <c r="T121">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="U121">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="V121">
         <v>1.36</v>
       </c>
       <c r="W121">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X121">
         <v>1.06</v>
@@ -20086,10 +20086,10 @@
         <v>1.05</v>
       </c>
       <c r="AF121">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG121">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20195,25 +20195,25 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="O122">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P122">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="Q122">
         <v>2.88</v>
       </c>
       <c r="R122">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="S122">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T122">
-        <v>2.93</v>
+        <v>3.24</v>
       </c>
       <c r="U122">
         <v>2.88</v>
@@ -20231,10 +20231,10 @@
         <v>1.3</v>
       </c>
       <c r="Z122">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="AA122">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AB122">
         <v>1.75</v>
@@ -20252,7 +20252,7 @@
         <v>1.67</v>
       </c>
       <c r="AG122">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20358,25 +20358,25 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O123">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P123">
         <v>5.75</v>
       </c>
       <c r="Q123">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R123">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="S123">
         <v>1.42</v>
       </c>
       <c r="T123">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="U123">
         <v>3.2</v>
@@ -20397,13 +20397,13 @@
         <v>2.9</v>
       </c>
       <c r="AA123">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AB123">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC123">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="AD123">
         <v>1.22</v>
@@ -20412,10 +20412,10 @@
         <v>1.06</v>
       </c>
       <c r="AF123">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AG123">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>

--- a/jogos_2026-09-11.xlsx
+++ b/jogos_2026-09-11.xlsx
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -3558,14 +3558,14 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "86", "90+1"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
@@ -6256,16 +6256,16 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ36">
         <v>0</v>
@@ -7458,13 +7458,13 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
@@ -7560,28 +7560,28 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7621,26 +7621,26 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "81"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "42", "68"]</t>
         </is>
       </c>
       <c r="AJ45">
@@ -7723,28 +7723,28 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -7959,14 +7959,14 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74", "85"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -8049,28 +8049,28 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>32</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8101,22 +8101,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -8129,111 +8129,111 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O48">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P48">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q48">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R48">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="S48">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T48">
-        <v>3.21</v>
+        <v>3.52</v>
       </c>
       <c r="U48">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="V48">
+        <v>1.62</v>
+      </c>
+      <c r="W48">
+        <v>1.11</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.11</v>
+      </c>
+      <c r="Z48">
+        <v>4.95</v>
+      </c>
+      <c r="AA48">
+        <v>1.62</v>
+      </c>
+      <c r="AB48">
+        <v>2.2</v>
+      </c>
+      <c r="AC48">
+        <v>2.55</v>
+      </c>
+      <c r="AD48">
         <v>1.48</v>
       </c>
-      <c r="W48">
-        <v>1.07</v>
-      </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
-      <c r="Y48">
-        <v>1.17</v>
-      </c>
-      <c r="Z48">
-        <v>3.94</v>
-      </c>
-      <c r="AA48">
-        <v>1.6</v>
-      </c>
-      <c r="AB48">
-        <v>2.3</v>
-      </c>
-      <c r="AC48">
-        <v>2.59</v>
-      </c>
-      <c r="AD48">
+      <c r="AE48">
+        <v>1.22</v>
+      </c>
+      <c r="AF48">
+        <v>1.57</v>
+      </c>
+      <c r="AG48">
+        <v>2.15</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>["16"]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.2</v>
+      </c>
+      <c r="AK48">
+        <v>2.05</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>5</v>
+      </c>
+      <c r="AN48">
+        <v>1</v>
+      </c>
+      <c r="AO48">
+        <v>11</v>
+      </c>
+      <c r="AP48">
+        <v>13</v>
+      </c>
+      <c r="AQ48">
+        <v>1.78</v>
+      </c>
+      <c r="AR48">
         <v>1.4</v>
       </c>
-      <c r="AE48">
-        <v>1.12</v>
-      </c>
-      <c r="AF48">
-        <v>1.59</v>
-      </c>
-      <c r="AG48">
-        <v>2.21</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.27</v>
-      </c>
-      <c r="AK48">
-        <v>1.76</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>-1</v>
-      </c>
-      <c r="AN48">
-        <v>-1</v>
-      </c>
-      <c r="AO48">
-        <v>-1</v>
-      </c>
-      <c r="AP48">
-        <v>-1</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
       <c r="AS48">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8264,97 +8264,97 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
+        <v>3.65</v>
+      </c>
+      <c r="O49">
+        <v>4.1</v>
+      </c>
+      <c r="P49">
         <v>1.85</v>
       </c>
-      <c r="O49">
-        <v>3.9</v>
-      </c>
-      <c r="P49">
-        <v>3.85</v>
-      </c>
       <c r="Q49">
-        <v>2.3</v>
+        <v>3.57</v>
       </c>
       <c r="R49">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="U49">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V49">
         <v>1.62</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z49">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA49">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB49">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="AC49">
+        <v>2.38</v>
+      </c>
+      <c r="AD49">
+        <v>1.57</v>
+      </c>
+      <c r="AE49">
+        <v>1.24</v>
+      </c>
+      <c r="AF49">
+        <v>1.5</v>
+      </c>
+      <c r="AG49">
         <v>2.55</v>
       </c>
-      <c r="AD49">
-        <v>1.48</v>
-      </c>
-      <c r="AE49">
-        <v>1.22</v>
-      </c>
-      <c r="AF49">
-        <v>1.57</v>
-      </c>
-      <c r="AG49">
-        <v>2.15</v>
-      </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8362,41 +8362,41 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "88"]</t>
         </is>
       </c>
       <c r="AJ49">
         <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>2.05</v>
+        <v>1.17</v>
       </c>
       <c r="AL49">
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8427,139 +8427,139 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
-        <v>3.65</v>
+        <v>1.9</v>
       </c>
       <c r="O50">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="P50">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q50">
-        <v>3.57</v>
+        <v>2.5</v>
       </c>
       <c r="R50">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T50">
-        <v>3.75</v>
+        <v>3.21</v>
       </c>
       <c r="U50">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W50">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
-        <v>5.5</v>
+        <v>3.94</v>
       </c>
       <c r="AA50">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB50">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="AC50">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="AD50">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AF50">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="AG50">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "24", "25", "67"]</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "59"]</t>
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK50">
-        <v>1.17</v>
+        <v>1.76</v>
       </c>
       <c r="AL50">
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN50">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8590,139 +8590,139 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
-        <v>3.01</v>
+        <v>2.3</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P51">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
+        <v>1.2</v>
+      </c>
+      <c r="T51">
+        <v>3.7</v>
+      </c>
+      <c r="U51">
+        <v>2.1</v>
+      </c>
+      <c r="V51">
+        <v>1.85</v>
+      </c>
+      <c r="W51">
         <v>1.25</v>
-      </c>
-      <c r="T51">
-        <v>3.6</v>
-      </c>
-      <c r="U51">
-        <v>2.2</v>
-      </c>
-      <c r="V51">
-        <v>1.6</v>
-      </c>
-      <c r="W51">
-        <v>1.11</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>4.98</v>
+        <v>7</v>
       </c>
       <c r="AA51">
+        <v>1.3</v>
+      </c>
+      <c r="AB51">
+        <v>3.2</v>
+      </c>
+      <c r="AC51">
+        <v>2.17</v>
+      </c>
+      <c r="AD51">
+        <v>1.67</v>
+      </c>
+      <c r="AE51">
+        <v>1.25</v>
+      </c>
+      <c r="AF51">
+        <v>1.4</v>
+      </c>
+      <c r="AG51">
+        <v>3.32</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>["5", "66"]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>["8"]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.25</v>
+      </c>
+      <c r="AK51">
         <v>1.56</v>
       </c>
-      <c r="AB51">
-        <v>2.38</v>
-      </c>
-      <c r="AC51">
-        <v>2.54</v>
-      </c>
-      <c r="AD51">
-        <v>1.5</v>
-      </c>
-      <c r="AE51">
-        <v>1.2</v>
-      </c>
-      <c r="AF51">
-        <v>1.5</v>
-      </c>
-      <c r="AG51">
-        <v>2.45</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.29</v>
-      </c>
-      <c r="AK51">
-        <v>1.44</v>
-      </c>
       <c r="AL51">
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8753,139 +8753,139 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
+        <v>3.01</v>
+      </c>
+      <c r="O52">
+        <v>3.6</v>
+      </c>
+      <c r="P52">
+        <v>2.25</v>
+      </c>
+      <c r="Q52">
+        <v>3.4</v>
+      </c>
+      <c r="R52">
         <v>2.3</v>
       </c>
-      <c r="O52">
-        <v>4</v>
-      </c>
-      <c r="P52">
-        <v>2.7</v>
-      </c>
-      <c r="Q52">
-        <v>2.88</v>
-      </c>
-      <c r="R52">
-        <v>2.4</v>
-      </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T52">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U52">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V52">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W52">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
   